--- a/research/traditional_assets/database/data/brazil/brazil_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_aerospace_defense.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bovespa_embr3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00455</v>
+        <v>0.199</v>
       </c>
       <c r="G2">
-        <v>0.09473094170403587</v>
+        <v>0.02941942687011537</v>
       </c>
       <c r="H2">
-        <v>0.07265641682682041</v>
+        <v>0.008262002232973575</v>
       </c>
       <c r="I2">
-        <v>-0.0321108263933376</v>
+        <v>0.04611090435429847</v>
       </c>
       <c r="J2">
-        <v>-0.0321108263933376</v>
+        <v>0.02305545217714924</v>
       </c>
       <c r="K2">
-        <v>-196.2</v>
+        <v>-8.18</v>
       </c>
       <c r="L2">
-        <v>-0.05237027546444586</v>
+        <v>-0.00152214365463342</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1303.7</v>
+        <v>1033.3</v>
       </c>
       <c r="V2">
-        <v>0.6501920103735475</v>
+        <v>0.3039743476598123</v>
       </c>
       <c r="W2">
-        <v>-0.07243861916189773</v>
+        <v>-0.003325879243748729</v>
       </c>
       <c r="X2">
-        <v>0.2803766425316989</v>
+        <v>0.1648977310846384</v>
       </c>
       <c r="Y2">
-        <v>-0.3528152616935966</v>
+        <v>-0.1682236103283871</v>
       </c>
       <c r="Z2">
-        <v>0.6850497366881217</v>
+        <v>1.241739451915523</v>
       </c>
       <c r="AA2">
-        <v>-0.02199751316559391</v>
+        <v>0.02862886455011784</v>
       </c>
       <c r="AB2">
-        <v>0.1514869871643876</v>
+        <v>0.1155696862876724</v>
       </c>
       <c r="AC2">
-        <v>-0.1734845003299816</v>
+        <v>-0.0869408217375546</v>
       </c>
       <c r="AD2">
-        <v>3193.6</v>
+        <v>2950.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3193.6</v>
+        <v>2950.6</v>
       </c>
       <c r="AG2">
-        <v>1889.9</v>
+        <v>1917.3</v>
       </c>
       <c r="AH2">
-        <v>0.6143074230095985</v>
+        <v>0.4646687349407078</v>
       </c>
       <c r="AI2">
-        <v>0.5411322161411118</v>
+        <v>0.5128089262748098</v>
       </c>
       <c r="AJ2">
-        <v>0.4852118100128369</v>
+        <v>0.3606252116013994</v>
       </c>
       <c r="AK2">
-        <v>0.4110265332753371</v>
+        <v>0.4061646012074992</v>
       </c>
       <c r="AL2">
-        <v>216.5</v>
+        <v>219.5</v>
       </c>
       <c r="AM2">
-        <v>174.1</v>
+        <v>109.5</v>
       </c>
       <c r="AN2">
-        <v>-34.60021668472373</v>
+        <v>10.920059215396</v>
       </c>
       <c r="AO2">
-        <v>-0.5556581986143186</v>
+        <v>1.128929384965832</v>
       </c>
       <c r="AP2">
-        <v>-20.47562296858072</v>
+        <v>7.095854922279793</v>
       </c>
       <c r="AQ2">
-        <v>-0.6909821941412981</v>
+        <v>2.263013698630137</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00455</v>
+        <v>0.199</v>
       </c>
       <c r="G3">
-        <v>0.09473094170403587</v>
+        <v>0.02941942687011537</v>
       </c>
       <c r="H3">
-        <v>0.07265641682682041</v>
+        <v>0.008262002232973575</v>
       </c>
       <c r="I3">
-        <v>-0.0321108263933376</v>
+        <v>0.04611090435429847</v>
       </c>
       <c r="J3">
-        <v>-0.0321108263933376</v>
+        <v>0.02305545217714924</v>
       </c>
       <c r="K3">
-        <v>-196.2</v>
+        <v>-8.18</v>
       </c>
       <c r="L3">
-        <v>-0.05237027546444586</v>
+        <v>-0.00152214365463342</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1303.7</v>
+        <v>1033.3</v>
       </c>
       <c r="V3">
-        <v>0.6501920103735475</v>
+        <v>0.3039743476598123</v>
       </c>
       <c r="W3">
-        <v>-0.07243861916189773</v>
+        <v>-0.003325879243748729</v>
       </c>
       <c r="X3">
-        <v>0.2803766425316989</v>
+        <v>0.1648977310846384</v>
       </c>
       <c r="Y3">
-        <v>-0.3528152616935966</v>
+        <v>-0.1682236103283871</v>
       </c>
       <c r="Z3">
-        <v>0.6850497366881217</v>
+        <v>1.241739451915523</v>
       </c>
       <c r="AA3">
-        <v>-0.02199751316559391</v>
+        <v>0.02862886455011784</v>
       </c>
       <c r="AB3">
-        <v>0.1514869871643876</v>
+        <v>0.1155696862876724</v>
       </c>
       <c r="AC3">
-        <v>-0.1734845003299816</v>
+        <v>-0.0869408217375546</v>
       </c>
       <c r="AD3">
-        <v>3193.6</v>
+        <v>2950.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3193.6</v>
+        <v>2950.6</v>
       </c>
       <c r="AG3">
-        <v>1889.9</v>
+        <v>1917.3</v>
       </c>
       <c r="AH3">
-        <v>0.6143074230095985</v>
+        <v>0.4646687349407078</v>
       </c>
       <c r="AI3">
-        <v>0.5411322161411118</v>
+        <v>0.5128089262748098</v>
       </c>
       <c r="AJ3">
-        <v>0.4852118100128369</v>
+        <v>0.3606252116013994</v>
       </c>
       <c r="AK3">
-        <v>0.4110265332753371</v>
+        <v>0.4061646012074992</v>
       </c>
       <c r="AL3">
-        <v>216.5</v>
+        <v>219.5</v>
       </c>
       <c r="AM3">
-        <v>174.1</v>
+        <v>109.5</v>
       </c>
       <c r="AN3">
-        <v>-34.60021668472373</v>
+        <v>10.920059215396</v>
       </c>
       <c r="AO3">
-        <v>-0.5556581986143186</v>
+        <v>1.128929384965832</v>
       </c>
       <c r="AP3">
-        <v>-20.47562296858072</v>
+        <v>7.095854922279793</v>
       </c>
       <c r="AQ3">
-        <v>-0.6909821941412981</v>
+        <v>2.263013698630137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Embraer S.A. (BOVESPA:EMBR3)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BOVESPA:EMBR3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.12892938496583</v>
+      </c>
+      <c r="F2">
+        <v>4.73741644479926</v>
+      </c>
+      <c r="G2">
+        <v>10.920059215396</v>
+      </c>
+      <c r="H2">
+        <v>3.99512583271651</v>
+      </c>
+      <c r="I2">
+        <v>0.464668734940708</v>
+      </c>
+      <c r="J2">
+        <v>0.17</v>
+      </c>
+      <c r="K2">
+        <v>3399.3</v>
+      </c>
+      <c r="L2">
+        <v>5164.58479770051</v>
+      </c>
+      <c r="M2">
+        <v>5316.6</v>
+      </c>
+      <c r="N2">
+        <v>5210.76779770051</v>
+      </c>
+      <c r="O2">
+        <v>2950.6</v>
+      </c>
+      <c r="P2">
+        <v>1079.483</v>
+      </c>
+      <c r="Q2">
+        <v>0.115569686287672</v>
+      </c>
+      <c r="R2">
+        <v>0.117128900838213</v>
+      </c>
+      <c r="S2">
+        <v>0.0587402879692537</v>
+      </c>
+      <c r="T2">
+        <v>0.0552284279692536</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.164897731084638</v>
+      </c>
+      <c r="X2">
+        <v>0.129807310943904</v>
+      </c>
+      <c r="Y2">
+        <v>1.40101720520101</v>
+      </c>
+      <c r="Z2">
+        <v>1.01114276470134</v>
+      </c>
+      <c r="AA2">
+        <v>2950.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.089000436317051</v>
+      </c>
+      <c r="AC2">
+        <v>1.128929384965832</v>
+      </c>
+      <c r="AD2">
+        <v>2950.6</v>
+      </c>
+      <c r="AE2">
+        <v>219.5</v>
+      </c>
+      <c r="AF2">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="AG2">
+        <v>270.2</v>
+      </c>
+      <c r="AH2">
+        <v>0.03277943631705099</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>3399.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.0900044129483385</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.34</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>244.4</v>
+      </c>
+      <c r="AR2">
+        <v>219.5</v>
+      </c>
+      <c r="AS2">
+        <v>2950.6</v>
+      </c>
+      <c r="AT2">
+        <v>1033.3</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1189698875859057</v>
+      </c>
+      <c r="C2">
+        <v>6124.409971679631</v>
+      </c>
+      <c r="D2">
+        <v>5091.109971679631</v>
+      </c>
+      <c r="E2">
+        <v>-2950.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1033.3</v>
+      </c>
+      <c r="H2">
+        <v>3399.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K2">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L2">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="O2">
+        <v>145.4973333333334</v>
+      </c>
+      <c r="P2">
+        <v>282.436</v>
+      </c>
+      <c r="Q2">
+        <v>304.836</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1189698875859057</v>
+      </c>
+      <c r="T2">
+        <v>0.890732853642657</v>
+      </c>
+      <c r="U2">
+        <v>0.077479436317051</v>
+      </c>
+      <c r="V2">
+        <v>0.34</v>
+      </c>
+      <c r="W2">
+        <v>0.05113642796925365</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1188206742478061</v>
+      </c>
+      <c r="C3">
+        <v>6070.404287258973</v>
+      </c>
+      <c r="D3">
+        <v>5100.603287258973</v>
+      </c>
+      <c r="E3">
+        <v>-2887.101</v>
+      </c>
+      <c r="F3">
+        <v>63.499</v>
+      </c>
+      <c r="G3">
+        <v>1033.3</v>
+      </c>
+      <c r="H3">
+        <v>3399.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K3">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L3">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M3">
+        <v>4.919866726696421</v>
+      </c>
+      <c r="N3">
+        <v>423.0134666066369</v>
+      </c>
+      <c r="O3">
+        <v>143.8245786462566</v>
+      </c>
+      <c r="P3">
+        <v>279.1888879603804</v>
+      </c>
+      <c r="Q3">
+        <v>301.5888879603804</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.119504353503145</v>
+      </c>
+      <c r="T3">
+        <v>0.8966710726669413</v>
+      </c>
+      <c r="U3">
+        <v>0.077479436317051</v>
+      </c>
+      <c r="V3">
+        <v>0.34</v>
+      </c>
+      <c r="W3">
+        <v>0.05113642796925365</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>86.98067592182134</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1186714609097066</v>
+      </c>
+      <c r="C4">
+        <v>6016.434073062377</v>
+      </c>
+      <c r="D4">
+        <v>5110.132073062377</v>
+      </c>
+      <c r="E4">
+        <v>-2823.602</v>
+      </c>
+      <c r="F4">
+        <v>126.998</v>
+      </c>
+      <c r="G4">
+        <v>1033.3</v>
+      </c>
+      <c r="H4">
+        <v>3399.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K4">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L4">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M4">
+        <v>9.839733453392842</v>
+      </c>
+      <c r="N4">
+        <v>418.0935998799405</v>
+      </c>
+      <c r="O4">
+        <v>142.1518239591798</v>
+      </c>
+      <c r="P4">
+        <v>275.9417759207607</v>
+      </c>
+      <c r="Q4">
+        <v>298.3417759207607</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1200497268880832</v>
+      </c>
+      <c r="T4">
+        <v>0.9027304798345784</v>
+      </c>
+      <c r="U4">
+        <v>0.077479436317051</v>
+      </c>
+      <c r="V4">
+        <v>0.34</v>
+      </c>
+      <c r="W4">
+        <v>0.05113642796925365</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>43.49033796091067</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.118522247571607</v>
+      </c>
+      <c r="C5">
+        <v>5962.499528254964</v>
+      </c>
+      <c r="D5">
+        <v>5119.696528254965</v>
+      </c>
+      <c r="E5">
+        <v>-2760.103</v>
+      </c>
+      <c r="F5">
+        <v>190.497</v>
+      </c>
+      <c r="G5">
+        <v>1033.3</v>
+      </c>
+      <c r="H5">
+        <v>3399.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K5">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L5">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M5">
+        <v>14.75960018008926</v>
+      </c>
+      <c r="N5">
+        <v>413.1737331532441</v>
+      </c>
+      <c r="O5">
+        <v>140.479069272103</v>
+      </c>
+      <c r="P5">
+        <v>272.6946638811411</v>
+      </c>
+      <c r="Q5">
+        <v>295.0946638811411</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1206063450850819</v>
+      </c>
+      <c r="T5">
+        <v>0.9089148232324763</v>
+      </c>
+      <c r="U5">
+        <v>0.077479436317051</v>
+      </c>
+      <c r="V5">
+        <v>0.34</v>
+      </c>
+      <c r="W5">
+        <v>0.05113642796925365</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>28.99355864060712</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1183730342335075</v>
+      </c>
+      <c r="C6">
+        <v>5908.600853495746</v>
+      </c>
+      <c r="D6">
+        <v>5129.296853495746</v>
+      </c>
+      <c r="E6">
+        <v>-2696.604</v>
+      </c>
+      <c r="F6">
+        <v>253.996</v>
+      </c>
+      <c r="G6">
+        <v>1033.3</v>
+      </c>
+      <c r="H6">
+        <v>3399.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K6">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L6">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M6">
+        <v>19.67946690678568</v>
+      </c>
+      <c r="N6">
+        <v>408.2538664265476</v>
+      </c>
+      <c r="O6">
+        <v>138.8063145850262</v>
+      </c>
+      <c r="P6">
+        <v>269.4475518415214</v>
+      </c>
+      <c r="Q6">
+        <v>291.8475518415214</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1211745594945181</v>
+      </c>
+      <c r="T6">
+        <v>0.9152280071178301</v>
+      </c>
+      <c r="U6">
+        <v>0.077479436317051</v>
+      </c>
+      <c r="V6">
+        <v>0.34</v>
+      </c>
+      <c r="W6">
+        <v>0.05113642796925365</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>21.74516898045533</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1182238208954079</v>
+      </c>
+      <c r="C7">
+        <v>5854.738250951637</v>
+      </c>
+      <c r="D7">
+        <v>5138.933250951637</v>
+      </c>
+      <c r="E7">
+        <v>-2633.105</v>
+      </c>
+      <c r="F7">
+        <v>317.495</v>
+      </c>
+      <c r="G7">
+        <v>1033.3</v>
+      </c>
+      <c r="H7">
+        <v>3399.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K7">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L7">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M7">
+        <v>24.59933363348211</v>
+      </c>
+      <c r="N7">
+        <v>403.3339996998512</v>
+      </c>
+      <c r="O7">
+        <v>137.1335598979494</v>
+      </c>
+      <c r="P7">
+        <v>266.2004398019018</v>
+      </c>
+      <c r="Q7">
+        <v>288.6004398019018</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.121754736312574</v>
+      </c>
+      <c r="T7">
+        <v>0.9216741001376124</v>
+      </c>
+      <c r="U7">
+        <v>0.077479436317051</v>
+      </c>
+      <c r="V7">
+        <v>0.34</v>
+      </c>
+      <c r="W7">
+        <v>0.05113642796925365</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>17.39613518436427</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1180746075573084</v>
+      </c>
+      <c r="C8">
+        <v>5800.911924311653</v>
+      </c>
+      <c r="D8">
+        <v>5148.605924311652</v>
+      </c>
+      <c r="E8">
+        <v>-2569.606</v>
+      </c>
+      <c r="F8">
+        <v>380.994</v>
+      </c>
+      <c r="G8">
+        <v>1033.3</v>
+      </c>
+      <c r="H8">
+        <v>3399.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K8">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L8">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M8">
+        <v>29.51920036017852</v>
+      </c>
+      <c r="N8">
+        <v>398.4141329731548</v>
+      </c>
+      <c r="O8">
+        <v>135.4608052108726</v>
+      </c>
+      <c r="P8">
+        <v>262.9533277622822</v>
+      </c>
+      <c r="Q8">
+        <v>285.3533277622822</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1223472573182481</v>
+      </c>
+      <c r="T8">
+        <v>0.9282573440727094</v>
+      </c>
+      <c r="U8">
+        <v>0.077479436317051</v>
+      </c>
+      <c r="V8">
+        <v>0.34</v>
+      </c>
+      <c r="W8">
+        <v>0.05113642796925365</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>14.49677932030356</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1179762142192089</v>
+      </c>
+      <c r="C9">
+        <v>5743.811165607322</v>
+      </c>
+      <c r="D9">
+        <v>5155.004165607322</v>
+      </c>
+      <c r="E9">
+        <v>-2506.107</v>
+      </c>
+      <c r="F9">
+        <v>444.493</v>
+      </c>
+      <c r="G9">
+        <v>1033.3</v>
+      </c>
+      <c r="H9">
+        <v>3399.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K9">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L9">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M9">
+        <v>34.92800938687495</v>
+      </c>
+      <c r="N9">
+        <v>393.0053239464584</v>
+      </c>
+      <c r="O9">
+        <v>133.6218101417959</v>
+      </c>
+      <c r="P9">
+        <v>259.3835138046625</v>
+      </c>
+      <c r="Q9">
+        <v>281.7835138046624</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.122952520711141</v>
+      </c>
+      <c r="T9">
+        <v>0.9349821631461955</v>
+      </c>
+      <c r="U9">
+        <v>0.078579436317051</v>
+      </c>
+      <c r="V9">
+        <v>0.34</v>
+      </c>
+      <c r="W9">
+        <v>0.05186242796925365</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>12.25186722190185</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1178342608811093</v>
+      </c>
+      <c r="C10">
+        <v>5689.571062205668</v>
+      </c>
+      <c r="D10">
+        <v>5164.263062205668</v>
+      </c>
+      <c r="E10">
+        <v>-2442.608</v>
+      </c>
+      <c r="F10">
+        <v>507.992</v>
+      </c>
+      <c r="G10">
+        <v>1033.3</v>
+      </c>
+      <c r="H10">
+        <v>3399.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K10">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L10">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M10">
+        <v>39.91772501357137</v>
+      </c>
+      <c r="N10">
+        <v>388.015608319762</v>
+      </c>
+      <c r="O10">
+        <v>131.9253068287191</v>
+      </c>
+      <c r="P10">
+        <v>256.0903014910429</v>
+      </c>
+      <c r="Q10">
+        <v>278.4903014910428</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1235709420038794</v>
+      </c>
+      <c r="T10">
+        <v>0.9418531739386703</v>
+      </c>
+      <c r="U10">
+        <v>0.078579436317051</v>
+      </c>
+      <c r="V10">
+        <v>0.34</v>
+      </c>
+      <c r="W10">
+        <v>0.05186242796925365</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>10.72038381916412</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1178229875430098</v>
+      </c>
+      <c r="C11">
+        <v>5626.808790660835</v>
+      </c>
+      <c r="D11">
+        <v>5164.999790660835</v>
+      </c>
+      <c r="E11">
+        <v>-2379.109</v>
+      </c>
+      <c r="F11">
+        <v>571.491</v>
+      </c>
+      <c r="G11">
+        <v>1033.3</v>
+      </c>
+      <c r="H11">
+        <v>3399.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K11">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L11">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M11">
+        <v>46.16472084026779</v>
+      </c>
+      <c r="N11">
+        <v>381.7686124930656</v>
+      </c>
+      <c r="O11">
+        <v>129.8013282476423</v>
+      </c>
+      <c r="P11">
+        <v>251.9672842454233</v>
+      </c>
+      <c r="Q11">
+        <v>274.3672842454232</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1242029549733813</v>
+      </c>
+      <c r="T11">
+        <v>0.9488751959573535</v>
+      </c>
+      <c r="U11">
+        <v>0.08077943631705099</v>
+      </c>
+      <c r="V11">
+        <v>0.34</v>
+      </c>
+      <c r="W11">
+        <v>0.05331442796925365</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>9.269704777680857</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1176955542049102</v>
+      </c>
+      <c r="C12">
+        <v>5571.652379432035</v>
+      </c>
+      <c r="D12">
+        <v>5173.342379432034</v>
+      </c>
+      <c r="E12">
+        <v>-2315.61</v>
+      </c>
+      <c r="F12">
+        <v>634.99</v>
+      </c>
+      <c r="G12">
+        <v>1033.3</v>
+      </c>
+      <c r="H12">
+        <v>3399.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K12">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L12">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M12">
+        <v>51.29413426696421</v>
+      </c>
+      <c r="N12">
+        <v>376.6391990663691</v>
+      </c>
+      <c r="O12">
+        <v>128.0573276825655</v>
+      </c>
+      <c r="P12">
+        <v>248.5818713838036</v>
+      </c>
+      <c r="Q12">
+        <v>270.9818713838036</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1248490126755387</v>
+      </c>
+      <c r="T12">
+        <v>0.9560532629097851</v>
+      </c>
+      <c r="U12">
+        <v>0.08077943631705099</v>
+      </c>
+      <c r="V12">
+        <v>0.34</v>
+      </c>
+      <c r="W12">
+        <v>0.05331442796925365</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.34273429991277</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1176770208668107</v>
+      </c>
+      <c r="C13">
+        <v>5509.368933751518</v>
+      </c>
+      <c r="D13">
+        <v>5174.557933751517</v>
+      </c>
+      <c r="E13">
+        <v>-2252.111</v>
+      </c>
+      <c r="F13">
+        <v>698.4889999999999</v>
+      </c>
+      <c r="G13">
+        <v>1033.3</v>
+      </c>
+      <c r="H13">
+        <v>3399.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K13">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L13">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M13">
+        <v>57.47128119366062</v>
+      </c>
+      <c r="N13">
+        <v>370.4620521396727</v>
+      </c>
+      <c r="O13">
+        <v>125.9570977274887</v>
+      </c>
+      <c r="P13">
+        <v>244.504954412184</v>
+      </c>
+      <c r="Q13">
+        <v>266.904954412184</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1255095885283065</v>
+      </c>
+      <c r="T13">
+        <v>0.9633926347375523</v>
+      </c>
+      <c r="U13">
+        <v>0.08227943631705099</v>
+      </c>
+      <c r="V13">
+        <v>0.34</v>
+      </c>
+      <c r="W13">
+        <v>0.05430442796925365</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>7.44603782002578</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1175594875287111</v>
+      </c>
+      <c r="C14">
+        <v>5453.591963010807</v>
+      </c>
+      <c r="D14">
+        <v>5182.279963010807</v>
+      </c>
+      <c r="E14">
+        <v>-2188.612</v>
+      </c>
+      <c r="F14">
+        <v>761.9879999999999</v>
+      </c>
+      <c r="G14">
+        <v>1033.3</v>
+      </c>
+      <c r="H14">
+        <v>3399.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K14">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L14">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M14">
+        <v>62.69594312035705</v>
+      </c>
+      <c r="N14">
+        <v>365.2373902129763</v>
+      </c>
+      <c r="O14">
+        <v>124.1807126724119</v>
+      </c>
+      <c r="P14">
+        <v>241.0566775405643</v>
+      </c>
+      <c r="Q14">
+        <v>263.4566775405643</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1261851774686372</v>
+      </c>
+      <c r="T14">
+        <v>0.9708988104704962</v>
+      </c>
+      <c r="U14">
+        <v>0.08227943631705099</v>
+      </c>
+      <c r="V14">
+        <v>0.34</v>
+      </c>
+      <c r="W14">
+        <v>0.05430442796925365</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>6.825534668356964</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1174419541906116</v>
+      </c>
+      <c r="C15">
+        <v>5397.838073992441</v>
+      </c>
+      <c r="D15">
+        <v>5190.025073992441</v>
+      </c>
+      <c r="E15">
+        <v>-2125.113</v>
+      </c>
+      <c r="F15">
+        <v>825.487</v>
+      </c>
+      <c r="G15">
+        <v>1033.3</v>
+      </c>
+      <c r="H15">
+        <v>3399.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K15">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L15">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M15">
+        <v>67.92060504705347</v>
+      </c>
+      <c r="N15">
+        <v>360.0127282862799</v>
+      </c>
+      <c r="O15">
+        <v>122.4043276173352</v>
+      </c>
+      <c r="P15">
+        <v>237.6084006689447</v>
+      </c>
+      <c r="Q15">
+        <v>260.0084006689447</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1268762971892053</v>
+      </c>
+      <c r="T15">
+        <v>0.9785775419674156</v>
+      </c>
+      <c r="U15">
+        <v>0.08227943631705099</v>
+      </c>
+      <c r="V15">
+        <v>0.34</v>
+      </c>
+      <c r="W15">
+        <v>0.05430442796925365</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.300493540021813</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.117453780852512</v>
+      </c>
+      <c r="C16">
+        <v>5333.558683385158</v>
+      </c>
+      <c r="D16">
+        <v>5189.244683385157</v>
+      </c>
+      <c r="E16">
+        <v>-2061.614</v>
+      </c>
+      <c r="F16">
+        <v>888.986</v>
+      </c>
+      <c r="G16">
+        <v>1033.3</v>
+      </c>
+      <c r="H16">
+        <v>3399.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K16">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L16">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M16">
+        <v>74.38984737374989</v>
+      </c>
+      <c r="N16">
+        <v>353.5434859595834</v>
+      </c>
+      <c r="O16">
+        <v>120.2047852262584</v>
+      </c>
+      <c r="P16">
+        <v>233.3387007333251</v>
+      </c>
+      <c r="Q16">
+        <v>255.7387007333251</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1275834894614146</v>
+      </c>
+      <c r="T16">
+        <v>0.9864348486154261</v>
+      </c>
+      <c r="U16">
+        <v>0.08367943631705099</v>
+      </c>
+      <c r="V16">
+        <v>0.34</v>
+      </c>
+      <c r="W16">
+        <v>0.05522842796925365</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.752577111541959</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1173454875144125</v>
+      </c>
+      <c r="C17">
+        <v>5277.214271723232</v>
+      </c>
+      <c r="D17">
+        <v>5196.399271723231</v>
+      </c>
+      <c r="E17">
+        <v>-1998.115</v>
+      </c>
+      <c r="F17">
+        <v>952.4849999999999</v>
+      </c>
+      <c r="G17">
+        <v>1033.3</v>
+      </c>
+      <c r="H17">
+        <v>3399.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K17">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L17">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M17">
+        <v>79.70340790044631</v>
+      </c>
+      <c r="N17">
+        <v>348.2299254328871</v>
+      </c>
+      <c r="O17">
+        <v>118.3981746471816</v>
+      </c>
+      <c r="P17">
+        <v>229.8317507857055</v>
+      </c>
+      <c r="Q17">
+        <v>252.2317507857054</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1283073215517935</v>
+      </c>
+      <c r="T17">
+        <v>0.9944770330669194</v>
+      </c>
+      <c r="U17">
+        <v>0.08367943631705099</v>
+      </c>
+      <c r="V17">
+        <v>0.34</v>
+      </c>
+      <c r="W17">
+        <v>0.05522842796925365</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.369071970772496</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.117237194176313</v>
+      </c>
+      <c r="C18">
+        <v>5220.889615848393</v>
+      </c>
+      <c r="D18">
+        <v>5203.573615848392</v>
+      </c>
+      <c r="E18">
+        <v>-1934.616</v>
+      </c>
+      <c r="F18">
+        <v>1015.984</v>
+      </c>
+      <c r="G18">
+        <v>1033.3</v>
+      </c>
+      <c r="H18">
+        <v>3399.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K18">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L18">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M18">
+        <v>85.01696842714273</v>
+      </c>
+      <c r="N18">
+        <v>342.9163649061906</v>
+      </c>
+      <c r="O18">
+        <v>116.5915640681048</v>
+      </c>
+      <c r="P18">
+        <v>226.3248008380858</v>
+      </c>
+      <c r="Q18">
+        <v>248.7248008380858</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1290483877395623</v>
+      </c>
+      <c r="T18">
+        <v>1.002710698100591</v>
+      </c>
+      <c r="U18">
+        <v>0.08367943631705099</v>
+      </c>
+      <c r="V18">
+        <v>0.34</v>
+      </c>
+      <c r="W18">
+        <v>0.05522842796925365</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.033504972599214</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1171289008382134</v>
+      </c>
+      <c r="C19">
+        <v>5164.584797700514</v>
+      </c>
+      <c r="D19">
+        <v>5210.767797700514</v>
+      </c>
+      <c r="E19">
+        <v>-1871.117</v>
+      </c>
+      <c r="F19">
+        <v>1079.483</v>
+      </c>
+      <c r="G19">
+        <v>1033.3</v>
+      </c>
+      <c r="H19">
+        <v>3399.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K19">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L19">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M19">
+        <v>90.33052895383915</v>
+      </c>
+      <c r="N19">
+        <v>337.6028043794942</v>
+      </c>
+      <c r="O19">
+        <v>114.784953489028</v>
+      </c>
+      <c r="P19">
+        <v>222.8178508904661</v>
+      </c>
+      <c r="Q19">
+        <v>245.2178508904661</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.129807310943904</v>
+      </c>
+      <c r="T19">
+        <v>1.011142764701339</v>
+      </c>
+      <c r="U19">
+        <v>0.08367943631705099</v>
+      </c>
+      <c r="V19">
+        <v>0.34</v>
+      </c>
+      <c r="W19">
+        <v>0.05522842796925365</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.73741644479926</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1173294875001139</v>
+      </c>
+      <c r="C20">
+        <v>5087.776013672219</v>
+      </c>
+      <c r="D20">
+        <v>5197.458013672219</v>
+      </c>
+      <c r="E20">
+        <v>-1807.618</v>
+      </c>
+      <c r="F20">
+        <v>1142.982</v>
+      </c>
+      <c r="G20">
+        <v>1033.3</v>
+      </c>
+      <c r="H20">
+        <v>3399.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K20">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L20">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M20">
+        <v>98.61584268053556</v>
+      </c>
+      <c r="N20">
+        <v>329.3174906527978</v>
+      </c>
+      <c r="O20">
+        <v>111.9679468219513</v>
+      </c>
+      <c r="P20">
+        <v>217.3495438308465</v>
+      </c>
+      <c r="Q20">
+        <v>239.7495438308465</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1305847444703027</v>
+      </c>
+      <c r="T20">
+        <v>1.019780491463081</v>
+      </c>
+      <c r="U20">
+        <v>0.08627943631705098</v>
+      </c>
+      <c r="V20">
+        <v>0.34</v>
+      </c>
+      <c r="W20">
+        <v>0.05694442796925364</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.339397420347728</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1172383541620143</v>
+      </c>
+      <c r="C21">
+        <v>5030.315662793284</v>
+      </c>
+      <c r="D21">
+        <v>5203.496662793284</v>
+      </c>
+      <c r="E21">
+        <v>-1744.119</v>
+      </c>
+      <c r="F21">
+        <v>1206.481</v>
+      </c>
+      <c r="G21">
+        <v>1033.3</v>
+      </c>
+      <c r="H21">
+        <v>3399.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K21">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L21">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M21">
+        <v>104.094500607232</v>
+      </c>
+      <c r="N21">
+        <v>323.8388327261014</v>
+      </c>
+      <c r="O21">
+        <v>110.1052031268745</v>
+      </c>
+      <c r="P21">
+        <v>213.7336295992269</v>
+      </c>
+      <c r="Q21">
+        <v>236.1336295992269</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1313813738862422</v>
+      </c>
+      <c r="T21">
+        <v>1.028631495428816</v>
+      </c>
+      <c r="U21">
+        <v>0.08627943631705098</v>
+      </c>
+      <c r="V21">
+        <v>0.34</v>
+      </c>
+      <c r="W21">
+        <v>0.05694442796925364</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.111008082434688</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1175036208239148</v>
+      </c>
+      <c r="C22">
+        <v>4949.278534616975</v>
+      </c>
+      <c r="D22">
+        <v>5185.958534616974</v>
+      </c>
+      <c r="E22">
+        <v>-1680.62</v>
+      </c>
+      <c r="F22">
+        <v>1269.98</v>
+      </c>
+      <c r="G22">
+        <v>1033.3</v>
+      </c>
+      <c r="H22">
+        <v>3399.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K22">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L22">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M22">
+        <v>113.0021045339284</v>
+      </c>
+      <c r="N22">
+        <v>314.9312287994049</v>
+      </c>
+      <c r="O22">
+        <v>107.0766177917977</v>
+      </c>
+      <c r="P22">
+        <v>207.8546110076073</v>
+      </c>
+      <c r="Q22">
+        <v>230.2546110076073</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1321979190375801</v>
+      </c>
+      <c r="T22">
+        <v>1.037703774493695</v>
+      </c>
+      <c r="U22">
+        <v>0.08897943631705099</v>
+      </c>
+      <c r="V22">
+        <v>0.34</v>
+      </c>
+      <c r="W22">
+        <v>0.05872642796925365</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.786950120073632</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1174303074858152</v>
+      </c>
+      <c r="C23">
+        <v>4890.614819427319</v>
+      </c>
+      <c r="D23">
+        <v>5190.793819427318</v>
+      </c>
+      <c r="E23">
+        <v>-1617.121</v>
+      </c>
+      <c r="F23">
+        <v>1333.479</v>
+      </c>
+      <c r="G23">
+        <v>1033.3</v>
+      </c>
+      <c r="H23">
+        <v>3399.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K23">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L23">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M23">
+        <v>118.6522097606248</v>
+      </c>
+      <c r="N23">
+        <v>309.2811235727085</v>
+      </c>
+      <c r="O23">
+        <v>105.1555820147209</v>
+      </c>
+      <c r="P23">
+        <v>204.1255415579876</v>
+      </c>
+      <c r="Q23">
+        <v>226.5255415579876</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1330351362180658</v>
+      </c>
+      <c r="T23">
+        <v>1.047005731509584</v>
+      </c>
+      <c r="U23">
+        <v>0.08897943631705099</v>
+      </c>
+      <c r="V23">
+        <v>0.34</v>
+      </c>
+      <c r="W23">
+        <v>0.05872642796925365</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.606619161974888</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1180394341477157</v>
+      </c>
+      <c r="C24">
+        <v>4787.213327115886</v>
+      </c>
+      <c r="D24">
+        <v>5150.891327115886</v>
+      </c>
+      <c r="E24">
+        <v>-1553.622</v>
+      </c>
+      <c r="F24">
+        <v>1396.978</v>
+      </c>
+      <c r="G24">
+        <v>1033.3</v>
+      </c>
+      <c r="H24">
+        <v>3399.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K24">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L24">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M24">
+        <v>130.8681115873213</v>
+      </c>
+      <c r="N24">
+        <v>297.0652217460121</v>
+      </c>
+      <c r="O24">
+        <v>101.0021753936441</v>
+      </c>
+      <c r="P24">
+        <v>196.063046352368</v>
+      </c>
+      <c r="Q24">
+        <v>218.4630463523679</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1338938205057435</v>
+      </c>
+      <c r="T24">
+        <v>1.056546200243828</v>
+      </c>
+      <c r="U24">
+        <v>0.093679436317051</v>
+      </c>
+      <c r="V24">
+        <v>0.34</v>
+      </c>
+      <c r="W24">
+        <v>0.06182842796925365</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.269958801596953</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1179971408096162</v>
+      </c>
+      <c r="C25">
+        <v>4726.465037383768</v>
+      </c>
+      <c r="D25">
+        <v>5153.642037383767</v>
+      </c>
+      <c r="E25">
+        <v>-1490.123</v>
+      </c>
+      <c r="F25">
+        <v>1460.477</v>
+      </c>
+      <c r="G25">
+        <v>1033.3</v>
+      </c>
+      <c r="H25">
+        <v>3399.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K25">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L25">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M25">
+        <v>136.8166621140177</v>
+      </c>
+      <c r="N25">
+        <v>291.1166712193157</v>
+      </c>
+      <c r="O25">
+        <v>98.97966821456733</v>
+      </c>
+      <c r="P25">
+        <v>192.1370030047484</v>
+      </c>
+      <c r="Q25">
+        <v>214.5370030047483</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1347748082814128</v>
+      </c>
+      <c r="T25">
+        <v>1.066334473360781</v>
+      </c>
+      <c r="U25">
+        <v>0.093679436317051</v>
+      </c>
+      <c r="V25">
+        <v>0.34</v>
+      </c>
+      <c r="W25">
+        <v>0.06182842796925365</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.12778667978839</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1194279674715166</v>
+      </c>
+      <c r="C26">
+        <v>4571.509329938121</v>
+      </c>
+      <c r="D26">
+        <v>5062.18532993812</v>
+      </c>
+      <c r="E26">
+        <v>-1426.624</v>
+      </c>
+      <c r="F26">
+        <v>1523.976</v>
+      </c>
+      <c r="G26">
+        <v>1033.3</v>
+      </c>
+      <c r="H26">
+        <v>3399.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K26">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L26">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M26">
+        <v>156.9381894407141</v>
+      </c>
+      <c r="N26">
+        <v>270.9951438926192</v>
+      </c>
+      <c r="O26">
+        <v>92.13834892349055</v>
+      </c>
+      <c r="P26">
+        <v>178.8567949691287</v>
+      </c>
+      <c r="Q26">
+        <v>201.2567949691287</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1356789799459154</v>
+      </c>
+      <c r="T26">
+        <v>1.07638033261239</v>
+      </c>
+      <c r="U26">
+        <v>0.102979436317051</v>
+      </c>
+      <c r="V26">
+        <v>0.34</v>
+      </c>
+      <c r="W26">
+        <v>0.06796642796925365</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.72676354212046</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1194470541334171</v>
+      </c>
+      <c r="C27">
+        <v>4506.812267331763</v>
+      </c>
+      <c r="D27">
+        <v>5060.987267331763</v>
+      </c>
+      <c r="E27">
+        <v>-1363.125</v>
+      </c>
+      <c r="F27">
+        <v>1587.475</v>
+      </c>
+      <c r="G27">
+        <v>1033.3</v>
+      </c>
+      <c r="H27">
+        <v>3399.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K27">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L27">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M27">
+        <v>163.4772806674105</v>
+      </c>
+      <c r="N27">
+        <v>264.4560526659228</v>
+      </c>
+      <c r="O27">
+        <v>89.91505790641376</v>
+      </c>
+      <c r="P27">
+        <v>174.540994759509</v>
+      </c>
+      <c r="Q27">
+        <v>196.940994759509</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1366072628548049</v>
+      </c>
+      <c r="T27">
+        <v>1.086694081444042</v>
+      </c>
+      <c r="U27">
+        <v>0.102979436317051</v>
+      </c>
+      <c r="V27">
+        <v>0.34</v>
+      </c>
+      <c r="W27">
+        <v>0.06796642796925365</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.617693000435641</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1194661407953175</v>
+      </c>
+      <c r="C28">
+        <v>4442.115771679911</v>
+      </c>
+      <c r="D28">
+        <v>5059.789771679911</v>
+      </c>
+      <c r="E28">
+        <v>-1299.626</v>
+      </c>
+      <c r="F28">
+        <v>1650.974</v>
+      </c>
+      <c r="G28">
+        <v>1033.3</v>
+      </c>
+      <c r="H28">
+        <v>3399.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K28">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L28">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M28">
+        <v>170.0163718941069</v>
+      </c>
+      <c r="N28">
+        <v>257.9169614392264</v>
+      </c>
+      <c r="O28">
+        <v>87.69176688933698</v>
+      </c>
+      <c r="P28">
+        <v>170.2251945498894</v>
+      </c>
+      <c r="Q28">
+        <v>192.6251945498894</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1375606344909616</v>
+      </c>
+      <c r="T28">
+        <v>1.097286580244117</v>
+      </c>
+      <c r="U28">
+        <v>0.102979436317051</v>
+      </c>
+      <c r="V28">
+        <v>0.34</v>
+      </c>
+      <c r="W28">
+        <v>0.06796642796925365</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.517012500418886</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.120322767457218</v>
+      </c>
+      <c r="C29">
+        <v>4325.449405590348</v>
+      </c>
+      <c r="D29">
+        <v>5006.622405590348</v>
+      </c>
+      <c r="E29">
+        <v>-1236.127</v>
+      </c>
+      <c r="F29">
+        <v>1714.473</v>
+      </c>
+      <c r="G29">
+        <v>1033.3</v>
+      </c>
+      <c r="H29">
+        <v>3399.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K29">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L29">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M29">
+        <v>184.6134862208033</v>
+      </c>
+      <c r="N29">
+        <v>243.31984711253</v>
+      </c>
+      <c r="O29">
+        <v>82.72874801826021</v>
+      </c>
+      <c r="P29">
+        <v>160.5910990942698</v>
+      </c>
+      <c r="Q29">
+        <v>182.9910990942698</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1385401258979719</v>
+      </c>
+      <c r="T29">
+        <v>1.108169284490768</v>
+      </c>
+      <c r="U29">
+        <v>0.107679436317051</v>
+      </c>
+      <c r="V29">
+        <v>0.34</v>
+      </c>
+      <c r="W29">
+        <v>0.07106842796925364</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.317996058107651</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1203728741191185</v>
+      </c>
+      <c r="C30">
+        <v>4258.875055618324</v>
+      </c>
+      <c r="D30">
+        <v>5003.547055618324</v>
+      </c>
+      <c r="E30">
+        <v>-1172.628</v>
+      </c>
+      <c r="F30">
+        <v>1777.972</v>
+      </c>
+      <c r="G30">
+        <v>1033.3</v>
+      </c>
+      <c r="H30">
+        <v>3399.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K30">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L30">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M30">
+        <v>191.4510227474998</v>
+      </c>
+      <c r="N30">
+        <v>236.4823105858336</v>
+      </c>
+      <c r="O30">
+        <v>80.40398559918341</v>
+      </c>
+      <c r="P30">
+        <v>156.0783249866502</v>
+      </c>
+      <c r="Q30">
+        <v>178.4783249866501</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1395468253996214</v>
+      </c>
+      <c r="T30">
+        <v>1.119354286077606</v>
+      </c>
+      <c r="U30">
+        <v>0.107679436317051</v>
+      </c>
+      <c r="V30">
+        <v>0.34</v>
+      </c>
+      <c r="W30">
+        <v>0.07106842796925364</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.235210484603806</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1204229807810189</v>
+      </c>
+      <c r="C31">
+        <v>4192.304481433947</v>
+      </c>
+      <c r="D31">
+        <v>5000.475481433947</v>
+      </c>
+      <c r="E31">
+        <v>-1109.129</v>
+      </c>
+      <c r="F31">
+        <v>1841.471</v>
+      </c>
+      <c r="G31">
+        <v>1033.3</v>
+      </c>
+      <c r="H31">
+        <v>3399.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K31">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L31">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M31">
+        <v>198.2885592741962</v>
+      </c>
+      <c r="N31">
+        <v>229.6447740591372</v>
+      </c>
+      <c r="O31">
+        <v>78.07922318010665</v>
+      </c>
+      <c r="P31">
+        <v>151.5655508790305</v>
+      </c>
+      <c r="Q31">
+        <v>173.9655508790305</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1405818826337118</v>
+      </c>
+      <c r="T31">
+        <v>1.130854358131677</v>
+      </c>
+      <c r="U31">
+        <v>0.107679436317051</v>
+      </c>
+      <c r="V31">
+        <v>0.34</v>
+      </c>
+      <c r="W31">
+        <v>0.07106842796925364</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.158134260996779</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1204730874429194</v>
+      </c>
+      <c r="C32">
+        <v>4125.737676087849</v>
+      </c>
+      <c r="D32">
+        <v>4997.407676087848</v>
+      </c>
+      <c r="E32">
+        <v>-1045.63</v>
+      </c>
+      <c r="F32">
+        <v>1904.97</v>
+      </c>
+      <c r="G32">
+        <v>1033.3</v>
+      </c>
+      <c r="H32">
+        <v>3399.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K32">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L32">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M32">
+        <v>205.1260958008926</v>
+      </c>
+      <c r="N32">
+        <v>222.8072375324408</v>
+      </c>
+      <c r="O32">
+        <v>75.75446076102986</v>
+      </c>
+      <c r="P32">
+        <v>147.0527767714109</v>
+      </c>
+      <c r="Q32">
+        <v>169.4527767714109</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1416465129316333</v>
+      </c>
+      <c r="T32">
+        <v>1.142683003673009</v>
+      </c>
+      <c r="U32">
+        <v>0.107679436317051</v>
+      </c>
+      <c r="V32">
+        <v>0.34</v>
+      </c>
+      <c r="W32">
+        <v>0.07106842796925364</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.086196452296886</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1205231941048198</v>
+      </c>
+      <c r="C33">
+        <v>4059.174632647705</v>
+      </c>
+      <c r="D33">
+        <v>4994.343632647705</v>
+      </c>
+      <c r="E33">
+        <v>-982.1310000000001</v>
+      </c>
+      <c r="F33">
+        <v>1968.469</v>
+      </c>
+      <c r="G33">
+        <v>1033.3</v>
+      </c>
+      <c r="H33">
+        <v>3399.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K33">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L33">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M33">
+        <v>211.963632327589</v>
+      </c>
+      <c r="N33">
+        <v>215.9697010057443</v>
+      </c>
+      <c r="O33">
+        <v>73.42969834195307</v>
+      </c>
+      <c r="P33">
+        <v>142.5400026637913</v>
+      </c>
+      <c r="Q33">
+        <v>164.9400026637912</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1427420020787699</v>
+      </c>
+      <c r="T33">
+        <v>1.154854508505393</v>
+      </c>
+      <c r="U33">
+        <v>0.107679436317051</v>
+      </c>
+      <c r="V33">
+        <v>0.34</v>
+      </c>
+      <c r="W33">
+        <v>0.07106842796925364</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.018899792545374</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1240158607667203</v>
+      </c>
+      <c r="C34">
+        <v>3790.976914042075</v>
+      </c>
+      <c r="D34">
+        <v>4789.644914042075</v>
+      </c>
+      <c r="E34">
+        <v>-918.6320000000001</v>
+      </c>
+      <c r="F34">
+        <v>2031.968</v>
+      </c>
+      <c r="G34">
+        <v>1033.3</v>
+      </c>
+      <c r="H34">
+        <v>3399.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K34">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L34">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M34">
+        <v>251.9222472542855</v>
+      </c>
+      <c r="N34">
+        <v>176.0110860790479</v>
+      </c>
+      <c r="O34">
+        <v>59.84376926687629</v>
+      </c>
+      <c r="P34">
+        <v>116.1673168121716</v>
+      </c>
+      <c r="Q34">
+        <v>138.5673168121716</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1438697114949399</v>
+      </c>
+      <c r="T34">
+        <v>1.167383998774023</v>
+      </c>
+      <c r="U34">
+        <v>0.123979436317051</v>
+      </c>
+      <c r="V34">
+        <v>0.34</v>
+      </c>
+      <c r="W34">
+        <v>0.08182642796925364</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>1.698672260974973</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1241735474286207</v>
+      </c>
+      <c r="C35">
+        <v>3718.631343401264</v>
+      </c>
+      <c r="D35">
+        <v>4780.798343401264</v>
+      </c>
+      <c r="E35">
+        <v>-855.1329999999998</v>
+      </c>
+      <c r="F35">
+        <v>2095.467</v>
+      </c>
+      <c r="G35">
+        <v>1033.3</v>
+      </c>
+      <c r="H35">
+        <v>3399.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K35">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L35">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M35">
+        <v>259.7948174809819</v>
+      </c>
+      <c r="N35">
+        <v>168.1385158523514</v>
+      </c>
+      <c r="O35">
+        <v>57.16709538979948</v>
+      </c>
+      <c r="P35">
+        <v>110.9714204625519</v>
+      </c>
+      <c r="Q35">
+        <v>133.3714204625519</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1450310838787568</v>
+      </c>
+      <c r="T35">
+        <v>1.180287503677539</v>
+      </c>
+      <c r="U35">
+        <v>0.123979436317051</v>
+      </c>
+      <c r="V35">
+        <v>0.34</v>
+      </c>
+      <c r="W35">
+        <v>0.08182642796925364</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>1.647197343975731</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1243312340905212</v>
+      </c>
+      <c r="C36">
+        <v>3646.318392100241</v>
+      </c>
+      <c r="D36">
+        <v>4771.984392100241</v>
+      </c>
+      <c r="E36">
+        <v>-791.634</v>
+      </c>
+      <c r="F36">
+        <v>2158.966</v>
+      </c>
+      <c r="G36">
+        <v>1033.3</v>
+      </c>
+      <c r="H36">
+        <v>3399.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K36">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L36">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M36">
+        <v>267.6673877076783</v>
+      </c>
+      <c r="N36">
+        <v>160.265945625655</v>
+      </c>
+      <c r="O36">
+        <v>54.49042151272272</v>
+      </c>
+      <c r="P36">
+        <v>105.7755241129323</v>
+      </c>
+      <c r="Q36">
+        <v>128.1755241129323</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1462276493651136</v>
+      </c>
+      <c r="T36">
+        <v>1.193582023881161</v>
+      </c>
+      <c r="U36">
+        <v>0.123979436317051</v>
+      </c>
+      <c r="V36">
+        <v>0.34</v>
+      </c>
+      <c r="W36">
+        <v>0.08182642796925364</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.598750363270563</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1244889207524216</v>
+      </c>
+      <c r="C37">
+        <v>3574.037880058499</v>
+      </c>
+      <c r="D37">
+        <v>4763.202880058499</v>
+      </c>
+      <c r="E37">
+        <v>-728.1349999999998</v>
+      </c>
+      <c r="F37">
+        <v>2222.465</v>
+      </c>
+      <c r="G37">
+        <v>1033.3</v>
+      </c>
+      <c r="H37">
+        <v>3399.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K37">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L37">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M37">
+        <v>275.5399579343747</v>
+      </c>
+      <c r="N37">
+        <v>152.3933753989586</v>
+      </c>
+      <c r="O37">
+        <v>51.81374763564592</v>
+      </c>
+      <c r="P37">
+        <v>100.5796277633127</v>
+      </c>
+      <c r="Q37">
+        <v>122.9796277633126</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1474610322510506</v>
+      </c>
+      <c r="T37">
+        <v>1.207285606244894</v>
+      </c>
+      <c r="U37">
+        <v>0.123979436317051</v>
+      </c>
+      <c r="V37">
+        <v>0.34</v>
+      </c>
+      <c r="W37">
+        <v>0.08182642796925364</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.553071781462833</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1246466074143221</v>
+      </c>
+      <c r="C38">
+        <v>3501.789628518644</v>
+      </c>
+      <c r="D38">
+        <v>4754.453628518644</v>
+      </c>
+      <c r="E38">
+        <v>-664.636</v>
+      </c>
+      <c r="F38">
+        <v>2285.964</v>
+      </c>
+      <c r="G38">
+        <v>1033.3</v>
+      </c>
+      <c r="H38">
+        <v>3399.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K38">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L38">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M38">
+        <v>283.4125281610712</v>
+      </c>
+      <c r="N38">
+        <v>144.5208051722622</v>
+      </c>
+      <c r="O38">
+        <v>49.13707375856914</v>
+      </c>
+      <c r="P38">
+        <v>95.38373141369303</v>
+      </c>
+      <c r="Q38">
+        <v>117.783731413693</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1487329583521731</v>
+      </c>
+      <c r="T38">
+        <v>1.221417425557493</v>
+      </c>
+      <c r="U38">
+        <v>0.123979436317051</v>
+      </c>
+      <c r="V38">
+        <v>0.34</v>
+      </c>
+      <c r="W38">
+        <v>0.08182642796925364</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.50993089864442</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1420710669152799</v>
+      </c>
+      <c r="C39">
+        <v>2636.093196325297</v>
+      </c>
+      <c r="D39">
+        <v>3952.256196325297</v>
+      </c>
+      <c r="E39">
+        <v>-601.1370000000002</v>
+      </c>
+      <c r="F39">
+        <v>2349.463</v>
+      </c>
+      <c r="G39">
+        <v>1033.3</v>
+      </c>
+      <c r="H39">
+        <v>3399.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K39">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L39">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M39">
+        <v>444.9399785877675</v>
+      </c>
+      <c r="N39">
+        <v>-17.0066452544342</v>
+      </c>
+      <c r="O39">
+        <v>-5.78225938650763</v>
+      </c>
+      <c r="P39">
+        <v>-11.22438586792657</v>
+      </c>
+      <c r="Q39">
+        <v>11.1756141320734</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1506571463444872</v>
+      </c>
+      <c r="T39">
+        <v>1.242796243876308</v>
+      </c>
+      <c r="U39">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V39">
+        <v>0.3270044058417488</v>
+      </c>
+      <c r="W39">
+        <v>0.1274515262655485</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.9617776642404375</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1435768612784504</v>
+      </c>
+      <c r="C40">
+        <v>2515.794583990886</v>
+      </c>
+      <c r="D40">
+        <v>3895.456583990886</v>
+      </c>
+      <c r="E40">
+        <v>-537.6379999999999</v>
+      </c>
+      <c r="F40">
+        <v>2412.962</v>
+      </c>
+      <c r="G40">
+        <v>1033.3</v>
+      </c>
+      <c r="H40">
+        <v>3399.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K40">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L40">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M40">
+        <v>456.965383414464</v>
+      </c>
+      <c r="N40">
+        <v>-29.03205008113071</v>
+      </c>
+      <c r="O40">
+        <v>-9.870897027584441</v>
+      </c>
+      <c r="P40">
+        <v>-19.16115305354626</v>
+      </c>
+      <c r="Q40">
+        <v>3.238846946453712</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1524612938661725</v>
+      </c>
+      <c r="T40">
+        <v>1.262841344583991</v>
+      </c>
+      <c r="U40">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V40">
+        <v>0.3183990267406501</v>
+      </c>
+      <c r="W40">
+        <v>0.1290812081090091</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.9364677257077942</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1450826556416209</v>
+      </c>
+      <c r="C41">
+        <v>2397.105425909703</v>
+      </c>
+      <c r="D41">
+        <v>3840.266425909703</v>
+      </c>
+      <c r="E41">
+        <v>-474.1390000000001</v>
+      </c>
+      <c r="F41">
+        <v>2476.461</v>
+      </c>
+      <c r="G41">
+        <v>1033.3</v>
+      </c>
+      <c r="H41">
+        <v>3399.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K41">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L41">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M41">
+        <v>468.9907882411604</v>
+      </c>
+      <c r="N41">
+        <v>-41.05745490782709</v>
+      </c>
+      <c r="O41">
+        <v>-13.95953466866121</v>
+      </c>
+      <c r="P41">
+        <v>-27.09792023916588</v>
+      </c>
+      <c r="Q41">
+        <v>-4.697920239165903</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.154324593765618</v>
+      </c>
+      <c r="T41">
+        <v>1.283543661708318</v>
+      </c>
+      <c r="U41">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V41">
+        <v>0.3102349491319155</v>
+      </c>
+      <c r="W41">
+        <v>0.1306273165245999</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.9124557327409277</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1465884500047915</v>
+      </c>
+      <c r="C42">
+        <v>2279.958270314639</v>
+      </c>
+      <c r="D42">
+        <v>3786.618270314639</v>
+      </c>
+      <c r="E42">
+        <v>-410.6399999999999</v>
+      </c>
+      <c r="F42">
+        <v>2539.96</v>
+      </c>
+      <c r="G42">
+        <v>1033.3</v>
+      </c>
+      <c r="H42">
+        <v>3399.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K42">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L42">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M42">
+        <v>481.0161930678569</v>
+      </c>
+      <c r="N42">
+        <v>-53.08285973452354</v>
+      </c>
+      <c r="O42">
+        <v>-18.048172309738</v>
+      </c>
+      <c r="P42">
+        <v>-35.03468742478553</v>
+      </c>
+      <c r="Q42">
+        <v>-12.63468742478555</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1562500036617117</v>
+      </c>
+      <c r="T42">
+        <v>1.304936056070124</v>
+      </c>
+      <c r="U42">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V42">
+        <v>0.3024790754036176</v>
+      </c>
+      <c r="W42">
+        <v>0.1320961195194112</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8896443394224045</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.148094244367962</v>
+      </c>
+      <c r="C43">
+        <v>2164.28938268797</v>
+      </c>
+      <c r="D43">
+        <v>3734.44838268797</v>
+      </c>
+      <c r="E43">
+        <v>-347.1410000000001</v>
+      </c>
+      <c r="F43">
+        <v>2603.459</v>
+      </c>
+      <c r="G43">
+        <v>1033.3</v>
+      </c>
+      <c r="H43">
+        <v>3399.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K43">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L43">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M43">
+        <v>493.0415978945533</v>
+      </c>
+      <c r="N43">
+        <v>-65.10826456121993</v>
+      </c>
+      <c r="O43">
+        <v>-22.13680995081478</v>
+      </c>
+      <c r="P43">
+        <v>-42.97145461040515</v>
+      </c>
+      <c r="Q43">
+        <v>-20.57145461040517</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1582406816898762</v>
+      </c>
+      <c r="T43">
+        <v>1.327053616342499</v>
+      </c>
+      <c r="U43">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V43">
+        <v>0.2951015369791391</v>
+      </c>
+      <c r="W43">
+        <v>0.1334932735876463</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.8679456969974679</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1496000387311325</v>
+      </c>
+      <c r="C44">
+        <v>2050.038493170599</v>
+      </c>
+      <c r="D44">
+        <v>3683.696493170599</v>
+      </c>
+      <c r="E44">
+        <v>-283.6420000000003</v>
+      </c>
+      <c r="F44">
+        <v>2666.958</v>
+      </c>
+      <c r="G44">
+        <v>1033.3</v>
+      </c>
+      <c r="H44">
+        <v>3399.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K44">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L44">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M44">
+        <v>505.0670027212497</v>
+      </c>
+      <c r="N44">
+        <v>-77.13366938791631</v>
+      </c>
+      <c r="O44">
+        <v>-26.22544759189155</v>
+      </c>
+      <c r="P44">
+        <v>-50.90822179602476</v>
+      </c>
+      <c r="Q44">
+        <v>-28.50822179602478</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1603000037879775</v>
+      </c>
+      <c r="T44">
+        <v>1.349933851107025</v>
+      </c>
+      <c r="U44">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V44">
+        <v>0.2880753099082072</v>
+      </c>
+      <c r="W44">
+        <v>0.1348238965097749</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.847280323259433</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.151105833094303</v>
+      </c>
+      <c r="C45">
+        <v>1937.148564291691</v>
+      </c>
+      <c r="D45">
+        <v>3634.305564291691</v>
+      </c>
+      <c r="E45">
+        <v>-220.143</v>
+      </c>
+      <c r="F45">
+        <v>2730.457</v>
+      </c>
+      <c r="G45">
+        <v>1033.3</v>
+      </c>
+      <c r="H45">
+        <v>3399.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K45">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L45">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M45">
+        <v>517.0924075479461</v>
+      </c>
+      <c r="N45">
+        <v>-89.15907421461276</v>
+      </c>
+      <c r="O45">
+        <v>-30.31408523296834</v>
+      </c>
+      <c r="P45">
+        <v>-58.84498898164442</v>
+      </c>
+      <c r="Q45">
+        <v>-36.44498898164444</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1624315828018017</v>
+      </c>
+      <c r="T45">
+        <v>1.373616901126446</v>
+      </c>
+      <c r="U45">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V45">
+        <v>0.2813758840963884</v>
+      </c>
+      <c r="W45">
+        <v>0.1360926299936651</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8275761296952602</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1526116274574735</v>
+      </c>
+      <c r="C46">
+        <v>1825.565577136736</v>
+      </c>
+      <c r="D46">
+        <v>3586.221577136736</v>
+      </c>
+      <c r="E46">
+        <v>-156.6440000000002</v>
+      </c>
+      <c r="F46">
+        <v>2793.956</v>
+      </c>
+      <c r="G46">
+        <v>1033.3</v>
+      </c>
+      <c r="H46">
+        <v>3399.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K46">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L46">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M46">
+        <v>529.1178123746425</v>
+      </c>
+      <c r="N46">
+        <v>-101.1844790413092</v>
+      </c>
+      <c r="O46">
+        <v>-34.40272287404513</v>
+      </c>
+      <c r="P46">
+        <v>-66.78175616726406</v>
+      </c>
+      <c r="Q46">
+        <v>-44.38175616726409</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1646392896375482</v>
+      </c>
+      <c r="T46">
+        <v>1.398145774360847</v>
+      </c>
+      <c r="U46">
+        <v>0.189379436317051</v>
+      </c>
+      <c r="V46">
+        <v>0.2749809776396523</v>
+      </c>
+      <c r="W46">
+        <v>0.137303693773742</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.808767581293095</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1797033535978626</v>
+      </c>
+      <c r="C47">
+        <v>1072.537688251465</v>
+      </c>
+      <c r="D47">
+        <v>2896.692688251464</v>
+      </c>
+      <c r="E47">
+        <v>-93.14499999999998</v>
+      </c>
+      <c r="F47">
+        <v>2857.455</v>
+      </c>
+      <c r="G47">
+        <v>1033.3</v>
+      </c>
+      <c r="H47">
+        <v>3399.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K47">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L47">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M47">
+        <v>690.3023682013389</v>
+      </c>
+      <c r="N47">
+        <v>-262.3690348680056</v>
+      </c>
+      <c r="O47">
+        <v>-89.20547185512191</v>
+      </c>
+      <c r="P47">
+        <v>-173.1635630128837</v>
+      </c>
+      <c r="Q47">
+        <v>-150.7635630128837</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1707380617713556</v>
+      </c>
+      <c r="T47">
+        <v>1.465906586681328</v>
+      </c>
+      <c r="U47">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V47">
+        <v>0.2107733364908527</v>
+      </c>
+      <c r="W47">
+        <v>0.1906609324969267</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6199215779142728</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1817311479610331</v>
+      </c>
+      <c r="C48">
+        <v>967.9426977072967</v>
+      </c>
+      <c r="D48">
+        <v>2855.596697707297</v>
+      </c>
+      <c r="E48">
+        <v>-29.64599999999973</v>
+      </c>
+      <c r="F48">
+        <v>2920.954</v>
+      </c>
+      <c r="G48">
+        <v>1033.3</v>
+      </c>
+      <c r="H48">
+        <v>3399.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K48">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L48">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M48">
+        <v>705.6424208280355</v>
+      </c>
+      <c r="N48">
+        <v>-277.7090874947021</v>
+      </c>
+      <c r="O48">
+        <v>-94.42108974819874</v>
+      </c>
+      <c r="P48">
+        <v>-183.2879977465034</v>
+      </c>
+      <c r="Q48">
+        <v>-160.8879977465034</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1731813592115659</v>
+      </c>
+      <c r="T48">
+        <v>1.493053004953204</v>
+      </c>
+      <c r="U48">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V48">
+        <v>0.2061913074367037</v>
+      </c>
+      <c r="W48">
+        <v>0.1917678564930163</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.606445021872658</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1837589423242036</v>
+      </c>
+      <c r="C49">
+        <v>864.4974702151817</v>
+      </c>
+      <c r="D49">
+        <v>2815.650470215182</v>
+      </c>
+      <c r="E49">
+        <v>33.85300000000007</v>
+      </c>
+      <c r="F49">
+        <v>2984.453</v>
+      </c>
+      <c r="G49">
+        <v>1033.3</v>
+      </c>
+      <c r="H49">
+        <v>3399.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K49">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L49">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M49">
+        <v>720.9824734547318</v>
+      </c>
+      <c r="N49">
+        <v>-293.0491401213985</v>
+      </c>
+      <c r="O49">
+        <v>-99.63670764127549</v>
+      </c>
+      <c r="P49">
+        <v>-193.412432480123</v>
+      </c>
+      <c r="Q49">
+        <v>-171.012432480123</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1757168565551804</v>
+      </c>
+      <c r="T49">
+        <v>1.521223816367416</v>
+      </c>
+      <c r="U49">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V49">
+        <v>0.2018042583423058</v>
+      </c>
+      <c r="W49">
+        <v>0.1928276773403362</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5935419363008994</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1857867366873741</v>
+      </c>
+      <c r="C50">
+        <v>762.1544201951833</v>
+      </c>
+      <c r="D50">
+        <v>2776.806420195183</v>
+      </c>
+      <c r="E50">
+        <v>97.35199999999986</v>
+      </c>
+      <c r="F50">
+        <v>3047.952</v>
+      </c>
+      <c r="G50">
+        <v>1033.3</v>
+      </c>
+      <c r="H50">
+        <v>3399.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K50">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L50">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M50">
+        <v>736.3225260814282</v>
+      </c>
+      <c r="N50">
+        <v>-308.3891927480949</v>
+      </c>
+      <c r="O50">
+        <v>-104.8523255343523</v>
+      </c>
+      <c r="P50">
+        <v>-203.5368672137426</v>
+      </c>
+      <c r="Q50">
+        <v>-181.1368672137426</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1783498730273954</v>
+      </c>
+      <c r="T50">
+        <v>1.550478120528328</v>
+      </c>
+      <c r="U50">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V50">
+        <v>0.1976000029601744</v>
+      </c>
+      <c r="W50">
+        <v>0.1938433389856845</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5811764792946307</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1878145310505446</v>
+      </c>
+      <c r="C51">
+        <v>660.868552251563</v>
+      </c>
+      <c r="D51">
+        <v>2739.019552251562</v>
+      </c>
+      <c r="E51">
+        <v>160.8509999999997</v>
+      </c>
+      <c r="F51">
+        <v>3111.451</v>
+      </c>
+      <c r="G51">
+        <v>1033.3</v>
+      </c>
+      <c r="H51">
+        <v>3399.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K51">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L51">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M51">
+        <v>751.6625787081246</v>
+      </c>
+      <c r="N51">
+        <v>-323.7292453747912</v>
+      </c>
+      <c r="O51">
+        <v>-110.067943427429</v>
+      </c>
+      <c r="P51">
+        <v>-213.6613019473622</v>
+      </c>
+      <c r="Q51">
+        <v>-191.2613019473622</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1810861450475403</v>
+      </c>
+      <c r="T51">
+        <v>1.580879652303393</v>
+      </c>
+      <c r="U51">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V51">
+        <v>0.1935673498385383</v>
+      </c>
+      <c r="W51">
+        <v>0.1948175450536715</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5693157348192301</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1898423254137152</v>
+      </c>
+      <c r="C52">
+        <v>560.5972873022756</v>
+      </c>
+      <c r="D52">
+        <v>2702.247287302276</v>
+      </c>
+      <c r="E52">
+        <v>224.3499999999999</v>
+      </c>
+      <c r="F52">
+        <v>3174.95</v>
+      </c>
+      <c r="G52">
+        <v>1033.3</v>
+      </c>
+      <c r="H52">
+        <v>3399.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K52">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L52">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M52">
+        <v>767.002631334821</v>
+      </c>
+      <c r="N52">
+        <v>-339.0692980014877</v>
+      </c>
+      <c r="O52">
+        <v>-115.2835613205058</v>
+      </c>
+      <c r="P52">
+        <v>-223.7857366809818</v>
+      </c>
+      <c r="Q52">
+        <v>-201.3857366809819</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1839318679484912</v>
+      </c>
+      <c r="T52">
+        <v>1.612497245349461</v>
+      </c>
+      <c r="U52">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V52">
+        <v>0.1896960028417675</v>
+      </c>
+      <c r="W52">
+        <v>0.1957527828789391</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5579294201228455</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1918701197768856</v>
+      </c>
+      <c r="C53">
+        <v>461.3003025285557</v>
+      </c>
+      <c r="D53">
+        <v>2666.449302528556</v>
+      </c>
+      <c r="E53">
+        <v>287.8490000000002</v>
+      </c>
+      <c r="F53">
+        <v>3238.449</v>
+      </c>
+      <c r="G53">
+        <v>1033.3</v>
+      </c>
+      <c r="H53">
+        <v>3399.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K53">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L53">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M53">
+        <v>782.3426839615175</v>
+      </c>
+      <c r="N53">
+        <v>-354.4093506281842</v>
+      </c>
+      <c r="O53">
+        <v>-120.4991792135826</v>
+      </c>
+      <c r="P53">
+        <v>-233.9101714146016</v>
+      </c>
+      <c r="Q53">
+        <v>-211.5101714146016</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1868937428045828</v>
+      </c>
+      <c r="T53">
+        <v>1.645405352397409</v>
+      </c>
+      <c r="U53">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V53">
+        <v>0.1859764733742818</v>
+      </c>
+      <c r="W53">
+        <v>0.196651344711059</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5469896275714171</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1938979141400562</v>
+      </c>
+      <c r="C54">
+        <v>362.9393838797682</v>
+      </c>
+      <c r="D54">
+        <v>2631.587383879768</v>
+      </c>
+      <c r="E54">
+        <v>351.348</v>
+      </c>
+      <c r="F54">
+        <v>3301.948</v>
+      </c>
+      <c r="G54">
+        <v>1033.3</v>
+      </c>
+      <c r="H54">
+        <v>3399.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K54">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L54">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M54">
+        <v>797.6827365882139</v>
+      </c>
+      <c r="N54">
+        <v>-369.7494032548805</v>
+      </c>
+      <c r="O54">
+        <v>-125.7147971066594</v>
+      </c>
+      <c r="P54">
+        <v>-244.0346061482211</v>
+      </c>
+      <c r="Q54">
+        <v>-221.6346061482212</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1899790291130116</v>
+      </c>
+      <c r="T54">
+        <v>1.679684630572355</v>
+      </c>
+      <c r="U54">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V54">
+        <v>0.1824000027324687</v>
+      </c>
+      <c r="W54">
+        <v>0.1975153464727127</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5364705962719668</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1959257085032267</v>
+      </c>
+      <c r="C55">
+        <v>265.478289999297</v>
+      </c>
+      <c r="D55">
+        <v>2597.625289999297</v>
+      </c>
+      <c r="E55">
+        <v>414.8470000000002</v>
+      </c>
+      <c r="F55">
+        <v>3365.447</v>
+      </c>
+      <c r="G55">
+        <v>1033.3</v>
+      </c>
+      <c r="H55">
+        <v>3399.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K55">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L55">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M55">
+        <v>813.0227892149104</v>
+      </c>
+      <c r="N55">
+        <v>-385.0894558815771</v>
+      </c>
+      <c r="O55">
+        <v>-130.9304149997362</v>
+      </c>
+      <c r="P55">
+        <v>-254.1590408818409</v>
+      </c>
+      <c r="Q55">
+        <v>-231.7590408818409</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1931956042005225</v>
+      </c>
+      <c r="T55">
+        <v>1.715422601435597</v>
+      </c>
+      <c r="U55">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V55">
+        <v>0.1789584932469504</v>
+      </c>
+      <c r="W55">
+        <v>0.1983467443943039</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5263485095498541</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1979535028663972</v>
+      </c>
+      <c r="C56">
+        <v>168.8826265528669</v>
+      </c>
+      <c r="D56">
+        <v>2564.528626552867</v>
+      </c>
+      <c r="E56">
+        <v>478.346</v>
+      </c>
+      <c r="F56">
+        <v>3428.946</v>
+      </c>
+      <c r="G56">
+        <v>1033.3</v>
+      </c>
+      <c r="H56">
+        <v>3399.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K56">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L56">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M56">
+        <v>828.3628418416067</v>
+      </c>
+      <c r="N56">
+        <v>-400.4295085082734</v>
+      </c>
+      <c r="O56">
+        <v>-136.146032892813</v>
+      </c>
+      <c r="P56">
+        <v>-264.2834756154604</v>
+      </c>
+      <c r="Q56">
+        <v>-241.8834756154604</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1965520303787948</v>
+      </c>
+      <c r="T56">
+        <v>1.752714397118979</v>
+      </c>
+      <c r="U56">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V56">
+        <v>0.1756444470757106</v>
+      </c>
+      <c r="W56">
+        <v>0.1991473498002807</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5166013149285607</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1999812972295677</v>
+      </c>
+      <c r="C57">
+        <v>73.11973004317088</v>
+      </c>
+      <c r="D57">
+        <v>2532.264730043171</v>
+      </c>
+      <c r="E57">
+        <v>541.8450000000003</v>
+      </c>
+      <c r="F57">
+        <v>3492.445</v>
+      </c>
+      <c r="G57">
+        <v>1033.3</v>
+      </c>
+      <c r="H57">
+        <v>3399.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K57">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L57">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M57">
+        <v>843.7028944683033</v>
+      </c>
+      <c r="N57">
+        <v>-415.7695611349699</v>
+      </c>
+      <c r="O57">
+        <v>-141.3616507858898</v>
+      </c>
+      <c r="P57">
+        <v>-274.4079103490801</v>
+      </c>
+      <c r="Q57">
+        <v>-252.0079103490801</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2000576310538791</v>
+      </c>
+      <c r="T57">
+        <v>1.791663605943846</v>
+      </c>
+      <c r="U57">
+        <v>0.241579436317051</v>
+      </c>
+      <c r="V57">
+        <v>0.172450911674334</v>
+      </c>
+      <c r="W57">
+        <v>0.1999188422824038</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5072085637480412</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2196490617003552</v>
+      </c>
+      <c r="C58">
+        <v>-265.769066397635</v>
+      </c>
+      <c r="D58">
+        <v>2256.874933602365</v>
+      </c>
+      <c r="E58">
+        <v>605.3440000000001</v>
+      </c>
+      <c r="F58">
+        <v>3555.944</v>
+      </c>
+      <c r="G58">
+        <v>1033.3</v>
+      </c>
+      <c r="H58">
+        <v>3399.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K58">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L58">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M58">
+        <v>965.7212670949996</v>
+      </c>
+      <c r="N58">
+        <v>-537.7879337616662</v>
+      </c>
+      <c r="O58">
+        <v>-182.8478974789665</v>
+      </c>
+      <c r="P58">
+        <v>-354.9400362826997</v>
+      </c>
+      <c r="Q58">
+        <v>-332.5400362826997</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2056316001860514</v>
+      </c>
+      <c r="T58">
+        <v>1.853593559704798</v>
+      </c>
+      <c r="U58">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V58">
+        <v>0.1506618299615644</v>
+      </c>
+      <c r="W58">
+        <v>0.230662781461594</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4431230292987188</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2219768560635257</v>
+      </c>
+      <c r="C59">
+        <v>-357.948222077338</v>
+      </c>
+      <c r="D59">
+        <v>2228.194777922663</v>
+      </c>
+      <c r="E59">
+        <v>668.8430000000003</v>
+      </c>
+      <c r="F59">
+        <v>3619.443</v>
+      </c>
+      <c r="G59">
+        <v>1033.3</v>
+      </c>
+      <c r="H59">
+        <v>3399.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K59">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L59">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M59">
+        <v>982.9662897216961</v>
+      </c>
+      <c r="N59">
+        <v>-555.0329563883627</v>
+      </c>
+      <c r="O59">
+        <v>-188.7112051720433</v>
+      </c>
+      <c r="P59">
+        <v>-366.3217512163193</v>
+      </c>
+      <c r="Q59">
+        <v>-343.9217512163194</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.209511404841541</v>
+      </c>
+      <c r="T59">
+        <v>1.896700386674677</v>
+      </c>
+      <c r="U59">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V59">
+        <v>0.1480186399622387</v>
+      </c>
+      <c r="W59">
+        <v>0.2313806175116897</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.435348941065408</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2243046504266962</v>
+      </c>
+      <c r="C60">
+        <v>-449.4075952117232</v>
+      </c>
+      <c r="D60">
+        <v>2200.234404788277</v>
+      </c>
+      <c r="E60">
+        <v>732.3419999999996</v>
+      </c>
+      <c r="F60">
+        <v>3682.942</v>
+      </c>
+      <c r="G60">
+        <v>1033.3</v>
+      </c>
+      <c r="H60">
+        <v>3399.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K60">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L60">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M60">
+        <v>1000.211312348392</v>
+      </c>
+      <c r="N60">
+        <v>-572.2779790150589</v>
+      </c>
+      <c r="O60">
+        <v>-194.5745128651201</v>
+      </c>
+      <c r="P60">
+        <v>-377.7034661499389</v>
+      </c>
+      <c r="Q60">
+        <v>-355.3034661499389</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2135759620996729</v>
+      </c>
+      <c r="T60">
+        <v>1.941859919690741</v>
+      </c>
+      <c r="U60">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V60">
+        <v>0.1454665944456484</v>
+      </c>
+      <c r="W60">
+        <v>0.2320737005945408</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4278429248401424</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2266324447898667</v>
+      </c>
+      <c r="C61">
+        <v>-540.1739464451584</v>
+      </c>
+      <c r="D61">
+        <v>2172.967053554842</v>
+      </c>
+      <c r="E61">
+        <v>795.8409999999999</v>
+      </c>
+      <c r="F61">
+        <v>3746.441</v>
+      </c>
+      <c r="G61">
+        <v>1033.3</v>
+      </c>
+      <c r="H61">
+        <v>3399.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K61">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L61">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M61">
+        <v>1017.456334975089</v>
+      </c>
+      <c r="N61">
+        <v>-589.5230016417554</v>
+      </c>
+      <c r="O61">
+        <v>-200.4378205581968</v>
+      </c>
+      <c r="P61">
+        <v>-389.0851810835586</v>
+      </c>
+      <c r="Q61">
+        <v>-366.6851810835586</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2178387904435673</v>
+      </c>
+      <c r="T61">
+        <v>1.989222356756368</v>
+      </c>
+      <c r="U61">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V61">
+        <v>0.1430010589465696</v>
+      </c>
+      <c r="W61">
+        <v>0.2327432893356003</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4205913498428518</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2289602391530373</v>
+      </c>
+      <c r="C62">
+        <v>-630.2727260896791</v>
+      </c>
+      <c r="D62">
+        <v>2146.367273910321</v>
+      </c>
+      <c r="E62">
+        <v>859.3399999999997</v>
+      </c>
+      <c r="F62">
+        <v>3809.94</v>
+      </c>
+      <c r="G62">
+        <v>1033.3</v>
+      </c>
+      <c r="H62">
+        <v>3399.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K62">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L62">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M62">
+        <v>1034.701357601785</v>
+      </c>
+      <c r="N62">
+        <v>-606.7680242684519</v>
+      </c>
+      <c r="O62">
+        <v>-206.3011282512737</v>
+      </c>
+      <c r="P62">
+        <v>-400.4668960171782</v>
+      </c>
+      <c r="Q62">
+        <v>-378.0668960171782</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2223147602046565</v>
+      </c>
+      <c r="T62">
+        <v>2.038952915675277</v>
+      </c>
+      <c r="U62">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V62">
+        <v>0.1406177079641268</v>
+      </c>
+      <c r="W62">
+        <v>0.2333905584519578</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4135814940121376</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2312880335162077</v>
+      </c>
+      <c r="C63">
+        <v>-719.7281533554883</v>
+      </c>
+      <c r="D63">
+        <v>2120.410846644512</v>
+      </c>
+      <c r="E63">
+        <v>922.8389999999999</v>
+      </c>
+      <c r="F63">
+        <v>3873.439</v>
+      </c>
+      <c r="G63">
+        <v>1033.3</v>
+      </c>
+      <c r="H63">
+        <v>3399.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K63">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L63">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M63">
+        <v>1051.946380228482</v>
+      </c>
+      <c r="N63">
+        <v>-624.0130468951484</v>
+      </c>
+      <c r="O63">
+        <v>-212.1644359443505</v>
+      </c>
+      <c r="P63">
+        <v>-411.8486109507979</v>
+      </c>
+      <c r="Q63">
+        <v>-389.448610950798</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2270202668765708</v>
+      </c>
+      <c r="T63">
+        <v>2.091233759666952</v>
+      </c>
+      <c r="U63">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V63">
+        <v>0.138312499636846</v>
+      </c>
+      <c r="W63">
+        <v>0.234016605630074</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4068014695201353</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2336158278793782</v>
+      </c>
+      <c r="C64">
+        <v>-808.5632899012348</v>
+      </c>
+      <c r="D64">
+        <v>2095.074710098765</v>
+      </c>
+      <c r="E64">
+        <v>986.3379999999997</v>
+      </c>
+      <c r="F64">
+        <v>3936.938</v>
+      </c>
+      <c r="G64">
+        <v>1033.3</v>
+      </c>
+      <c r="H64">
+        <v>3399.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K64">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L64">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M64">
+        <v>1069.191402855178</v>
+      </c>
+      <c r="N64">
+        <v>-641.2580695218446</v>
+      </c>
+      <c r="O64">
+        <v>-218.0277436374272</v>
+      </c>
+      <c r="P64">
+        <v>-423.2303258844174</v>
+      </c>
+      <c r="Q64">
+        <v>-400.8303258844174</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2319734317943752</v>
+      </c>
+      <c r="T64">
+        <v>2.146266227026608</v>
+      </c>
+      <c r="U64">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V64">
+        <v>0.1360816528685098</v>
+      </c>
+      <c r="W64">
+        <v>0.2346224577379285</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4002401554956171</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2359436222425488</v>
+      </c>
+      <c r="C65">
+        <v>-896.8001081735856</v>
+      </c>
+      <c r="D65">
+        <v>2070.336891826415</v>
+      </c>
+      <c r="E65">
+        <v>1049.837</v>
+      </c>
+      <c r="F65">
+        <v>4000.437</v>
+      </c>
+      <c r="G65">
+        <v>1033.3</v>
+      </c>
+      <c r="H65">
+        <v>3399.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K65">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L65">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M65">
+        <v>1086.436425481874</v>
+      </c>
+      <c r="N65">
+        <v>-658.5030921485411</v>
+      </c>
+      <c r="O65">
+        <v>-223.891051330504</v>
+      </c>
+      <c r="P65">
+        <v>-434.6120408180371</v>
+      </c>
+      <c r="Q65">
+        <v>-412.2120408180372</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2371943353563854</v>
+      </c>
+      <c r="T65">
+        <v>2.204273422351652</v>
+      </c>
+      <c r="U65">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V65">
+        <v>0.1339216266325017</v>
+      </c>
+      <c r="W65">
+        <v>0.2352090764455337</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3938871371544168</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2382714166057193</v>
+      </c>
+      <c r="C66">
+        <v>-984.4595549617256</v>
+      </c>
+      <c r="D66">
+        <v>2046.176445038274</v>
+      </c>
+      <c r="E66">
+        <v>1113.336</v>
+      </c>
+      <c r="F66">
+        <v>4063.936</v>
+      </c>
+      <c r="G66">
+        <v>1033.3</v>
+      </c>
+      <c r="H66">
+        <v>3399.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K66">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L66">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M66">
+        <v>1103.681448108571</v>
+      </c>
+      <c r="N66">
+        <v>-675.7481147752376</v>
+      </c>
+      <c r="O66">
+        <v>-229.7543590235808</v>
+      </c>
+      <c r="P66">
+        <v>-445.9937557516567</v>
+      </c>
+      <c r="Q66">
+        <v>-423.5937557516568</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.242705289116285</v>
+      </c>
+      <c r="T66">
+        <v>2.265503239639198</v>
+      </c>
+      <c r="U66">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V66">
+        <v>0.1318291012163688</v>
+      </c>
+      <c r="W66">
+        <v>0.2357773633185261</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.387732650636379</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2405992109688898</v>
+      </c>
+      <c r="C67">
+        <v>-1071.56161055319</v>
+      </c>
+      <c r="D67">
+        <v>2022.57338944681</v>
+      </c>
+      <c r="E67">
+        <v>1176.835</v>
+      </c>
+      <c r="F67">
+        <v>4127.434999999999</v>
+      </c>
+      <c r="G67">
+        <v>1033.3</v>
+      </c>
+      <c r="H67">
+        <v>3399.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K67">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L67">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M67">
+        <v>1120.926470735267</v>
+      </c>
+      <c r="N67">
+        <v>-692.9931374019338</v>
+      </c>
+      <c r="O67">
+        <v>-235.6176667166575</v>
+      </c>
+      <c r="P67">
+        <v>-457.3754706852764</v>
+      </c>
+      <c r="Q67">
+        <v>-434.9754706852764</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2485311545196074</v>
+      </c>
+      <c r="T67">
+        <v>2.330231903628889</v>
+      </c>
+      <c r="U67">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V67">
+        <v>0.1298009611976555</v>
+      </c>
+      <c r="W67">
+        <v>0.2363281644415803</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3817675329342809</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2429270053320604</v>
+      </c>
+      <c r="C68">
+        <v>-1158.125343842126</v>
+      </c>
+      <c r="D68">
+        <v>1999.508656157874</v>
+      </c>
+      <c r="E68">
+        <v>1240.334</v>
+      </c>
+      <c r="F68">
+        <v>4190.934</v>
+      </c>
+      <c r="G68">
+        <v>1033.3</v>
+      </c>
+      <c r="H68">
+        <v>3399.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K68">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L68">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M68">
+        <v>1138.171493361964</v>
+      </c>
+      <c r="N68">
+        <v>-710.2381600286305</v>
+      </c>
+      <c r="O68">
+        <v>-241.4809744097344</v>
+      </c>
+      <c r="P68">
+        <v>-468.7571856188961</v>
+      </c>
+      <c r="Q68">
+        <v>-446.3571856188962</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2546997178878312</v>
+      </c>
+      <c r="T68">
+        <v>2.398768136088563</v>
+      </c>
+      <c r="U68">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V68">
+        <v>0.127834279967388</v>
+      </c>
+      <c r="W68">
+        <v>0.2368622746215117</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3759831763746705</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2452547996952308</v>
+      </c>
+      <c r="C69">
+        <v>-1244.168963709456</v>
+      </c>
+      <c r="D69">
+        <v>1976.964036290544</v>
+      </c>
+      <c r="E69">
+        <v>1303.833</v>
+      </c>
+      <c r="F69">
+        <v>4254.433</v>
+      </c>
+      <c r="G69">
+        <v>1033.3</v>
+      </c>
+      <c r="H69">
+        <v>3399.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K69">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L69">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M69">
+        <v>1155.41651598866</v>
+      </c>
+      <c r="N69">
+        <v>-727.4831826553268</v>
+      </c>
+      <c r="O69">
+        <v>-247.3442821028111</v>
+      </c>
+      <c r="P69">
+        <v>-480.1389005525157</v>
+      </c>
+      <c r="Q69">
+        <v>-457.7389005525157</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2612421335814018</v>
+      </c>
+      <c r="T69">
+        <v>2.471458079606397</v>
+      </c>
+      <c r="U69">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V69">
+        <v>0.1259263056395165</v>
+      </c>
+      <c r="W69">
+        <v>0.2373804412139824</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3703714871750486</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2475825940584014</v>
+      </c>
+      <c r="C70">
+        <v>-1329.709866965915</v>
+      </c>
+      <c r="D70">
+        <v>1954.922133034084</v>
+      </c>
+      <c r="E70">
+        <v>1367.332</v>
+      </c>
+      <c r="F70">
+        <v>4317.932</v>
+      </c>
+      <c r="G70">
+        <v>1033.3</v>
+      </c>
+      <c r="H70">
+        <v>3399.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K70">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L70">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M70">
+        <v>1172.661538615357</v>
+      </c>
+      <c r="N70">
+        <v>-744.7282052820233</v>
+      </c>
+      <c r="O70">
+        <v>-253.2075897958879</v>
+      </c>
+      <c r="P70">
+        <v>-491.5206154861353</v>
+      </c>
+      <c r="Q70">
+        <v>-469.1206154861354</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2681934502558207</v>
+      </c>
+      <c r="T70">
+        <v>2.548691144594098</v>
+      </c>
+      <c r="U70">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V70">
+        <v>0.1240744482036413</v>
+      </c>
+      <c r="W70">
+        <v>0.237883367612557</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3649248476577684</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2499103884215719</v>
+      </c>
+      <c r="C71">
+        <v>-1414.764683123228</v>
+      </c>
+      <c r="D71">
+        <v>1933.366316876773</v>
+      </c>
+      <c r="E71">
+        <v>1430.831000000001</v>
+      </c>
+      <c r="F71">
+        <v>4381.431</v>
+      </c>
+      <c r="G71">
+        <v>1033.3</v>
+      </c>
+      <c r="H71">
+        <v>3399.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K71">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L71">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M71">
+        <v>1189.906561242053</v>
+      </c>
+      <c r="N71">
+        <v>-761.9732279087198</v>
+      </c>
+      <c r="O71">
+        <v>-259.0708974889648</v>
+      </c>
+      <c r="P71">
+        <v>-502.902330419755</v>
+      </c>
+      <c r="Q71">
+        <v>-480.502330419755</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2755932389737504</v>
+      </c>
+      <c r="T71">
+        <v>2.630906987968101</v>
+      </c>
+      <c r="U71">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V71">
+        <v>0.1222762677948928</v>
+      </c>
+      <c r="W71">
+        <v>0.2383717164343612</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3596360817496849</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2522381827847424</v>
+      </c>
+      <c r="C72">
+        <v>-1499.349316235595</v>
+      </c>
+      <c r="D72">
+        <v>1912.280683764405</v>
+      </c>
+      <c r="E72">
+        <v>1494.33</v>
+      </c>
+      <c r="F72">
+        <v>4444.93</v>
+      </c>
+      <c r="G72">
+        <v>1033.3</v>
+      </c>
+      <c r="H72">
+        <v>3399.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K72">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L72">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M72">
+        <v>1207.15158386875</v>
+      </c>
+      <c r="N72">
+        <v>-779.2182505354162</v>
+      </c>
+      <c r="O72">
+        <v>-264.9342051820415</v>
+      </c>
+      <c r="P72">
+        <v>-514.2840453533747</v>
+      </c>
+      <c r="Q72">
+        <v>-491.8840453533747</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2834863469395421</v>
+      </c>
+      <c r="T72">
+        <v>2.718603887567038</v>
+      </c>
+      <c r="U72">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V72">
+        <v>0.1205294639692515</v>
+      </c>
+      <c r="W72">
+        <v>0.2388461124326854</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3544984234389751</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2545659771479128</v>
+      </c>
+      <c r="C73">
+        <v>-1583.478984032746</v>
+      </c>
+      <c r="D73">
+        <v>1891.650015967253</v>
+      </c>
+      <c r="E73">
+        <v>1557.828999999999</v>
+      </c>
+      <c r="F73">
+        <v>4508.428999999999</v>
+      </c>
+      <c r="G73">
+        <v>1033.3</v>
+      </c>
+      <c r="H73">
+        <v>3399.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K73">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L73">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M73">
+        <v>1224.396606495446</v>
+      </c>
+      <c r="N73">
+        <v>-796.4632731621123</v>
+      </c>
+      <c r="O73">
+        <v>-270.7975128751182</v>
+      </c>
+      <c r="P73">
+        <v>-525.6657602869941</v>
+      </c>
+      <c r="Q73">
+        <v>-503.2657602869941</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2919238071788365</v>
+      </c>
+      <c r="T73">
+        <v>2.81234884920728</v>
+      </c>
+      <c r="U73">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V73">
+        <v>0.1188318658851776</v>
+      </c>
+      <c r="W73">
+        <v>0.2393071451634511</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3495054878975812</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2568937715110834</v>
+      </c>
+      <c r="C74">
+        <v>-1667.168254546897</v>
+      </c>
+      <c r="D74">
+        <v>1871.459745453103</v>
+      </c>
+      <c r="E74">
+        <v>1621.328</v>
+      </c>
+      <c r="F74">
+        <v>4571.928</v>
+      </c>
+      <c r="G74">
+        <v>1033.3</v>
+      </c>
+      <c r="H74">
+        <v>3399.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K74">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L74">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M74">
+        <v>1241.641629122142</v>
+      </c>
+      <c r="N74">
+        <v>-813.708295788809</v>
+      </c>
+      <c r="O74">
+        <v>-276.660820568195</v>
+      </c>
+      <c r="P74">
+        <v>-537.0474752206139</v>
+      </c>
+      <c r="Q74">
+        <v>-514.647475220614</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3009639431495093</v>
+      </c>
+      <c r="T74">
+        <v>2.912789879536111</v>
+      </c>
+      <c r="U74">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V74">
+        <v>0.117181423303439</v>
+      </c>
+      <c r="W74">
+        <v>0.2397553714294733</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3446512450101147</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2592215658742539</v>
+      </c>
+      <c r="C75">
+        <v>-1750.431080418869</v>
+      </c>
+      <c r="D75">
+        <v>1851.69591958113</v>
+      </c>
+      <c r="E75">
+        <v>1684.827</v>
+      </c>
+      <c r="F75">
+        <v>4635.427</v>
+      </c>
+      <c r="G75">
+        <v>1033.3</v>
+      </c>
+      <c r="H75">
+        <v>3399.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K75">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L75">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M75">
+        <v>1258.886651748839</v>
+      </c>
+      <c r="N75">
+        <v>-830.9533184155052</v>
+      </c>
+      <c r="O75">
+        <v>-282.5241282612718</v>
+      </c>
+      <c r="P75">
+        <v>-548.4291901542334</v>
+      </c>
+      <c r="Q75">
+        <v>-526.0291901542334</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3106737188217134</v>
+      </c>
+      <c r="T75">
+        <v>3.020670986185597</v>
+      </c>
+      <c r="U75">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V75">
+        <v>0.1155761983266795</v>
+      </c>
+      <c r="W75">
+        <v>0.2401913175238237</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3399299950784693</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2615493602374244</v>
+      </c>
+      <c r="C76">
+        <v>-1833.28083105318</v>
+      </c>
+      <c r="D76">
+        <v>1832.345168946819</v>
+      </c>
+      <c r="E76">
+        <v>1748.326</v>
+      </c>
+      <c r="F76">
+        <v>4698.925999999999</v>
+      </c>
+      <c r="G76">
+        <v>1033.3</v>
+      </c>
+      <c r="H76">
+        <v>3399.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K76">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L76">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M76">
+        <v>1276.131674375535</v>
+      </c>
+      <c r="N76">
+        <v>-848.1983410422017</v>
+      </c>
+      <c r="O76">
+        <v>-288.3874359543486</v>
+      </c>
+      <c r="P76">
+        <v>-559.8109050878531</v>
+      </c>
+      <c r="Q76">
+        <v>-537.4109050878532</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3211304003148561</v>
+      </c>
+      <c r="T76">
+        <v>3.136850639500427</v>
+      </c>
+      <c r="U76">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V76">
+        <v>0.1140143578087515</v>
+      </c>
+      <c r="W76">
+        <v>0.2406154812912997</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3353363464963278</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2638771546005949</v>
+      </c>
+      <c r="C77">
+        <v>-1915.730322777789</v>
+      </c>
+      <c r="D77">
+        <v>1813.39467722221</v>
+      </c>
+      <c r="E77">
+        <v>1811.824999999999</v>
+      </c>
+      <c r="F77">
+        <v>4762.424999999999</v>
+      </c>
+      <c r="G77">
+        <v>1033.3</v>
+      </c>
+      <c r="H77">
+        <v>3399.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K77">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L77">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M77">
+        <v>1293.376697002231</v>
+      </c>
+      <c r="N77">
+        <v>-865.443363668898</v>
+      </c>
+      <c r="O77">
+        <v>-294.2507436474253</v>
+      </c>
+      <c r="P77">
+        <v>-571.1926200214726</v>
+      </c>
+      <c r="Q77">
+        <v>-548.7926200214727</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3324236163274504</v>
+      </c>
+      <c r="T77">
+        <v>3.262324665080444</v>
+      </c>
+      <c r="U77">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V77">
+        <v>0.1124941663713014</v>
+      </c>
+      <c r="W77">
+        <v>0.2410283340249764</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3308651952097101</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2662049489637655</v>
+      </c>
+      <c r="C78">
+        <v>-1997.791847151497</v>
+      </c>
+      <c r="D78">
+        <v>1794.832152848503</v>
+      </c>
+      <c r="E78">
+        <v>1875.324</v>
+      </c>
+      <c r="F78">
+        <v>4825.924</v>
+      </c>
+      <c r="G78">
+        <v>1033.3</v>
+      </c>
+      <c r="H78">
+        <v>3399.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K78">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L78">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M78">
+        <v>1310.621719628928</v>
+      </c>
+      <c r="N78">
+        <v>-882.6883862955947</v>
+      </c>
+      <c r="O78">
+        <v>-300.1140513405022</v>
+      </c>
+      <c r="P78">
+        <v>-582.5743349550925</v>
+      </c>
+      <c r="Q78">
+        <v>-560.1743349550925</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3446579336744275</v>
+      </c>
+      <c r="T78">
+        <v>3.398254859458797</v>
+      </c>
+      <c r="U78">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V78">
+        <v>0.111013979971679</v>
+      </c>
+      <c r="W78">
+        <v>0.24143032221303</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.326511705799056</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2685327433269359</v>
+      </c>
+      <c r="C79">
+        <v>-2079.477197550368</v>
+      </c>
+      <c r="D79">
+        <v>1776.645802449631</v>
+      </c>
+      <c r="E79">
+        <v>1938.823</v>
+      </c>
+      <c r="F79">
+        <v>4889.423</v>
+      </c>
+      <c r="G79">
+        <v>1033.3</v>
+      </c>
+      <c r="H79">
+        <v>3399.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K79">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L79">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M79">
+        <v>1327.866742255624</v>
+      </c>
+      <c r="N79">
+        <v>-899.9334089222909</v>
+      </c>
+      <c r="O79">
+        <v>-305.9773590335789</v>
+      </c>
+      <c r="P79">
+        <v>-593.956049888712</v>
+      </c>
+      <c r="Q79">
+        <v>-571.556049888712</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3579561047037504</v>
+      </c>
+      <c r="T79">
+        <v>3.546005070739614</v>
+      </c>
+      <c r="U79">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V79">
+        <v>0.1095722399720468</v>
+      </c>
+      <c r="W79">
+        <v>0.2418218691494459</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3222712940354319</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2708605376901065</v>
+      </c>
+      <c r="C80">
+        <v>-2160.79769415405</v>
+      </c>
+      <c r="D80">
+        <v>1758.824305845949</v>
+      </c>
+      <c r="E80">
+        <v>2002.322</v>
+      </c>
+      <c r="F80">
+        <v>4952.922</v>
+      </c>
+      <c r="G80">
+        <v>1033.3</v>
+      </c>
+      <c r="H80">
+        <v>3399.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K80">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L80">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M80">
+        <v>1345.111764882321</v>
+      </c>
+      <c r="N80">
+        <v>-917.1784315489874</v>
+      </c>
+      <c r="O80">
+        <v>-311.8406667266557</v>
+      </c>
+      <c r="P80">
+        <v>-605.3377648223317</v>
+      </c>
+      <c r="Q80">
+        <v>-582.9377648223317</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3724632003721028</v>
+      </c>
+      <c r="T80">
+        <v>3.707187119409597</v>
+      </c>
+      <c r="U80">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V80">
+        <v>0.1081674676647129</v>
+      </c>
+      <c r="W80">
+        <v>0.2422033764208255</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3181396107785673</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.273188332053277</v>
+      </c>
+      <c r="C81">
+        <v>-2241.764207443172</v>
+      </c>
+      <c r="D81">
+        <v>1741.356792556828</v>
+      </c>
+      <c r="E81">
+        <v>2065.821</v>
+      </c>
+      <c r="F81">
+        <v>5016.421</v>
+      </c>
+      <c r="G81">
+        <v>1033.3</v>
+      </c>
+      <c r="H81">
+        <v>3399.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K81">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L81">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M81">
+        <v>1362.356787509017</v>
+      </c>
+      <c r="N81">
+        <v>-934.4234541756839</v>
+      </c>
+      <c r="O81">
+        <v>-317.7039744197326</v>
+      </c>
+      <c r="P81">
+        <v>-616.7194797559514</v>
+      </c>
+      <c r="Q81">
+        <v>-594.3194797559514</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3883519241993458</v>
+      </c>
+      <c r="T81">
+        <v>3.883719839381482</v>
+      </c>
+      <c r="U81">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V81">
+        <v>0.1067982592132608</v>
+      </c>
+      <c r="W81">
+        <v>0.2425752252802713</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.314112527097826</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2755161264164475</v>
+      </c>
+      <c r="C82">
+        <v>-2322.387180310366</v>
+      </c>
+      <c r="D82">
+        <v>1724.232819689635</v>
+      </c>
+      <c r="E82">
+        <v>2129.32</v>
+      </c>
+      <c r="F82">
+        <v>5079.92</v>
+      </c>
+      <c r="G82">
+        <v>1033.3</v>
+      </c>
+      <c r="H82">
+        <v>3399.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K82">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L82">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M82">
+        <v>1379.601810135714</v>
+      </c>
+      <c r="N82">
+        <v>-951.6684768023804</v>
+      </c>
+      <c r="O82">
+        <v>-323.5672821128094</v>
+      </c>
+      <c r="P82">
+        <v>-628.101194689571</v>
+      </c>
+      <c r="Q82">
+        <v>-605.701194689571</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4058295204093131</v>
+      </c>
+      <c r="T82">
+        <v>4.077905831350557</v>
+      </c>
+      <c r="U82">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V82">
+        <v>0.1054632809730951</v>
+      </c>
+      <c r="W82">
+        <v>0.2429377779182311</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3101861205091032</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2778439207796179</v>
+      </c>
+      <c r="C83">
+        <v>-2402.676648879392</v>
+      </c>
+      <c r="D83">
+        <v>1707.442351120608</v>
+      </c>
+      <c r="E83">
+        <v>2192.819</v>
+      </c>
+      <c r="F83">
+        <v>5143.419</v>
+      </c>
+      <c r="G83">
+        <v>1033.3</v>
+      </c>
+      <c r="H83">
+        <v>3399.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K83">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L83">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M83">
+        <v>1396.84683276241</v>
+      </c>
+      <c r="N83">
+        <v>-968.9134994290766</v>
+      </c>
+      <c r="O83">
+        <v>-329.4305898058861</v>
+      </c>
+      <c r="P83">
+        <v>-639.4829096231906</v>
+      </c>
+      <c r="Q83">
+        <v>-617.0829096231906</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4251468635887506</v>
+      </c>
+      <c r="T83">
+        <v>4.292532454053218</v>
+      </c>
+      <c r="U83">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V83">
+        <v>0.1041612651586124</v>
+      </c>
+      <c r="W83">
+        <v>0.2432913786392041</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3063566622312131</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2801717151427885</v>
+      </c>
+      <c r="C84">
+        <v>-2482.64226211958</v>
+      </c>
+      <c r="D84">
+        <v>1690.97573788042</v>
+      </c>
+      <c r="E84">
+        <v>2256.318</v>
+      </c>
+      <c r="F84">
+        <v>5206.918</v>
+      </c>
+      <c r="G84">
+        <v>1033.3</v>
+      </c>
+      <c r="H84">
+        <v>3399.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K84">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L84">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M84">
+        <v>1414.091855389107</v>
+      </c>
+      <c r="N84">
+        <v>-986.1585220557731</v>
+      </c>
+      <c r="O84">
+        <v>-335.2938974989629</v>
+      </c>
+      <c r="P84">
+        <v>-650.8646245568102</v>
+      </c>
+      <c r="Q84">
+        <v>-628.4646245568102</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4466105782325702</v>
+      </c>
+      <c r="T84">
+        <v>4.531006479278397</v>
+      </c>
+      <c r="U84">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V84">
+        <v>0.1028910058274098</v>
+      </c>
+      <c r="W84">
+        <v>0.2436363549523486</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3026206053747348</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.282499509505959</v>
+      </c>
+      <c r="C85">
+        <v>-2562.293300336136</v>
+      </c>
+      <c r="D85">
+        <v>1674.823699663864</v>
+      </c>
+      <c r="E85">
+        <v>2319.817</v>
+      </c>
+      <c r="F85">
+        <v>5270.417</v>
+      </c>
+      <c r="G85">
+        <v>1033.3</v>
+      </c>
+      <c r="H85">
+        <v>3399.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K85">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L85">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M85">
+        <v>1431.336878015803</v>
+      </c>
+      <c r="N85">
+        <v>-1003.40354468247</v>
+      </c>
+      <c r="O85">
+        <v>-341.1572051920397</v>
+      </c>
+      <c r="P85">
+        <v>-662.2463394904299</v>
+      </c>
+      <c r="Q85">
+        <v>-639.84633949043</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4705994357756625</v>
+      </c>
+      <c r="T85">
+        <v>4.797536272177126</v>
+      </c>
+      <c r="U85">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V85">
+        <v>0.1016513551547904</v>
+      </c>
+      <c r="W85">
+        <v>0.2439730185832487</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2989745739846777</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2848273038691295</v>
+      </c>
+      <c r="C86">
+        <v>-2641.638692610773</v>
+      </c>
+      <c r="D86">
+        <v>1658.977307389226</v>
+      </c>
+      <c r="E86">
+        <v>2383.315999999999</v>
+      </c>
+      <c r="F86">
+        <v>5333.915999999999</v>
+      </c>
+      <c r="G86">
+        <v>1033.3</v>
+      </c>
+      <c r="H86">
+        <v>3399.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K86">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L86">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M86">
+        <v>1448.581900642499</v>
+      </c>
+      <c r="N86">
+        <v>-1020.648567309166</v>
+      </c>
+      <c r="O86">
+        <v>-347.0205128851164</v>
+      </c>
+      <c r="P86">
+        <v>-673.6280544240494</v>
+      </c>
+      <c r="Q86">
+        <v>-651.2280544240494</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4975869005116412</v>
+      </c>
+      <c r="T86">
+        <v>5.097382289188194</v>
+      </c>
+      <c r="U86">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V86">
+        <v>0.1004412199743763</v>
+      </c>
+      <c r="W86">
+        <v>0.244301666413413</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2954153528658126</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2871550982323</v>
+      </c>
+      <c r="C87">
+        <v>-2720.68703326154</v>
+      </c>
+      <c r="D87">
+        <v>1643.42796673846</v>
+      </c>
+      <c r="E87">
+        <v>2446.815</v>
+      </c>
+      <c r="F87">
+        <v>5397.415</v>
+      </c>
+      <c r="G87">
+        <v>1033.3</v>
+      </c>
+      <c r="H87">
+        <v>3399.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K87">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L87">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M87">
+        <v>1465.826923269196</v>
+      </c>
+      <c r="N87">
+        <v>-1037.893589935862</v>
+      </c>
+      <c r="O87">
+        <v>-352.8838205781932</v>
+      </c>
+      <c r="P87">
+        <v>-685.0097693576691</v>
+      </c>
+      <c r="Q87">
+        <v>-662.6097693576692</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5281726938790839</v>
+      </c>
+      <c r="T87">
+        <v>5.437207775134073</v>
+      </c>
+      <c r="U87">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V87">
+        <v>0.09925955856291302</v>
+      </c>
+      <c r="W87">
+        <v>0.2446225813534558</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2919398781262148</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2894828925954706</v>
+      </c>
+      <c r="C88">
+        <v>-2799.44659738557</v>
+      </c>
+      <c r="D88">
+        <v>1628.167402614429</v>
+      </c>
+      <c r="E88">
+        <v>2510.314</v>
+      </c>
+      <c r="F88">
+        <v>5460.914</v>
+      </c>
+      <c r="G88">
+        <v>1033.3</v>
+      </c>
+      <c r="H88">
+        <v>3399.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K88">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L88">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M88">
+        <v>1483.071945895892</v>
+      </c>
+      <c r="N88">
+        <v>-1055.138612562559</v>
+      </c>
+      <c r="O88">
+        <v>-358.74712827127</v>
+      </c>
+      <c r="P88">
+        <v>-696.3914842912889</v>
+      </c>
+      <c r="Q88">
+        <v>-673.9914842912889</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5631278862990186</v>
+      </c>
+      <c r="T88">
+        <v>5.825579759072222</v>
+      </c>
+      <c r="U88">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V88">
+        <v>0.09810537764939077</v>
+      </c>
+      <c r="W88">
+        <v>0.2449360331553581</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2885452283805611</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.291810686958641</v>
+      </c>
+      <c r="C89">
+        <v>-2877.925355543862</v>
+      </c>
+      <c r="D89">
+        <v>1613.187644456137</v>
+      </c>
+      <c r="E89">
+        <v>2573.813</v>
+      </c>
+      <c r="F89">
+        <v>5524.413</v>
+      </c>
+      <c r="G89">
+        <v>1033.3</v>
+      </c>
+      <c r="H89">
+        <v>3399.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K89">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L89">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M89">
+        <v>1500.316968522588</v>
+      </c>
+      <c r="N89">
+        <v>-1072.383635189255</v>
+      </c>
+      <c r="O89">
+        <v>-364.6104359643468</v>
+      </c>
+      <c r="P89">
+        <v>-707.7731992249082</v>
+      </c>
+      <c r="Q89">
+        <v>-685.3731992249083</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6034608006297122</v>
+      </c>
+      <c r="T89">
+        <v>6.273701279000854</v>
+      </c>
+      <c r="U89">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V89">
+        <v>0.09697772963043227</v>
+      </c>
+      <c r="W89">
+        <v>0.2452422791687108</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2852286165600949</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2941384813218115</v>
+      </c>
+      <c r="C90">
+        <v>-2956.130987642799</v>
+      </c>
+      <c r="D90">
+        <v>1598.4810123572</v>
+      </c>
+      <c r="E90">
+        <v>2637.311999999999</v>
+      </c>
+      <c r="F90">
+        <v>5587.911999999999</v>
+      </c>
+      <c r="G90">
+        <v>1033.3</v>
+      </c>
+      <c r="H90">
+        <v>3399.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K90">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L90">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M90">
+        <v>1517.561991149285</v>
+      </c>
+      <c r="N90">
+        <v>-1089.628657815952</v>
+      </c>
+      <c r="O90">
+        <v>-370.4737436574235</v>
+      </c>
+      <c r="P90">
+        <v>-719.1549141585281</v>
+      </c>
+      <c r="Q90">
+        <v>-696.7549141585281</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6505158673488551</v>
+      </c>
+      <c r="T90">
+        <v>6.796509718917593</v>
+      </c>
+      <c r="U90">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V90">
+        <v>0.09587570997554098</v>
+      </c>
+      <c r="W90">
+        <v>0.2455415650453965</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.281987382281003</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2964662756849821</v>
+      </c>
+      <c r="C91">
+        <v>-3034.070896063231</v>
+      </c>
+      <c r="D91">
+        <v>1584.040103936769</v>
+      </c>
+      <c r="E91">
+        <v>2700.811</v>
+      </c>
+      <c r="F91">
+        <v>5651.411</v>
+      </c>
+      <c r="G91">
+        <v>1033.3</v>
+      </c>
+      <c r="H91">
+        <v>3399.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K91">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L91">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M91">
+        <v>1534.807013775982</v>
+      </c>
+      <c r="N91">
+        <v>-1106.873680442648</v>
+      </c>
+      <c r="O91">
+        <v>-376.3370513505004</v>
+      </c>
+      <c r="P91">
+        <v>-730.5366290921479</v>
+      </c>
+      <c r="Q91">
+        <v>-708.1366290921479</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7061264007442056</v>
+      </c>
+      <c r="T91">
+        <v>7.414374238819193</v>
+      </c>
+      <c r="U91">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V91">
+        <v>0.09479845480727647</v>
+      </c>
+      <c r="W91">
+        <v>0.2458341253967634</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2788189847272837</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2987940700481526</v>
+      </c>
+      <c r="C92">
+        <v>-3111.752218084256</v>
+      </c>
+      <c r="D92">
+        <v>1569.857781915744</v>
+      </c>
+      <c r="E92">
+        <v>2764.31</v>
+      </c>
+      <c r="F92">
+        <v>5714.91</v>
+      </c>
+      <c r="G92">
+        <v>1033.3</v>
+      </c>
+      <c r="H92">
+        <v>3399.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K92">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L92">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M92">
+        <v>1552.052036402678</v>
+      </c>
+      <c r="N92">
+        <v>-1124.118703069345</v>
+      </c>
+      <c r="O92">
+        <v>-382.2003590435772</v>
+      </c>
+      <c r="P92">
+        <v>-741.9183440257673</v>
+      </c>
+      <c r="Q92">
+        <v>-719.5183440257673</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7728590408186262</v>
+      </c>
+      <c r="T92">
+        <v>8.155811662701113</v>
+      </c>
+      <c r="U92">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V92">
+        <v>0.09374513864275118</v>
+      </c>
+      <c r="W92">
+        <v>0.2461201844069889</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2757209960080917</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.301121864411323</v>
+      </c>
+      <c r="C93">
+        <v>-3189.181837645547</v>
+      </c>
+      <c r="D93">
+        <v>1555.927162354453</v>
+      </c>
+      <c r="E93">
+        <v>2827.809</v>
+      </c>
+      <c r="F93">
+        <v>5778.409</v>
+      </c>
+      <c r="G93">
+        <v>1033.3</v>
+      </c>
+      <c r="H93">
+        <v>3399.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K93">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L93">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M93">
+        <v>1569.297059029374</v>
+      </c>
+      <c r="N93">
+        <v>-1141.363725696041</v>
+      </c>
+      <c r="O93">
+        <v>-388.0636667366539</v>
+      </c>
+      <c r="P93">
+        <v>-753.3000589593869</v>
+      </c>
+      <c r="Q93">
+        <v>-730.9000589593869</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8544211564651403</v>
+      </c>
+      <c r="T93">
+        <v>9.062012958556792</v>
+      </c>
+      <c r="U93">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V93">
+        <v>0.09271497228403965</v>
+      </c>
+      <c r="W93">
+        <v>0.2463999564060005</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2726910949530578</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3034496587744936</v>
+      </c>
+      <c r="C94">
+        <v>-3266.366396488905</v>
+      </c>
+      <c r="D94">
+        <v>1542.241603511095</v>
+      </c>
+      <c r="E94">
+        <v>2891.308</v>
+      </c>
+      <c r="F94">
+        <v>5841.908</v>
+      </c>
+      <c r="G94">
+        <v>1033.3</v>
+      </c>
+      <c r="H94">
+        <v>3399.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K94">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L94">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M94">
+        <v>1586.542081656071</v>
+      </c>
+      <c r="N94">
+        <v>-1158.608748322737</v>
+      </c>
+      <c r="O94">
+        <v>-393.9269744297308</v>
+      </c>
+      <c r="P94">
+        <v>-764.6817738930067</v>
+      </c>
+      <c r="Q94">
+        <v>-742.2817738930067</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.956373801023283</v>
+      </c>
+      <c r="T94">
+        <v>10.19476457837639</v>
+      </c>
+      <c r="U94">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V94">
+        <v>0.09170720084616962</v>
+      </c>
+      <c r="W94">
+        <v>0.2466736464050337</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2697270613122636</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3057774531376641</v>
+      </c>
+      <c r="C95">
+        <v>-3343.312304716953</v>
+      </c>
+      <c r="D95">
+        <v>1528.794695283048</v>
+      </c>
+      <c r="E95">
+        <v>2954.807</v>
+      </c>
+      <c r="F95">
+        <v>5905.407</v>
+      </c>
+      <c r="G95">
+        <v>1033.3</v>
+      </c>
+      <c r="H95">
+        <v>3399.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K95">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L95">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M95">
+        <v>1603.787104282767</v>
+      </c>
+      <c r="N95">
+        <v>-1175.853770949434</v>
+      </c>
+      <c r="O95">
+        <v>-399.7902821228076</v>
+      </c>
+      <c r="P95">
+        <v>-776.0634888266263</v>
+      </c>
+      <c r="Q95">
+        <v>-753.6634888266263</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.087455772598038</v>
+      </c>
+      <c r="T95">
+        <v>11.65115951814445</v>
+      </c>
+      <c r="U95">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V95">
+        <v>0.09072110191233985</v>
+      </c>
+      <c r="W95">
+        <v>0.246941450597636</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2668267703304114</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3081052475008346</v>
+      </c>
+      <c r="C96">
+        <v>-3420.025750804245</v>
+      </c>
+      <c r="D96">
+        <v>1515.580249195755</v>
+      </c>
+      <c r="E96">
+        <v>3018.306</v>
+      </c>
+      <c r="F96">
+        <v>5968.906</v>
+      </c>
+      <c r="G96">
+        <v>1033.3</v>
+      </c>
+      <c r="H96">
+        <v>3399.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K96">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L96">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M96">
+        <v>1621.032126909464</v>
+      </c>
+      <c r="N96">
+        <v>-1193.09879357613</v>
+      </c>
+      <c r="O96">
+        <v>-405.6535898158843</v>
+      </c>
+      <c r="P96">
+        <v>-787.4452037602459</v>
+      </c>
+      <c r="Q96">
+        <v>-765.045203760246</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.262231734697711</v>
+      </c>
+      <c r="T96">
+        <v>13.5930194378352</v>
+      </c>
+      <c r="U96">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V96">
+        <v>0.08975598380688944</v>
+      </c>
+      <c r="W96">
+        <v>0.2472035568286936</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2639881876673219</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3104330418640052</v>
+      </c>
+      <c r="C97">
+        <v>-3496.512711093616</v>
+      </c>
+      <c r="D97">
+        <v>1502.592288906385</v>
+      </c>
+      <c r="E97">
+        <v>3081.805</v>
+      </c>
+      <c r="F97">
+        <v>6032.405</v>
+      </c>
+      <c r="G97">
+        <v>1033.3</v>
+      </c>
+      <c r="H97">
+        <v>3399.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K97">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L97">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M97">
+        <v>1638.27714953616</v>
+      </c>
+      <c r="N97">
+        <v>-1210.343816202827</v>
+      </c>
+      <c r="O97">
+        <v>-411.5168975089611</v>
+      </c>
+      <c r="P97">
+        <v>-798.8269186938655</v>
+      </c>
+      <c r="Q97">
+        <v>-776.4269186938656</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.506918081637254</v>
+      </c>
+      <c r="T97">
+        <v>16.31162332540224</v>
+      </c>
+      <c r="U97">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V97">
+        <v>0.08881118397734322</v>
+      </c>
+      <c r="W97">
+        <v>0.2474601450338342</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2612093646392448</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3127608362271757</v>
+      </c>
+      <c r="C98">
+        <v>-3572.778958808392</v>
+      </c>
+      <c r="D98">
+        <v>1489.825041191608</v>
+      </c>
+      <c r="E98">
+        <v>3145.304</v>
+      </c>
+      <c r="F98">
+        <v>6095.904</v>
+      </c>
+      <c r="G98">
+        <v>1033.3</v>
+      </c>
+      <c r="H98">
+        <v>3399.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K98">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L98">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M98">
+        <v>1655.522172162856</v>
+      </c>
+      <c r="N98">
+        <v>-1227.588838829523</v>
+      </c>
+      <c r="O98">
+        <v>-417.3802052020378</v>
+      </c>
+      <c r="P98">
+        <v>-810.2086336274851</v>
+      </c>
+      <c r="Q98">
+        <v>-787.8086336274852</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.873947602046564</v>
+      </c>
+      <c r="T98">
+        <v>20.38952915675276</v>
+      </c>
+      <c r="U98">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V98">
+        <v>0.08788606747757922</v>
+      </c>
+      <c r="W98">
+        <v>0.2477113876513677</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.258488433757586</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3150886305903461</v>
+      </c>
+      <c r="C99">
+        <v>-3648.830072609043</v>
+      </c>
+      <c r="D99">
+        <v>1477.272927390957</v>
+      </c>
+      <c r="E99">
+        <v>3208.802999999999</v>
+      </c>
+      <c r="F99">
+        <v>6159.402999999999</v>
+      </c>
+      <c r="G99">
+        <v>1033.3</v>
+      </c>
+      <c r="H99">
+        <v>3399.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K99">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L99">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M99">
+        <v>1672.767194789553</v>
+      </c>
+      <c r="N99">
+        <v>-1244.833861456219</v>
+      </c>
+      <c r="O99">
+        <v>-423.2435128951146</v>
+      </c>
+      <c r="P99">
+        <v>-821.5903485611047</v>
+      </c>
+      <c r="Q99">
+        <v>-799.1903485611048</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.485663469395419</v>
+      </c>
+      <c r="T99">
+        <v>27.18603887567035</v>
+      </c>
+      <c r="U99">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V99">
+        <v>0.08698002554482068</v>
+      </c>
+      <c r="W99">
+        <v>0.2479574500087459</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2558236045435903</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3174164249535166</v>
+      </c>
+      <c r="C100">
+        <v>-3724.671444720876</v>
+      </c>
+      <c r="D100">
+        <v>1464.930555279123</v>
+      </c>
+      <c r="E100">
+        <v>3272.301999999999</v>
+      </c>
+      <c r="F100">
+        <v>6222.901999999999</v>
+      </c>
+      <c r="G100">
+        <v>1033.3</v>
+      </c>
+      <c r="H100">
+        <v>3399.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K100">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L100">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M100">
+        <v>1690.012217416249</v>
+      </c>
+      <c r="N100">
+        <v>-1262.078884082916</v>
+      </c>
+      <c r="O100">
+        <v>-429.1068205881913</v>
+      </c>
+      <c r="P100">
+        <v>-832.9720634947244</v>
+      </c>
+      <c r="Q100">
+        <v>-810.5720634947244</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.709095204093126</v>
+      </c>
+      <c r="T100">
+        <v>40.77905831350552</v>
+      </c>
+      <c r="U100">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V100">
+        <v>0.08609247426375111</v>
+      </c>
+      <c r="W100">
+        <v>0.2481984906853613</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2532131595992679</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3197442193166872</v>
+      </c>
+      <c r="C101">
+        <v>-3800.308288657687</v>
+      </c>
+      <c r="D101">
+        <v>1452.792711342313</v>
+      </c>
+      <c r="E101">
+        <v>3335.801</v>
+      </c>
+      <c r="F101">
+        <v>6286.401</v>
+      </c>
+      <c r="G101">
+        <v>1033.3</v>
+      </c>
+      <c r="H101">
+        <v>3399.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>450.3333333333333</v>
+      </c>
+      <c r="K101">
+        <v>22.39999999999998</v>
+      </c>
+      <c r="L101">
+        <v>427.9333333333333</v>
+      </c>
+      <c r="M101">
+        <v>1707.257240042946</v>
+      </c>
+      <c r="N101">
+        <v>-1279.323906709612</v>
+      </c>
+      <c r="O101">
+        <v>-434.9701282812683</v>
+      </c>
+      <c r="P101">
+        <v>-844.3537784283442</v>
+      </c>
+      <c r="Q101">
+        <v>-821.9537784283442</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.379390408186254</v>
+      </c>
+      <c r="T101">
+        <v>81.55811662701105</v>
+      </c>
+      <c r="U101">
+        <v>0.271579436317051</v>
+      </c>
+      <c r="V101">
+        <v>0.08522285331159198</v>
+      </c>
+      <c r="W101">
+        <v>0.2484346618533581</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.250655450916447</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_aerospace_defense.xlsx
@@ -644,10 +644,10 @@
         <v>0.1868075944411822</v>
       </c>
       <c r="X2">
-        <v>0.1328119862221327</v>
+        <v>0.1327988012704464</v>
       </c>
       <c r="Y2">
-        <v>0.05399560821904947</v>
+        <v>0.05400879317073587</v>
       </c>
       <c r="Z2">
         <v>1.296655127455829</v>
@@ -656,10 +656,10 @@
         <v>0.08222472555748127</v>
       </c>
       <c r="AB2">
-        <v>0.1102884348157697</v>
+        <v>0.1102791076506722</v>
       </c>
       <c r="AC2">
-        <v>-0.02806370925828841</v>
+        <v>-0.02805438209319093</v>
       </c>
       <c r="AD2">
         <v>2760.5</v>
@@ -775,10 +775,10 @@
         <v>0.1868075944411822</v>
       </c>
       <c r="X3">
-        <v>0.1328119862221327</v>
+        <v>0.1327988012704464</v>
       </c>
       <c r="Y3">
-        <v>0.05399560821904947</v>
+        <v>0.05400879317073587</v>
       </c>
       <c r="Z3">
         <v>1.296655127455829</v>
@@ -787,10 +787,10 @@
         <v>0.08222472555748127</v>
       </c>
       <c r="AB3">
-        <v>0.1102884348157697</v>
+        <v>0.1102791076506722</v>
       </c>
       <c r="AC3">
-        <v>-0.02806370925828841</v>
+        <v>-0.02805438209319093</v>
       </c>
       <c r="AD3">
         <v>2760.5</v>
@@ -1127,49 +1127,49 @@
         <v>1.991</v>
       </c>
       <c r="F2">
-        <v>2.52757375643948</v>
+        <v>2.5098077914431</v>
       </c>
       <c r="G2">
         <v>6.25679963735267</v>
       </c>
       <c r="H2">
-        <v>5.34604487760653</v>
+        <v>5.55988667271079</v>
       </c>
       <c r="I2">
         <v>0.292590119452659</v>
       </c>
       <c r="J2">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="K2">
         <v>6674.2</v>
       </c>
       <c r="L2">
-        <v>6986.51702477833</v>
+        <v>6970.06855724073</v>
       </c>
       <c r="M2">
         <v>8602.799999999999</v>
       </c>
       <c r="N2">
-        <v>8513.29202477833</v>
+        <v>8591.19055724073</v>
       </c>
       <c r="O2">
         <v>2760.5</v>
       </c>
       <c r="P2">
-        <v>2358.675</v>
+        <v>2453.022</v>
       </c>
       <c r="Q2">
-        <v>0.11028843481577</v>
+        <v>0.110279107650672</v>
       </c>
       <c r="R2">
-        <v>0.110966460332664</v>
+        <v>0.110366239521913</v>
       </c>
       <c r="S2">
         <v>0.0558321092239028</v>
       </c>
       <c r="T2">
-        <v>0.0562941092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.132811986222133</v>
+        <v>0.132798801270446</v>
       </c>
       <c r="X2">
-        <v>0.129190577368918</v>
+        <v>0.129990663680673</v>
       </c>
       <c r="Y2">
         <v>1.13388602676261</v>
       </c>
       <c r="Z2">
-        <v>1.08669408144404</v>
+        <v>1.09728658024412</v>
       </c>
       <c r="AA2">
         <v>2760.5</v>
@@ -1224,7 +1224,7 @@
         <v>6674.2</v>
       </c>
       <c r="AK2">
-        <v>0.07673785915729414</v>
+        <v>0.07672623104708272</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1141529322696049</v>
+        <v>0.1141425747298138</v>
       </c>
       <c r="C2">
-        <v>8948.320007335995</v>
+        <v>8948.375995968287</v>
       </c>
       <c r="D2">
-        <v>8116.420007335995</v>
+        <v>8116.475995968286</v>
       </c>
       <c r="E2">
         <v>-2760.5</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1141529322696049</v>
+        <v>0.1141425747298138</v>
       </c>
       <c r="T2">
         <v>0.8907328536426571</v>
       </c>
       <c r="U2">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V2">
         <v>0.34</v>
       </c>
       <c r="W2">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1139673933921273</v>
+        <v>0.1139478310679715</v>
       </c>
       <c r="C3">
-        <v>8876.06438244015</v>
+        <v>8877.223164174959</v>
       </c>
       <c r="D3">
-        <v>8138.511382440151</v>
+        <v>8139.670164174959</v>
       </c>
       <c r="E3">
         <v>-2666.153</v>
@@ -1527,37 +1527,37 @@
         <v>508.5</v>
       </c>
       <c r="M3">
-        <v>7.216989313556907</v>
+        <v>7.084903513556907</v>
       </c>
       <c r="N3">
-        <v>501.2830106864431</v>
+        <v>501.4150964864431</v>
       </c>
       <c r="O3">
-        <v>170.4362236333907</v>
+        <v>170.4811328053907</v>
       </c>
       <c r="P3">
-        <v>330.8467870530524</v>
+        <v>330.9339636810524</v>
       </c>
       <c r="Q3">
-        <v>373.8467870530524</v>
+        <v>373.9339636810524</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1146086184847356</v>
+        <v>0.1145981918946792</v>
       </c>
       <c r="T3">
         <v>0.8966710726669415</v>
       </c>
       <c r="U3">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V3">
         <v>0.34</v>
       </c>
       <c r="W3">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>70.45874365433761</v>
+        <v>71.77232534317359</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1137818545146497</v>
+        <v>0.1137530874061291</v>
       </c>
       <c r="C4">
-        <v>8803.92934292604</v>
+        <v>8806.203274604633</v>
       </c>
       <c r="D4">
-        <v>8160.72334292604</v>
+        <v>8162.997274604632</v>
       </c>
       <c r="E4">
         <v>-2571.806</v>
@@ -1609,37 +1609,37 @@
         <v>508.5</v>
       </c>
       <c r="M4">
-        <v>14.43397862711381</v>
+        <v>14.16980702711381</v>
       </c>
       <c r="N4">
-        <v>494.0660213728862</v>
+        <v>494.3301929728862</v>
       </c>
       <c r="O4">
-        <v>167.9824472667813</v>
+        <v>168.0722656107813</v>
       </c>
       <c r="P4">
-        <v>326.0835741061049</v>
+        <v>326.2579273621049</v>
       </c>
       <c r="Q4">
-        <v>369.0835741061049</v>
+        <v>369.2579273621049</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1150736044185424</v>
+        <v>0.1150631073690317</v>
       </c>
       <c r="T4">
         <v>0.9027304798345785</v>
       </c>
       <c r="U4">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V4">
         <v>0.34</v>
       </c>
       <c r="W4">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.2293718271688</v>
+        <v>35.8861626715868</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.113596315637172</v>
+        <v>0.1135583437442868</v>
       </c>
       <c r="C5">
-        <v>8731.91587881544</v>
+        <v>8735.317473521547</v>
       </c>
       <c r="D5">
-        <v>8183.05687881544</v>
+        <v>8186.458473521546</v>
       </c>
       <c r="E5">
         <v>-2477.459</v>
@@ -1691,37 +1691,37 @@
         <v>508.5</v>
       </c>
       <c r="M5">
-        <v>21.65096794067072</v>
+        <v>21.25471054067072</v>
       </c>
       <c r="N5">
-        <v>486.8490320593293</v>
+        <v>487.2452894593293</v>
       </c>
       <c r="O5">
-        <v>165.528670900172</v>
+        <v>165.663398416172</v>
       </c>
       <c r="P5">
-        <v>321.3203611591573</v>
+        <v>321.5818910431573</v>
       </c>
       <c r="Q5">
-        <v>364.3203611591573</v>
+        <v>364.5818910431573</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1155481776911907</v>
+        <v>0.1155376087294533</v>
       </c>
       <c r="T5">
         <v>0.9089148232324764</v>
       </c>
       <c r="U5">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V5">
         <v>0.34</v>
       </c>
       <c r="W5">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.4862478847792</v>
+        <v>23.92410844772453</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1134107767596944</v>
+        <v>0.1133636000824445</v>
       </c>
       <c r="C6">
-        <v>8660.024990997486</v>
+        <v>8664.566920405794</v>
       </c>
       <c r="D6">
-        <v>8205.512990997488</v>
+        <v>8210.054920405795</v>
       </c>
       <c r="E6">
         <v>-2383.112</v>
@@ -1773,37 +1773,37 @@
         <v>508.5</v>
       </c>
       <c r="M6">
-        <v>28.86795725422763</v>
+        <v>28.33961405422763</v>
       </c>
       <c r="N6">
-        <v>479.6320427457724</v>
+        <v>480.1603859457724</v>
       </c>
       <c r="O6">
-        <v>163.0748945335626</v>
+        <v>163.2545312215626</v>
       </c>
       <c r="P6">
-        <v>316.5571482122098</v>
+        <v>316.9058547242097</v>
       </c>
       <c r="Q6">
-        <v>359.5571482122098</v>
+        <v>359.9058547242097</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1160326379070191</v>
+        <v>0.1160219955348837</v>
       </c>
       <c r="T6">
         <v>0.9152280071178303</v>
       </c>
       <c r="U6">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V6">
         <v>0.34</v>
       </c>
       <c r="W6">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.6146859135844</v>
+        <v>17.9430813357934</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1132252378822168</v>
+        <v>0.1131688564206021</v>
       </c>
       <c r="C7">
-        <v>8588.257691378185</v>
+        <v>8593.95278814433</v>
       </c>
       <c r="D7">
-        <v>8228.092691378186</v>
+        <v>8233.787788144331</v>
       </c>
       <c r="E7">
         <v>-2288.765</v>
@@ -1855,37 +1855,37 @@
         <v>508.5</v>
       </c>
       <c r="M7">
-        <v>36.08494656778453</v>
+        <v>35.42451756778453</v>
       </c>
       <c r="N7">
-        <v>472.4150534322155</v>
+        <v>473.0754824322155</v>
       </c>
       <c r="O7">
-        <v>160.6211181669533</v>
+        <v>160.8456640269533</v>
       </c>
       <c r="P7">
-        <v>311.7939352652622</v>
+        <v>312.2298184052622</v>
       </c>
       <c r="Q7">
-        <v>354.7939352652622</v>
+        <v>355.2298184052622</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1165272972852859</v>
+        <v>0.1165165799572705</v>
       </c>
       <c r="T7">
         <v>0.9216741001376125</v>
       </c>
       <c r="U7">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V7">
         <v>0.34</v>
       </c>
       <c r="W7">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>14.09174873086752</v>
+        <v>14.35446506863472</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1130396990047392</v>
+        <v>0.1129741127587598</v>
       </c>
       <c r="C8">
-        <v>8516.615003032413</v>
+        <v>8523.476263225326</v>
       </c>
       <c r="D8">
-        <v>8250.797003032414</v>
+        <v>8257.658263225327</v>
       </c>
       <c r="E8">
         <v>-2194.418</v>
@@ -1937,37 +1937,37 @@
         <v>508.5</v>
       </c>
       <c r="M8">
-        <v>43.30193588134144</v>
+        <v>42.50942108134144</v>
       </c>
       <c r="N8">
-        <v>465.1980641186586</v>
+        <v>465.9905789186586</v>
       </c>
       <c r="O8">
-        <v>158.1673418003439</v>
+        <v>158.4367968323439</v>
       </c>
       <c r="P8">
-        <v>307.0307223183146</v>
+        <v>307.5537820863146</v>
       </c>
       <c r="Q8">
-        <v>350.0307223183146</v>
+        <v>350.5537820863146</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1170324813311755</v>
+        <v>0.1170216874524741</v>
       </c>
       <c r="T8">
         <v>0.9282573440727095</v>
       </c>
       <c r="U8">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V8">
         <v>0.34</v>
       </c>
       <c r="W8">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.7431239423896</v>
+        <v>11.96205422386227</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1128541601272615</v>
+        <v>0.1127793690969174</v>
       </c>
       <c r="C9">
-        <v>8445.097960358449</v>
+        <v>8453.138545935892</v>
       </c>
       <c r="D9">
-        <v>8273.62696035845</v>
+        <v>8281.667545935892</v>
       </c>
       <c r="E9">
         <v>-2100.071</v>
@@ -2019,37 +2019,37 @@
         <v>508.5</v>
       </c>
       <c r="M9">
-        <v>50.51892519489835</v>
+        <v>49.59432459489835</v>
       </c>
       <c r="N9">
-        <v>457.9810748051016</v>
+        <v>458.9056754051016</v>
       </c>
       <c r="O9">
-        <v>155.7135654337346</v>
+        <v>156.0279296377346</v>
       </c>
       <c r="P9">
-        <v>302.2675093713671</v>
+        <v>302.8777457673671</v>
       </c>
       <c r="Q9">
-        <v>345.2675093713671</v>
+        <v>345.8777457673671</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.117548529550095</v>
+        <v>0.1175376574744562</v>
       </c>
       <c r="T9">
         <v>0.9349821631461956</v>
       </c>
       <c r="U9">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V9">
         <v>0.34</v>
       </c>
       <c r="W9">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.06553480776251</v>
+        <v>10.25318933473908</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1126686212497839</v>
+        <v>0.1125846254350751</v>
       </c>
       <c r="C10">
-        <v>8373.707609235049</v>
+        <v>8382.940850563262</v>
       </c>
       <c r="D10">
-        <v>8296.583609235049</v>
+        <v>8305.816850563262</v>
       </c>
       <c r="E10">
         <v>-2005.724</v>
@@ -2101,37 +2101,37 @@
         <v>508.5</v>
       </c>
       <c r="M10">
-        <v>57.73591450845525</v>
+        <v>56.67922810845526</v>
       </c>
       <c r="N10">
-        <v>450.7640854915447</v>
+        <v>451.8207718915447</v>
       </c>
       <c r="O10">
-        <v>153.2597890671252</v>
+        <v>153.6190624431252</v>
       </c>
       <c r="P10">
-        <v>297.5042964244195</v>
+        <v>298.2017094484195</v>
       </c>
       <c r="Q10">
-        <v>340.5042964244195</v>
+        <v>341.2017094484195</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1180757962085562</v>
+        <v>0.1180648442360466</v>
       </c>
       <c r="T10">
         <v>0.9418531739386704</v>
       </c>
       <c r="U10">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V10">
         <v>0.34</v>
       </c>
       <c r="W10">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.807342956792201</v>
+        <v>8.971540667896697</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1125484223723063</v>
+        <v>0.1124789817732328</v>
       </c>
       <c r="C11">
-        <v>8294.300887990506</v>
+        <v>8301.753273268147</v>
       </c>
       <c r="D11">
-        <v>8311.523887990506</v>
+        <v>8318.976273268147</v>
       </c>
       <c r="E11">
         <v>-1911.377</v>
@@ -2183,37 +2183,37 @@
         <v>508.5</v>
       </c>
       <c r="M11">
-        <v>65.88693912201217</v>
+        <v>65.03781612201216</v>
       </c>
       <c r="N11">
-        <v>442.6130608779878</v>
+        <v>443.4621838779879</v>
       </c>
       <c r="O11">
-        <v>150.4884406985159</v>
+        <v>150.7771425185159</v>
       </c>
       <c r="P11">
-        <v>292.1246201794719</v>
+        <v>292.6850413594719</v>
       </c>
       <c r="Q11">
-        <v>335.1246201794719</v>
+        <v>335.6850413594719</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1186146511452253</v>
+        <v>0.1186036175198698</v>
       </c>
       <c r="T11">
         <v>0.9488751959573536</v>
       </c>
       <c r="U11">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V11">
         <v>0.34</v>
       </c>
       <c r="W11">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.717766324799801</v>
+        <v>7.818528208973753</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1123701434948286</v>
+        <v>0.1122941381113904</v>
       </c>
       <c r="C12">
-        <v>8222.212652522008</v>
+        <v>8230.531770955693</v>
       </c>
       <c r="D12">
-        <v>8333.782652522008</v>
+        <v>8342.101770955693</v>
       </c>
       <c r="E12">
         <v>-1817.03</v>
@@ -2265,37 +2265,37 @@
         <v>508.5</v>
       </c>
       <c r="M12">
-        <v>73.20771013556907</v>
+        <v>72.26424013556908</v>
       </c>
       <c r="N12">
-        <v>435.2922898644309</v>
+        <v>436.2357598644309</v>
       </c>
       <c r="O12">
-        <v>147.9993785539065</v>
+        <v>148.3201583539065</v>
       </c>
       <c r="P12">
-        <v>287.2929113105244</v>
+        <v>287.9156015105244</v>
       </c>
       <c r="Q12">
-        <v>330.2929113105244</v>
+        <v>330.9156015105244</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1191654806360426</v>
+        <v>0.1191543635433335</v>
       </c>
       <c r="T12">
         <v>0.9560532629097852</v>
       </c>
       <c r="U12">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V12">
         <v>0.34</v>
       </c>
       <c r="W12">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.94598969231982</v>
+        <v>7.036675388076376</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.112351584617351</v>
+        <v>0.1122327144495481</v>
       </c>
       <c r="C13">
-        <v>8130.189649043842</v>
+        <v>8143.897874996063</v>
       </c>
       <c r="D13">
-        <v>8336.106649043842</v>
+        <v>8349.814874996064</v>
       </c>
       <c r="E13">
         <v>-1722.683</v>
@@ -2347,37 +2347,37 @@
         <v>508.5</v>
       </c>
       <c r="M13">
-        <v>82.81167854912597</v>
+        <v>81.25495304912596</v>
       </c>
       <c r="N13">
-        <v>425.688321450874</v>
+        <v>427.245046950874</v>
       </c>
       <c r="O13">
-        <v>144.7340292932972</v>
+        <v>145.2633159632972</v>
       </c>
       <c r="P13">
-        <v>280.9542921575768</v>
+        <v>281.9817309875768</v>
       </c>
       <c r="Q13">
-        <v>323.9542921575768</v>
+        <v>324.9817309875768</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1197286883176648</v>
+        <v>0.1197174858819312</v>
       </c>
       <c r="T13">
         <v>0.9633926347375524</v>
       </c>
       <c r="U13">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V13">
         <v>0.34</v>
       </c>
       <c r="W13">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.140438267995558</v>
+        <v>6.258080042118365</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1121878257398734</v>
+        <v>0.1120590907877058</v>
       </c>
       <c r="C14">
-        <v>8056.405326796389</v>
+        <v>8071.430520748331</v>
       </c>
       <c r="D14">
-        <v>8356.669326796389</v>
+        <v>8371.694520748331</v>
       </c>
       <c r="E14">
         <v>-1628.336</v>
@@ -2429,37 +2429,37 @@
         <v>508.5</v>
       </c>
       <c r="M14">
-        <v>90.34001296268288</v>
+        <v>88.64176696268287</v>
       </c>
       <c r="N14">
-        <v>418.1599870373171</v>
+        <v>419.8582330373171</v>
       </c>
       <c r="O14">
-        <v>142.1743955926878</v>
+        <v>142.7517992326878</v>
       </c>
       <c r="P14">
-        <v>275.9855914446293</v>
+        <v>277.1064338046293</v>
       </c>
       <c r="Q14">
-        <v>318.9855914446293</v>
+        <v>320.1064338046293</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1203046961738694</v>
+        <v>0.1202934064554971</v>
       </c>
       <c r="T14">
         <v>0.9708988104704963</v>
       </c>
       <c r="U14">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V14">
         <v>0.34</v>
       </c>
       <c r="W14">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.628735078995929</v>
+        <v>5.736573371941835</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1121527668623957</v>
+        <v>0.1119541071258634</v>
       </c>
       <c r="C15">
-        <v>7966.473748487193</v>
+        <v>7990.369032182132</v>
       </c>
       <c r="D15">
-        <v>8361.084748487194</v>
+        <v>8384.980032182133</v>
       </c>
       <c r="E15">
         <v>-1533.989</v>
@@ -2511,37 +2511,37 @@
         <v>508.5</v>
       </c>
       <c r="M15">
-        <v>99.70811387623979</v>
+        <v>97.00978967623981</v>
       </c>
       <c r="N15">
-        <v>408.7918861237602</v>
+        <v>411.4902103237602</v>
       </c>
       <c r="O15">
-        <v>138.9892412820785</v>
+        <v>139.9066715100785</v>
       </c>
       <c r="P15">
-        <v>269.8026448416817</v>
+        <v>271.5835388136817</v>
       </c>
       <c r="Q15">
-        <v>312.8026448416817</v>
+        <v>314.5835388136817</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1208939455899866</v>
+        <v>0.1208825665824782</v>
       </c>
       <c r="T15">
         <v>0.9785775419674158</v>
       </c>
       <c r="U15">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V15">
         <v>0.34</v>
       </c>
       <c r="W15">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.099885859150469</v>
+        <v>5.241739021361313</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1119989079849181</v>
+        <v>0.1117857634640211</v>
       </c>
       <c r="C16">
-        <v>7891.559502788677</v>
+        <v>7917.41389262279</v>
       </c>
       <c r="D16">
-        <v>8380.517502788678</v>
+        <v>8406.37189262279</v>
       </c>
       <c r="E16">
         <v>-1439.642</v>
@@ -2593,37 +2593,37 @@
         <v>508.5</v>
       </c>
       <c r="M16">
-        <v>107.3779687897967</v>
+        <v>104.4720811897967</v>
       </c>
       <c r="N16">
-        <v>401.1220312102033</v>
+        <v>404.0279188102033</v>
       </c>
       <c r="O16">
-        <v>136.3814906114691</v>
+        <v>137.3694923954691</v>
       </c>
       <c r="P16">
-        <v>264.7405405987342</v>
+        <v>266.6584264147342</v>
       </c>
       <c r="Q16">
-        <v>307.7405405987342</v>
+        <v>309.6584264147342</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1214968984808973</v>
+        <v>0.1214854281077613</v>
       </c>
       <c r="T16">
         <v>0.9864348486154262</v>
       </c>
       <c r="U16">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V16">
         <v>0.34</v>
       </c>
       <c r="W16">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.735608297782579</v>
+        <v>4.867329091264076</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1118450491074405</v>
+        <v>0.1116174198021787</v>
       </c>
       <c r="C17">
-        <v>7816.735798373833</v>
+        <v>7844.568182577123</v>
       </c>
       <c r="D17">
-        <v>8400.040798373833</v>
+        <v>8427.873182577123</v>
       </c>
       <c r="E17">
         <v>-1345.295</v>
@@ -2675,37 +2675,37 @@
         <v>508.5</v>
       </c>
       <c r="M17">
-        <v>115.0478237033536</v>
+        <v>111.9343727033536</v>
       </c>
       <c r="N17">
-        <v>393.4521762966464</v>
+        <v>396.5656272966464</v>
       </c>
       <c r="O17">
-        <v>133.7737399408598</v>
+        <v>134.8323132808598</v>
       </c>
       <c r="P17">
-        <v>259.6784363557866</v>
+        <v>261.7333140157866</v>
       </c>
       <c r="Q17">
-        <v>302.6784363557866</v>
+        <v>304.7333140157866</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.122114038498653</v>
+        <v>0.1221024746101098</v>
       </c>
       <c r="T17">
         <v>0.9944770330669195</v>
       </c>
       <c r="U17">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V17">
         <v>0.34</v>
       </c>
       <c r="W17">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.419901077930406</v>
+        <v>4.542840485179804</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1118390302299629</v>
+        <v>0.1114490761403364</v>
       </c>
       <c r="C18">
-        <v>7723.154388301433</v>
+        <v>7771.832743874116</v>
       </c>
       <c r="D18">
-        <v>8400.806388301433</v>
+        <v>8449.484743874116</v>
       </c>
       <c r="E18">
         <v>-1250.948</v>
@@ -2757,45 +2757,45 @@
         <v>508.5</v>
       </c>
       <c r="M18">
-        <v>124.8310514169105</v>
+        <v>119.3966642169105</v>
       </c>
       <c r="N18">
-        <v>383.6689485830895</v>
+        <v>389.1033357830895</v>
       </c>
       <c r="O18">
-        <v>130.4474425182504</v>
+        <v>132.2951341662504</v>
       </c>
       <c r="P18">
-        <v>253.2215060648391</v>
+        <v>256.808201616839</v>
       </c>
       <c r="Q18">
-        <v>296.2215060648391</v>
+        <v>299.808201616839</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1227458723263553</v>
+        <v>0.1227342126958476</v>
       </c>
       <c r="T18">
         <v>1.002710698100591</v>
       </c>
       <c r="U18">
-        <v>0.08269410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V18">
         <v>0.34</v>
       </c>
       <c r="W18">
-        <v>0.0545781092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.073505704135365</v>
+        <v>4.258912954856067</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1116944113524852</v>
+        <v>0.111392932478494</v>
       </c>
       <c r="C19">
-        <v>7647.244690719756</v>
+        <v>7684.718001928101</v>
       </c>
       <c r="D19">
-        <v>8419.243690719757</v>
+        <v>8456.717001928102</v>
       </c>
       <c r="E19">
         <v>-1156.601</v>
@@ -2839,37 +2839,37 @@
         <v>508.5</v>
       </c>
       <c r="M19">
-        <v>132.6329921304674</v>
+        <v>128.4628547304675</v>
       </c>
       <c r="N19">
-        <v>375.8670078695326</v>
+        <v>380.0371452695325</v>
       </c>
       <c r="O19">
-        <v>127.7947826756411</v>
+        <v>129.2126293916411</v>
       </c>
       <c r="P19">
-        <v>248.0722251938915</v>
+        <v>250.8245158778915</v>
       </c>
       <c r="Q19">
-        <v>291.0722251938915</v>
+        <v>293.8245158778915</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1233929310655684</v>
+        <v>0.1233811733860609</v>
       </c>
       <c r="T19">
         <v>1.011142764701339</v>
       </c>
       <c r="U19">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V19">
         <v>0.34</v>
       </c>
       <c r="W19">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.833887721539166</v>
+        <v>3.958342674751407</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1115497924750076</v>
+        <v>0.1112311888166517</v>
       </c>
       <c r="C20">
-        <v>7571.416100070252</v>
+        <v>7611.275717244965</v>
       </c>
       <c r="D20">
-        <v>8437.762100070253</v>
+        <v>8477.621717244965</v>
       </c>
       <c r="E20">
         <v>-1062.254</v>
@@ -2921,37 +2921,37 @@
         <v>508.5</v>
       </c>
       <c r="M20">
-        <v>140.4349328440243</v>
+        <v>136.0194932440243</v>
       </c>
       <c r="N20">
-        <v>368.0650671559757</v>
+        <v>372.4805067559757</v>
       </c>
       <c r="O20">
-        <v>125.1421228330317</v>
+        <v>126.6433722970317</v>
       </c>
       <c r="P20">
-        <v>242.922944322944</v>
+        <v>245.8371344589439</v>
       </c>
       <c r="Q20">
-        <v>285.922944322944</v>
+        <v>288.8371344589439</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1240557717252501</v>
+        <v>0.1240439136053039</v>
       </c>
       <c r="T20">
         <v>1.019780491463081</v>
       </c>
       <c r="U20">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.620893959231436</v>
+        <v>3.73843474837633</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.11140517359753</v>
+        <v>0.1110694451548094</v>
       </c>
       <c r="C21">
-        <v>7495.669152724963</v>
+        <v>7537.937040159449</v>
       </c>
       <c r="D21">
-        <v>8456.362152724963</v>
+        <v>8498.630040159449</v>
       </c>
       <c r="E21">
         <v>-967.9069999999999</v>
@@ -3003,37 +3003,37 @@
         <v>508.5</v>
       </c>
       <c r="M21">
-        <v>148.2368735575812</v>
+        <v>143.5761317575812</v>
       </c>
       <c r="N21">
-        <v>360.2631264424188</v>
+        <v>364.9238682424187</v>
       </c>
       <c r="O21">
-        <v>122.4894629904224</v>
+        <v>124.0741152024224</v>
       </c>
       <c r="P21">
-        <v>237.7736634519964</v>
+        <v>240.8497530399964</v>
       </c>
       <c r="Q21">
-        <v>280.7736634519964</v>
+        <v>283.8497530399964</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1247349788209734</v>
+        <v>0.1247230177805776</v>
       </c>
       <c r="T21">
         <v>1.028631495428816</v>
       </c>
       <c r="U21">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V21">
         <v>0.34</v>
       </c>
       <c r="W21">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.430320592956097</v>
+        <v>3.541675024777576</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1112605547200523</v>
+        <v>0.110907701492967</v>
       </c>
       <c r="C22">
-        <v>7420.004389795842</v>
+        <v>7464.702742832374</v>
       </c>
       <c r="D22">
-        <v>8475.044389795843</v>
+        <v>8519.742742832375</v>
       </c>
       <c r="E22">
         <v>-873.5599999999997</v>
@@ -3085,37 +3085,37 @@
         <v>508.5</v>
       </c>
       <c r="M22">
-        <v>156.0388142711381</v>
+        <v>151.1327702711382</v>
       </c>
       <c r="N22">
-        <v>352.4611857288619</v>
+        <v>357.3672297288618</v>
       </c>
       <c r="O22">
-        <v>119.8368031478131</v>
+        <v>121.504858107813</v>
       </c>
       <c r="P22">
-        <v>232.6243825810488</v>
+        <v>235.8623716210488</v>
       </c>
       <c r="Q22">
-        <v>275.6243825810488</v>
+        <v>278.8623716210488</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1254311660940897</v>
+        <v>0.1254190995602331</v>
       </c>
       <c r="T22">
         <v>1.037703774493695</v>
       </c>
       <c r="U22">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V22">
         <v>0.34</v>
       </c>
       <c r="W22">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.258804563308292</v>
+        <v>3.364591273538696</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1111159358425747</v>
+        <v>0.1107459578311247</v>
       </c>
       <c r="C23">
-        <v>7344.422357187254</v>
+        <v>7391.573605116639</v>
       </c>
       <c r="D23">
-        <v>8493.809357187254</v>
+        <v>8540.960605116639</v>
       </c>
       <c r="E23">
         <v>-779.213</v>
@@ -3167,37 +3167,37 @@
         <v>508.5</v>
       </c>
       <c r="M23">
-        <v>163.840754984695</v>
+        <v>158.689408784695</v>
       </c>
       <c r="N23">
-        <v>344.659245015305</v>
+        <v>349.810591215305</v>
       </c>
       <c r="O23">
-        <v>117.1841433052037</v>
+        <v>118.9356010132037</v>
       </c>
       <c r="P23">
-        <v>227.4751017101013</v>
+        <v>230.8749902021013</v>
       </c>
       <c r="Q23">
-        <v>270.4751017101013</v>
+        <v>273.8749902021012</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1261449783614622</v>
+        <v>0.1261328036634242</v>
       </c>
       <c r="T23">
         <v>1.047005731509584</v>
       </c>
       <c r="U23">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V23">
         <v>0.34</v>
       </c>
       <c r="W23">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.103623393626945</v>
+        <v>3.204372641465426</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1113488369650971</v>
+        <v>0.1105842141692824</v>
       </c>
       <c r="C24">
-        <v>7219.896061483909</v>
+        <v>7318.550414653217</v>
       </c>
       <c r="D24">
-        <v>8463.630061483909</v>
+        <v>8562.284414653217</v>
       </c>
       <c r="E24">
         <v>-684.866</v>
@@ -3249,45 +3249,45 @@
         <v>508.5</v>
       </c>
       <c r="M24">
-        <v>177.0393440982519</v>
+        <v>166.2460472982519</v>
       </c>
       <c r="N24">
-        <v>331.4606559017481</v>
+        <v>342.2539527017481</v>
       </c>
       <c r="O24">
-        <v>112.6966230065944</v>
+        <v>116.3663439185944</v>
       </c>
       <c r="P24">
-        <v>218.7640328951537</v>
+        <v>225.8876087831537</v>
       </c>
       <c r="Q24">
-        <v>261.7640328951537</v>
+        <v>268.8876087831537</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1268770935074852</v>
+        <v>0.1268648078718253</v>
       </c>
       <c r="T24">
         <v>1.056546200243829</v>
       </c>
       <c r="U24">
-        <v>0.08529410488470121</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.05629410922390279</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.872242905044862</v>
+        <v>3.058719339580634</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1112213780876194</v>
+        <v>0.11080197050744</v>
       </c>
       <c r="C25">
-        <v>7142.038545786396</v>
+        <v>7195.519796512968</v>
       </c>
       <c r="D25">
-        <v>8480.119545786396</v>
+        <v>8533.600796512968</v>
       </c>
       <c r="E25">
         <v>-590.5189999999998</v>
@@ -3331,37 +3331,37 @@
         <v>508.5</v>
       </c>
       <c r="M25">
-        <v>185.0865870118088</v>
+        <v>179.2276383118089</v>
       </c>
       <c r="N25">
-        <v>323.4134129881912</v>
+        <v>329.2723616881912</v>
       </c>
       <c r="O25">
-        <v>109.960560415985</v>
+        <v>111.952602973985</v>
       </c>
       <c r="P25">
-        <v>213.4528525722062</v>
+        <v>217.3197587142062</v>
       </c>
       <c r="Q25">
-        <v>256.4528525722062</v>
+        <v>260.3197587142062</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.127628224631327</v>
+        <v>0.1276158251765485</v>
       </c>
       <c r="T25">
         <v>1.066334473360781</v>
       </c>
       <c r="U25">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V25">
         <v>0.34</v>
       </c>
       <c r="W25">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.747362778738563</v>
+        <v>2.837174025109587</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1110939192101418</v>
+        <v>0.1106567268455977</v>
       </c>
       <c r="C26">
-        <v>7064.245407635357</v>
+        <v>7120.283403672298</v>
       </c>
       <c r="D26">
-        <v>8496.673407635357</v>
+        <v>8552.711403672298</v>
       </c>
       <c r="E26">
         <v>-496.172</v>
@@ -3413,37 +3413,37 @@
         <v>508.5</v>
       </c>
       <c r="M26">
-        <v>193.1338299253657</v>
+        <v>187.0201443253658</v>
       </c>
       <c r="N26">
-        <v>315.3661700746343</v>
+        <v>321.4798556746342</v>
       </c>
       <c r="O26">
-        <v>107.2244978253757</v>
+        <v>109.3031509293756</v>
       </c>
       <c r="P26">
-        <v>208.1416722492586</v>
+        <v>212.1767047452586</v>
       </c>
       <c r="Q26">
-        <v>251.1416722492586</v>
+        <v>255.1767047452586</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.128399122363691</v>
+        <v>0.128386606094554</v>
       </c>
       <c r="T26">
         <v>1.07638033261239</v>
       </c>
       <c r="U26">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V26">
         <v>0.34</v>
       </c>
       <c r="W26">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.632889329624457</v>
+        <v>2.718958440730021</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1109664603326642</v>
+        <v>0.1105114831837553</v>
       </c>
       <c r="C27">
-        <v>6986.517024778329</v>
+        <v>7045.132797601683</v>
       </c>
       <c r="D27">
-        <v>8513.29202477833</v>
+        <v>8571.907797601683</v>
       </c>
       <c r="E27">
         <v>-401.8249999999998</v>
@@ -3495,37 +3495,37 @@
         <v>508.5</v>
       </c>
       <c r="M27">
-        <v>201.1810728389226</v>
+        <v>194.8126503389227</v>
       </c>
       <c r="N27">
-        <v>307.3189271610773</v>
+        <v>313.6873496610773</v>
       </c>
       <c r="O27">
-        <v>104.4884352347663</v>
+        <v>106.6536988847663</v>
       </c>
       <c r="P27">
-        <v>202.830491926311</v>
+        <v>207.033650776311</v>
       </c>
       <c r="Q27">
-        <v>245.830491926311</v>
+        <v>250.033650776311</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.129190577368918</v>
+        <v>0.1291779411703728</v>
       </c>
       <c r="T27">
         <v>1.086694081444042</v>
       </c>
       <c r="U27">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V27">
         <v>0.34</v>
       </c>
       <c r="W27">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.527573756439478</v>
+        <v>2.61020010310082</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1113023214551866</v>
+        <v>0.110366239521913</v>
       </c>
       <c r="C28">
-        <v>6848.518383855051</v>
+        <v>6970.068557240733</v>
       </c>
       <c r="D28">
-        <v>8469.640383855052</v>
+        <v>8591.190557240734</v>
       </c>
       <c r="E28">
         <v>-307.4779999999996</v>
@@ -3577,45 +3577,45 @@
         <v>508.5</v>
       </c>
       <c r="M28">
-        <v>215.8514751524796</v>
+        <v>202.6051563524796</v>
       </c>
       <c r="N28">
-        <v>292.6485248475204</v>
+        <v>305.8948436475204</v>
       </c>
       <c r="O28">
-        <v>99.50049844815696</v>
+        <v>104.0042468401569</v>
       </c>
       <c r="P28">
-        <v>193.1480263993635</v>
+        <v>201.8905968073634</v>
       </c>
       <c r="Q28">
-        <v>236.1480263993635</v>
+        <v>244.8905968073634</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.130003423049962</v>
+        <v>0.1299906636806734</v>
       </c>
       <c r="T28">
         <v>1.097286580244117</v>
       </c>
       <c r="U28">
-        <v>0.08799410488470122</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V28">
         <v>0.34</v>
       </c>
       <c r="W28">
-        <v>0.0580761092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.355786540911016</v>
+        <v>2.509807791443096</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1111926825777089</v>
+        <v>0.1108446958600707</v>
       </c>
       <c r="C29">
-        <v>6768.371777962171</v>
+        <v>6812.526403199659</v>
       </c>
       <c r="D29">
-        <v>8483.840777962172</v>
+        <v>8527.99540319966</v>
       </c>
       <c r="E29">
         <v>-213.1309999999999</v>
@@ -3659,37 +3659,37 @@
         <v>508.5</v>
       </c>
       <c r="M29">
-        <v>224.1534549660365</v>
+        <v>219.3134538660365</v>
       </c>
       <c r="N29">
-        <v>284.3465450339635</v>
+        <v>289.1865461339635</v>
       </c>
       <c r="O29">
-        <v>96.67782531154761</v>
+        <v>98.3234256855476</v>
       </c>
       <c r="P29">
-        <v>187.6687197224159</v>
+        <v>190.8631204484159</v>
       </c>
       <c r="Q29">
-        <v>230.6687197224159</v>
+        <v>233.8631204484159</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.130838538475692</v>
+        <v>0.1308256525611191</v>
       </c>
       <c r="T29">
         <v>1.108169284490769</v>
       </c>
       <c r="U29">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V29">
         <v>0.34</v>
       </c>
       <c r="W29">
-        <v>0.0580761092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.268535187543942</v>
+        <v>2.318599206004971</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1119516037002313</v>
+        <v>0.1112399921982283</v>
       </c>
       <c r="C30">
-        <v>6576.694318738704</v>
+        <v>6666.665256552169</v>
       </c>
       <c r="D30">
-        <v>8386.510318738705</v>
+        <v>8476.48125655217</v>
       </c>
       <c r="E30">
         <v>-118.7839999999997</v>
@@ -3741,37 +3741,37 @@
         <v>508.5</v>
       </c>
       <c r="M30">
-        <v>244.8714999795934</v>
+        <v>234.8329791795934</v>
       </c>
       <c r="N30">
-        <v>263.6285000204066</v>
+        <v>273.6670208204066</v>
       </c>
       <c r="O30">
-        <v>89.63369000693825</v>
+        <v>93.04678707893825</v>
       </c>
       <c r="P30">
-        <v>173.9948100134683</v>
+        <v>180.6202337414684</v>
       </c>
       <c r="Q30">
-        <v>216.9948100134683</v>
+        <v>223.6202337414684</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1316968515521368</v>
+        <v>0.1316838355771327</v>
       </c>
       <c r="T30">
         <v>1.119354286077606</v>
       </c>
       <c r="U30">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V30">
         <v>0.34</v>
       </c>
       <c r="W30">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.076599359428828</v>
+        <v>2.165368773059401</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1118729848227537</v>
+        <v>0.111136328536386</v>
       </c>
       <c r="C31">
-        <v>6492.326253835745</v>
+        <v>6585.767177026832</v>
       </c>
       <c r="D31">
-        <v>8396.489253835745</v>
+        <v>8489.930177026832</v>
       </c>
       <c r="E31">
         <v>-24.4369999999999</v>
@@ -3823,37 +3823,37 @@
         <v>508.5</v>
       </c>
       <c r="M31">
-        <v>253.6169106931503</v>
+        <v>243.2198712931503</v>
       </c>
       <c r="N31">
-        <v>254.8830893068497</v>
+        <v>265.2801287068497</v>
       </c>
       <c r="O31">
-        <v>86.6602503643289</v>
+        <v>90.19524376032891</v>
       </c>
       <c r="P31">
-        <v>168.2228389425208</v>
+        <v>175.0848849465208</v>
       </c>
       <c r="Q31">
-        <v>211.2228389425208</v>
+        <v>218.0848849465208</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1325793424617209</v>
+        <v>0.1325661927626115</v>
       </c>
       <c r="T31">
         <v>1.130854358131677</v>
       </c>
       <c r="U31">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V31">
         <v>0.34</v>
       </c>
       <c r="W31">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.004992484965765</v>
+        <v>2.090700884333215</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1136357659452761</v>
+        <v>0.1110326648745437</v>
       </c>
       <c r="C32">
-        <v>6179.787971613561</v>
+        <v>6504.911841864207</v>
       </c>
       <c r="D32">
-        <v>8178.297971613561</v>
+        <v>8503.421841864207</v>
       </c>
       <c r="E32">
         <v>69.91000000000031</v>
@@ -3905,45 +3905,45 @@
         <v>508.5</v>
       </c>
       <c r="M32">
-        <v>288.6851344067072</v>
+        <v>251.6067634067072</v>
       </c>
       <c r="N32">
-        <v>219.8148655932928</v>
+        <v>256.8932365932927</v>
       </c>
       <c r="O32">
-        <v>74.73705430171955</v>
+        <v>87.34370044171953</v>
       </c>
       <c r="P32">
-        <v>145.0778112915732</v>
+        <v>169.5495361515732</v>
       </c>
       <c r="Q32">
-        <v>188.0778112915732</v>
+        <v>212.5495361515732</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1334870473972932</v>
+        <v>0.1334737601533897</v>
       </c>
       <c r="T32">
         <v>1.142683003673009</v>
       </c>
       <c r="U32">
-        <v>0.1019941048847012</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V32">
         <v>0.34</v>
       </c>
       <c r="W32">
-        <v>0.0673161092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.761434654559011</v>
+        <v>2.02101085485544</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1145801470677984</v>
+        <v>0.1125248812127013</v>
       </c>
       <c r="C33">
-        <v>5973.149408596961</v>
+        <v>6220.396725082892</v>
       </c>
       <c r="D33">
-        <v>8066.006408596961</v>
+        <v>8313.253725082892</v>
       </c>
       <c r="E33">
         <v>164.2570000000001</v>
@@ -3987,45 +3987,45 @@
         <v>508.5</v>
       </c>
       <c r="M33">
-        <v>312.0543301202641</v>
+        <v>282.8067601202641</v>
       </c>
       <c r="N33">
-        <v>196.4456698797359</v>
+        <v>225.6932398797359</v>
       </c>
       <c r="O33">
-        <v>66.79152775911022</v>
+        <v>76.7357015591102</v>
       </c>
       <c r="P33">
-        <v>129.6541421206257</v>
+        <v>148.9575383206257</v>
       </c>
       <c r="Q33">
-        <v>172.6541421206257</v>
+        <v>191.9575383206257</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.134421062620853</v>
+        <v>0.1344076338453499</v>
       </c>
       <c r="T33">
         <v>1.154854508505393</v>
       </c>
       <c r="U33">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V33">
         <v>0.34</v>
       </c>
       <c r="W33">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.629523935155865</v>
+        <v>1.798047542370484</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1145939281903208</v>
+        <v>0.113296377550859</v>
       </c>
       <c r="C34">
-        <v>5877.186588342075</v>
+        <v>6031.027665532446</v>
       </c>
       <c r="D34">
-        <v>8064.390588342075</v>
+        <v>8218.231665532447</v>
       </c>
       <c r="E34">
         <v>258.6040000000003</v>
@@ -4069,37 +4069,37 @@
         <v>508.5</v>
       </c>
       <c r="M34">
-        <v>322.120598833821</v>
+        <v>303.704064433821</v>
       </c>
       <c r="N34">
-        <v>186.379401166179</v>
+        <v>204.795935566179</v>
       </c>
       <c r="O34">
-        <v>63.36899639650085</v>
+        <v>69.63061809250085</v>
       </c>
       <c r="P34">
-        <v>123.0104047696781</v>
+        <v>135.1653174736781</v>
       </c>
       <c r="Q34">
-        <v>166.0104047696781</v>
+        <v>178.1653174736781</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1353825488803999</v>
+        <v>0.1353689744106031</v>
       </c>
       <c r="T34">
         <v>1.167383998774024</v>
       </c>
       <c r="U34">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V34">
         <v>0.34</v>
       </c>
       <c r="W34">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.578601312182244</v>
+        <v>1.67432727957714</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1146077093128432</v>
+        <v>0.1132699338890166</v>
       </c>
       <c r="C35">
-        <v>5781.224415334918</v>
+        <v>5939.901657855675</v>
       </c>
       <c r="D35">
-        <v>8062.775415334919</v>
+        <v>8221.452657855676</v>
       </c>
       <c r="E35">
         <v>352.9510000000005</v>
@@ -4151,37 +4151,37 @@
         <v>508.5</v>
       </c>
       <c r="M35">
-        <v>332.1868675473779</v>
+        <v>313.1948164473779</v>
       </c>
       <c r="N35">
-        <v>176.3131324526221</v>
+        <v>195.3051835526221</v>
       </c>
       <c r="O35">
-        <v>59.94646503389151</v>
+        <v>66.40376240789151</v>
       </c>
       <c r="P35">
-        <v>116.3666674187306</v>
+        <v>128.9014211447305</v>
       </c>
       <c r="Q35">
-        <v>159.3666674187306</v>
+        <v>171.9014211447305</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1363727362223213</v>
+        <v>0.1363590117091474</v>
       </c>
       <c r="T35">
         <v>1.180287503677539</v>
       </c>
       <c r="U35">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V35">
         <v>0.34</v>
       </c>
       <c r="W35">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.530764908782782</v>
+        <v>1.623590089286924</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1182792104353655</v>
+        <v>0.1132434902271743</v>
       </c>
       <c r="C36">
-        <v>5278.45010479673</v>
+        <v>5848.778175992193</v>
       </c>
       <c r="D36">
-        <v>7654.34810479673</v>
+        <v>8224.676175992194</v>
       </c>
       <c r="E36">
         <v>447.2980000000007</v>
@@ -4233,45 +4233,45 @@
         <v>508.5</v>
       </c>
       <c r="M36">
-        <v>394.5402436609349</v>
+        <v>322.6855684609349</v>
       </c>
       <c r="N36">
-        <v>113.9597563390651</v>
+        <v>185.8144315390651</v>
       </c>
       <c r="O36">
-        <v>38.74631715528214</v>
+        <v>63.17690672328215</v>
       </c>
       <c r="P36">
-        <v>75.21343918378297</v>
+        <v>122.637524815783</v>
       </c>
       <c r="Q36">
-        <v>118.213439183783</v>
+        <v>165.637524815783</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1373929292412706</v>
+        <v>0.1373790501379505</v>
       </c>
       <c r="T36">
         <v>1.193582023881161</v>
       </c>
       <c r="U36">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V36">
         <v>0.34</v>
       </c>
       <c r="W36">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.288841906928514</v>
+        <v>1.575837439602014</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1184005715578879</v>
+        <v>0.1132170465653319</v>
       </c>
       <c r="C37">
-        <v>5171.307884893611</v>
+        <v>5757.657222914168</v>
       </c>
       <c r="D37">
-        <v>7641.552884893612</v>
+        <v>8227.902222914168</v>
       </c>
       <c r="E37">
         <v>541.6450000000004</v>
@@ -4315,45 +4315,45 @@
         <v>508.5</v>
       </c>
       <c r="M37">
-        <v>406.1443684744918</v>
+        <v>332.1763204744918</v>
       </c>
       <c r="N37">
-        <v>102.3556315255082</v>
+        <v>176.3236795255082</v>
       </c>
       <c r="O37">
-        <v>34.80091471867279</v>
+        <v>59.9500510386728</v>
       </c>
       <c r="P37">
-        <v>67.55471680683542</v>
+        <v>116.3736284868354</v>
       </c>
       <c r="Q37">
-        <v>110.5547168068354</v>
+        <v>159.3736284868354</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1384445128146491</v>
+        <v>0.138430474364563</v>
       </c>
       <c r="T37">
         <v>1.207285606244894</v>
       </c>
       <c r="U37">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V37">
         <v>0.34</v>
       </c>
       <c r="W37">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.252017852444842</v>
+        <v>1.530813512756242</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1273448898516882</v>
+        <v>0.1165645229034896</v>
       </c>
       <c r="C38">
-        <v>4238.790873434805</v>
+        <v>5274.093891427787</v>
       </c>
       <c r="D38">
-        <v>6803.382873434805</v>
+        <v>7838.685891427787</v>
       </c>
       <c r="E38">
         <v>635.9920000000002</v>
@@ -4397,45 +4397,45 @@
         <v>508.5</v>
       </c>
       <c r="M38">
-        <v>528.8137816880487</v>
+        <v>389.8972588880487</v>
       </c>
       <c r="N38">
-        <v>-20.31378168804872</v>
+        <v>118.6027411119513</v>
       </c>
       <c r="O38">
-        <v>-6.906685773936566</v>
+        <v>40.32493197806345</v>
       </c>
       <c r="P38">
-        <v>-13.40709591411215</v>
+        <v>78.27780913388787</v>
       </c>
       <c r="Q38">
-        <v>29.59290408588785</v>
+        <v>121.2778091338879</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1400311235710453</v>
+        <v>0.1395147555982572</v>
       </c>
       <c r="T38">
-        <v>1.22796132972506</v>
+        <v>1.221417425557493</v>
       </c>
       <c r="U38">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V38">
-        <v>0.3269392855990072</v>
+        <v>0.34</v>
       </c>
       <c r="W38">
-        <v>0.1047915854617201</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.961586134114727</v>
+        <v>1.304189727956015</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1284438309005352</v>
+        <v>0.1166317992416473</v>
       </c>
       <c r="C39">
-        <v>4053.977148584665</v>
+        <v>5172.301674895247</v>
       </c>
       <c r="D39">
-        <v>6712.916148584666</v>
+        <v>7831.240674895247</v>
       </c>
       <c r="E39">
         <v>730.3390000000004</v>
@@ -4479,45 +4479,45 @@
         <v>508.5</v>
       </c>
       <c r="M39">
-        <v>543.5030534016056</v>
+        <v>400.7277383016057</v>
       </c>
       <c r="N39">
-        <v>-35.0030534016056</v>
+        <v>107.7722616983943</v>
       </c>
       <c r="O39">
-        <v>-11.9010381565459</v>
+        <v>36.64256897745408</v>
       </c>
       <c r="P39">
-        <v>-23.10201524505969</v>
+        <v>71.12969272094026</v>
       </c>
       <c r="Q39">
-        <v>19.89798475494031</v>
+        <v>114.1296927209403</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1415268556912206</v>
+        <v>0.1406334584584178</v>
       </c>
       <c r="T39">
-        <v>1.247452779403236</v>
+        <v>1.23599787405462</v>
       </c>
       <c r="U39">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V39">
-        <v>0.318103088690926</v>
+        <v>0.34</v>
       </c>
       <c r="W39">
-        <v>0.1061673292299088</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.9355973196791939</v>
+        <v>1.268941356930176</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1295427719493823</v>
+        <v>0.1241696562399932</v>
       </c>
       <c r="C40">
-        <v>3871.537780235466</v>
+        <v>4324.719619911481</v>
       </c>
       <c r="D40">
-        <v>6624.823780235467</v>
+        <v>7078.005619911481</v>
       </c>
       <c r="E40">
         <v>824.6860000000001</v>
@@ -4561,37 +4561,37 @@
         <v>508.5</v>
       </c>
       <c r="M40">
-        <v>558.1923251151625</v>
+        <v>514.0945373151625</v>
       </c>
       <c r="N40">
-        <v>-49.69232511516248</v>
+        <v>-5.594537315162484</v>
       </c>
       <c r="O40">
-        <v>-16.89539053915524</v>
+        <v>-1.902142687155244</v>
       </c>
       <c r="P40">
-        <v>-32.79693457600723</v>
+        <v>-3.692394628007239</v>
       </c>
       <c r="Q40">
-        <v>10.20306542399277</v>
+        <v>39.30760537199276</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1430708372346274</v>
+        <v>0.1419432312517418</v>
       </c>
       <c r="T40">
-        <v>1.267572985522643</v>
+        <v>1.253068604304881</v>
       </c>
       <c r="U40">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V40">
-        <v>0.3097319547780069</v>
+        <v>0.3363000138124612</v>
       </c>
       <c r="W40">
-        <v>0.1074706654313507</v>
+        <v>0.09517066543135069</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9109763375823731</v>
+        <v>0.9891176876837094</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1306417129982293</v>
+        <v>0.1251455972888402</v>
       </c>
       <c r="C41">
-        <v>3691.380504414768</v>
+        <v>4143.31402479756</v>
       </c>
       <c r="D41">
-        <v>6539.013504414769</v>
+        <v>6990.947024797561</v>
       </c>
       <c r="E41">
         <v>919.0330000000004</v>
@@ -4643,37 +4643,37 @@
         <v>508.5</v>
       </c>
       <c r="M41">
-        <v>572.8815968287195</v>
+        <v>527.6233409287194</v>
       </c>
       <c r="N41">
-        <v>-64.38159682871947</v>
+        <v>-19.12334092871936</v>
       </c>
       <c r="O41">
-        <v>-21.88974292176462</v>
+        <v>-6.501935915764582</v>
       </c>
       <c r="P41">
-        <v>-42.49185390695484</v>
+        <v>-12.62140501295478</v>
       </c>
       <c r="Q41">
-        <v>0.5081460930451556</v>
+        <v>30.37859498704523</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1446654411237197</v>
+        <v>0.1435193497968523</v>
       </c>
       <c r="T41">
-        <v>1.288352870531211</v>
+        <v>1.273610712572174</v>
       </c>
       <c r="U41">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V41">
-        <v>0.301790109783699</v>
+        <v>0.3276769365352187</v>
       </c>
       <c r="W41">
-        <v>0.1087071638788725</v>
+        <v>0.09640716387887249</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8876179699520557</v>
+        <v>0.9637556956918195</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1317406540470763</v>
+        <v>0.1261215383376872</v>
       </c>
       <c r="C42">
-        <v>3513.417776344675</v>
+        <v>3964.02402802463</v>
       </c>
       <c r="D42">
-        <v>6455.397776344676</v>
+        <v>6906.004028024631</v>
       </c>
       <c r="E42">
         <v>1013.380000000001</v>
@@ -4725,37 +4725,37 @@
         <v>508.5</v>
       </c>
       <c r="M42">
-        <v>587.5708685422763</v>
+        <v>541.1521445422763</v>
       </c>
       <c r="N42">
-        <v>-79.07086854227634</v>
+        <v>-32.65214454227635</v>
       </c>
       <c r="O42">
-        <v>-26.88409530437396</v>
+        <v>-11.10172914437396</v>
       </c>
       <c r="P42">
-        <v>-52.18677323790239</v>
+        <v>-21.55041539790239</v>
       </c>
       <c r="Q42">
-        <v>-9.186773237902386</v>
+        <v>21.44958460209761</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1463131984757817</v>
+        <v>0.1451480056267999</v>
       </c>
       <c r="T42">
-        <v>1.309825418373398</v>
+        <v>1.294837557781711</v>
       </c>
       <c r="U42">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V42">
-        <v>0.2942453570391065</v>
+        <v>0.3194850131218381</v>
       </c>
       <c r="W42">
-        <v>0.1098818374040182</v>
+        <v>0.09758183740401823</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8654275207032543</v>
+        <v>0.9396618032995239</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1328395950959233</v>
+        <v>0.1270974793865342</v>
       </c>
       <c r="C43">
-        <v>3337.566472524757</v>
+        <v>3786.773439065775</v>
       </c>
       <c r="D43">
-        <v>6373.893472524758</v>
+        <v>6823.100439065776</v>
       </c>
       <c r="E43">
         <v>1107.727000000001</v>
@@ -4807,37 +4807,37 @@
         <v>508.5</v>
       </c>
       <c r="M43">
-        <v>602.2601402558333</v>
+        <v>554.6809481558332</v>
       </c>
       <c r="N43">
-        <v>-93.76014025583333</v>
+        <v>-46.18094815583322</v>
       </c>
       <c r="O43">
-        <v>-31.87844768698334</v>
+        <v>-15.7015223729833</v>
       </c>
       <c r="P43">
-        <v>-61.88169256885</v>
+        <v>-30.47942578284992</v>
       </c>
       <c r="Q43">
-        <v>-18.88169256885</v>
+        <v>12.52057421715008</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1480168120092695</v>
+        <v>0.146831870128949</v>
       </c>
       <c r="T43">
-        <v>1.332025849193286</v>
+        <v>1.316783957066147</v>
       </c>
       <c r="U43">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V43">
-        <v>0.2870686410137624</v>
+        <v>0.3116926957286226</v>
       </c>
       <c r="W43">
-        <v>0.1109992097815959</v>
+        <v>0.09869920978159585</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8443195323934187</v>
+        <v>0.9167432227312429</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1339385361447703</v>
+        <v>0.1280734204353812</v>
       </c>
       <c r="C44">
-        <v>3163.747615102141</v>
+        <v>3611.489682533085</v>
       </c>
       <c r="D44">
-        <v>6294.421615102141</v>
+        <v>6742.163682533085</v>
       </c>
       <c r="E44">
         <v>1202.074</v>
@@ -4889,37 +4889,37 @@
         <v>508.5</v>
       </c>
       <c r="M44">
-        <v>616.9494119693901</v>
+        <v>568.2097517693901</v>
       </c>
       <c r="N44">
-        <v>-108.4494119693901</v>
+        <v>-59.7097517693901</v>
       </c>
       <c r="O44">
-        <v>-36.87280006959264</v>
+        <v>-20.30131560159263</v>
       </c>
       <c r="P44">
-        <v>-71.57661189979746</v>
+        <v>-39.40843616779746</v>
       </c>
       <c r="Q44">
-        <v>-28.57661189979746</v>
+        <v>3.591563832202539</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1497791708370155</v>
+        <v>0.1485737989242757</v>
       </c>
       <c r="T44">
-        <v>1.354991812110411</v>
+        <v>1.339487128739701</v>
       </c>
       <c r="U44">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V44">
-        <v>0.2802336733705776</v>
+        <v>0.3042714410684173</v>
       </c>
       <c r="W44">
-        <v>0.1120633739507174</v>
+        <v>0.09976337395071741</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8242166863840519</v>
+        <v>0.8949160031424038</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1350374771936174</v>
+        <v>0.1290493614842282</v>
       </c>
       <c r="C45">
-        <v>2991.886116607546</v>
+        <v>3438.103586274355</v>
       </c>
       <c r="D45">
-        <v>6216.907116607546</v>
+        <v>6663.124586274355</v>
       </c>
       <c r="E45">
         <v>1296.421</v>
@@ -4971,37 +4971,37 @@
         <v>508.5</v>
       </c>
       <c r="M45">
-        <v>631.6386836829471</v>
+        <v>581.738555382947</v>
       </c>
       <c r="N45">
-        <v>-123.1386836829471</v>
+        <v>-73.23855538294697</v>
       </c>
       <c r="O45">
-        <v>-41.86715245220201</v>
+        <v>-24.90110883020197</v>
       </c>
       <c r="P45">
-        <v>-81.27153123074507</v>
+        <v>-48.337446552745</v>
       </c>
       <c r="Q45">
-        <v>-38.27153123074507</v>
+        <v>-5.337446552745</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1516033668166123</v>
+        <v>0.1503768480282104</v>
       </c>
       <c r="T45">
-        <v>1.378763598287787</v>
+        <v>1.362986902928117</v>
       </c>
       <c r="U45">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V45">
-        <v>0.2737166111991688</v>
+        <v>0.2971953610435704</v>
       </c>
       <c r="W45">
-        <v>0.1130780421119729</v>
+        <v>0.1007780421119728</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8050488564681435</v>
+        <v>0.8741040030693247</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1519208097658735</v>
+        <v>0.1300253025330752</v>
       </c>
       <c r="C46">
-        <v>1908.457798324345</v>
+        <v>3266.54918420212</v>
       </c>
       <c r="D46">
-        <v>5227.825798324346</v>
+        <v>6585.917184202121</v>
       </c>
       <c r="E46">
         <v>1390.768</v>
@@ -5053,45 +5053,45 @@
         <v>508.5</v>
       </c>
       <c r="M46">
-        <v>782.0744189965039</v>
+        <v>595.2673589965038</v>
       </c>
       <c r="N46">
-        <v>-273.5744189965039</v>
+        <v>-86.76735899650384</v>
       </c>
       <c r="O46">
-        <v>-93.01530245881135</v>
+        <v>-29.50090205881131</v>
       </c>
       <c r="P46">
-        <v>-180.5591165376926</v>
+        <v>-57.26645693769254</v>
       </c>
       <c r="Q46">
-        <v>-137.5591165376926</v>
+        <v>-14.26645693769254</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1559862689444252</v>
+        <v>0.1522442917429998</v>
       </c>
       <c r="T46">
-        <v>1.435878849820007</v>
+        <v>1.387325954766119</v>
       </c>
       <c r="U46">
-        <v>0.1883941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V46">
-        <v>0.2210659187930463</v>
+        <v>0.290440921019853</v>
       </c>
       <c r="W46">
-        <v>0.1467465889931712</v>
+        <v>0.1017465889931712</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.6501938788030773</v>
+        <v>0.8542380029995673</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1782792551971793</v>
+        <v>0.1310012435819223</v>
       </c>
       <c r="C47">
-        <v>773.9678655730204</v>
+        <v>3096.763532673637</v>
       </c>
       <c r="D47">
-        <v>4187.682865573021</v>
+        <v>6510.478532673638</v>
       </c>
       <c r="E47">
         <v>1485.115000000001</v>
@@ -5135,45 +5135,45 @@
         <v>508.5</v>
       </c>
       <c r="M47">
-        <v>1021.469940610061</v>
+        <v>608.7961626100608</v>
       </c>
       <c r="N47">
-        <v>-512.969940610061</v>
+        <v>-100.2961626100608</v>
       </c>
       <c r="O47">
-        <v>-174.4097798074208</v>
+        <v>-34.10069528742068</v>
       </c>
       <c r="P47">
-        <v>-338.5601608026403</v>
+        <v>-66.19546732264016</v>
       </c>
       <c r="Q47">
-        <v>-295.5601608026403</v>
+        <v>-23.19546732264016</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1606123908933399</v>
+        <v>0.1541796425019635</v>
       </c>
       <c r="T47">
-        <v>1.496163590620923</v>
+        <v>1.412550063034593</v>
       </c>
       <c r="U47">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V47">
-        <v>0.169256081972166</v>
+        <v>0.2839866783305228</v>
       </c>
       <c r="W47">
-        <v>0.1998720893463163</v>
+        <v>0.1026720893463163</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.4978120058004881</v>
+        <v>0.8352549362662436</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1802271962460263</v>
+        <v>0.1319771846307693</v>
       </c>
       <c r="C48">
-        <v>618.9385067854919</v>
+        <v>2928.686539347714</v>
       </c>
       <c r="D48">
-        <v>4127.000506785493</v>
+        <v>6436.748539347715</v>
       </c>
       <c r="E48">
         <v>1579.462</v>
@@ -5217,45 +5217,45 @@
         <v>508.5</v>
       </c>
       <c r="M48">
-        <v>1044.169272623618</v>
+        <v>622.3249662236177</v>
       </c>
       <c r="N48">
-        <v>-535.6692726236179</v>
+        <v>-113.8249662236177</v>
       </c>
       <c r="O48">
-        <v>-182.1275526920301</v>
+        <v>-38.70048851603002</v>
       </c>
       <c r="P48">
-        <v>-353.5417199315877</v>
+        <v>-75.12447770758769</v>
       </c>
       <c r="Q48">
-        <v>-310.5417199315877</v>
+        <v>-32.12447770758769</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1627385462802536</v>
+        <v>0.1561866729186665</v>
       </c>
       <c r="T48">
-        <v>1.52387032378057</v>
+        <v>1.438708397535234</v>
       </c>
       <c r="U48">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V48">
-        <v>0.1655766019292928</v>
+        <v>0.277813054888555</v>
       </c>
       <c r="W48">
-        <v>0.2007573505536725</v>
+        <v>0.1035573505536725</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.4869900056743907</v>
+        <v>0.8170972202604556</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1821751372948733</v>
+        <v>0.1476424451058914</v>
       </c>
       <c r="C49">
-        <v>465.6426847696621</v>
+        <v>1844.248007502605</v>
       </c>
       <c r="D49">
-        <v>4068.051684769662</v>
+        <v>5446.657007502606</v>
       </c>
       <c r="E49">
         <v>1673.809</v>
@@ -5299,45 +5299,45 @@
         <v>508.5</v>
       </c>
       <c r="M49">
-        <v>1066.868604637175</v>
+        <v>760.9012836371746</v>
       </c>
       <c r="N49">
-        <v>-558.3686046371747</v>
+        <v>-252.4012836371746</v>
       </c>
       <c r="O49">
-        <v>-189.8453255766394</v>
+        <v>-85.81643643663938</v>
       </c>
       <c r="P49">
-        <v>-368.5232790605353</v>
+        <v>-166.5848472005353</v>
       </c>
       <c r="Q49">
-        <v>-325.5232790605353</v>
+        <v>-123.5848472005353</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1649449339459187</v>
+        <v>0.1609775901931226</v>
       </c>
       <c r="T49">
-        <v>1.552622594040581</v>
+        <v>1.501150110220381</v>
       </c>
       <c r="U49">
-        <v>0.2405941048847012</v>
+        <v>0.1715941048847012</v>
       </c>
       <c r="V49">
-        <v>0.1620536955052653</v>
+        <v>0.2272173851167272</v>
       </c>
       <c r="W49">
-        <v>0.201604941071354</v>
+        <v>0.132604941071354</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.4766285161919568</v>
+        <v>0.6682864268139036</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1841230783437203</v>
+        <v>0.1489003861547384</v>
       </c>
       <c r="C50">
-        <v>314.0071616939777</v>
+        <v>1683.445646041159</v>
       </c>
       <c r="D50">
-        <v>4010.763161693978</v>
+        <v>5380.20164604116</v>
       </c>
       <c r="E50">
         <v>1768.156</v>
@@ -5381,45 +5381,45 @@
         <v>508.5</v>
       </c>
       <c r="M50">
-        <v>1089.567936650732</v>
+        <v>777.0906726507316</v>
       </c>
       <c r="N50">
-        <v>-581.0679366507316</v>
+        <v>-268.5906726507316</v>
       </c>
       <c r="O50">
-        <v>-197.5630984612487</v>
+        <v>-91.32082870124874</v>
       </c>
       <c r="P50">
-        <v>-383.5048381894828</v>
+        <v>-177.2698439494828</v>
       </c>
       <c r="Q50">
-        <v>-340.5048381894828</v>
+        <v>-134.2698439494828</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.167236182675648</v>
+        <v>0.1631925438506827</v>
       </c>
       <c r="T50">
-        <v>1.582480720849053</v>
+        <v>1.530018381570773</v>
       </c>
       <c r="U50">
-        <v>0.2405941048847012</v>
+        <v>0.1715941048847012</v>
       </c>
       <c r="V50">
-        <v>0.1586775768489057</v>
+        <v>0.2224836895934621</v>
       </c>
       <c r="W50">
-        <v>0.2024172153174654</v>
+        <v>0.1334172153174654</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.4666987554379577</v>
+        <v>0.6543637929219472</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1860710193925673</v>
+        <v>0.178365342730805</v>
       </c>
       <c r="C51">
-        <v>163.962767936524</v>
+        <v>393.2551125393456</v>
       </c>
       <c r="D51">
-        <v>3955.065767936524</v>
+        <v>4184.358112539347</v>
       </c>
       <c r="E51">
         <v>1862.503000000001</v>
@@ -5463,37 +5463,37 @@
         <v>508.5</v>
       </c>
       <c r="M51">
-        <v>1112.267268664289</v>
+        <v>1042.922223664289</v>
       </c>
       <c r="N51">
-        <v>-603.7672686642886</v>
+        <v>-534.4222236642886</v>
       </c>
       <c r="O51">
-        <v>-205.2808713458581</v>
+        <v>-181.7035560458581</v>
       </c>
       <c r="P51">
-        <v>-398.4863973184305</v>
+        <v>-352.7186676184305</v>
       </c>
       <c r="Q51">
-        <v>-355.4863973184305</v>
+        <v>-309.7186676184305</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1696172842967391</v>
+        <v>0.1689198790775972</v>
       </c>
       <c r="T51">
-        <v>1.613509754591192</v>
+        <v>1.604664759331724</v>
       </c>
       <c r="U51">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V51">
-        <v>0.15543925895403</v>
+        <v>0.1657745861360151</v>
       </c>
       <c r="W51">
-        <v>0.2031963355127151</v>
+        <v>0.1881963355127151</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4571742910412646</v>
+        <v>0.4875723121647503</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1880189604414144</v>
+        <v>0.180163283779652</v>
       </c>
       <c r="C52">
-        <v>15.44412347828074</v>
+        <v>242.9164085411885</v>
       </c>
       <c r="D52">
-        <v>3900.894123478281</v>
+        <v>4128.366408541189</v>
       </c>
       <c r="E52">
         <v>1956.85</v>
@@ -5545,37 +5545,37 @@
         <v>508.5</v>
       </c>
       <c r="M52">
-        <v>1134.966600677845</v>
+        <v>1064.206350677845</v>
       </c>
       <c r="N52">
-        <v>-626.4666006778455</v>
+        <v>-555.7063506778454</v>
       </c>
       <c r="O52">
-        <v>-212.9986442304675</v>
+        <v>-188.9401592304675</v>
       </c>
       <c r="P52">
-        <v>-413.467956447378</v>
+        <v>-366.766191447378</v>
       </c>
       <c r="Q52">
-        <v>-370.467956447378</v>
+        <v>-323.766191447378</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1720936299826739</v>
+        <v>0.1713822766591492</v>
       </c>
       <c r="T52">
-        <v>1.645779949683016</v>
+        <v>1.636758054518358</v>
       </c>
       <c r="U52">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V52">
-        <v>0.1523304737749494</v>
+        <v>0.1624590944132948</v>
       </c>
       <c r="W52">
-        <v>0.2039442909001548</v>
+        <v>0.1889442909001548</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4480308052204394</v>
+        <v>0.4778208659214552</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1899669014902614</v>
+        <v>0.181961224828499</v>
       </c>
       <c r="C53">
-        <v>-131.6106181169189</v>
+        <v>94.05638958189047</v>
       </c>
       <c r="D53">
-        <v>3848.186381883082</v>
+        <v>4073.853389581891</v>
       </c>
       <c r="E53">
         <v>2051.197</v>
@@ -5627,37 +5627,37 @@
         <v>508.5</v>
       </c>
       <c r="M53">
-        <v>1157.665932691402</v>
+        <v>1085.490477691402</v>
       </c>
       <c r="N53">
-        <v>-649.1659326914023</v>
+        <v>-576.9904776914022</v>
       </c>
       <c r="O53">
-        <v>-220.7164171150768</v>
+        <v>-196.1767624150768</v>
       </c>
       <c r="P53">
-        <v>-428.4495155763255</v>
+        <v>-380.8137152763255</v>
       </c>
       <c r="Q53">
-        <v>-385.4495155763255</v>
+        <v>-337.8137152763255</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1746710510027285</v>
+        <v>0.1739451802644379</v>
       </c>
       <c r="T53">
-        <v>1.679367295594914</v>
+        <v>1.670161280120774</v>
       </c>
       <c r="U53">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V53">
-        <v>0.1493436017401465</v>
+        <v>0.1592736219738184</v>
       </c>
       <c r="W53">
-        <v>0.2046629147037734</v>
+        <v>0.1896629147037734</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.439245887471019</v>
+        <v>0.4684518293347602</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1919148425391084</v>
+        <v>0.183759165877346</v>
       </c>
       <c r="C54">
-        <v>-277.2600052435246</v>
+        <v>-53.38275684806104</v>
       </c>
       <c r="D54">
-        <v>3796.883994756476</v>
+        <v>4020.76124315194</v>
       </c>
       <c r="E54">
         <v>2145.544000000001</v>
@@ -5709,37 +5709,37 @@
         <v>508.5</v>
       </c>
       <c r="M54">
-        <v>1180.365264704959</v>
+        <v>1106.774604704959</v>
       </c>
       <c r="N54">
-        <v>-671.8652647049594</v>
+        <v>-598.2746047049593</v>
       </c>
       <c r="O54">
-        <v>-228.4341899996862</v>
+        <v>-203.4133655996862</v>
       </c>
       <c r="P54">
-        <v>-443.4310747052732</v>
+        <v>-394.8612391052731</v>
       </c>
       <c r="Q54">
-        <v>-400.4310747052732</v>
+        <v>-351.8612391052731</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1773558645652853</v>
+        <v>0.1766148715199471</v>
       </c>
       <c r="T54">
-        <v>1.714354114253142</v>
+        <v>1.704956306789957</v>
       </c>
       <c r="U54">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V54">
-        <v>0.1464716093989898</v>
+        <v>0.1562106677050911</v>
       </c>
       <c r="W54">
-        <v>0.2053538991303297</v>
+        <v>0.1903538991303297</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4307988511734994</v>
+        <v>0.4594431403090916</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1938627835879554</v>
+        <v>0.185557106926193</v>
       </c>
       <c r="C55">
-        <v>-421.5595052024537</v>
+        <v>-199.4558682829074</v>
       </c>
       <c r="D55">
-        <v>3746.931494797547</v>
+        <v>3969.035131717093</v>
       </c>
       <c r="E55">
         <v>2239.891000000001</v>
@@ -5791,37 +5791,37 @@
         <v>508.5</v>
       </c>
       <c r="M55">
-        <v>1203.064596718516</v>
+        <v>1128.058731718516</v>
       </c>
       <c r="N55">
-        <v>-694.5645967185162</v>
+        <v>-619.5587317185161</v>
       </c>
       <c r="O55">
-        <v>-236.1519628842955</v>
+        <v>-210.6499687842955</v>
       </c>
       <c r="P55">
-        <v>-458.4126338342207</v>
+        <v>-408.9087629342206</v>
       </c>
       <c r="Q55">
-        <v>-415.4126338342207</v>
+        <v>-365.9087629342206</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1801549255134829</v>
+        <v>0.1793981666586693</v>
       </c>
       <c r="T55">
-        <v>1.750829733705336</v>
+        <v>1.741231972891871</v>
       </c>
       <c r="U55">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V55">
-        <v>0.1437079941273108</v>
+        <v>0.1532632966163159</v>
       </c>
       <c r="W55">
-        <v>0.206018808672865</v>
+        <v>0.191018808672865</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4226705709626787</v>
+        <v>0.4507744018126937</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1958107246368024</v>
+        <v>0.18735504797504</v>
       </c>
       <c r="C56">
-        <v>-564.5617042464237</v>
+        <v>-344.2149962127305</v>
       </c>
       <c r="D56">
-        <v>3698.276295753577</v>
+        <v>3918.62300378727</v>
       </c>
       <c r="E56">
         <v>2334.238</v>
@@ -5873,37 +5873,37 @@
         <v>508.5</v>
       </c>
       <c r="M56">
-        <v>1225.763928732073</v>
+        <v>1149.342858732073</v>
       </c>
       <c r="N56">
-        <v>-717.2639287320731</v>
+        <v>-640.842858732073</v>
       </c>
       <c r="O56">
-        <v>-243.8697357689049</v>
+        <v>-217.8865719689048</v>
       </c>
       <c r="P56">
-        <v>-473.3941929631682</v>
+        <v>-422.9562867631681</v>
       </c>
       <c r="Q56">
-        <v>-430.3941929631682</v>
+        <v>-379.9562867631681</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.183075684763776</v>
+        <v>0.18230247462951</v>
       </c>
       <c r="T56">
-        <v>1.788891249655452</v>
+        <v>1.779084841867781</v>
       </c>
       <c r="U56">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V56">
-        <v>0.141046734976805</v>
+        <v>0.1504250874197174</v>
       </c>
       <c r="W56">
-        <v>0.2066590919360471</v>
+        <v>0.1916590919360471</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4148433381670735</v>
+        <v>0.4424267277050512</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1977586656856494</v>
+        <v>0.1891529890238871</v>
       </c>
       <c r="C57">
-        <v>-706.316492239107</v>
+        <v>-487.7095807970418</v>
       </c>
       <c r="D57">
-        <v>3650.868507760894</v>
+        <v>3869.475419202959</v>
       </c>
       <c r="E57">
         <v>2428.585000000001</v>
@@ -5955,37 +5955,37 @@
         <v>508.5</v>
       </c>
       <c r="M57">
-        <v>1248.46326074563</v>
+        <v>1170.62698574563</v>
       </c>
       <c r="N57">
-        <v>-739.9632607456301</v>
+        <v>-662.12698574563</v>
       </c>
       <c r="O57">
-        <v>-251.5875086535142</v>
+        <v>-225.1231751535142</v>
       </c>
       <c r="P57">
-        <v>-488.3757520921159</v>
+        <v>-437.0038105921158</v>
       </c>
       <c r="Q57">
-        <v>-445.3757520921159</v>
+        <v>-394.0038105921158</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1861262555363044</v>
+        <v>0.1853358629546102</v>
       </c>
       <c r="T57">
-        <v>1.828644388536684</v>
+        <v>1.818620060575954</v>
       </c>
       <c r="U57">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V57">
-        <v>0.1384822488863176</v>
+        <v>0.147690085830268</v>
       </c>
       <c r="W57">
-        <v>0.2072760921714772</v>
+        <v>0.1922760921714772</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4073007320185812</v>
+        <v>0.4343826053831411</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1997066067344965</v>
+        <v>0.1909509300727341</v>
       </c>
       <c r="C58">
-        <v>-846.8712332913074</v>
+        <v>-629.9866125936223</v>
       </c>
       <c r="D58">
-        <v>3604.660766708693</v>
+        <v>3821.545387406378</v>
       </c>
       <c r="E58">
         <v>2522.932000000001</v>
@@ -6037,37 +6037,37 @@
         <v>508.5</v>
       </c>
       <c r="M58">
-        <v>1271.162592759187</v>
+        <v>1191.911112759187</v>
       </c>
       <c r="N58">
-        <v>-762.662592759187</v>
+        <v>-683.4111127591868</v>
       </c>
       <c r="O58">
-        <v>-259.3052815381236</v>
+        <v>-232.3597783381235</v>
       </c>
       <c r="P58">
-        <v>-503.3573112210634</v>
+        <v>-451.0513344210633</v>
       </c>
       <c r="Q58">
-        <v>-460.3573112210634</v>
+        <v>-408.0513344210633</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1893154886166749</v>
+        <v>0.188507132567215</v>
       </c>
       <c r="T58">
-        <v>1.870204488276154</v>
+        <v>1.859952334679953</v>
       </c>
       <c r="U58">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V58">
-        <v>0.1360093515847763</v>
+        <v>0.1450527628690132</v>
       </c>
       <c r="W58">
-        <v>0.2078710566842134</v>
+        <v>0.1928710566842133</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4000275046611066</v>
+        <v>0.4266257731441565</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2016545477833435</v>
+        <v>0.1927488711215811</v>
       </c>
       <c r="C59">
-        <v>-986.2709236010005</v>
+        <v>-771.0907824147171</v>
       </c>
       <c r="D59">
-        <v>3559.608076399001</v>
+        <v>3774.788217585284</v>
       </c>
       <c r="E59">
         <v>2617.279000000001</v>
@@ -6119,37 +6119,37 @@
         <v>508.5</v>
       </c>
       <c r="M59">
-        <v>1293.861924772744</v>
+        <v>1213.195239772744</v>
       </c>
       <c r="N59">
-        <v>-785.361924772744</v>
+        <v>-704.6952397727439</v>
       </c>
       <c r="O59">
-        <v>-267.023054422733</v>
+        <v>-239.5963815227329</v>
       </c>
       <c r="P59">
-        <v>-518.3388703500111</v>
+        <v>-465.0988582500109</v>
       </c>
       <c r="Q59">
-        <v>-475.3388703500111</v>
+        <v>-422.0988582500109</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1926530581193883</v>
+        <v>0.1918259030920339</v>
       </c>
       <c r="T59">
-        <v>1.913697615910484</v>
+        <v>1.903207040137626</v>
       </c>
       <c r="U59">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V59">
-        <v>0.1336232226096047</v>
+        <v>0.1425079775555217</v>
       </c>
       <c r="W59">
-        <v>0.2084451452491342</v>
+        <v>0.1934451452491342</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3930094782635433</v>
+        <v>0.4191411104574169</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2036024888321905</v>
+        <v>0.1945468121704281</v>
       </c>
       <c r="C60">
-        <v>-1124.558337602952</v>
+        <v>-911.0646203151109</v>
       </c>
       <c r="D60">
-        <v>3515.667662397049</v>
+        <v>3729.161379684889</v>
       </c>
       <c r="E60">
         <v>2711.626</v>
@@ -6201,37 +6201,37 @@
         <v>508.5</v>
       </c>
       <c r="M60">
-        <v>1316.561256786301</v>
+        <v>1234.4793667863</v>
       </c>
       <c r="N60">
-        <v>-808.0612567863006</v>
+        <v>-725.9793667863005</v>
       </c>
       <c r="O60">
-        <v>-274.7408273073422</v>
+        <v>-246.8329847073422</v>
       </c>
       <c r="P60">
-        <v>-533.3204294789584</v>
+        <v>-479.1463820789583</v>
       </c>
       <c r="Q60">
-        <v>-490.3204294789584</v>
+        <v>-436.1463820789583</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1961495595031832</v>
+        <v>0.1953027103085109</v>
       </c>
       <c r="T60">
-        <v>1.959261844860732</v>
+        <v>1.948521493474236</v>
       </c>
       <c r="U60">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V60">
-        <v>0.1313193739439219</v>
+        <v>0.1400509434597369</v>
       </c>
       <c r="W60">
-        <v>0.208999437656644</v>
+        <v>0.193999437656644</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3862334527762409</v>
+        <v>0.4119145395874615</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2055504298810374</v>
+        <v>0.1963447532192751</v>
       </c>
       <c r="C61">
-        <v>-1261.774163425748</v>
+        <v>-1049.948624620699</v>
       </c>
       <c r="D61">
-        <v>3472.798836574252</v>
+        <v>3684.624375379301</v>
       </c>
       <c r="E61">
         <v>2805.973</v>
@@ -6283,37 +6283,37 @@
         <v>508.5</v>
       </c>
       <c r="M61">
-        <v>1339.260588799857</v>
+        <v>1255.763493799858</v>
       </c>
       <c r="N61">
-        <v>-830.7605887998575</v>
+        <v>-747.2634937998575</v>
       </c>
       <c r="O61">
-        <v>-282.4586001919516</v>
+        <v>-254.0695878919516</v>
       </c>
       <c r="P61">
-        <v>-548.301988607906</v>
+        <v>-493.193905907906</v>
       </c>
       <c r="Q61">
-        <v>-505.301988607906</v>
+        <v>-450.193905907906</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1998166219300901</v>
+        <v>0.1989491178770112</v>
       </c>
       <c r="T61">
-        <v>2.007048719125629</v>
+        <v>1.996046407949217</v>
       </c>
       <c r="U61">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V61">
-        <v>0.1290936218431775</v>
+        <v>0.1376771986553346</v>
       </c>
       <c r="W61">
-        <v>0.2095349404910178</v>
+        <v>0.1945349404910178</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.379687123068169</v>
+        <v>0.4049329372215723</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2074983709298845</v>
+        <v>0.1981426942681221</v>
       </c>
       <c r="C62">
-        <v>-1397.957128557919</v>
+        <v>-1187.781381820301</v>
       </c>
       <c r="D62">
-        <v>3430.962871442082</v>
+        <v>3641.1386181797</v>
       </c>
       <c r="E62">
         <v>2900.320000000001</v>
@@ -6365,37 +6365,37 @@
         <v>508.5</v>
       </c>
       <c r="M62">
-        <v>1361.959920813415</v>
+        <v>1277.047620813415</v>
       </c>
       <c r="N62">
-        <v>-853.4599208134146</v>
+        <v>-768.5476208134146</v>
       </c>
       <c r="O62">
-        <v>-290.176373076561</v>
+        <v>-261.306191076561</v>
       </c>
       <c r="P62">
-        <v>-563.2835477368535</v>
+        <v>-507.2414297368536</v>
       </c>
       <c r="Q62">
-        <v>-520.2835477368535</v>
+        <v>-464.2414297368536</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2036670374783423</v>
+        <v>0.2027778458239365</v>
       </c>
       <c r="T62">
-        <v>2.057224937103769</v>
+        <v>2.045947568147948</v>
       </c>
       <c r="U62">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V62">
-        <v>0.1269420614791245</v>
+        <v>0.1353825786777457</v>
       </c>
       <c r="W62">
-        <v>0.2100525932309125</v>
+        <v>0.1950525932309126</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3733590043503662</v>
+        <v>0.398184054934546</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2094463119787315</v>
+        <v>0.1999406353169692</v>
       </c>
       <c r="C63">
-        <v>-1533.144116538952</v>
+        <v>-1324.59967806678</v>
       </c>
       <c r="D63">
-        <v>3390.122883461048</v>
+        <v>3598.667321933221</v>
       </c>
       <c r="E63">
         <v>2994.667</v>
@@ -6447,37 +6447,37 @@
         <v>508.5</v>
       </c>
       <c r="M63">
-        <v>1384.659252826971</v>
+        <v>1298.331747826971</v>
       </c>
       <c r="N63">
-        <v>-876.1592528269714</v>
+        <v>-789.8317478269714</v>
       </c>
       <c r="O63">
-        <v>-297.8941459611703</v>
+        <v>-268.5427942611703</v>
       </c>
       <c r="P63">
-        <v>-578.265106865801</v>
+        <v>-521.2889535658012</v>
       </c>
       <c r="Q63">
-        <v>-535.265106865801</v>
+        <v>-478.2889535658012</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2077149102341973</v>
+        <v>0.206802918793781</v>
       </c>
       <c r="T63">
-        <v>2.109974294465404</v>
+        <v>2.098407762203024</v>
       </c>
       <c r="U63">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V63">
-        <v>0.1248610440778274</v>
+        <v>0.1331631921420449</v>
       </c>
       <c r="W63">
-        <v>0.2105532737498271</v>
+        <v>0.1955532737498271</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3672383649347865</v>
+        <v>0.3916564474766027</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2113942530275785</v>
+        <v>0.2017385763658162</v>
       </c>
       <c r="C64">
-        <v>-1667.370275414288</v>
+        <v>-1460.438602964629</v>
       </c>
       <c r="D64">
-        <v>3350.243724585712</v>
+        <v>3557.175397035371</v>
       </c>
       <c r="E64">
         <v>3089.014</v>
@@ -6529,37 +6529,37 @@
         <v>508.5</v>
       </c>
       <c r="M64">
-        <v>1407.358584840528</v>
+        <v>1319.615874840528</v>
       </c>
       <c r="N64">
-        <v>-898.8585848405282</v>
+        <v>-811.1158748405282</v>
       </c>
       <c r="O64">
-        <v>-305.6119188457796</v>
+        <v>-275.7793974457796</v>
       </c>
       <c r="P64">
-        <v>-593.2466659947486</v>
+        <v>-535.3364773947486</v>
       </c>
       <c r="Q64">
-        <v>-550.2466659947486</v>
+        <v>-492.3364773947486</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2119758289245709</v>
+        <v>0.2110398377094068</v>
       </c>
       <c r="T64">
-        <v>2.165499933793441</v>
+        <v>2.153629019103103</v>
       </c>
       <c r="U64">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V64">
-        <v>0.1228471562701205</v>
+        <v>0.131015398720399</v>
       </c>
       <c r="W64">
-        <v>0.2110378032842606</v>
+        <v>0.1960378032842606</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3613151655003544</v>
+        <v>0.3853394080011736</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2133421940764255</v>
+        <v>0.2035365174146632</v>
       </c>
       <c r="C65">
-        <v>-1800.669118624517</v>
+        <v>-1595.33164625951</v>
       </c>
       <c r="D65">
-        <v>3311.291881375484</v>
+        <v>3516.629353740491</v>
       </c>
       <c r="E65">
         <v>3183.361000000001</v>
@@ -6611,37 +6611,37 @@
         <v>508.5</v>
       </c>
       <c r="M65">
-        <v>1430.057916854085</v>
+        <v>1340.900001854085</v>
       </c>
       <c r="N65">
-        <v>-921.5579168540853</v>
+        <v>-832.4000018540853</v>
       </c>
       <c r="O65">
-        <v>-313.329691730389</v>
+        <v>-283.016000630389</v>
       </c>
       <c r="P65">
-        <v>-608.2282251236963</v>
+        <v>-549.3840012236963</v>
       </c>
       <c r="Q65">
-        <v>-565.2282251236963</v>
+        <v>-506.3840012236963</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2164670675441539</v>
+        <v>0.2155057792691205</v>
       </c>
       <c r="T65">
-        <v>2.224026959031102</v>
+        <v>2.211835208808592</v>
       </c>
       <c r="U65">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V65">
-        <v>0.12089720140869</v>
+        <v>0.1289357892169006</v>
       </c>
       <c r="W65">
-        <v>0.211506950928712</v>
+        <v>0.196506950928712</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3555800041432059</v>
+        <v>0.3792229094614724</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2152901351252725</v>
+        <v>0.2053344584635102</v>
       </c>
       <c r="C66">
-        <v>-1933.072618937516</v>
+        <v>-1729.310787989672</v>
       </c>
       <c r="D66">
-        <v>3273.235381062484</v>
+        <v>3476.997212010329</v>
       </c>
       <c r="E66">
         <v>3277.708000000001</v>
@@ -6693,37 +6693,37 @@
         <v>508.5</v>
       </c>
       <c r="M66">
-        <v>1452.757248867642</v>
+        <v>1362.184128867642</v>
       </c>
       <c r="N66">
-        <v>-944.2572488676421</v>
+        <v>-853.6841288676421</v>
       </c>
       <c r="O66">
-        <v>-321.0474646149984</v>
+        <v>-290.2526038149983</v>
       </c>
       <c r="P66">
-        <v>-623.2097842526438</v>
+        <v>-563.4315250526438</v>
       </c>
       <c r="Q66">
-        <v>-580.2097842526438</v>
+        <v>-520.4315250526438</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2212078194203805</v>
+        <v>0.2202198286932627</v>
       </c>
       <c r="T66">
-        <v>2.285805485670855</v>
+        <v>2.273275075719942</v>
       </c>
       <c r="U66">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V66">
-        <v>0.1190081826366792</v>
+        <v>0.1269211675103866</v>
       </c>
       <c r="W66">
-        <v>0.2119614377092743</v>
+        <v>0.1969614377092744</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3500240665784683</v>
+        <v>0.373297551501137</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2172380761741195</v>
+        <v>0.2071323995123572</v>
       </c>
       <c r="C67">
-        <v>-2064.611295976834</v>
+        <v>-1862.406582609322</v>
       </c>
       <c r="D67">
-        <v>3236.043704023166</v>
+        <v>3438.248417390678</v>
       </c>
       <c r="E67">
         <v>3372.055</v>
@@ -6775,37 +6775,37 @@
         <v>508.5</v>
       </c>
       <c r="M67">
-        <v>1475.456580881199</v>
+        <v>1383.468255881199</v>
       </c>
       <c r="N67">
-        <v>-966.956580881199</v>
+        <v>-874.968255881199</v>
       </c>
       <c r="O67">
-        <v>-328.7652374996077</v>
+        <v>-297.4892069996077</v>
       </c>
       <c r="P67">
-        <v>-638.1913433815913</v>
+        <v>-577.4790488815913</v>
       </c>
       <c r="Q67">
-        <v>-595.1913433815913</v>
+        <v>-534.4790488815913</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2262194714038198</v>
+        <v>0.2252032523702131</v>
       </c>
       <c r="T67">
-        <v>2.351114213832879</v>
+        <v>2.338225792169083</v>
       </c>
       <c r="U67">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V67">
-        <v>0.1171772875191919</v>
+        <v>0.1249685341640729</v>
       </c>
       <c r="W67">
-        <v>0.212401940281204</v>
+        <v>0.197401940281204</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3446390809387996</v>
+        <v>0.3675545122472733</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2191860172229666</v>
+        <v>0.2089303405612042</v>
       </c>
       <c r="C68">
-        <v>-2195.314297849948</v>
+        <v>-1994.648237549008</v>
       </c>
       <c r="D68">
-        <v>3199.687702150053</v>
+        <v>3400.353762450993</v>
       </c>
       <c r="E68">
         <v>3466.402000000001</v>
@@ -6857,37 +6857,37 @@
         <v>508.5</v>
       </c>
       <c r="M68">
-        <v>1498.155912894756</v>
+        <v>1404.752382894756</v>
       </c>
       <c r="N68">
-        <v>-989.6559128947561</v>
+        <v>-896.252382894756</v>
       </c>
       <c r="O68">
-        <v>-336.4830103842171</v>
+        <v>-304.725810184217</v>
       </c>
       <c r="P68">
-        <v>-653.172902510539</v>
+        <v>-591.526572710539</v>
       </c>
       <c r="Q68">
-        <v>-610.172902510539</v>
+        <v>-548.526572710539</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2315259264451087</v>
+        <v>0.2304798186163959</v>
       </c>
       <c r="T68">
-        <v>2.420264631886788</v>
+        <v>2.406997138997586</v>
       </c>
       <c r="U68">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V68">
-        <v>0.1154018740719314</v>
+        <v>0.1230750715252233</v>
       </c>
       <c r="W68">
-        <v>0.2128290942903479</v>
+        <v>0.1978290942903479</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.339417276682151</v>
+        <v>0.3619855044859509</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2211339582718136</v>
+        <v>0.2107282816100512</v>
       </c>
       <c r="C69">
-        <v>-2325.209477335216</v>
+        <v>-2126.063686637483</v>
       </c>
       <c r="D69">
-        <v>3164.139522664784</v>
+        <v>3363.285313362518</v>
       </c>
       <c r="E69">
         <v>3560.749000000001</v>
@@ -6939,37 +6939,37 @@
         <v>508.5</v>
       </c>
       <c r="M69">
-        <v>1520.855244908313</v>
+        <v>1426.036509908313</v>
       </c>
       <c r="N69">
-        <v>-1012.355244908313</v>
+        <v>-917.5365099083128</v>
       </c>
       <c r="O69">
-        <v>-344.2007832688264</v>
+        <v>-311.9624133688264</v>
       </c>
       <c r="P69">
-        <v>-668.1544616394865</v>
+        <v>-605.5740965394864</v>
       </c>
       <c r="Q69">
-        <v>-625.1544616394865</v>
+        <v>-562.5740965394864</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2371539848222332</v>
+        <v>0.2360761767562866</v>
       </c>
       <c r="T69">
-        <v>2.493605984368206</v>
+        <v>2.479936446239937</v>
       </c>
       <c r="U69">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V69">
-        <v>0.113679458041007</v>
+        <v>0.1212381301591752</v>
       </c>
       <c r="W69">
-        <v>0.2132434974335472</v>
+        <v>0.1982434974335472</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3343513471794324</v>
+        <v>0.3565827357622801</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2230818993206606</v>
+        <v>0.2125262226588982</v>
       </c>
       <c r="C70">
-        <v>-2454.32346304609</v>
+        <v>-2256.67965877302</v>
       </c>
       <c r="D70">
-        <v>3129.372536953911</v>
+        <v>3327.016341226981</v>
       </c>
       <c r="E70">
         <v>3655.096000000001</v>
@@ -7021,37 +7021,37 @@
         <v>508.5</v>
       </c>
       <c r="M70">
-        <v>1543.55457692187</v>
+        <v>1447.32063692187</v>
       </c>
       <c r="N70">
-        <v>-1035.05457692187</v>
+        <v>-938.8206369218699</v>
       </c>
       <c r="O70">
-        <v>-351.9185561534358</v>
+        <v>-319.1990165534358</v>
       </c>
       <c r="P70">
-        <v>-683.1360207684342</v>
+        <v>-619.6216203684342</v>
       </c>
       <c r="Q70">
-        <v>-640.1360207684342</v>
+        <v>-576.6216203684342</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.243133796847928</v>
+        <v>0.2420223072799206</v>
       </c>
       <c r="T70">
-        <v>2.571531171379712</v>
+        <v>2.557434460184935</v>
       </c>
       <c r="U70">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V70">
-        <v>0.1120077013051099</v>
+        <v>0.1194552164803638</v>
       </c>
       <c r="W70">
-        <v>0.2136457122490054</v>
+        <v>0.1986457122490053</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3294344156032643</v>
+        <v>0.3513388720010701</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2250298403695076</v>
+        <v>0.2143241637077452</v>
       </c>
       <c r="C71">
-        <v>-2582.681725954653</v>
+        <v>-2386.521742198863</v>
       </c>
       <c r="D71">
-        <v>3095.361274045348</v>
+        <v>3291.521257801139</v>
       </c>
       <c r="E71">
         <v>3749.443000000001</v>
@@ -7103,37 +7103,37 @@
         <v>508.5</v>
       </c>
       <c r="M71">
-        <v>1566.253908935427</v>
+        <v>1468.604763935427</v>
       </c>
       <c r="N71">
-        <v>-1057.753908935427</v>
+        <v>-960.1047639354267</v>
       </c>
       <c r="O71">
-        <v>-359.6363290380451</v>
+        <v>-326.4356197380451</v>
       </c>
       <c r="P71">
-        <v>-698.1175798973817</v>
+        <v>-633.6691441973817</v>
       </c>
       <c r="Q71">
-        <v>-655.1175798973817</v>
+        <v>-590.6691441973817</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2494994031978612</v>
+        <v>0.24835205912766</v>
       </c>
       <c r="T71">
-        <v>2.654483789811316</v>
+        <v>2.639932345997352</v>
       </c>
       <c r="U71">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V71">
-        <v>0.1103844012861952</v>
+        <v>0.1177239814589093</v>
       </c>
       <c r="W71">
-        <v>0.2140362686640154</v>
+        <v>0.1990362686640154</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.324660003782927</v>
+        <v>0.3462470042909096</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2269777814183546</v>
+        <v>0.2161221047565922</v>
       </c>
       <c r="C72">
-        <v>-2710.30864162379</v>
+        <v>-2515.614444707709</v>
       </c>
       <c r="D72">
-        <v>3062.081358376211</v>
+        <v>3256.775555292291</v>
       </c>
       <c r="E72">
         <v>3843.790000000001</v>
@@ -7185,37 +7185,37 @@
         <v>508.5</v>
       </c>
       <c r="M72">
-        <v>1588.953240948984</v>
+        <v>1489.888890948984</v>
       </c>
       <c r="N72">
-        <v>-1080.453240948984</v>
+        <v>-981.3888909489835</v>
       </c>
       <c r="O72">
-        <v>-367.3541019226545</v>
+        <v>-333.6722229226544</v>
       </c>
       <c r="P72">
-        <v>-713.0991390263291</v>
+        <v>-647.7166680263291</v>
       </c>
       <c r="Q72">
-        <v>-670.0991390263291</v>
+        <v>-604.7166680263291</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2562893833044565</v>
+        <v>0.2551037944319153</v>
       </c>
       <c r="T72">
-        <v>2.742966582805026</v>
+        <v>2.727930090863931</v>
       </c>
       <c r="U72">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V72">
-        <v>0.108807481267821</v>
+        <v>0.1160422102952106</v>
       </c>
       <c r="W72">
-        <v>0.2144156663243109</v>
+        <v>0.1994156663243109</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3200220037288852</v>
+        <v>0.3413006185153252</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2289257224672016</v>
+        <v>0.2179200458054393</v>
       </c>
       <c r="C73">
-        <v>-2837.227548467508</v>
+        <v>-2643.981250072858</v>
       </c>
       <c r="D73">
-        <v>3029.509451532492</v>
+        <v>3222.755749927142</v>
       </c>
       <c r="E73">
         <v>3938.137000000001</v>
@@ -7267,37 +7267,37 @@
         <v>508.5</v>
       </c>
       <c r="M73">
-        <v>1611.65257296254</v>
+        <v>1511.17301796254</v>
       </c>
       <c r="N73">
-        <v>-1103.15257296254</v>
+        <v>-1002.67301796254</v>
       </c>
       <c r="O73">
-        <v>-375.0718748072638</v>
+        <v>-340.9088261072637</v>
       </c>
       <c r="P73">
-        <v>-728.0806981552767</v>
+        <v>-661.7641918552766</v>
       </c>
       <c r="Q73">
-        <v>-685.0806981552767</v>
+        <v>-618.7641918552766</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2635476379011619</v>
+        <v>0.2623211666537055</v>
       </c>
       <c r="T73">
-        <v>2.83755163738451</v>
+        <v>2.821996645721307</v>
       </c>
       <c r="U73">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V73">
-        <v>0.1072749815316545</v>
+        <v>0.114407812967109</v>
       </c>
       <c r="W73">
-        <v>0.21478437672657</v>
+        <v>0.19978437672657</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3155146515636897</v>
+        <v>0.3364935675503207</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2308736635160486</v>
+        <v>0.2197179868542862</v>
       </c>
       <c r="C74">
-        <v>-2963.460802332031</v>
+        <v>-2771.644670979088</v>
       </c>
       <c r="D74">
-        <v>2997.623197667969</v>
+        <v>3189.439329020913</v>
       </c>
       <c r="E74">
         <v>4032.484</v>
@@ -7349,37 +7349,37 @@
         <v>508.5</v>
       </c>
       <c r="M74">
-        <v>1634.351904976097</v>
+        <v>1532.457144976097</v>
       </c>
       <c r="N74">
-        <v>-1125.851904976097</v>
+        <v>-1023.957144976097</v>
       </c>
       <c r="O74">
-        <v>-382.7896476918731</v>
+        <v>-348.1454292918731</v>
       </c>
       <c r="P74">
-        <v>-743.0622572842242</v>
+        <v>-675.8117156842241</v>
       </c>
       <c r="Q74">
-        <v>-700.0622572842242</v>
+        <v>-632.8117156842241</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2713243392547748</v>
+        <v>0.2700540654627663</v>
       </c>
       <c r="T74">
-        <v>2.938892767291099</v>
+        <v>2.922782240211354</v>
       </c>
       <c r="U74">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V74">
-        <v>0.1057850512326038</v>
+        <v>0.1128188155647881</v>
       </c>
       <c r="W74">
-        <v>0.2151428451732107</v>
+        <v>0.2001428451732107</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3111325036253052</v>
+        <v>0.3318200457787884</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2328216045648956</v>
+        <v>0.2215159279031333</v>
       </c>
       <c r="C75">
-        <v>-3089.02982766594</v>
+        <v>-2898.626298703986</v>
       </c>
       <c r="D75">
-        <v>2966.40117233406</v>
+        <v>3156.804701296014</v>
       </c>
       <c r="E75">
         <v>4126.831</v>
@@ -7431,37 +7431,37 @@
         <v>508.5</v>
       </c>
       <c r="M75">
-        <v>1657.051236989654</v>
+        <v>1553.741271989654</v>
       </c>
       <c r="N75">
-        <v>-1148.551236989654</v>
+        <v>-1045.241271989654</v>
       </c>
       <c r="O75">
-        <v>-390.5074205764824</v>
+        <v>-355.3820324764825</v>
       </c>
       <c r="P75">
-        <v>-758.0438164131717</v>
+        <v>-689.8592395131718</v>
       </c>
       <c r="Q75">
-        <v>-715.0438164131717</v>
+        <v>-646.8592395131718</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2796770925605072</v>
+        <v>0.2783597715910169</v>
       </c>
       <c r="T75">
-        <v>3.047740647561139</v>
+        <v>3.031033434293255</v>
       </c>
       <c r="U75">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V75">
-        <v>0.1043359409417462</v>
+        <v>0.1112733523378732</v>
       </c>
       <c r="W75">
-        <v>0.2154914925665188</v>
+        <v>0.2004914925665187</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3068704145345476</v>
+        <v>0.3272745656996269</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2347695456137426</v>
+        <v>0.2233138689519803</v>
       </c>
       <c r="C76">
-        <v>-3213.955165525463</v>
+        <v>-3024.946849780093</v>
       </c>
       <c r="D76">
-        <v>2935.822834474538</v>
+        <v>3124.831150219908</v>
       </c>
       <c r="E76">
         <v>4221.178000000001</v>
@@ -7513,37 +7513,37 @@
         <v>508.5</v>
       </c>
       <c r="M76">
-        <v>1679.750569003211</v>
+        <v>1575.025399003211</v>
       </c>
       <c r="N76">
-        <v>-1171.250569003211</v>
+        <v>-1066.525399003211</v>
       </c>
       <c r="O76">
-        <v>-398.2251934610919</v>
+        <v>-362.6186356610918</v>
       </c>
       <c r="P76">
-        <v>-773.0253755421194</v>
+        <v>-703.9067633421195</v>
       </c>
       <c r="Q76">
-        <v>-730.0253755421194</v>
+        <v>-660.9067633421195</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2886723653512959</v>
+        <v>0.2873043781906715</v>
       </c>
       <c r="T76">
-        <v>3.164961441698106</v>
+        <v>3.147611643304535</v>
       </c>
       <c r="U76">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V76">
-        <v>0.1029259957938847</v>
+        <v>0.1097696583873613</v>
       </c>
       <c r="W76">
-        <v>0.215830717057305</v>
+        <v>0.200830717057305</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3027235170408374</v>
+        <v>0.3228519364334157</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2367174866625897</v>
+        <v>0.2251118100008273</v>
       </c>
       <c r="C77">
-        <v>-3338.256518640965</v>
+        <v>-3150.626209849796</v>
       </c>
       <c r="D77">
-        <v>2905.868481359035</v>
+        <v>3093.498790150204</v>
       </c>
       <c r="E77">
         <v>4315.525000000001</v>
@@ -7595,37 +7595,37 @@
         <v>508.5</v>
       </c>
       <c r="M77">
-        <v>1702.449901016768</v>
+        <v>1596.309526016768</v>
       </c>
       <c r="N77">
-        <v>-1193.949901016768</v>
+        <v>-1087.809526016768</v>
       </c>
       <c r="O77">
-        <v>-405.9429663457012</v>
+        <v>-369.8552388457012</v>
       </c>
       <c r="P77">
-        <v>-788.0069346710669</v>
+        <v>-717.9542871710669</v>
       </c>
       <c r="Q77">
-        <v>-745.0069346710669</v>
+        <v>-674.9542871710669</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2983872599653478</v>
+        <v>0.2969645533182984</v>
       </c>
       <c r="T77">
-        <v>3.291559899366031</v>
+        <v>3.273516109036716</v>
       </c>
       <c r="U77">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V77">
-        <v>0.1015536491832996</v>
+        <v>0.1083060629421965</v>
       </c>
       <c r="W77">
-        <v>0.2161608955616703</v>
+        <v>0.2011608955616703</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.298687203480293</v>
+        <v>0.3185472439476369</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2386654277114367</v>
+        <v>0.2269097510496743</v>
       </c>
       <c r="C78">
-        <v>-3461.952793752412</v>
+        <v>-3275.683474908049</v>
       </c>
       <c r="D78">
-        <v>2876.519206247588</v>
+        <v>3062.788525091952</v>
       </c>
       <c r="E78">
         <v>4409.872</v>
@@ -7677,37 +7677,37 @@
         <v>508.5</v>
       </c>
       <c r="M78">
-        <v>1725.149233030325</v>
+        <v>1617.593653030325</v>
       </c>
       <c r="N78">
-        <v>-1216.649233030325</v>
+        <v>-1109.093653030325</v>
       </c>
       <c r="O78">
-        <v>-413.6607392303105</v>
+        <v>-377.0918420303105</v>
       </c>
       <c r="P78">
-        <v>-802.9884938000143</v>
+        <v>-732.0018110000144</v>
       </c>
       <c r="Q78">
-        <v>-759.9884938000143</v>
+        <v>-689.0018110000144</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3089117291305706</v>
+        <v>0.3074297430398941</v>
       </c>
       <c r="T78">
-        <v>3.428708228506283</v>
+        <v>3.409912613579913</v>
       </c>
       <c r="U78">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V78">
-        <v>0.1002174169572036</v>
+        <v>0.1068809831666413</v>
       </c>
       <c r="W78">
-        <v>0.216482385158026</v>
+        <v>0.201482385158026</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2947571086976575</v>
+        <v>0.3143558328430627</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2406133687602837</v>
+        <v>0.2287076920985213</v>
       </c>
       <c r="C79">
-        <v>-3585.062141404958</v>
+        <v>-3400.136990112638</v>
       </c>
       <c r="D79">
-        <v>2847.756858595043</v>
+        <v>3032.682009887363</v>
       </c>
       <c r="E79">
         <v>4504.219000000001</v>
@@ -7759,37 +7759,37 @@
         <v>508.5</v>
       </c>
       <c r="M79">
-        <v>1747.848565043882</v>
+        <v>1638.877780043882</v>
       </c>
       <c r="N79">
-        <v>-1239.348565043882</v>
+        <v>-1130.377780043882</v>
       </c>
       <c r="O79">
-        <v>-421.3785121149199</v>
+        <v>-384.3284452149199</v>
       </c>
       <c r="P79">
-        <v>-817.9700529289621</v>
+        <v>-746.0493348289622</v>
       </c>
       <c r="Q79">
-        <v>-774.9700529289621</v>
+        <v>-703.0493348289622</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3203513695275519</v>
+        <v>0.31880494925902</v>
       </c>
       <c r="T79">
-        <v>3.577782499310903</v>
+        <v>3.558169683735562</v>
       </c>
       <c r="U79">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V79">
-        <v>0.09891589206165545</v>
+        <v>0.1054929184501914</v>
       </c>
       <c r="W79">
-        <v>0.2167955243752555</v>
+        <v>0.2017955243752555</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2909290942989866</v>
+        <v>0.3102732895593865</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2425613098091307</v>
+        <v>0.2305056331473683</v>
       </c>
       <c r="C80">
-        <v>-3707.601993380652</v>
+        <v>-3524.004386327765</v>
       </c>
       <c r="D80">
-        <v>2819.564006619349</v>
+        <v>3003.161613672235</v>
       </c>
       <c r="E80">
         <v>4598.566000000001</v>
@@ -7841,37 +7841,37 @@
         <v>508.5</v>
       </c>
       <c r="M80">
-        <v>1770.547897057439</v>
+        <v>1660.161907057439</v>
       </c>
       <c r="N80">
-        <v>-1262.047897057439</v>
+        <v>-1151.661907057439</v>
       </c>
       <c r="O80">
-        <v>-429.0962849995292</v>
+        <v>-391.5650483995292</v>
       </c>
       <c r="P80">
-        <v>-832.9516120579096</v>
+        <v>-760.0968586579096</v>
       </c>
       <c r="Q80">
-        <v>-789.9516120579096</v>
+        <v>-717.0968586579096</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3328309772333498</v>
+        <v>0.33121426513443</v>
       </c>
       <c r="T80">
-        <v>3.740408976552309</v>
+        <v>3.719904669359905</v>
       </c>
       <c r="U80">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V80">
-        <v>0.09764773959932654</v>
+        <v>0.1041404451367274</v>
       </c>
       <c r="W80">
-        <v>0.2171006343817869</v>
+        <v>0.2021006343817869</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2871992341156663</v>
+        <v>0.3062954268727277</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2445092508579777</v>
+        <v>0.2323035741962153</v>
       </c>
       <c r="C81">
-        <v>-3829.589097928532</v>
+        <v>-3647.302614553892</v>
       </c>
       <c r="D81">
-        <v>2791.923902071468</v>
+        <v>2974.210385446109</v>
       </c>
       <c r="E81">
         <v>4692.913</v>
@@ -7923,37 +7923,37 @@
         <v>508.5</v>
       </c>
       <c r="M81">
-        <v>1793.247229070996</v>
+        <v>1681.446034070996</v>
       </c>
       <c r="N81">
-        <v>-1284.747229070996</v>
+        <v>-1172.946034070996</v>
       </c>
       <c r="O81">
-        <v>-436.8140578841385</v>
+        <v>-398.8016515841385</v>
       </c>
       <c r="P81">
-        <v>-847.9331711868572</v>
+        <v>-774.1443824868571</v>
       </c>
       <c r="Q81">
-        <v>-804.9331711868572</v>
+        <v>-731.1443824868571</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3464991190063665</v>
+        <v>0.3448054206170219</v>
       </c>
       <c r="T81">
-        <v>3.918523689721467</v>
+        <v>3.897042986948473</v>
       </c>
       <c r="U81">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V81">
-        <v>0.09641169226262622</v>
+        <v>0.1028222116539841</v>
       </c>
       <c r="W81">
-        <v>0.2173980200843554</v>
+        <v>0.2023980200843554</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.28356380077243</v>
+        <v>0.3024182695705413</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2464571919068247</v>
+        <v>0.2341015152450623</v>
       </c>
       <c r="C82">
-        <v>-3951.039552942633</v>
+        <v>-3770.047978385119</v>
       </c>
       <c r="D82">
-        <v>2764.820447057368</v>
+        <v>2945.812021614882</v>
       </c>
       <c r="E82">
         <v>4787.260000000001</v>
@@ -8005,37 +8005,37 @@
         <v>508.5</v>
       </c>
       <c r="M82">
-        <v>1815.946561084553</v>
+        <v>1702.730161084553</v>
       </c>
       <c r="N82">
-        <v>-1307.446561084553</v>
+        <v>-1194.230161084553</v>
       </c>
       <c r="O82">
-        <v>-444.531830768748</v>
+        <v>-406.0382547687479</v>
       </c>
       <c r="P82">
-        <v>-862.9147303158047</v>
+        <v>-788.1919063158048</v>
       </c>
       <c r="Q82">
-        <v>-819.9147303158047</v>
+        <v>-745.1919063158048</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3615340749566848</v>
+        <v>0.359755691647873</v>
       </c>
       <c r="T82">
-        <v>4.11444987420754</v>
+        <v>4.091895136295896</v>
       </c>
       <c r="U82">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V82">
-        <v>0.09520654610934337</v>
+        <v>0.1015369340083093</v>
       </c>
       <c r="W82">
-        <v>0.2176879711443597</v>
+        <v>0.2026879711443597</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2800192532627747</v>
+        <v>0.2986380412009095</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2484051329556718</v>
+        <v>0.2358994562939094</v>
       </c>
       <c r="C83">
-        <v>-4071.968837226085</v>
+        <v>-3892.256164624705</v>
       </c>
       <c r="D83">
-        <v>2738.238162773916</v>
+        <v>2917.950835375296</v>
       </c>
       <c r="E83">
         <v>4881.607000000001</v>
@@ -8087,37 +8087,37 @@
         <v>508.5</v>
       </c>
       <c r="M83">
-        <v>1838.64589309811</v>
+        <v>1724.01428809811</v>
       </c>
       <c r="N83">
-        <v>-1330.14589309811</v>
+        <v>-1215.51428809811</v>
       </c>
       <c r="O83">
-        <v>-452.2496036533573</v>
+        <v>-413.2748579533573</v>
       </c>
       <c r="P83">
-        <v>-877.8962894447523</v>
+        <v>-802.2394301447523</v>
       </c>
       <c r="Q83">
-        <v>-834.8962894447523</v>
+        <v>-759.2394301447523</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3781516578491419</v>
+        <v>0.3762796754188137</v>
       </c>
       <c r="T83">
-        <v>4.330999867586884</v>
+        <v>4.307258038206207</v>
       </c>
       <c r="U83">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V83">
-        <v>0.09403115665120335</v>
+        <v>0.1002833916131449</v>
       </c>
       <c r="W83">
-        <v>0.2179707629189319</v>
+        <v>0.2029707629189318</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2765622254447156</v>
+        <v>0.2949511518033675</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2503530740045188</v>
+        <v>0.2376973973427564</v>
       </c>
       <c r="C84">
-        <v>-4192.391839968872</v>
+        <v>-4013.942272179499</v>
       </c>
       <c r="D84">
-        <v>2712.16216003113</v>
+        <v>2890.611727820502</v>
       </c>
       <c r="E84">
         <v>4975.954000000002</v>
@@ -8169,37 +8169,37 @@
         <v>508.5</v>
       </c>
       <c r="M84">
-        <v>1861.345225111667</v>
+        <v>1745.298415111667</v>
       </c>
       <c r="N84">
-        <v>-1352.845225111667</v>
+        <v>-1236.798415111667</v>
       </c>
       <c r="O84">
-        <v>-459.9673765379667</v>
+        <v>-420.5114611379666</v>
       </c>
       <c r="P84">
-        <v>-892.8778485737</v>
+        <v>-816.2869539737</v>
       </c>
       <c r="Q84">
-        <v>-849.8778485737</v>
+        <v>-773.2869539737</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.396615638840761</v>
+        <v>0.3946396573865256</v>
       </c>
       <c r="T84">
-        <v>4.571610971341712</v>
+        <v>4.546550151439885</v>
       </c>
       <c r="U84">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V84">
-        <v>0.09288443522862769</v>
+        <v>0.09906042342274073</v>
       </c>
       <c r="W84">
-        <v>0.2182466573331485</v>
+        <v>0.2032466573331485</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2731895153783167</v>
+        <v>0.2913541865374727</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2523010150533658</v>
+        <v>0.2394953383916034</v>
       </c>
       <c r="C85">
-        <v>-4312.32288855715</v>
+        <v>-4135.120839345146</v>
       </c>
       <c r="D85">
-        <v>2686.578111442852</v>
+        <v>2863.780160654855</v>
       </c>
       <c r="E85">
         <v>5070.301000000001</v>
@@ -8251,37 +8251,37 @@
         <v>508.5</v>
       </c>
       <c r="M85">
-        <v>1884.044557125223</v>
+        <v>1766.582542125223</v>
       </c>
       <c r="N85">
-        <v>-1375.544557125223</v>
+        <v>-1258.082542125223</v>
       </c>
       <c r="O85">
-        <v>-467.685149422576</v>
+        <v>-427.748064322576</v>
       </c>
       <c r="P85">
-        <v>-907.8594077026474</v>
+        <v>-830.3344778026474</v>
       </c>
       <c r="Q85">
-        <v>-864.8594077026474</v>
+        <v>-787.3344778026474</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.4172518528902174</v>
+        <v>0.4151596372327919</v>
       </c>
       <c r="T85">
-        <v>4.840529263773576</v>
+        <v>4.813994277995174</v>
       </c>
       <c r="U85">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V85">
-        <v>0.09176534564755988</v>
+        <v>0.09786692434535832</v>
       </c>
       <c r="W85">
-        <v>0.2185159036891914</v>
+        <v>0.2035159036891913</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2698980754339997</v>
+        <v>0.2878438951334068</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2542489561022128</v>
+        <v>0.2412932794404504</v>
       </c>
       <c r="C86">
-        <v>-4431.775774823363</v>
+        <v>-4255.805869585634</v>
       </c>
       <c r="D86">
-        <v>2661.472225176637</v>
+        <v>2837.442130414366</v>
       </c>
       <c r="E86">
         <v>5164.648</v>
@@ -8333,37 +8333,37 @@
         <v>508.5</v>
       </c>
       <c r="M86">
-        <v>1906.74388913878</v>
+        <v>1787.86666913878</v>
       </c>
       <c r="N86">
-        <v>-1398.24388913878</v>
+        <v>-1279.36666913878</v>
       </c>
       <c r="O86">
-        <v>-475.4029223071853</v>
+        <v>-434.9846675071852</v>
       </c>
       <c r="P86">
-        <v>-922.840966831595</v>
+        <v>-844.3820016315948</v>
       </c>
       <c r="Q86">
-        <v>-879.840966831595</v>
+        <v>-801.3820016315948</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4404675936958559</v>
+        <v>0.4382446145598411</v>
       </c>
       <c r="T86">
-        <v>5.143062342759423</v>
+        <v>5.114868920369869</v>
       </c>
       <c r="U86">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V86">
-        <v>0.0906729010565175</v>
+        <v>0.0967018419126755</v>
       </c>
       <c r="W86">
-        <v>0.2187787394177093</v>
+        <v>0.2037787394177093</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2666850031074044</v>
+        <v>0.2844171820961043</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2561968971510598</v>
+        <v>0.2430912204892974</v>
       </c>
       <c r="C87">
-        <v>-4550.763779838117</v>
+        <v>-4376.01085590326</v>
       </c>
       <c r="D87">
-        <v>2636.831220161884</v>
+        <v>2811.584144096741</v>
       </c>
       <c r="E87">
         <v>5258.995000000001</v>
@@ -8415,37 +8415,37 @@
         <v>508.5</v>
       </c>
       <c r="M87">
-        <v>1929.443221152337</v>
+        <v>1809.150796152337</v>
       </c>
       <c r="N87">
-        <v>-1420.943221152337</v>
+        <v>-1300.650796152337</v>
       </c>
       <c r="O87">
-        <v>-483.1206951917948</v>
+        <v>-442.2212706917946</v>
       </c>
       <c r="P87">
-        <v>-937.8225259605426</v>
+        <v>-858.4295254605424</v>
       </c>
       <c r="Q87">
-        <v>-894.8225259605426</v>
+        <v>-815.4295254605424</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4667787666089129</v>
+        <v>0.4644075888638305</v>
       </c>
       <c r="T87">
-        <v>5.485933165610051</v>
+        <v>5.45586018172786</v>
       </c>
       <c r="U87">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V87">
-        <v>0.08960616104408788</v>
+        <v>0.09556417318429107</v>
       </c>
       <c r="W87">
-        <v>0.2190353907761445</v>
+        <v>0.2040353907761445</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2635475324826114</v>
+        <v>0.281071097600856</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2581448381999068</v>
+        <v>0.2448891615381444</v>
       </c>
       <c r="C88">
-        <v>-4669.299697337487</v>
+        <v>-4495.748803888092</v>
       </c>
       <c r="D88">
-        <v>2612.642302662513</v>
+        <v>2786.193196111908</v>
       </c>
       <c r="E88">
         <v>5353.342000000001</v>
@@ -8497,37 +8497,37 @@
         <v>508.5</v>
       </c>
       <c r="M88">
-        <v>1952.142553165894</v>
+        <v>1830.434923165894</v>
       </c>
       <c r="N88">
-        <v>-1443.642553165894</v>
+        <v>-1321.934923165894</v>
       </c>
       <c r="O88">
-        <v>-490.8384680764041</v>
+        <v>-449.4578738764041</v>
       </c>
       <c r="P88">
-        <v>-952.8040850894902</v>
+        <v>-872.4770492894901</v>
       </c>
       <c r="Q88">
-        <v>-909.8040850894902</v>
+        <v>-829.4770492894901</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4968486785095496</v>
+        <v>0.4943081309255327</v>
       </c>
       <c r="T88">
-        <v>5.877785534582198</v>
+        <v>5.845564480422707</v>
       </c>
       <c r="U88">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V88">
-        <v>0.08856422893892409</v>
+        <v>0.09445296186819466</v>
       </c>
       <c r="W88">
-        <v>0.219286073498337</v>
+        <v>0.204286073498337</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2604830262909531</v>
+        <v>0.2778028290241019</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2600927792487538</v>
+        <v>0.2466871025869914</v>
       </c>
       <c r="C89">
-        <v>-4787.395855872608</v>
+        <v>-4615.032253529695</v>
       </c>
       <c r="D89">
-        <v>2588.893144127392</v>
+        <v>2761.256746470306</v>
       </c>
       <c r="E89">
         <v>5447.689</v>
@@ -8579,37 +8579,37 @@
         <v>508.5</v>
       </c>
       <c r="M89">
-        <v>1974.841885179451</v>
+        <v>1851.719050179451</v>
       </c>
       <c r="N89">
-        <v>-1466.341885179451</v>
+        <v>-1343.219050179451</v>
       </c>
       <c r="O89">
-        <v>-498.5562409610134</v>
+        <v>-456.6944770610133</v>
       </c>
       <c r="P89">
-        <v>-967.7856442184377</v>
+        <v>-886.5245731184376</v>
       </c>
       <c r="Q89">
-        <v>-924.7856442184377</v>
+        <v>-843.5245731184376</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5315447307025918</v>
+        <v>0.5288087563813429</v>
       </c>
       <c r="T89">
-        <v>6.329922883396213</v>
+        <v>6.29522328660907</v>
       </c>
       <c r="U89">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V89">
-        <v>0.08754624929594794</v>
+        <v>0.0933672956398246</v>
       </c>
       <c r="W89">
-        <v>0.2195309933993297</v>
+        <v>0.2045309933993297</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2574889685174939</v>
+        <v>0.2746096930583076</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2620407202976008</v>
+        <v>0.2484850436358385</v>
       </c>
       <c r="C90">
-        <v>-4905.06413976208</v>
+        <v>-4733.873299867935</v>
       </c>
       <c r="D90">
-        <v>2565.571860237919</v>
+        <v>2736.762700132064</v>
       </c>
       <c r="E90">
         <v>5542.036</v>
@@ -8661,37 +8661,37 @@
         <v>508.5</v>
       </c>
       <c r="M90">
-        <v>1997.541217193008</v>
+        <v>1873.003177193008</v>
       </c>
       <c r="N90">
-        <v>-1489.041217193008</v>
+        <v>-1364.503177193008</v>
       </c>
       <c r="O90">
-        <v>-506.2740138456227</v>
+        <v>-463.9310802456227</v>
       </c>
       <c r="P90">
-        <v>-982.7672033473852</v>
+        <v>-900.572096947385</v>
       </c>
       <c r="Q90">
-        <v>-939.7672033473852</v>
+        <v>-857.572096947385</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5720234582611412</v>
+        <v>0.5690594860797882</v>
       </c>
       <c r="T90">
-        <v>6.857416457012566</v>
+        <v>6.819825227159826</v>
       </c>
       <c r="U90">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V90">
-        <v>0.08655140555394852</v>
+        <v>0.09230630364391751</v>
       </c>
       <c r="W90">
-        <v>0.2197703469389362</v>
+        <v>0.2047703469389362</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2545629575116133</v>
+        <v>0.2714891283644633</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2639886613464478</v>
+        <v>0.2502829846846855</v>
       </c>
       <c r="C91">
-        <v>-5022.316008922029</v>
+        <v>-4852.283612554361</v>
       </c>
       <c r="D91">
-        <v>2542.666991077972</v>
+        <v>2712.699387445641</v>
       </c>
       <c r="E91">
         <v>5636.383000000002</v>
@@ -8743,37 +8743,37 @@
         <v>508.5</v>
       </c>
       <c r="M91">
-        <v>2020.240549206565</v>
+        <v>1894.287304206565</v>
       </c>
       <c r="N91">
-        <v>-1511.740549206565</v>
+        <v>-1385.787304206565</v>
       </c>
       <c r="O91">
-        <v>-513.9917867302322</v>
+        <v>-471.1676834302322</v>
       </c>
       <c r="P91">
-        <v>-997.748762476333</v>
+        <v>-914.6196207763329</v>
       </c>
       <c r="Q91">
-        <v>-954.748762476333</v>
+        <v>-871.6196207763329</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.6198619544666996</v>
+        <v>0.6166285302688599</v>
       </c>
       <c r="T91">
-        <v>7.480817953104618</v>
+        <v>7.439809338719811</v>
       </c>
       <c r="U91">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V91">
-        <v>0.08557891785109516</v>
+        <v>0.09126915416477235</v>
       </c>
       <c r="W91">
-        <v>0.2200043217473156</v>
+        <v>0.2050043217473156</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2517026995620446</v>
+        <v>0.2684386887199187</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2659366023952949</v>
+        <v>0.2520809257335325</v>
       </c>
       <c r="C92">
-        <v>-5139.162517643324</v>
+        <v>-4970.27445439057</v>
       </c>
       <c r="D92">
-        <v>2520.167482356677</v>
+        <v>2689.055545609431</v>
       </c>
       <c r="E92">
         <v>5730.730000000001</v>
@@ -8825,37 +8825,37 @@
         <v>508.5</v>
       </c>
       <c r="M92">
-        <v>2042.939881220122</v>
+        <v>1915.571431220122</v>
       </c>
       <c r="N92">
-        <v>-1534.439881220122</v>
+        <v>-1407.071431220122</v>
       </c>
       <c r="O92">
-        <v>-521.7095596148415</v>
+        <v>-478.4042866148415</v>
       </c>
       <c r="P92">
-        <v>-1012.730321605281</v>
+        <v>-928.6671446052804</v>
       </c>
       <c r="Q92">
-        <v>-969.7303216052806</v>
+        <v>-885.6671446052804</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6772681499133695</v>
+        <v>0.6737113832957459</v>
       </c>
       <c r="T92">
-        <v>8.228899748415079</v>
+        <v>8.183790272591793</v>
       </c>
       <c r="U92">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V92">
-        <v>0.08462804098608299</v>
+        <v>0.09025505245183044</v>
       </c>
       <c r="W92">
-        <v>0.2202330971155088</v>
+        <v>0.2052330971155088</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2489060029002441</v>
+        <v>0.2654560366230307</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2678845434441419</v>
+        <v>0.2538788667823795</v>
       </c>
       <c r="C93">
-        <v>-5255.61433238063</v>
+        <v>-5087.856698905514</v>
       </c>
       <c r="D93">
-        <v>2498.062667619371</v>
+        <v>2665.820301094487</v>
       </c>
       <c r="E93">
         <v>5825.077000000001</v>
@@ -8907,37 +8907,37 @@
         <v>508.5</v>
       </c>
       <c r="M93">
-        <v>2065.639213233679</v>
+        <v>1936.855558233679</v>
       </c>
       <c r="N93">
-        <v>-1557.139213233679</v>
+        <v>-1428.355558233679</v>
       </c>
       <c r="O93">
-        <v>-529.4273324994508</v>
+        <v>-485.6408897994508</v>
       </c>
       <c r="P93">
-        <v>-1027.711880734228</v>
+        <v>-942.7146684342279</v>
       </c>
       <c r="Q93">
-        <v>-984.7118807342279</v>
+        <v>-899.7146684342279</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7474312776815218</v>
+        <v>0.7434793147730511</v>
       </c>
       <c r="T93">
-        <v>9.143221942683423</v>
+        <v>9.093100302879771</v>
       </c>
       <c r="U93">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V93">
-        <v>0.08369806251370847</v>
+        <v>0.08926323868862351</v>
       </c>
       <c r="W93">
-        <v>0.2204568444536318</v>
+        <v>0.2054568444536318</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2461707720991425</v>
+        <v>0.262538937319481</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2698324844929889</v>
+        <v>0.2556768078312265</v>
       </c>
       <c r="C94">
-        <v>-5371.681748613393</v>
+        <v>-5205.040847029291</v>
       </c>
       <c r="D94">
-        <v>2476.342251386607</v>
+        <v>2642.983152970709</v>
       </c>
       <c r="E94">
         <v>5919.424000000001</v>
@@ -8989,37 +8989,37 @@
         <v>508.5</v>
       </c>
       <c r="M94">
-        <v>2088.338545247236</v>
+        <v>1958.139685247236</v>
       </c>
       <c r="N94">
-        <v>-1579.838545247236</v>
+        <v>-1449.639685247236</v>
       </c>
       <c r="O94">
-        <v>-537.1451053840602</v>
+        <v>-492.8774929840601</v>
       </c>
       <c r="P94">
-        <v>-1042.693439863176</v>
+        <v>-956.7621922631754</v>
       </c>
       <c r="Q94">
-        <v>-999.6934398631756</v>
+        <v>-913.7621922631754</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8351351873917122</v>
+        <v>0.8306892291196828</v>
       </c>
       <c r="T94">
-        <v>10.28612468551885</v>
+        <v>10.22973784073975</v>
       </c>
       <c r="U94">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V94">
-        <v>0.08278830096464641</v>
+        <v>0.08829298609418196</v>
       </c>
       <c r="W94">
-        <v>0.2206757277191869</v>
+        <v>0.2056757277191869</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2434950028371953</v>
+        <v>0.2596852532181823</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2717804255418359</v>
+        <v>0.2574747488800735</v>
       </c>
       <c r="C95">
-        <v>-5487.374706834793</v>
+        <v>-5321.837042917221</v>
       </c>
       <c r="D95">
-        <v>2454.996293165207</v>
+        <v>2620.53395708278</v>
       </c>
       <c r="E95">
         <v>6013.771000000001</v>
@@ -9071,37 +9071,37 @@
         <v>508.5</v>
       </c>
       <c r="M95">
-        <v>2111.037877260792</v>
+        <v>1979.423812260792</v>
       </c>
       <c r="N95">
-        <v>-1602.537877260792</v>
+        <v>-1470.923812260792</v>
       </c>
       <c r="O95">
-        <v>-544.8628782686694</v>
+        <v>-500.1140961686694</v>
       </c>
       <c r="P95">
-        <v>-1057.674998992123</v>
+        <v>-970.8097160921229</v>
       </c>
       <c r="Q95">
-        <v>-1014.674998992123</v>
+        <v>-927.8097160921229</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.9478973570190997</v>
+        <v>0.942816261851066</v>
       </c>
       <c r="T95">
-        <v>11.7555710691644</v>
+        <v>11.69112896084542</v>
       </c>
       <c r="U95">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V95">
-        <v>0.08189810418008034</v>
+        <v>0.08734359914693271</v>
       </c>
       <c r="W95">
-        <v>0.2208899038177408</v>
+        <v>0.2058899038177408</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2408767770002362</v>
+        <v>0.2568929386674491</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2737283665906829</v>
+        <v>0.2592726899289206</v>
       </c>
       <c r="C96">
-        <v>-5602.702807720807</v>
+        <v>-5438.255088974239</v>
       </c>
       <c r="D96">
-        <v>2434.015192279193</v>
+        <v>2598.462911025762</v>
       </c>
       <c r="E96">
         <v>6108.118</v>
@@ -9153,37 +9153,37 @@
         <v>508.5</v>
       </c>
       <c r="M96">
-        <v>2133.737209274349</v>
+        <v>2000.707939274349</v>
       </c>
       <c r="N96">
-        <v>-1625.237209274349</v>
+        <v>-1492.207939274349</v>
       </c>
       <c r="O96">
-        <v>-552.5806511532788</v>
+        <v>-507.3506993532787</v>
       </c>
       <c r="P96">
-        <v>-1072.656558121071</v>
+        <v>-984.8572399210705</v>
       </c>
       <c r="Q96">
-        <v>-1029.656558121071</v>
+        <v>-941.8572399210705</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.098246916522283</v>
+        <v>1.092318972159577</v>
       </c>
       <c r="T96">
-        <v>13.71483291402514</v>
+        <v>13.63965045431966</v>
       </c>
       <c r="U96">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V96">
-        <v>0.08102684775263266</v>
+        <v>0.08641441192196532</v>
       </c>
       <c r="W96">
-        <v>0.2210995229780276</v>
+        <v>0.2060995229780276</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2383142580959784</v>
+        <v>0.2541600350646039</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2756763076395299</v>
+        <v>0.2610706309777676</v>
       </c>
       <c r="C97">
-        <v>-5717.675326528049</v>
+        <v>-5554.304460126403</v>
       </c>
       <c r="D97">
-        <v>2413.389673471952</v>
+        <v>2576.760539873599</v>
       </c>
       <c r="E97">
         <v>6202.465000000002</v>
@@ -9235,37 +9235,37 @@
         <v>508.5</v>
       </c>
       <c r="M97">
-        <v>2156.436541287906</v>
+        <v>2021.992066287906</v>
       </c>
       <c r="N97">
-        <v>-1647.936541287906</v>
+        <v>-1513.492066287906</v>
       </c>
       <c r="O97">
-        <v>-560.2984240378883</v>
+        <v>-514.5873025378883</v>
       </c>
       <c r="P97">
-        <v>-1087.638117250018</v>
+        <v>-998.9047637500182</v>
       </c>
       <c r="Q97">
-        <v>-1044.638117250018</v>
+        <v>-955.9047637500182</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.308736299826741</v>
+        <v>1.301622766591493</v>
       </c>
       <c r="T97">
-        <v>16.45779949683018</v>
+        <v>16.3675805451836</v>
       </c>
       <c r="U97">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V97">
-        <v>0.08017393356576284</v>
+        <v>0.08550478653331306</v>
       </c>
       <c r="W97">
-        <v>0.221304729103361</v>
+        <v>0.206304729103361</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.235805686958126</v>
+        <v>0.2514846662744501</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2776242486883769</v>
+        <v>0.2628685720266146</v>
       </c>
       <c r="C98">
-        <v>-5832.301226765696</v>
+        <v>-5669.994317383138</v>
       </c>
       <c r="D98">
-        <v>2393.110773234304</v>
+        <v>2555.417682616861</v>
       </c>
       <c r="E98">
         <v>6296.812</v>
@@ -9317,37 +9317,37 @@
         <v>508.5</v>
       </c>
       <c r="M98">
-        <v>2179.135873301463</v>
+        <v>2043.276193301463</v>
       </c>
       <c r="N98">
-        <v>-1670.635873301463</v>
+        <v>-1534.776193301463</v>
       </c>
       <c r="O98">
-        <v>-568.0161969224974</v>
+        <v>-521.8239057224974</v>
       </c>
       <c r="P98">
-        <v>-1102.619676378966</v>
+        <v>-1012.952287578965</v>
       </c>
       <c r="Q98">
-        <v>-1059.619676378966</v>
+        <v>-969.9522875789654</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.624470374783422</v>
+        <v>1.615578458239364</v>
       </c>
       <c r="T98">
-        <v>20.57224937103768</v>
+        <v>20.45947568147946</v>
       </c>
       <c r="U98">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V98">
-        <v>0.07933878842445283</v>
+        <v>0.08461411167359105</v>
       </c>
       <c r="W98">
-        <v>0.2215056601010833</v>
+        <v>0.2065056601010833</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2333493777189789</v>
+        <v>0.2488650343340914</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.279572189737224</v>
+        <v>0.2646665130754616</v>
       </c>
       <c r="C99">
-        <v>-5946.589173183921</v>
+        <v>-5785.333520731041</v>
       </c>
       <c r="D99">
-        <v>2373.169826816079</v>
+        <v>2534.425479268958</v>
       </c>
       <c r="E99">
         <v>6391.159</v>
@@ -9399,37 +9399,37 @@
         <v>508.5</v>
       </c>
       <c r="M99">
-        <v>2201.83520531502</v>
+        <v>2064.56032031502</v>
       </c>
       <c r="N99">
-        <v>-1693.33520531502</v>
+        <v>-1556.06032031502</v>
       </c>
       <c r="O99">
-        <v>-575.7339698071067</v>
+        <v>-529.0605089071069</v>
       </c>
       <c r="P99">
-        <v>-1117.601235507913</v>
+        <v>-1026.999811407913</v>
       </c>
       <c r="Q99">
-        <v>-1074.601235507913</v>
+        <v>-983.9998114079131</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.150693833044563</v>
+        <v>2.138837944319151</v>
       </c>
       <c r="T99">
-        <v>27.42966582805024</v>
+        <v>27.27930090863929</v>
       </c>
       <c r="U99">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V99">
-        <v>0.07852086277059249</v>
+        <v>0.08374180124396641</v>
       </c>
       <c r="W99">
-        <v>0.2217024481916361</v>
+        <v>0.2067024481916361</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2309437140311543</v>
+        <v>0.2462994154234306</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.281520130786071</v>
+        <v>0.2664644541243086</v>
       </c>
       <c r="C100">
-        <v>-6060.547544118277</v>
+        <v>-5900.330641397302</v>
       </c>
       <c r="D100">
-        <v>2353.558455881724</v>
+        <v>2513.775358602699</v>
       </c>
       <c r="E100">
         <v>6485.506000000001</v>
@@ -9481,37 +9481,37 @@
         <v>508.5</v>
       </c>
       <c r="M100">
-        <v>2224.534537328577</v>
+        <v>2085.844447328577</v>
       </c>
       <c r="N100">
-        <v>-1716.034537328577</v>
+        <v>-1577.344447328577</v>
       </c>
       <c r="O100">
-        <v>-583.4517426917163</v>
+        <v>-536.2971120917163</v>
       </c>
       <c r="P100">
-        <v>-1132.582794636861</v>
+        <v>-1041.047335236861</v>
       </c>
       <c r="Q100">
-        <v>-1089.582794636861</v>
+        <v>-998.0473352368608</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.203140749566844</v>
+        <v>3.185356916478726</v>
       </c>
       <c r="T100">
-        <v>41.14449874207536</v>
+        <v>40.91895136295892</v>
       </c>
       <c r="U100">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V100">
-        <v>0.077719629477015</v>
+        <v>0.08288729306800756</v>
       </c>
       <c r="W100">
-        <v>0.2218952201987082</v>
+        <v>0.2068952201987082</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2285871455206323</v>
+        <v>0.2437861560823751</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.283468071834918</v>
+        <v>0.2682623951731556</v>
       </c>
       <c r="C101">
-        <v>-6174.184443227053</v>
+        <v>-6014.993973518487</v>
       </c>
       <c r="D101">
-        <v>2334.268556772948</v>
+        <v>2493.459026481514</v>
       </c>
       <c r="E101">
         <v>6579.853000000001</v>
@@ -9563,37 +9563,37 @@
         <v>508.5</v>
       </c>
       <c r="M101">
-        <v>2247.233869342134</v>
+        <v>2107.128574342134</v>
       </c>
       <c r="N101">
-        <v>-1738.733869342134</v>
+        <v>-1598.628574342134</v>
       </c>
       <c r="O101">
-        <v>-591.1695155763256</v>
+        <v>-543.5337152763256</v>
       </c>
       <c r="P101">
-        <v>-1147.564353765808</v>
+        <v>-1055.094859065809</v>
       </c>
       <c r="Q101">
-        <v>-1104.564353765808</v>
+        <v>-1012.094859065809</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.360481499133689</v>
+        <v>6.324913832957453</v>
       </c>
       <c r="T101">
-        <v>82.28899748415071</v>
+        <v>81.83790272591784</v>
       </c>
       <c r="U101">
-        <v>0.2405941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V101">
-        <v>0.07693458271462092</v>
+        <v>0.08205004768348223</v>
       </c>
       <c r="W101">
-        <v>0.222084097821799</v>
+        <v>0.207084097821799</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2262781844547674</v>
+        <v>0.2413236696573007</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/brazil/brazil_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_aerospace_defense.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1141425747298138</v>
+        <v>0.1139478310679715</v>
       </c>
       <c r="C2">
-        <v>8948.375995968287</v>
+        <v>8877.223164174959</v>
       </c>
       <c r="D2">
-        <v>8116.475995968286</v>
+        <v>8139.670164174959</v>
       </c>
       <c r="E2">
-        <v>-2760.5</v>
+        <v>-2666.153</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>94.34700000000001</v>
       </c>
       <c r="G2">
         <v>831.9</v>
@@ -1445,28 +1445,28 @@
         <v>508.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.084903513556907</v>
       </c>
       <c r="N2">
-        <v>508.5</v>
+        <v>501.4150964864431</v>
       </c>
       <c r="O2">
-        <v>172.89</v>
+        <v>170.4811328053907</v>
       </c>
       <c r="P2">
-        <v>335.61</v>
+        <v>330.9339636810524</v>
       </c>
       <c r="Q2">
-        <v>378.61</v>
+        <v>373.9339636810524</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1141425747298138</v>
+        <v>0.1145981918946792</v>
       </c>
       <c r="T2">
-        <v>0.8907328536426571</v>
+        <v>0.8966710726669415</v>
       </c>
       <c r="U2">
         <v>0.07509410488470122</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>71.77232534317359</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1139478310679715</v>
+        <v>0.1137530874061291</v>
       </c>
       <c r="C3">
-        <v>8877.223164174959</v>
+        <v>8806.203274604633</v>
       </c>
       <c r="D3">
-        <v>8139.670164174959</v>
+        <v>8162.997274604632</v>
       </c>
       <c r="E3">
-        <v>-2666.153</v>
+        <v>-2571.806</v>
       </c>
       <c r="F3">
-        <v>94.34700000000001</v>
+        <v>188.694</v>
       </c>
       <c r="G3">
         <v>831.9</v>
@@ -1527,28 +1527,28 @@
         <v>508.5</v>
       </c>
       <c r="M3">
-        <v>7.084903513556907</v>
+        <v>14.16980702711381</v>
       </c>
       <c r="N3">
-        <v>501.4150964864431</v>
+        <v>494.3301929728862</v>
       </c>
       <c r="O3">
-        <v>170.4811328053907</v>
+        <v>168.0722656107813</v>
       </c>
       <c r="P3">
-        <v>330.9339636810524</v>
+        <v>326.2579273621049</v>
       </c>
       <c r="Q3">
-        <v>373.9339636810524</v>
+        <v>369.2579273621049</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1145981918946792</v>
+        <v>0.1150631073690317</v>
       </c>
       <c r="T3">
-        <v>0.8966710726669415</v>
+        <v>0.9027304798345785</v>
       </c>
       <c r="U3">
         <v>0.07509410488470122</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>71.77232534317359</v>
+        <v>35.8861626715868</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1137530874061291</v>
+        <v>0.1135583437442868</v>
       </c>
       <c r="C4">
-        <v>8806.203274604633</v>
+        <v>8735.317473521547</v>
       </c>
       <c r="D4">
-        <v>8162.997274604632</v>
+        <v>8186.458473521546</v>
       </c>
       <c r="E4">
-        <v>-2571.806</v>
+        <v>-2477.459</v>
       </c>
       <c r="F4">
-        <v>188.694</v>
+        <v>283.041</v>
       </c>
       <c r="G4">
         <v>831.9</v>
@@ -1609,28 +1609,28 @@
         <v>508.5</v>
       </c>
       <c r="M4">
-        <v>14.16980702711381</v>
+        <v>21.25471054067072</v>
       </c>
       <c r="N4">
-        <v>494.3301929728862</v>
+        <v>487.2452894593293</v>
       </c>
       <c r="O4">
-        <v>168.0722656107813</v>
+        <v>165.663398416172</v>
       </c>
       <c r="P4">
-        <v>326.2579273621049</v>
+        <v>321.5818910431573</v>
       </c>
       <c r="Q4">
-        <v>369.2579273621049</v>
+        <v>364.5818910431573</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1150631073690317</v>
+        <v>0.1155376087294533</v>
       </c>
       <c r="T4">
-        <v>0.9027304798345785</v>
+        <v>0.9089148232324764</v>
       </c>
       <c r="U4">
         <v>0.07509410488470122</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.8861626715868</v>
+        <v>23.92410844772453</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1135583437442868</v>
+        <v>0.1133636000824445</v>
       </c>
       <c r="C5">
-        <v>8735.317473521547</v>
+        <v>8664.566920405794</v>
       </c>
       <c r="D5">
-        <v>8186.458473521546</v>
+        <v>8210.054920405795</v>
       </c>
       <c r="E5">
-        <v>-2477.459</v>
+        <v>-2383.112</v>
       </c>
       <c r="F5">
-        <v>283.041</v>
+        <v>377.388</v>
       </c>
       <c r="G5">
         <v>831.9</v>
@@ -1691,28 +1691,28 @@
         <v>508.5</v>
       </c>
       <c r="M5">
-        <v>21.25471054067072</v>
+        <v>28.33961405422763</v>
       </c>
       <c r="N5">
-        <v>487.2452894593293</v>
+        <v>480.1603859457724</v>
       </c>
       <c r="O5">
-        <v>165.663398416172</v>
+        <v>163.2545312215626</v>
       </c>
       <c r="P5">
-        <v>321.5818910431573</v>
+        <v>316.9058547242097</v>
       </c>
       <c r="Q5">
-        <v>364.5818910431573</v>
+        <v>359.9058547242097</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1155376087294533</v>
+        <v>0.1160219955348837</v>
       </c>
       <c r="T5">
-        <v>0.9089148232324764</v>
+        <v>0.9152280071178303</v>
       </c>
       <c r="U5">
         <v>0.07509410488470122</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.92410844772453</v>
+        <v>17.9430813357934</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1133636000824445</v>
+        <v>0.1131688564206021</v>
       </c>
       <c r="C6">
-        <v>8664.566920405794</v>
+        <v>8593.95278814433</v>
       </c>
       <c r="D6">
-        <v>8210.054920405795</v>
+        <v>8233.787788144331</v>
       </c>
       <c r="E6">
-        <v>-2383.112</v>
+        <v>-2288.765</v>
       </c>
       <c r="F6">
-        <v>377.388</v>
+        <v>471.7350000000001</v>
       </c>
       <c r="G6">
         <v>831.9</v>
@@ -1773,28 +1773,28 @@
         <v>508.5</v>
       </c>
       <c r="M6">
-        <v>28.33961405422763</v>
+        <v>35.42451756778453</v>
       </c>
       <c r="N6">
-        <v>480.1603859457724</v>
+        <v>473.0754824322155</v>
       </c>
       <c r="O6">
-        <v>163.2545312215626</v>
+        <v>160.8456640269533</v>
       </c>
       <c r="P6">
-        <v>316.9058547242097</v>
+        <v>312.2298184052622</v>
       </c>
       <c r="Q6">
-        <v>359.9058547242097</v>
+        <v>355.2298184052622</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1160219955348837</v>
+        <v>0.1165165799572705</v>
       </c>
       <c r="T6">
-        <v>0.9152280071178303</v>
+        <v>0.9216741001376125</v>
       </c>
       <c r="U6">
         <v>0.07509410488470122</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.9430813357934</v>
+        <v>14.35446506863472</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1131688564206021</v>
+        <v>0.1129741127587598</v>
       </c>
       <c r="C7">
-        <v>8593.95278814433</v>
+        <v>8523.476263225326</v>
       </c>
       <c r="D7">
-        <v>8233.787788144331</v>
+        <v>8257.658263225327</v>
       </c>
       <c r="E7">
-        <v>-2288.765</v>
+        <v>-2194.418</v>
       </c>
       <c r="F7">
-        <v>471.7350000000001</v>
+        <v>566.0820000000001</v>
       </c>
       <c r="G7">
         <v>831.9</v>
@@ -1855,28 +1855,28 @@
         <v>508.5</v>
       </c>
       <c r="M7">
-        <v>35.42451756778453</v>
+        <v>42.50942108134144</v>
       </c>
       <c r="N7">
-        <v>473.0754824322155</v>
+        <v>465.9905789186586</v>
       </c>
       <c r="O7">
-        <v>160.8456640269533</v>
+        <v>158.4367968323439</v>
       </c>
       <c r="P7">
-        <v>312.2298184052622</v>
+        <v>307.5537820863146</v>
       </c>
       <c r="Q7">
-        <v>355.2298184052622</v>
+        <v>350.5537820863146</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1165165799572705</v>
+        <v>0.1170216874524741</v>
       </c>
       <c r="T7">
-        <v>0.9216741001376125</v>
+        <v>0.9282573440727095</v>
       </c>
       <c r="U7">
         <v>0.07509410488470122</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>14.35446506863472</v>
+        <v>11.96205422386226</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1129741127587598</v>
+        <v>0.1127793690969175</v>
       </c>
       <c r="C8">
-        <v>8523.476263225326</v>
+        <v>8453.138545935892</v>
       </c>
       <c r="D8">
-        <v>8257.658263225327</v>
+        <v>8281.667545935892</v>
       </c>
       <c r="E8">
-        <v>-2194.418</v>
+        <v>-2100.071</v>
       </c>
       <c r="F8">
-        <v>566.082</v>
+        <v>660.429</v>
       </c>
       <c r="G8">
         <v>831.9</v>
@@ -1937,28 +1937,28 @@
         <v>508.5</v>
       </c>
       <c r="M8">
-        <v>42.50942108134144</v>
+        <v>49.59432459489835</v>
       </c>
       <c r="N8">
-        <v>465.9905789186586</v>
+        <v>458.9056754051016</v>
       </c>
       <c r="O8">
-        <v>158.4367968323439</v>
+        <v>156.0279296377346</v>
       </c>
       <c r="P8">
-        <v>307.5537820863146</v>
+        <v>302.8777457673671</v>
       </c>
       <c r="Q8">
-        <v>350.5537820863146</v>
+        <v>345.8777457673671</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1170216874524741</v>
+        <v>0.1175376574744562</v>
       </c>
       <c r="T8">
-        <v>0.9282573440727095</v>
+        <v>0.9349821631461954</v>
       </c>
       <c r="U8">
         <v>0.07509410488470122</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.96205422386227</v>
+        <v>10.25318933473909</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1127793690969174</v>
+        <v>0.1125846254350751</v>
       </c>
       <c r="C9">
-        <v>8453.138545935892</v>
+        <v>8382.940850563262</v>
       </c>
       <c r="D9">
-        <v>8281.667545935892</v>
+        <v>8305.816850563262</v>
       </c>
       <c r="E9">
-        <v>-2100.071</v>
+        <v>-2005.724</v>
       </c>
       <c r="F9">
-        <v>660.4290000000001</v>
+        <v>754.7760000000001</v>
       </c>
       <c r="G9">
         <v>831.9</v>
@@ -2019,28 +2019,28 @@
         <v>508.5</v>
       </c>
       <c r="M9">
-        <v>49.59432459489835</v>
+        <v>56.67922810845526</v>
       </c>
       <c r="N9">
-        <v>458.9056754051016</v>
+        <v>451.8207718915447</v>
       </c>
       <c r="O9">
-        <v>156.0279296377346</v>
+        <v>153.6190624431252</v>
       </c>
       <c r="P9">
-        <v>302.8777457673671</v>
+        <v>298.2017094484195</v>
       </c>
       <c r="Q9">
-        <v>345.8777457673671</v>
+        <v>341.2017094484195</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1175376574744562</v>
+        <v>0.1180648442360466</v>
       </c>
       <c r="T9">
-        <v>0.9349821631461956</v>
+        <v>0.9418531739386704</v>
       </c>
       <c r="U9">
         <v>0.07509410488470122</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.25318933473908</v>
+        <v>8.971540667896697</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1125846254350751</v>
+        <v>0.1124789817732328</v>
       </c>
       <c r="C10">
-        <v>8382.940850563262</v>
+        <v>8301.753273268147</v>
       </c>
       <c r="D10">
-        <v>8305.816850563262</v>
+        <v>8318.976273268147</v>
       </c>
       <c r="E10">
-        <v>-2005.724</v>
+        <v>-1911.377</v>
       </c>
       <c r="F10">
-        <v>754.7760000000001</v>
+        <v>849.123</v>
       </c>
       <c r="G10">
         <v>831.9</v>
@@ -2101,45 +2101,45 @@
         <v>508.5</v>
       </c>
       <c r="M10">
-        <v>56.67922810845526</v>
+        <v>65.03781612201216</v>
       </c>
       <c r="N10">
-        <v>451.8207718915447</v>
+        <v>443.4621838779879</v>
       </c>
       <c r="O10">
-        <v>153.6190624431252</v>
+        <v>150.7771425185159</v>
       </c>
       <c r="P10">
-        <v>298.2017094484195</v>
+        <v>292.6850413594719</v>
       </c>
       <c r="Q10">
-        <v>341.2017094484195</v>
+        <v>335.6850413594719</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1180648442360466</v>
+        <v>0.1186036175198698</v>
       </c>
       <c r="T10">
-        <v>0.9418531739386704</v>
+        <v>0.9488751959573536</v>
       </c>
       <c r="U10">
-        <v>0.07509410488470122</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V10">
         <v>0.34</v>
       </c>
       <c r="W10">
-        <v>0.0495621092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.971540667896697</v>
+        <v>7.818528208973753</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1124789817732328</v>
+        <v>0.1122941381113904</v>
       </c>
       <c r="C11">
-        <v>8301.753273268147</v>
+        <v>8230.531770955693</v>
       </c>
       <c r="D11">
-        <v>8318.976273268147</v>
+        <v>8342.101770955693</v>
       </c>
       <c r="E11">
-        <v>-1911.377</v>
+        <v>-1817.03</v>
       </c>
       <c r="F11">
-        <v>849.123</v>
+        <v>943.47</v>
       </c>
       <c r="G11">
         <v>831.9</v>
@@ -2183,28 +2183,28 @@
         <v>508.5</v>
       </c>
       <c r="M11">
-        <v>65.03781612201216</v>
+        <v>72.26424013556907</v>
       </c>
       <c r="N11">
-        <v>443.4621838779879</v>
+        <v>436.2357598644309</v>
       </c>
       <c r="O11">
-        <v>150.7771425185159</v>
+        <v>148.3201583539065</v>
       </c>
       <c r="P11">
-        <v>292.6850413594719</v>
+        <v>287.9156015105244</v>
       </c>
       <c r="Q11">
-        <v>335.6850413594719</v>
+        <v>330.9156015105244</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1186036175198698</v>
+        <v>0.1191543635433335</v>
       </c>
       <c r="T11">
-        <v>0.9488751959573536</v>
+        <v>0.9560532629097852</v>
       </c>
       <c r="U11">
         <v>0.07659410488470123</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.818528208973753</v>
+        <v>7.036675388076377</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1122941381113904</v>
+        <v>0.1122327144495481</v>
       </c>
       <c r="C12">
-        <v>8230.531770955693</v>
+        <v>8143.897874996063</v>
       </c>
       <c r="D12">
-        <v>8342.101770955693</v>
+        <v>8349.814874996064</v>
       </c>
       <c r="E12">
-        <v>-1817.03</v>
+        <v>-1722.683</v>
       </c>
       <c r="F12">
-        <v>943.4700000000001</v>
+        <v>1037.817</v>
       </c>
       <c r="G12">
         <v>831.9</v>
@@ -2265,45 +2265,45 @@
         <v>508.5</v>
       </c>
       <c r="M12">
-        <v>72.26424013556908</v>
+        <v>81.25495304912596</v>
       </c>
       <c r="N12">
-        <v>436.2357598644309</v>
+        <v>427.245046950874</v>
       </c>
       <c r="O12">
-        <v>148.3201583539065</v>
+        <v>145.2633159632972</v>
       </c>
       <c r="P12">
-        <v>287.9156015105244</v>
+        <v>281.9817309875768</v>
       </c>
       <c r="Q12">
-        <v>330.9156015105244</v>
+        <v>324.9817309875768</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1191543635433335</v>
+        <v>0.1197174858819312</v>
       </c>
       <c r="T12">
-        <v>0.9560532629097852</v>
+        <v>0.9633926347375524</v>
       </c>
       <c r="U12">
-        <v>0.07659410488470123</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V12">
         <v>0.34</v>
       </c>
       <c r="W12">
-        <v>0.0505521092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.036675388076376</v>
+        <v>6.258080042118365</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1122327144495481</v>
+        <v>0.1120590907877058</v>
       </c>
       <c r="C13">
-        <v>8143.897874996063</v>
+        <v>8071.430520748331</v>
       </c>
       <c r="D13">
-        <v>8349.814874996064</v>
+        <v>8371.694520748331</v>
       </c>
       <c r="E13">
-        <v>-1722.683</v>
+        <v>-1628.336</v>
       </c>
       <c r="F13">
-        <v>1037.817</v>
+        <v>1132.164</v>
       </c>
       <c r="G13">
         <v>831.9</v>
@@ -2347,28 +2347,28 @@
         <v>508.5</v>
       </c>
       <c r="M13">
-        <v>81.25495304912596</v>
+        <v>88.64176696268287</v>
       </c>
       <c r="N13">
-        <v>427.245046950874</v>
+        <v>419.8582330373171</v>
       </c>
       <c r="O13">
-        <v>145.2633159632972</v>
+        <v>142.7517992326878</v>
       </c>
       <c r="P13">
-        <v>281.9817309875768</v>
+        <v>277.1064338046293</v>
       </c>
       <c r="Q13">
-        <v>324.9817309875768</v>
+        <v>320.1064338046293</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1197174858819312</v>
+        <v>0.1202934064554971</v>
       </c>
       <c r="T13">
-        <v>0.9633926347375524</v>
+        <v>0.9708988104704963</v>
       </c>
       <c r="U13">
         <v>0.07829410488470122</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.258080042118365</v>
+        <v>5.736573371941835</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1120590907877058</v>
+        <v>0.1119541071258634</v>
       </c>
       <c r="C14">
-        <v>8071.430520748331</v>
+        <v>7990.369032182132</v>
       </c>
       <c r="D14">
-        <v>8371.694520748331</v>
+        <v>8384.980032182133</v>
       </c>
       <c r="E14">
-        <v>-1628.336</v>
+        <v>-1533.989</v>
       </c>
       <c r="F14">
-        <v>1132.164</v>
+        <v>1226.511</v>
       </c>
       <c r="G14">
         <v>831.9</v>
@@ -2429,45 +2429,45 @@
         <v>508.5</v>
       </c>
       <c r="M14">
-        <v>88.64176696268287</v>
+        <v>97.00978967623981</v>
       </c>
       <c r="N14">
-        <v>419.8582330373171</v>
+        <v>411.4902103237602</v>
       </c>
       <c r="O14">
-        <v>142.7517992326878</v>
+        <v>139.9066715100785</v>
       </c>
       <c r="P14">
-        <v>277.1064338046293</v>
+        <v>271.5835388136817</v>
       </c>
       <c r="Q14">
-        <v>320.1064338046293</v>
+        <v>314.5835388136817</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1202934064554971</v>
+        <v>0.1208825665824782</v>
       </c>
       <c r="T14">
-        <v>0.9708988104704963</v>
+        <v>0.9785775419674158</v>
       </c>
       <c r="U14">
-        <v>0.07829410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V14">
         <v>0.34</v>
       </c>
       <c r="W14">
-        <v>0.05167410922390279</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>5.736573371941835</v>
+        <v>5.241739021361313</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1119541071258634</v>
+        <v>0.1117857634640211</v>
       </c>
       <c r="C15">
-        <v>7990.369032182132</v>
+        <v>7917.41389262279</v>
       </c>
       <c r="D15">
-        <v>8384.980032182133</v>
+        <v>8406.37189262279</v>
       </c>
       <c r="E15">
-        <v>-1533.989</v>
+        <v>-1439.642</v>
       </c>
       <c r="F15">
-        <v>1226.511</v>
+        <v>1320.858</v>
       </c>
       <c r="G15">
         <v>831.9</v>
@@ -2511,28 +2511,28 @@
         <v>508.5</v>
       </c>
       <c r="M15">
-        <v>97.00978967623981</v>
+        <v>104.4720811897967</v>
       </c>
       <c r="N15">
-        <v>411.4902103237602</v>
+        <v>404.0279188102033</v>
       </c>
       <c r="O15">
-        <v>139.9066715100785</v>
+        <v>137.3694923954691</v>
       </c>
       <c r="P15">
-        <v>271.5835388136817</v>
+        <v>266.6584264147342</v>
       </c>
       <c r="Q15">
-        <v>314.5835388136817</v>
+        <v>309.6584264147342</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1208825665824782</v>
+        <v>0.1214854281077613</v>
       </c>
       <c r="T15">
-        <v>0.9785775419674158</v>
+        <v>0.9864348486154262</v>
       </c>
       <c r="U15">
         <v>0.07909410488470123</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.241739021361313</v>
+        <v>4.867329091264076</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1117857634640211</v>
+        <v>0.1116174198021787</v>
       </c>
       <c r="C16">
-        <v>7917.41389262279</v>
+        <v>7844.568182577123</v>
       </c>
       <c r="D16">
-        <v>8406.37189262279</v>
+        <v>8427.873182577123</v>
       </c>
       <c r="E16">
-        <v>-1439.642</v>
+        <v>-1345.295</v>
       </c>
       <c r="F16">
-        <v>1320.858</v>
+        <v>1415.205</v>
       </c>
       <c r="G16">
         <v>831.9</v>
@@ -2593,28 +2593,28 @@
         <v>508.5</v>
       </c>
       <c r="M16">
-        <v>104.4720811897967</v>
+        <v>111.9343727033536</v>
       </c>
       <c r="N16">
-        <v>404.0279188102033</v>
+        <v>396.5656272966464</v>
       </c>
       <c r="O16">
-        <v>137.3694923954691</v>
+        <v>134.8323132808598</v>
       </c>
       <c r="P16">
-        <v>266.6584264147342</v>
+        <v>261.7333140157866</v>
       </c>
       <c r="Q16">
-        <v>309.6584264147342</v>
+        <v>304.7333140157866</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1214854281077613</v>
+        <v>0.1221024746101098</v>
       </c>
       <c r="T16">
-        <v>0.9864348486154262</v>
+        <v>0.9944770330669195</v>
       </c>
       <c r="U16">
         <v>0.07909410488470123</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.867329091264076</v>
+        <v>4.542840485179804</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1116174198021787</v>
+        <v>0.1114490761403364</v>
       </c>
       <c r="C17">
-        <v>7844.568182577123</v>
+        <v>7771.832743874116</v>
       </c>
       <c r="D17">
-        <v>8427.873182577123</v>
+        <v>8449.484743874116</v>
       </c>
       <c r="E17">
-        <v>-1345.295</v>
+        <v>-1250.948</v>
       </c>
       <c r="F17">
-        <v>1415.205</v>
+        <v>1509.552</v>
       </c>
       <c r="G17">
         <v>831.9</v>
@@ -2675,28 +2675,28 @@
         <v>508.5</v>
       </c>
       <c r="M17">
-        <v>111.9343727033536</v>
+        <v>119.3966642169105</v>
       </c>
       <c r="N17">
-        <v>396.5656272966464</v>
+        <v>389.1033357830895</v>
       </c>
       <c r="O17">
-        <v>134.8323132808598</v>
+        <v>132.2951341662504</v>
       </c>
       <c r="P17">
-        <v>261.7333140157866</v>
+        <v>256.808201616839</v>
       </c>
       <c r="Q17">
-        <v>304.7333140157866</v>
+        <v>299.808201616839</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1221024746101098</v>
+        <v>0.1227342126958476</v>
       </c>
       <c r="T17">
-        <v>0.9944770330669195</v>
+        <v>1.002710698100591</v>
       </c>
       <c r="U17">
         <v>0.07909410488470123</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.542840485179804</v>
+        <v>4.258912954856067</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1114490761403364</v>
+        <v>0.111392932478494</v>
       </c>
       <c r="C18">
-        <v>7771.832743874116</v>
+        <v>7684.718001928101</v>
       </c>
       <c r="D18">
-        <v>8449.484743874116</v>
+        <v>8456.717001928102</v>
       </c>
       <c r="E18">
-        <v>-1250.948</v>
+        <v>-1156.601</v>
       </c>
       <c r="F18">
-        <v>1509.552</v>
+        <v>1603.899</v>
       </c>
       <c r="G18">
         <v>831.9</v>
@@ -2757,45 +2757,45 @@
         <v>508.5</v>
       </c>
       <c r="M18">
-        <v>119.3966642169105</v>
+        <v>128.4628547304675</v>
       </c>
       <c r="N18">
-        <v>389.1033357830895</v>
+        <v>380.0371452695325</v>
       </c>
       <c r="O18">
-        <v>132.2951341662504</v>
+        <v>129.2126293916411</v>
       </c>
       <c r="P18">
-        <v>256.808201616839</v>
+        <v>250.8245158778915</v>
       </c>
       <c r="Q18">
-        <v>299.808201616839</v>
+        <v>293.8245158778915</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1227342126958476</v>
+        <v>0.1233811733860609</v>
       </c>
       <c r="T18">
-        <v>1.002710698100591</v>
+        <v>1.011142764701339</v>
       </c>
       <c r="U18">
-        <v>0.07909410488470123</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V18">
         <v>0.34</v>
       </c>
       <c r="W18">
-        <v>0.0522021092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.258912954856067</v>
+        <v>3.958342674751407</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.111392932478494</v>
+        <v>0.1112311888166517</v>
       </c>
       <c r="C19">
-        <v>7684.718001928101</v>
+        <v>7611.275717244966</v>
       </c>
       <c r="D19">
-        <v>8456.717001928102</v>
+        <v>8477.621717244967</v>
       </c>
       <c r="E19">
-        <v>-1156.601</v>
+        <v>-1062.254</v>
       </c>
       <c r="F19">
-        <v>1603.899</v>
+        <v>1698.246</v>
       </c>
       <c r="G19">
         <v>831.9</v>
@@ -2839,28 +2839,28 @@
         <v>508.5</v>
       </c>
       <c r="M19">
-        <v>128.4628547304675</v>
+        <v>136.0194932440243</v>
       </c>
       <c r="N19">
-        <v>380.0371452695325</v>
+        <v>372.4805067559756</v>
       </c>
       <c r="O19">
-        <v>129.2126293916411</v>
+        <v>126.6433722970317</v>
       </c>
       <c r="P19">
-        <v>250.8245158778915</v>
+        <v>245.8371344589439</v>
       </c>
       <c r="Q19">
-        <v>293.8245158778915</v>
+        <v>288.8371344589439</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1233811733860609</v>
+        <v>0.1240439136053039</v>
       </c>
       <c r="T19">
-        <v>1.011142764701339</v>
+        <v>1.019780491463081</v>
       </c>
       <c r="U19">
         <v>0.08009410488470123</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.958342674751407</v>
+        <v>3.738434748376329</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1112311888166517</v>
+        <v>0.1110694451548094</v>
       </c>
       <c r="C20">
-        <v>7611.275717244965</v>
+        <v>7537.937040159449</v>
       </c>
       <c r="D20">
-        <v>8477.621717244965</v>
+        <v>8498.630040159449</v>
       </c>
       <c r="E20">
-        <v>-1062.254</v>
+        <v>-967.9069999999999</v>
       </c>
       <c r="F20">
-        <v>1698.246</v>
+        <v>1792.593</v>
       </c>
       <c r="G20">
         <v>831.9</v>
@@ -2921,28 +2921,28 @@
         <v>508.5</v>
       </c>
       <c r="M20">
-        <v>136.0194932440243</v>
+        <v>143.5761317575812</v>
       </c>
       <c r="N20">
-        <v>372.4805067559757</v>
+        <v>364.9238682424187</v>
       </c>
       <c r="O20">
-        <v>126.6433722970317</v>
+        <v>124.0741152024224</v>
       </c>
       <c r="P20">
-        <v>245.8371344589439</v>
+        <v>240.8497530399964</v>
       </c>
       <c r="Q20">
-        <v>288.8371344589439</v>
+        <v>283.8497530399964</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1240439136053039</v>
+        <v>0.1247230177805776</v>
       </c>
       <c r="T20">
-        <v>1.019780491463081</v>
+        <v>1.028631495428816</v>
       </c>
       <c r="U20">
         <v>0.08009410488470123</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.73843474837633</v>
+        <v>3.541675024777576</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1110694451548094</v>
+        <v>0.110907701492967</v>
       </c>
       <c r="C21">
-        <v>7537.937040159449</v>
+        <v>7464.702742832374</v>
       </c>
       <c r="D21">
-        <v>8498.630040159449</v>
+        <v>8519.742742832375</v>
       </c>
       <c r="E21">
-        <v>-967.9069999999999</v>
+        <v>-873.5599999999997</v>
       </c>
       <c r="F21">
-        <v>1792.593</v>
+        <v>1886.94</v>
       </c>
       <c r="G21">
         <v>831.9</v>
@@ -3003,28 +3003,28 @@
         <v>508.5</v>
       </c>
       <c r="M21">
-        <v>143.5761317575812</v>
+        <v>151.1327702711382</v>
       </c>
       <c r="N21">
-        <v>364.9238682424187</v>
+        <v>357.3672297288618</v>
       </c>
       <c r="O21">
-        <v>124.0741152024224</v>
+        <v>121.504858107813</v>
       </c>
       <c r="P21">
-        <v>240.8497530399964</v>
+        <v>235.8623716210488</v>
       </c>
       <c r="Q21">
-        <v>283.8497530399964</v>
+        <v>278.8623716210488</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1247230177805776</v>
+        <v>0.1254190995602331</v>
       </c>
       <c r="T21">
-        <v>1.028631495428816</v>
+        <v>1.037703774493695</v>
       </c>
       <c r="U21">
         <v>0.08009410488470123</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.541675024777576</v>
+        <v>3.364591273538696</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.110907701492967</v>
+        <v>0.1107459578311247</v>
       </c>
       <c r="C22">
-        <v>7464.702742832374</v>
+        <v>7391.573605116635</v>
       </c>
       <c r="D22">
-        <v>8519.742742832375</v>
+        <v>8540.960605116636</v>
       </c>
       <c r="E22">
-        <v>-873.5599999999997</v>
+        <v>-779.2129999999997</v>
       </c>
       <c r="F22">
-        <v>1886.94</v>
+        <v>1981.287</v>
       </c>
       <c r="G22">
         <v>831.9</v>
@@ -3085,28 +3085,28 @@
         <v>508.5</v>
       </c>
       <c r="M22">
-        <v>151.1327702711382</v>
+        <v>158.6894087846951</v>
       </c>
       <c r="N22">
-        <v>357.3672297288618</v>
+        <v>349.810591215305</v>
       </c>
       <c r="O22">
-        <v>121.504858107813</v>
+        <v>118.9356010132037</v>
       </c>
       <c r="P22">
-        <v>235.8623716210488</v>
+        <v>230.8749902021013</v>
       </c>
       <c r="Q22">
-        <v>278.8623716210488</v>
+        <v>273.8749902021012</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1254190995602331</v>
+        <v>0.1261328036634242</v>
       </c>
       <c r="T22">
-        <v>1.037703774493695</v>
+        <v>1.047005731509584</v>
       </c>
       <c r="U22">
         <v>0.08009410488470123</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.364591273538696</v>
+        <v>3.204372641465425</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1107459578311247</v>
+        <v>0.1105842141692824</v>
       </c>
       <c r="C23">
-        <v>7391.573605116639</v>
+        <v>7318.550414653217</v>
       </c>
       <c r="D23">
-        <v>8540.960605116639</v>
+        <v>8562.284414653217</v>
       </c>
       <c r="E23">
-        <v>-779.213</v>
+        <v>-684.866</v>
       </c>
       <c r="F23">
-        <v>1981.287</v>
+        <v>2075.634</v>
       </c>
       <c r="G23">
         <v>831.9</v>
@@ -3167,28 +3167,28 @@
         <v>508.5</v>
       </c>
       <c r="M23">
-        <v>158.689408784695</v>
+        <v>166.2460472982519</v>
       </c>
       <c r="N23">
-        <v>349.810591215305</v>
+        <v>342.2539527017481</v>
       </c>
       <c r="O23">
-        <v>118.9356010132037</v>
+        <v>116.3663439185944</v>
       </c>
       <c r="P23">
-        <v>230.8749902021013</v>
+        <v>225.8876087831537</v>
       </c>
       <c r="Q23">
-        <v>273.8749902021012</v>
+        <v>268.8876087831537</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1261328036634242</v>
+        <v>0.1268648078718253</v>
       </c>
       <c r="T23">
-        <v>1.047005731509584</v>
+        <v>1.056546200243829</v>
       </c>
       <c r="U23">
         <v>0.08009410488470123</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.204372641465426</v>
+        <v>3.058719339580634</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1105842141692824</v>
+        <v>0.11080197050744</v>
       </c>
       <c r="C24">
-        <v>7318.550414653217</v>
+        <v>7195.519796512968</v>
       </c>
       <c r="D24">
-        <v>8562.284414653217</v>
+        <v>8533.600796512968</v>
       </c>
       <c r="E24">
-        <v>-684.866</v>
+        <v>-590.5189999999998</v>
       </c>
       <c r="F24">
-        <v>2075.634</v>
+        <v>2169.981</v>
       </c>
       <c r="G24">
         <v>831.9</v>
@@ -3249,45 +3249,45 @@
         <v>508.5</v>
       </c>
       <c r="M24">
-        <v>166.2460472982519</v>
+        <v>179.2276383118089</v>
       </c>
       <c r="N24">
-        <v>342.2539527017481</v>
+        <v>329.2723616881912</v>
       </c>
       <c r="O24">
-        <v>116.3663439185944</v>
+        <v>111.952602973985</v>
       </c>
       <c r="P24">
-        <v>225.8876087831537</v>
+        <v>217.3197587142062</v>
       </c>
       <c r="Q24">
-        <v>268.8876087831537</v>
+        <v>260.3197587142062</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1268648078718253</v>
+        <v>0.1276158251765485</v>
       </c>
       <c r="T24">
-        <v>1.056546200243829</v>
+        <v>1.066334473360781</v>
       </c>
       <c r="U24">
-        <v>0.08009410488470123</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.0528621092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.058719339580634</v>
+        <v>2.837174025109587</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.11080197050744</v>
+        <v>0.1106567268455977</v>
       </c>
       <c r="C25">
-        <v>7195.519796512968</v>
+        <v>7120.283403672295</v>
       </c>
       <c r="D25">
-        <v>8533.600796512968</v>
+        <v>8552.711403672296</v>
       </c>
       <c r="E25">
-        <v>-590.5189999999998</v>
+        <v>-496.1719999999996</v>
       </c>
       <c r="F25">
-        <v>2169.981</v>
+        <v>2264.328</v>
       </c>
       <c r="G25">
         <v>831.9</v>
@@ -3331,28 +3331,28 @@
         <v>508.5</v>
       </c>
       <c r="M25">
-        <v>179.2276383118089</v>
+        <v>187.0201443253658</v>
       </c>
       <c r="N25">
-        <v>329.2723616881912</v>
+        <v>321.4798556746342</v>
       </c>
       <c r="O25">
-        <v>111.952602973985</v>
+        <v>109.3031509293756</v>
       </c>
       <c r="P25">
-        <v>217.3197587142062</v>
+        <v>212.1767047452586</v>
       </c>
       <c r="Q25">
-        <v>260.3197587142062</v>
+        <v>255.1767047452586</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1276158251765485</v>
+        <v>0.128386606094554</v>
       </c>
       <c r="T25">
-        <v>1.066334473360781</v>
+        <v>1.07638033261239</v>
       </c>
       <c r="U25">
         <v>0.08259410488470123</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.837174025109587</v>
+        <v>2.718958440730021</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1106567268455977</v>
+        <v>0.1105114831837553</v>
       </c>
       <c r="C26">
-        <v>7120.283403672298</v>
+        <v>7045.132797601683</v>
       </c>
       <c r="D26">
-        <v>8552.711403672298</v>
+        <v>8571.907797601683</v>
       </c>
       <c r="E26">
-        <v>-496.172</v>
+        <v>-401.8249999999998</v>
       </c>
       <c r="F26">
-        <v>2264.328</v>
+        <v>2358.675</v>
       </c>
       <c r="G26">
         <v>831.9</v>
@@ -3413,28 +3413,28 @@
         <v>508.5</v>
       </c>
       <c r="M26">
-        <v>187.0201443253658</v>
+        <v>194.8126503389227</v>
       </c>
       <c r="N26">
-        <v>321.4798556746342</v>
+        <v>313.6873496610773</v>
       </c>
       <c r="O26">
-        <v>109.3031509293756</v>
+        <v>106.6536988847663</v>
       </c>
       <c r="P26">
-        <v>212.1767047452586</v>
+        <v>207.033650776311</v>
       </c>
       <c r="Q26">
-        <v>255.1767047452586</v>
+        <v>250.033650776311</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.128386606094554</v>
+        <v>0.1291779411703728</v>
       </c>
       <c r="T26">
-        <v>1.07638033261239</v>
+        <v>1.086694081444042</v>
       </c>
       <c r="U26">
         <v>0.08259410488470123</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.718958440730021</v>
+        <v>2.61020010310082</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1105114831837553</v>
+        <v>0.110366239521913</v>
       </c>
       <c r="C27">
-        <v>7045.132797601683</v>
+        <v>6970.068557240733</v>
       </c>
       <c r="D27">
-        <v>8571.907797601683</v>
+        <v>8591.190557240734</v>
       </c>
       <c r="E27">
-        <v>-401.8249999999998</v>
+        <v>-307.4779999999996</v>
       </c>
       <c r="F27">
-        <v>2358.675</v>
+        <v>2453.022</v>
       </c>
       <c r="G27">
         <v>831.9</v>
@@ -3495,28 +3495,28 @@
         <v>508.5</v>
       </c>
       <c r="M27">
-        <v>194.8126503389227</v>
+        <v>202.6051563524796</v>
       </c>
       <c r="N27">
-        <v>313.6873496610773</v>
+        <v>305.8948436475204</v>
       </c>
       <c r="O27">
-        <v>106.6536988847663</v>
+        <v>104.0042468401569</v>
       </c>
       <c r="P27">
-        <v>207.033650776311</v>
+        <v>201.8905968073634</v>
       </c>
       <c r="Q27">
-        <v>250.033650776311</v>
+        <v>244.8905968073634</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1291779411703728</v>
+        <v>0.1299906636806734</v>
       </c>
       <c r="T27">
-        <v>1.086694081444042</v>
+        <v>1.097286580244117</v>
       </c>
       <c r="U27">
         <v>0.08259410488470123</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.61020010310082</v>
+        <v>2.509807791443096</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.110366239521913</v>
+        <v>0.1108446958600707</v>
       </c>
       <c r="C28">
-        <v>6970.068557240733</v>
+        <v>6812.526403199659</v>
       </c>
       <c r="D28">
-        <v>8591.190557240734</v>
+        <v>8527.99540319966</v>
       </c>
       <c r="E28">
-        <v>-307.4779999999996</v>
+        <v>-213.1309999999999</v>
       </c>
       <c r="F28">
-        <v>2453.022</v>
+        <v>2547.369</v>
       </c>
       <c r="G28">
         <v>831.9</v>
@@ -3577,45 +3577,45 @@
         <v>508.5</v>
       </c>
       <c r="M28">
-        <v>202.6051563524796</v>
+        <v>219.3134538660365</v>
       </c>
       <c r="N28">
-        <v>305.8948436475204</v>
+        <v>289.1865461339635</v>
       </c>
       <c r="O28">
-        <v>104.0042468401569</v>
+        <v>98.3234256855476</v>
       </c>
       <c r="P28">
-        <v>201.8905968073634</v>
+        <v>190.8631204484159</v>
       </c>
       <c r="Q28">
-        <v>244.8905968073634</v>
+        <v>233.8631204484159</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1299906636806734</v>
+        <v>0.1308256525611191</v>
       </c>
       <c r="T28">
-        <v>1.097286580244117</v>
+        <v>1.108169284490769</v>
       </c>
       <c r="U28">
-        <v>0.08259410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V28">
         <v>0.34</v>
       </c>
       <c r="W28">
-        <v>0.0545121092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.509807791443096</v>
+        <v>2.318599206004971</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1108446958600707</v>
+        <v>0.1112399921982283</v>
       </c>
       <c r="C29">
-        <v>6812.526403199659</v>
+        <v>6666.665256552169</v>
       </c>
       <c r="D29">
-        <v>8527.99540319966</v>
+        <v>8476.48125655217</v>
       </c>
       <c r="E29">
-        <v>-213.1309999999999</v>
+        <v>-118.7839999999997</v>
       </c>
       <c r="F29">
-        <v>2547.369</v>
+        <v>2641.716</v>
       </c>
       <c r="G29">
         <v>831.9</v>
@@ -3659,45 +3659,45 @@
         <v>508.5</v>
       </c>
       <c r="M29">
-        <v>219.3134538660365</v>
+        <v>234.8329791795934</v>
       </c>
       <c r="N29">
-        <v>289.1865461339635</v>
+        <v>273.6670208204066</v>
       </c>
       <c r="O29">
-        <v>98.3234256855476</v>
+        <v>93.04678707893825</v>
       </c>
       <c r="P29">
-        <v>190.8631204484159</v>
+        <v>180.6202337414684</v>
       </c>
       <c r="Q29">
-        <v>233.8631204484159</v>
+        <v>223.6202337414684</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1308256525611191</v>
+        <v>0.1316838355771327</v>
       </c>
       <c r="T29">
-        <v>1.108169284490769</v>
+        <v>1.119354286077606</v>
       </c>
       <c r="U29">
-        <v>0.08609410488470122</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V29">
         <v>0.34</v>
       </c>
       <c r="W29">
-        <v>0.05682210922390279</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.318599206004971</v>
+        <v>2.165368773059401</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1112399921982283</v>
+        <v>0.111136328536386</v>
       </c>
       <c r="C30">
-        <v>6666.665256552169</v>
+        <v>6585.767177026832</v>
       </c>
       <c r="D30">
-        <v>8476.48125655217</v>
+        <v>8489.930177026832</v>
       </c>
       <c r="E30">
-        <v>-118.7839999999997</v>
+        <v>-24.43699999999944</v>
       </c>
       <c r="F30">
-        <v>2641.716</v>
+        <v>2736.063000000001</v>
       </c>
       <c r="G30">
         <v>831.9</v>
@@ -3741,28 +3741,28 @@
         <v>508.5</v>
       </c>
       <c r="M30">
-        <v>234.8329791795934</v>
+        <v>243.2198712931504</v>
       </c>
       <c r="N30">
-        <v>273.6670208204066</v>
+        <v>265.2801287068496</v>
       </c>
       <c r="O30">
-        <v>93.04678707893825</v>
+        <v>90.19524376032888</v>
       </c>
       <c r="P30">
-        <v>180.6202337414684</v>
+        <v>175.0848849465207</v>
       </c>
       <c r="Q30">
-        <v>223.6202337414684</v>
+        <v>218.0848849465207</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1316838355771327</v>
+        <v>0.1325661927626115</v>
       </c>
       <c r="T30">
-        <v>1.119354286077606</v>
+        <v>1.130854358131677</v>
       </c>
       <c r="U30">
         <v>0.08889410488470123</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.165368773059401</v>
+        <v>2.090700884333214</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.111136328536386</v>
+        <v>0.1110326648745437</v>
       </c>
       <c r="C31">
-        <v>6585.767177026832</v>
+        <v>6504.911841864207</v>
       </c>
       <c r="D31">
-        <v>8489.930177026832</v>
+        <v>8503.421841864207</v>
       </c>
       <c r="E31">
-        <v>-24.4369999999999</v>
+        <v>69.91000000000031</v>
       </c>
       <c r="F31">
-        <v>2736.063</v>
+        <v>2830.41</v>
       </c>
       <c r="G31">
         <v>831.9</v>
@@ -3823,28 +3823,28 @@
         <v>508.5</v>
       </c>
       <c r="M31">
-        <v>243.2198712931503</v>
+        <v>251.6067634067072</v>
       </c>
       <c r="N31">
-        <v>265.2801287068497</v>
+        <v>256.8932365932927</v>
       </c>
       <c r="O31">
-        <v>90.19524376032891</v>
+        <v>87.34370044171953</v>
       </c>
       <c r="P31">
-        <v>175.0848849465208</v>
+        <v>169.5495361515732</v>
       </c>
       <c r="Q31">
-        <v>218.0848849465208</v>
+        <v>212.5495361515732</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1325661927626115</v>
+        <v>0.1334737601533897</v>
       </c>
       <c r="T31">
-        <v>1.130854358131677</v>
+        <v>1.142683003673009</v>
       </c>
       <c r="U31">
         <v>0.08889410488470123</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.090700884333215</v>
+        <v>2.02101085485544</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1110326648745437</v>
+        <v>0.1125248812127013</v>
       </c>
       <c r="C32">
-        <v>6504.911841864207</v>
+        <v>6220.396725082892</v>
       </c>
       <c r="D32">
-        <v>8503.421841864207</v>
+        <v>8313.253725082892</v>
       </c>
       <c r="E32">
-        <v>69.91000000000031</v>
+        <v>164.2570000000001</v>
       </c>
       <c r="F32">
-        <v>2830.41</v>
+        <v>2924.757</v>
       </c>
       <c r="G32">
         <v>831.9</v>
@@ -3905,45 +3905,45 @@
         <v>508.5</v>
       </c>
       <c r="M32">
-        <v>251.6067634067072</v>
+        <v>282.8067601202641</v>
       </c>
       <c r="N32">
-        <v>256.8932365932927</v>
+        <v>225.6932398797359</v>
       </c>
       <c r="O32">
-        <v>87.34370044171953</v>
+        <v>76.7357015591102</v>
       </c>
       <c r="P32">
-        <v>169.5495361515732</v>
+        <v>148.9575383206257</v>
       </c>
       <c r="Q32">
-        <v>212.5495361515732</v>
+        <v>191.9575383206257</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1334737601533897</v>
+        <v>0.1344076338453499</v>
       </c>
       <c r="T32">
-        <v>1.142683003673009</v>
+        <v>1.154854508505393</v>
       </c>
       <c r="U32">
-        <v>0.08889410488470123</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V32">
         <v>0.34</v>
       </c>
       <c r="W32">
-        <v>0.0586701092239028</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.02101085485544</v>
+        <v>1.798047542370484</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1125248812127013</v>
+        <v>0.113296377550859</v>
       </c>
       <c r="C33">
-        <v>6220.396725082892</v>
+        <v>6031.027665532446</v>
       </c>
       <c r="D33">
-        <v>8313.253725082892</v>
+        <v>8218.231665532447</v>
       </c>
       <c r="E33">
-        <v>164.2570000000001</v>
+        <v>258.6040000000003</v>
       </c>
       <c r="F33">
-        <v>2924.757</v>
+        <v>3019.104</v>
       </c>
       <c r="G33">
         <v>831.9</v>
@@ -3987,45 +3987,45 @@
         <v>508.5</v>
       </c>
       <c r="M33">
-        <v>282.8067601202641</v>
+        <v>303.704064433821</v>
       </c>
       <c r="N33">
-        <v>225.6932398797359</v>
+        <v>204.795935566179</v>
       </c>
       <c r="O33">
-        <v>76.7357015591102</v>
+        <v>69.63061809250085</v>
       </c>
       <c r="P33">
-        <v>148.9575383206257</v>
+        <v>135.1653174736781</v>
       </c>
       <c r="Q33">
-        <v>191.9575383206257</v>
+        <v>178.1653174736781</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1344076338453499</v>
+        <v>0.1353689744106031</v>
       </c>
       <c r="T33">
-        <v>1.154854508505393</v>
+        <v>1.167383998774024</v>
       </c>
       <c r="U33">
-        <v>0.09669410488470123</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V33">
         <v>0.34</v>
       </c>
       <c r="W33">
-        <v>0.06381810922390281</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.798047542370484</v>
+        <v>1.67432727957714</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.113296377550859</v>
+        <v>0.1132699338890166</v>
       </c>
       <c r="C34">
-        <v>6031.027665532446</v>
+        <v>5939.901657855675</v>
       </c>
       <c r="D34">
-        <v>8218.231665532447</v>
+        <v>8221.452657855676</v>
       </c>
       <c r="E34">
-        <v>258.6040000000003</v>
+        <v>352.9510000000005</v>
       </c>
       <c r="F34">
-        <v>3019.104</v>
+        <v>3113.451</v>
       </c>
       <c r="G34">
         <v>831.9</v>
@@ -4069,28 +4069,28 @@
         <v>508.5</v>
       </c>
       <c r="M34">
-        <v>303.704064433821</v>
+        <v>313.1948164473779</v>
       </c>
       <c r="N34">
-        <v>204.795935566179</v>
+        <v>195.3051835526221</v>
       </c>
       <c r="O34">
-        <v>69.63061809250085</v>
+        <v>66.40376240789151</v>
       </c>
       <c r="P34">
-        <v>135.1653174736781</v>
+        <v>128.9014211447305</v>
       </c>
       <c r="Q34">
-        <v>178.1653174736781</v>
+        <v>171.9014211447305</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1353689744106031</v>
+        <v>0.1363590117091474</v>
       </c>
       <c r="T34">
-        <v>1.167383998774024</v>
+        <v>1.180287503677539</v>
       </c>
       <c r="U34">
         <v>0.1005941048847012</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.67432727957714</v>
+        <v>1.623590089286924</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1132699338890166</v>
+        <v>0.1132434902271743</v>
       </c>
       <c r="C35">
-        <v>5939.901657855675</v>
+        <v>5848.778175992193</v>
       </c>
       <c r="D35">
-        <v>8221.452657855676</v>
+        <v>8224.676175992194</v>
       </c>
       <c r="E35">
-        <v>352.9510000000005</v>
+        <v>447.2980000000007</v>
       </c>
       <c r="F35">
-        <v>3113.451</v>
+        <v>3207.798000000001</v>
       </c>
       <c r="G35">
         <v>831.9</v>
@@ -4151,28 +4151,28 @@
         <v>508.5</v>
       </c>
       <c r="M35">
-        <v>313.1948164473779</v>
+        <v>322.6855684609349</v>
       </c>
       <c r="N35">
-        <v>195.3051835526221</v>
+        <v>185.8144315390651</v>
       </c>
       <c r="O35">
-        <v>66.40376240789151</v>
+        <v>63.17690672328215</v>
       </c>
       <c r="P35">
-        <v>128.9014211447305</v>
+        <v>122.637524815783</v>
       </c>
       <c r="Q35">
-        <v>171.9014211447305</v>
+        <v>165.637524815783</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1363590117091474</v>
+        <v>0.1373790501379505</v>
       </c>
       <c r="T35">
-        <v>1.180287503677539</v>
+        <v>1.193582023881161</v>
       </c>
       <c r="U35">
         <v>0.1005941048847012</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.623590089286924</v>
+        <v>1.575837439602014</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1132434902271743</v>
+        <v>0.1132170465653319</v>
       </c>
       <c r="C36">
-        <v>5848.778175992193</v>
+        <v>5757.657222914168</v>
       </c>
       <c r="D36">
-        <v>8224.676175992194</v>
+        <v>8227.902222914168</v>
       </c>
       <c r="E36">
-        <v>447.2980000000007</v>
+        <v>541.6450000000004</v>
       </c>
       <c r="F36">
-        <v>3207.798000000001</v>
+        <v>3302.145</v>
       </c>
       <c r="G36">
         <v>831.9</v>
@@ -4233,28 +4233,28 @@
         <v>508.5</v>
       </c>
       <c r="M36">
-        <v>322.6855684609349</v>
+        <v>332.1763204744918</v>
       </c>
       <c r="N36">
-        <v>185.8144315390651</v>
+        <v>176.3236795255082</v>
       </c>
       <c r="O36">
-        <v>63.17690672328215</v>
+        <v>59.9500510386728</v>
       </c>
       <c r="P36">
-        <v>122.637524815783</v>
+        <v>116.3736284868354</v>
       </c>
       <c r="Q36">
-        <v>165.637524815783</v>
+        <v>159.3736284868354</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1373790501379505</v>
+        <v>0.138430474364563</v>
       </c>
       <c r="T36">
-        <v>1.193582023881161</v>
+        <v>1.207285606244894</v>
       </c>
       <c r="U36">
         <v>0.1005941048847012</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.575837439602014</v>
+        <v>1.530813512756242</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1132170465653319</v>
+        <v>0.1165645229034896</v>
       </c>
       <c r="C37">
-        <v>5757.657222914168</v>
+        <v>5274.093891427787</v>
       </c>
       <c r="D37">
-        <v>8227.902222914168</v>
+        <v>7838.685891427787</v>
       </c>
       <c r="E37">
-        <v>541.6450000000004</v>
+        <v>635.9920000000006</v>
       </c>
       <c r="F37">
-        <v>3302.145</v>
+        <v>3396.492000000001</v>
       </c>
       <c r="G37">
         <v>831.9</v>
@@ -4315,45 +4315,45 @@
         <v>508.5</v>
       </c>
       <c r="M37">
-        <v>332.1763204744918</v>
+        <v>389.8972588880487</v>
       </c>
       <c r="N37">
-        <v>176.3236795255082</v>
+        <v>118.6027411119513</v>
       </c>
       <c r="O37">
-        <v>59.9500510386728</v>
+        <v>40.32493197806344</v>
       </c>
       <c r="P37">
-        <v>116.3736284868354</v>
+        <v>78.27780913388784</v>
       </c>
       <c r="Q37">
-        <v>159.3736284868354</v>
+        <v>121.2778091338878</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.138430474364563</v>
+        <v>0.1395147555982572</v>
       </c>
       <c r="T37">
-        <v>1.207285606244894</v>
+        <v>1.221417425557494</v>
       </c>
       <c r="U37">
-        <v>0.1005941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V37">
         <v>0.34</v>
       </c>
       <c r="W37">
-        <v>0.06639210922390279</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.530813512756242</v>
+        <v>1.304189727956014</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1165645229034896</v>
+        <v>0.1166317992416473</v>
       </c>
       <c r="C38">
-        <v>5274.093891427787</v>
+        <v>5172.301674895247</v>
       </c>
       <c r="D38">
-        <v>7838.685891427787</v>
+        <v>7831.240674895247</v>
       </c>
       <c r="E38">
-        <v>635.9920000000002</v>
+        <v>730.3390000000004</v>
       </c>
       <c r="F38">
-        <v>3396.492</v>
+        <v>3490.839</v>
       </c>
       <c r="G38">
         <v>831.9</v>
@@ -4397,28 +4397,28 @@
         <v>508.5</v>
       </c>
       <c r="M38">
-        <v>389.8972588880487</v>
+        <v>400.7277383016057</v>
       </c>
       <c r="N38">
-        <v>118.6027411119513</v>
+        <v>107.7722616983943</v>
       </c>
       <c r="O38">
-        <v>40.32493197806345</v>
+        <v>36.64256897745408</v>
       </c>
       <c r="P38">
-        <v>78.27780913388787</v>
+        <v>71.12969272094026</v>
       </c>
       <c r="Q38">
-        <v>121.2778091338879</v>
+        <v>114.1296927209403</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1395147555982572</v>
+        <v>0.1406334584584178</v>
       </c>
       <c r="T38">
-        <v>1.221417425557493</v>
+        <v>1.23599787405462</v>
       </c>
       <c r="U38">
         <v>0.1147941048847012</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.304189727956015</v>
+        <v>1.268941356930176</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1166317992416473</v>
+        <v>0.1241696562399932</v>
       </c>
       <c r="C39">
-        <v>5172.301674895247</v>
+        <v>4324.719619911481</v>
       </c>
       <c r="D39">
-        <v>7831.240674895247</v>
+        <v>7078.005619911481</v>
       </c>
       <c r="E39">
-        <v>730.3390000000004</v>
+        <v>824.6860000000001</v>
       </c>
       <c r="F39">
-        <v>3490.839</v>
+        <v>3585.186</v>
       </c>
       <c r="G39">
         <v>831.9</v>
@@ -4479,45 +4479,45 @@
         <v>508.5</v>
       </c>
       <c r="M39">
-        <v>400.7277383016057</v>
+        <v>514.0945373151625</v>
       </c>
       <c r="N39">
-        <v>107.7722616983943</v>
+        <v>-5.594537315162484</v>
       </c>
       <c r="O39">
-        <v>36.64256897745408</v>
+        <v>-1.902142687155244</v>
       </c>
       <c r="P39">
-        <v>71.12969272094026</v>
+        <v>-3.692394628007239</v>
       </c>
       <c r="Q39">
-        <v>114.1296927209403</v>
+        <v>39.30760537199276</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1406334584584178</v>
+        <v>0.1419432312517418</v>
       </c>
       <c r="T39">
-        <v>1.23599787405462</v>
+        <v>1.253068604304881</v>
       </c>
       <c r="U39">
-        <v>0.1147941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V39">
-        <v>0.34</v>
+        <v>0.3363000138124612</v>
       </c>
       <c r="W39">
-        <v>0.07576410922390281</v>
+        <v>0.09517066543135069</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.268941356930176</v>
+        <v>0.9891176876837094</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1241696562399932</v>
+        <v>0.1251455972888402</v>
       </c>
       <c r="C40">
-        <v>4324.719619911481</v>
+        <v>4143.31402479756</v>
       </c>
       <c r="D40">
-        <v>7078.005619911481</v>
+        <v>6990.947024797561</v>
       </c>
       <c r="E40">
-        <v>824.6860000000001</v>
+        <v>919.0330000000004</v>
       </c>
       <c r="F40">
-        <v>3585.186</v>
+        <v>3679.533</v>
       </c>
       <c r="G40">
         <v>831.9</v>
@@ -4561,37 +4561,37 @@
         <v>508.5</v>
       </c>
       <c r="M40">
-        <v>514.0945373151625</v>
+        <v>527.6233409287194</v>
       </c>
       <c r="N40">
-        <v>-5.594537315162484</v>
+        <v>-19.12334092871936</v>
       </c>
       <c r="O40">
-        <v>-1.902142687155244</v>
+        <v>-6.501935915764582</v>
       </c>
       <c r="P40">
-        <v>-3.692394628007239</v>
+        <v>-12.62140501295478</v>
       </c>
       <c r="Q40">
-        <v>39.30760537199276</v>
+        <v>30.37859498704523</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1419432312517418</v>
+        <v>0.1435193497968523</v>
       </c>
       <c r="T40">
-        <v>1.253068604304881</v>
+        <v>1.273610712572174</v>
       </c>
       <c r="U40">
         <v>0.1433941048847012</v>
       </c>
       <c r="V40">
-        <v>0.3363000138124612</v>
+        <v>0.3276769365352187</v>
       </c>
       <c r="W40">
-        <v>0.09517066543135069</v>
+        <v>0.09640716387887249</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9891176876837094</v>
+        <v>0.9637556956918195</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1251455972888402</v>
+        <v>0.1261215383376872</v>
       </c>
       <c r="C41">
-        <v>4143.31402479756</v>
+        <v>3964.02402802463</v>
       </c>
       <c r="D41">
-        <v>6990.947024797561</v>
+        <v>6906.004028024631</v>
       </c>
       <c r="E41">
-        <v>919.0330000000004</v>
+        <v>1013.380000000001</v>
       </c>
       <c r="F41">
-        <v>3679.533</v>
+        <v>3773.880000000001</v>
       </c>
       <c r="G41">
         <v>831.9</v>
@@ -4643,37 +4643,37 @@
         <v>508.5</v>
       </c>
       <c r="M41">
-        <v>527.6233409287194</v>
+        <v>541.1521445422763</v>
       </c>
       <c r="N41">
-        <v>-19.12334092871936</v>
+        <v>-32.65214454227635</v>
       </c>
       <c r="O41">
-        <v>-6.501935915764582</v>
+        <v>-11.10172914437396</v>
       </c>
       <c r="P41">
-        <v>-12.62140501295478</v>
+        <v>-21.55041539790239</v>
       </c>
       <c r="Q41">
-        <v>30.37859498704523</v>
+        <v>21.44958460209761</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1435193497968523</v>
+        <v>0.1451480056267999</v>
       </c>
       <c r="T41">
-        <v>1.273610712572174</v>
+        <v>1.294837557781711</v>
       </c>
       <c r="U41">
         <v>0.1433941048847012</v>
       </c>
       <c r="V41">
-        <v>0.3276769365352187</v>
+        <v>0.3194850131218381</v>
       </c>
       <c r="W41">
-        <v>0.09640716387887249</v>
+        <v>0.09758183740401823</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9637556956918195</v>
+        <v>0.9396618032995239</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1261215383376872</v>
+        <v>0.1270974793865342</v>
       </c>
       <c r="C42">
-        <v>3964.02402802463</v>
+        <v>3786.773439065775</v>
       </c>
       <c r="D42">
-        <v>6906.004028024631</v>
+        <v>6823.100439065776</v>
       </c>
       <c r="E42">
-        <v>1013.380000000001</v>
+        <v>1107.727000000001</v>
       </c>
       <c r="F42">
-        <v>3773.880000000001</v>
+        <v>3868.227000000001</v>
       </c>
       <c r="G42">
         <v>831.9</v>
@@ -4725,37 +4725,37 @@
         <v>508.5</v>
       </c>
       <c r="M42">
-        <v>541.1521445422763</v>
+        <v>554.6809481558332</v>
       </c>
       <c r="N42">
-        <v>-32.65214454227635</v>
+        <v>-46.18094815583322</v>
       </c>
       <c r="O42">
-        <v>-11.10172914437396</v>
+        <v>-15.7015223729833</v>
       </c>
       <c r="P42">
-        <v>-21.55041539790239</v>
+        <v>-30.47942578284992</v>
       </c>
       <c r="Q42">
-        <v>21.44958460209761</v>
+        <v>12.52057421715008</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1451480056267999</v>
+        <v>0.146831870128949</v>
       </c>
       <c r="T42">
-        <v>1.294837557781711</v>
+        <v>1.316783957066147</v>
       </c>
       <c r="U42">
         <v>0.1433941048847012</v>
       </c>
       <c r="V42">
-        <v>0.3194850131218381</v>
+        <v>0.3116926957286226</v>
       </c>
       <c r="W42">
-        <v>0.09758183740401823</v>
+        <v>0.09869920978159585</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.9396618032995239</v>
+        <v>0.9167432227312429</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1270974793865342</v>
+        <v>0.1280734204353812</v>
       </c>
       <c r="C43">
-        <v>3786.773439065775</v>
+        <v>3611.489682533084</v>
       </c>
       <c r="D43">
-        <v>6823.100439065776</v>
+        <v>6742.163682533085</v>
       </c>
       <c r="E43">
-        <v>1107.727000000001</v>
+        <v>1202.074000000001</v>
       </c>
       <c r="F43">
-        <v>3868.227000000001</v>
+        <v>3962.574000000001</v>
       </c>
       <c r="G43">
         <v>831.9</v>
@@ -4807,37 +4807,37 @@
         <v>508.5</v>
       </c>
       <c r="M43">
-        <v>554.6809481558332</v>
+        <v>568.2097517693901</v>
       </c>
       <c r="N43">
-        <v>-46.18094815583322</v>
+        <v>-59.7097517693901</v>
       </c>
       <c r="O43">
-        <v>-15.7015223729833</v>
+        <v>-20.30131560159263</v>
       </c>
       <c r="P43">
-        <v>-30.47942578284992</v>
+        <v>-39.40843616779746</v>
       </c>
       <c r="Q43">
-        <v>12.52057421715008</v>
+        <v>3.591563832202539</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.146831870128949</v>
+        <v>0.1485737989242757</v>
       </c>
       <c r="T43">
-        <v>1.316783957066147</v>
+        <v>1.339487128739701</v>
       </c>
       <c r="U43">
         <v>0.1433941048847012</v>
       </c>
       <c r="V43">
-        <v>0.3116926957286226</v>
+        <v>0.3042714410684173</v>
       </c>
       <c r="W43">
-        <v>0.09869920978159585</v>
+        <v>0.09976337395071741</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9167432227312429</v>
+        <v>0.8949160031424038</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1280734204353812</v>
+        <v>0.1290493614842282</v>
       </c>
       <c r="C44">
-        <v>3611.489682533085</v>
+        <v>3438.103586274355</v>
       </c>
       <c r="D44">
-        <v>6742.163682533085</v>
+        <v>6663.124586274355</v>
       </c>
       <c r="E44">
-        <v>1202.074</v>
+        <v>1296.421</v>
       </c>
       <c r="F44">
-        <v>3962.574</v>
+        <v>4056.921</v>
       </c>
       <c r="G44">
         <v>831.9</v>
@@ -4889,37 +4889,37 @@
         <v>508.5</v>
       </c>
       <c r="M44">
-        <v>568.2097517693901</v>
+        <v>581.738555382947</v>
       </c>
       <c r="N44">
-        <v>-59.7097517693901</v>
+        <v>-73.23855538294697</v>
       </c>
       <c r="O44">
-        <v>-20.30131560159263</v>
+        <v>-24.90110883020197</v>
       </c>
       <c r="P44">
-        <v>-39.40843616779746</v>
+        <v>-48.337446552745</v>
       </c>
       <c r="Q44">
-        <v>3.591563832202539</v>
+        <v>-5.337446552745</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1485737989242757</v>
+        <v>0.1503768480282104</v>
       </c>
       <c r="T44">
-        <v>1.339487128739701</v>
+        <v>1.362986902928117</v>
       </c>
       <c r="U44">
         <v>0.1433941048847012</v>
       </c>
       <c r="V44">
-        <v>0.3042714410684173</v>
+        <v>0.2971953610435704</v>
       </c>
       <c r="W44">
-        <v>0.09976337395071741</v>
+        <v>0.1007780421119728</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8949160031424038</v>
+        <v>0.8741040030693247</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1290493614842282</v>
+        <v>0.1300253025330752</v>
       </c>
       <c r="C45">
-        <v>3438.103586274355</v>
+        <v>3266.54918420212</v>
       </c>
       <c r="D45">
-        <v>6663.124586274355</v>
+        <v>6585.917184202121</v>
       </c>
       <c r="E45">
-        <v>1296.421</v>
+        <v>1390.768</v>
       </c>
       <c r="F45">
-        <v>4056.921</v>
+        <v>4151.268</v>
       </c>
       <c r="G45">
         <v>831.9</v>
@@ -4971,37 +4971,37 @@
         <v>508.5</v>
       </c>
       <c r="M45">
-        <v>581.738555382947</v>
+        <v>595.2673589965038</v>
       </c>
       <c r="N45">
-        <v>-73.23855538294697</v>
+        <v>-86.76735899650384</v>
       </c>
       <c r="O45">
-        <v>-24.90110883020197</v>
+        <v>-29.50090205881131</v>
       </c>
       <c r="P45">
-        <v>-48.337446552745</v>
+        <v>-57.26645693769254</v>
       </c>
       <c r="Q45">
-        <v>-5.337446552745</v>
+        <v>-14.26645693769254</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1503768480282104</v>
+        <v>0.1522442917429998</v>
       </c>
       <c r="T45">
-        <v>1.362986902928117</v>
+        <v>1.387325954766119</v>
       </c>
       <c r="U45">
         <v>0.1433941048847012</v>
       </c>
       <c r="V45">
-        <v>0.2971953610435704</v>
+        <v>0.290440921019853</v>
       </c>
       <c r="W45">
-        <v>0.1007780421119728</v>
+        <v>0.1017465889931712</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8741040030693247</v>
+        <v>0.8542380029995673</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1300253025330752</v>
+        <v>0.1310012435819223</v>
       </c>
       <c r="C46">
-        <v>3266.54918420212</v>
+        <v>3096.763532673637</v>
       </c>
       <c r="D46">
-        <v>6585.917184202121</v>
+        <v>6510.478532673638</v>
       </c>
       <c r="E46">
-        <v>1390.768</v>
+        <v>1485.115000000001</v>
       </c>
       <c r="F46">
-        <v>4151.268</v>
+        <v>4245.615000000001</v>
       </c>
       <c r="G46">
         <v>831.9</v>
@@ -5053,37 +5053,37 @@
         <v>508.5</v>
       </c>
       <c r="M46">
-        <v>595.2673589965038</v>
+        <v>608.7961626100608</v>
       </c>
       <c r="N46">
-        <v>-86.76735899650384</v>
+        <v>-100.2961626100608</v>
       </c>
       <c r="O46">
-        <v>-29.50090205881131</v>
+        <v>-34.10069528742068</v>
       </c>
       <c r="P46">
-        <v>-57.26645693769254</v>
+        <v>-66.19546732264016</v>
       </c>
       <c r="Q46">
-        <v>-14.26645693769254</v>
+        <v>-23.19546732264016</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1522442917429998</v>
+        <v>0.1541796425019635</v>
       </c>
       <c r="T46">
-        <v>1.387325954766119</v>
+        <v>1.412550063034593</v>
       </c>
       <c r="U46">
         <v>0.1433941048847012</v>
       </c>
       <c r="V46">
-        <v>0.290440921019853</v>
+        <v>0.2839866783305228</v>
       </c>
       <c r="W46">
-        <v>0.1017465889931712</v>
+        <v>0.1026720893463163</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8542380029995673</v>
+        <v>0.8352549362662436</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1310012435819223</v>
+        <v>0.1319771846307693</v>
       </c>
       <c r="C47">
-        <v>3096.763532673637</v>
+        <v>2928.686539347714</v>
       </c>
       <c r="D47">
-        <v>6510.478532673638</v>
+        <v>6436.748539347715</v>
       </c>
       <c r="E47">
-        <v>1485.115000000001</v>
+        <v>1579.462</v>
       </c>
       <c r="F47">
-        <v>4245.615000000001</v>
+        <v>4339.962</v>
       </c>
       <c r="G47">
         <v>831.9</v>
@@ -5135,37 +5135,37 @@
         <v>508.5</v>
       </c>
       <c r="M47">
-        <v>608.7961626100608</v>
+        <v>622.3249662236177</v>
       </c>
       <c r="N47">
-        <v>-100.2961626100608</v>
+        <v>-113.8249662236177</v>
       </c>
       <c r="O47">
-        <v>-34.10069528742068</v>
+        <v>-38.70048851603002</v>
       </c>
       <c r="P47">
-        <v>-66.19546732264016</v>
+        <v>-75.12447770758769</v>
       </c>
       <c r="Q47">
-        <v>-23.19546732264016</v>
+        <v>-32.12447770758769</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1541796425019635</v>
+        <v>0.1561866729186665</v>
       </c>
       <c r="T47">
-        <v>1.412550063034593</v>
+        <v>1.438708397535234</v>
       </c>
       <c r="U47">
         <v>0.1433941048847012</v>
       </c>
       <c r="V47">
-        <v>0.2839866783305228</v>
+        <v>0.277813054888555</v>
       </c>
       <c r="W47">
-        <v>0.1026720893463163</v>
+        <v>0.1035573505536725</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8352549362662436</v>
+        <v>0.8170972202604556</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1319771846307693</v>
+        <v>0.1476424451058914</v>
       </c>
       <c r="C48">
-        <v>2928.686539347714</v>
+        <v>1844.248007502605</v>
       </c>
       <c r="D48">
-        <v>6436.748539347715</v>
+        <v>5446.657007502606</v>
       </c>
       <c r="E48">
-        <v>1579.462</v>
+        <v>1673.809</v>
       </c>
       <c r="F48">
-        <v>4339.962</v>
+        <v>4434.309</v>
       </c>
       <c r="G48">
         <v>831.9</v>
@@ -5217,45 +5217,45 @@
         <v>508.5</v>
       </c>
       <c r="M48">
-        <v>622.3249662236177</v>
+        <v>760.9012836371746</v>
       </c>
       <c r="N48">
-        <v>-113.8249662236177</v>
+        <v>-252.4012836371746</v>
       </c>
       <c r="O48">
-        <v>-38.70048851603002</v>
+        <v>-85.81643643663938</v>
       </c>
       <c r="P48">
-        <v>-75.12447770758769</v>
+        <v>-166.5848472005353</v>
       </c>
       <c r="Q48">
-        <v>-32.12447770758769</v>
+        <v>-123.5848472005353</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1561866729186665</v>
+        <v>0.1609775901931226</v>
       </c>
       <c r="T48">
-        <v>1.438708397535234</v>
+        <v>1.501150110220381</v>
       </c>
       <c r="U48">
-        <v>0.1433941048847012</v>
+        <v>0.1715941048847012</v>
       </c>
       <c r="V48">
-        <v>0.277813054888555</v>
+        <v>0.2272173851167272</v>
       </c>
       <c r="W48">
-        <v>0.1035573505536725</v>
+        <v>0.132604941071354</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8170972202604556</v>
+        <v>0.6682864268139036</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1476424451058914</v>
+        <v>0.1489003861547384</v>
       </c>
       <c r="C49">
-        <v>1844.248007502605</v>
+        <v>1683.445646041158</v>
       </c>
       <c r="D49">
-        <v>5446.657007502606</v>
+        <v>5380.20164604116</v>
       </c>
       <c r="E49">
-        <v>1673.809</v>
+        <v>1768.156000000001</v>
       </c>
       <c r="F49">
-        <v>4434.309</v>
+        <v>4528.656000000001</v>
       </c>
       <c r="G49">
         <v>831.9</v>
@@ -5299,37 +5299,37 @@
         <v>508.5</v>
       </c>
       <c r="M49">
-        <v>760.9012836371746</v>
+        <v>777.0906726507317</v>
       </c>
       <c r="N49">
-        <v>-252.4012836371746</v>
+        <v>-268.5906726507317</v>
       </c>
       <c r="O49">
-        <v>-85.81643643663938</v>
+        <v>-91.32082870124877</v>
       </c>
       <c r="P49">
-        <v>-166.5848472005353</v>
+        <v>-177.2698439494829</v>
       </c>
       <c r="Q49">
-        <v>-123.5848472005353</v>
+        <v>-134.2698439494829</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1609775901931226</v>
+        <v>0.1631925438506827</v>
       </c>
       <c r="T49">
-        <v>1.501150110220381</v>
+        <v>1.530018381570773</v>
       </c>
       <c r="U49">
         <v>0.1715941048847012</v>
       </c>
       <c r="V49">
-        <v>0.2272173851167272</v>
+        <v>0.222483689593462</v>
       </c>
       <c r="W49">
-        <v>0.132604941071354</v>
+        <v>0.1334172153174654</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.6682864268139036</v>
+        <v>0.6543637929219471</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1489003861547384</v>
+        <v>0.178365342730805</v>
       </c>
       <c r="C50">
-        <v>1683.445646041159</v>
+        <v>393.2551125393456</v>
       </c>
       <c r="D50">
-        <v>5380.20164604116</v>
+        <v>4184.358112539347</v>
       </c>
       <c r="E50">
-        <v>1768.156</v>
+        <v>1862.503000000001</v>
       </c>
       <c r="F50">
-        <v>4528.656</v>
+        <v>4623.003000000001</v>
       </c>
       <c r="G50">
         <v>831.9</v>
@@ -5381,45 +5381,45 @@
         <v>508.5</v>
       </c>
       <c r="M50">
-        <v>777.0906726507316</v>
+        <v>1042.922223664289</v>
       </c>
       <c r="N50">
-        <v>-268.5906726507316</v>
+        <v>-534.4222236642886</v>
       </c>
       <c r="O50">
-        <v>-91.32082870124874</v>
+        <v>-181.7035560458581</v>
       </c>
       <c r="P50">
-        <v>-177.2698439494828</v>
+        <v>-352.7186676184305</v>
       </c>
       <c r="Q50">
-        <v>-134.2698439494828</v>
+        <v>-309.7186676184305</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1631925438506827</v>
+        <v>0.1689198790775972</v>
       </c>
       <c r="T50">
-        <v>1.530018381570773</v>
+        <v>1.604664759331724</v>
       </c>
       <c r="U50">
-        <v>0.1715941048847012</v>
+        <v>0.2255941048847012</v>
       </c>
       <c r="V50">
-        <v>0.2224836895934621</v>
+        <v>0.1657745861360151</v>
       </c>
       <c r="W50">
-        <v>0.1334172153174654</v>
+        <v>0.1881963355127151</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.6543637929219472</v>
+        <v>0.4875723121647503</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.178365342730805</v>
+        <v>0.180163283779652</v>
       </c>
       <c r="C51">
-        <v>393.2551125393456</v>
+        <v>242.9164085411885</v>
       </c>
       <c r="D51">
-        <v>4184.358112539347</v>
+        <v>4128.366408541189</v>
       </c>
       <c r="E51">
-        <v>1862.503000000001</v>
+        <v>1956.85</v>
       </c>
       <c r="F51">
-        <v>4623.003000000001</v>
+        <v>4717.35</v>
       </c>
       <c r="G51">
         <v>831.9</v>
@@ -5463,37 +5463,37 @@
         <v>508.5</v>
       </c>
       <c r="M51">
-        <v>1042.922223664289</v>
+        <v>1064.206350677845</v>
       </c>
       <c r="N51">
-        <v>-534.4222236642886</v>
+        <v>-555.7063506778454</v>
       </c>
       <c r="O51">
-        <v>-181.7035560458581</v>
+        <v>-188.9401592304675</v>
       </c>
       <c r="P51">
-        <v>-352.7186676184305</v>
+        <v>-366.766191447378</v>
       </c>
       <c r="Q51">
-        <v>-309.7186676184305</v>
+        <v>-323.766191447378</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1689198790775972</v>
+        <v>0.1713822766591492</v>
       </c>
       <c r="T51">
-        <v>1.604664759331724</v>
+        <v>1.636758054518358</v>
       </c>
       <c r="U51">
         <v>0.2255941048847012</v>
       </c>
       <c r="V51">
-        <v>0.1657745861360151</v>
+        <v>0.1624590944132948</v>
       </c>
       <c r="W51">
-        <v>0.1881963355127151</v>
+        <v>0.1889442909001548</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4875723121647503</v>
+        <v>0.4778208659214552</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.180163283779652</v>
+        <v>0.181961224828499</v>
       </c>
       <c r="C52">
-        <v>242.9164085411885</v>
+        <v>94.05638958189047</v>
       </c>
       <c r="D52">
-        <v>4128.366408541189</v>
+        <v>4073.853389581891</v>
       </c>
       <c r="E52">
-        <v>1956.85</v>
+        <v>2051.197</v>
       </c>
       <c r="F52">
-        <v>4717.35</v>
+        <v>4811.697</v>
       </c>
       <c r="G52">
         <v>831.9</v>
@@ -5545,37 +5545,37 @@
         <v>508.5</v>
       </c>
       <c r="M52">
-        <v>1064.206350677845</v>
+        <v>1085.490477691402</v>
       </c>
       <c r="N52">
-        <v>-555.7063506778454</v>
+        <v>-576.9904776914022</v>
       </c>
       <c r="O52">
-        <v>-188.9401592304675</v>
+        <v>-196.1767624150768</v>
       </c>
       <c r="P52">
-        <v>-366.766191447378</v>
+        <v>-380.8137152763255</v>
       </c>
       <c r="Q52">
-        <v>-323.766191447378</v>
+        <v>-337.8137152763255</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1713822766591492</v>
+        <v>0.1739451802644379</v>
       </c>
       <c r="T52">
-        <v>1.636758054518358</v>
+        <v>1.670161280120774</v>
       </c>
       <c r="U52">
         <v>0.2255941048847012</v>
       </c>
       <c r="V52">
-        <v>0.1624590944132948</v>
+        <v>0.1592736219738184</v>
       </c>
       <c r="W52">
-        <v>0.1889442909001548</v>
+        <v>0.1896629147037734</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4778208659214552</v>
+        <v>0.4684518293347602</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.181961224828499</v>
+        <v>0.183759165877346</v>
       </c>
       <c r="C53">
-        <v>94.05638958189047</v>
+        <v>-53.38275684806104</v>
       </c>
       <c r="D53">
-        <v>4073.853389581891</v>
+        <v>4020.76124315194</v>
       </c>
       <c r="E53">
-        <v>2051.197</v>
+        <v>2145.544000000001</v>
       </c>
       <c r="F53">
-        <v>4811.697</v>
+        <v>4906.044000000001</v>
       </c>
       <c r="G53">
         <v>831.9</v>
@@ -5627,37 +5627,37 @@
         <v>508.5</v>
       </c>
       <c r="M53">
-        <v>1085.490477691402</v>
+        <v>1106.774604704959</v>
       </c>
       <c r="N53">
-        <v>-576.9904776914022</v>
+        <v>-598.2746047049593</v>
       </c>
       <c r="O53">
-        <v>-196.1767624150768</v>
+        <v>-203.4133655996862</v>
       </c>
       <c r="P53">
-        <v>-380.8137152763255</v>
+        <v>-394.8612391052731</v>
       </c>
       <c r="Q53">
-        <v>-337.8137152763255</v>
+        <v>-351.8612391052731</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1739451802644379</v>
+        <v>0.1766148715199471</v>
       </c>
       <c r="T53">
-        <v>1.670161280120774</v>
+        <v>1.704956306789957</v>
       </c>
       <c r="U53">
         <v>0.2255941048847012</v>
       </c>
       <c r="V53">
-        <v>0.1592736219738184</v>
+        <v>0.1562106677050911</v>
       </c>
       <c r="W53">
-        <v>0.1896629147037734</v>
+        <v>0.1903538991303297</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4684518293347602</v>
+        <v>0.4594431403090916</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.183759165877346</v>
+        <v>0.185557106926193</v>
       </c>
       <c r="C54">
-        <v>-53.38275684806104</v>
+        <v>-199.4558682829074</v>
       </c>
       <c r="D54">
-        <v>4020.76124315194</v>
+        <v>3969.035131717093</v>
       </c>
       <c r="E54">
-        <v>2145.544000000001</v>
+        <v>2239.891000000001</v>
       </c>
       <c r="F54">
-        <v>4906.044000000001</v>
+        <v>5000.391000000001</v>
       </c>
       <c r="G54">
         <v>831.9</v>
@@ -5709,37 +5709,37 @@
         <v>508.5</v>
       </c>
       <c r="M54">
-        <v>1106.774604704959</v>
+        <v>1128.058731718516</v>
       </c>
       <c r="N54">
-        <v>-598.2746047049593</v>
+        <v>-619.5587317185161</v>
       </c>
       <c r="O54">
-        <v>-203.4133655996862</v>
+        <v>-210.6499687842955</v>
       </c>
       <c r="P54">
-        <v>-394.8612391052731</v>
+        <v>-408.9087629342206</v>
       </c>
       <c r="Q54">
-        <v>-351.8612391052731</v>
+        <v>-365.9087629342206</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1766148715199471</v>
+        <v>0.1793981666586693</v>
       </c>
       <c r="T54">
-        <v>1.704956306789957</v>
+        <v>1.741231972891871</v>
       </c>
       <c r="U54">
         <v>0.2255941048847012</v>
       </c>
       <c r="V54">
-        <v>0.1562106677050911</v>
+        <v>0.1532632966163159</v>
       </c>
       <c r="W54">
-        <v>0.1903538991303297</v>
+        <v>0.191018808672865</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4594431403090916</v>
+        <v>0.4507744018126937</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.185557106926193</v>
+        <v>0.18735504797504</v>
       </c>
       <c r="C55">
-        <v>-199.4558682829074</v>
+        <v>-344.2149962127305</v>
       </c>
       <c r="D55">
-        <v>3969.035131717093</v>
+        <v>3918.62300378727</v>
       </c>
       <c r="E55">
-        <v>2239.891000000001</v>
+        <v>2334.238</v>
       </c>
       <c r="F55">
-        <v>5000.391000000001</v>
+        <v>5094.738</v>
       </c>
       <c r="G55">
         <v>831.9</v>
@@ -5791,37 +5791,37 @@
         <v>508.5</v>
       </c>
       <c r="M55">
-        <v>1128.058731718516</v>
+        <v>1149.342858732073</v>
       </c>
       <c r="N55">
-        <v>-619.5587317185161</v>
+        <v>-640.842858732073</v>
       </c>
       <c r="O55">
-        <v>-210.6499687842955</v>
+        <v>-217.8865719689048</v>
       </c>
       <c r="P55">
-        <v>-408.9087629342206</v>
+        <v>-422.9562867631681</v>
       </c>
       <c r="Q55">
-        <v>-365.9087629342206</v>
+        <v>-379.9562867631681</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1793981666586693</v>
+        <v>0.18230247462951</v>
       </c>
       <c r="T55">
-        <v>1.741231972891871</v>
+        <v>1.779084841867781</v>
       </c>
       <c r="U55">
         <v>0.2255941048847012</v>
       </c>
       <c r="V55">
-        <v>0.1532632966163159</v>
+        <v>0.1504250874197174</v>
       </c>
       <c r="W55">
-        <v>0.191018808672865</v>
+        <v>0.1916590919360471</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4507744018126937</v>
+        <v>0.4424267277050512</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.18735504797504</v>
+        <v>0.1891529890238871</v>
       </c>
       <c r="C56">
-        <v>-344.2149962127305</v>
+        <v>-487.7095807970418</v>
       </c>
       <c r="D56">
-        <v>3918.62300378727</v>
+        <v>3869.475419202959</v>
       </c>
       <c r="E56">
-        <v>2334.238</v>
+        <v>2428.585000000001</v>
       </c>
       <c r="F56">
-        <v>5094.738</v>
+        <v>5189.085000000001</v>
       </c>
       <c r="G56">
         <v>831.9</v>
@@ -5873,37 +5873,37 @@
         <v>508.5</v>
       </c>
       <c r="M56">
-        <v>1149.342858732073</v>
+        <v>1170.62698574563</v>
       </c>
       <c r="N56">
-        <v>-640.842858732073</v>
+        <v>-662.12698574563</v>
       </c>
       <c r="O56">
-        <v>-217.8865719689048</v>
+        <v>-225.1231751535142</v>
       </c>
       <c r="P56">
-        <v>-422.9562867631681</v>
+        <v>-437.0038105921158</v>
       </c>
       <c r="Q56">
-        <v>-379.9562867631681</v>
+        <v>-394.0038105921158</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.18230247462951</v>
+        <v>0.1853358629546102</v>
       </c>
       <c r="T56">
-        <v>1.779084841867781</v>
+        <v>1.818620060575954</v>
       </c>
       <c r="U56">
         <v>0.2255941048847012</v>
       </c>
       <c r="V56">
-        <v>0.1504250874197174</v>
+        <v>0.147690085830268</v>
       </c>
       <c r="W56">
-        <v>0.1916590919360471</v>
+        <v>0.1922760921714772</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4424267277050512</v>
+        <v>0.4343826053831411</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1891529890238871</v>
+        <v>0.1909509300727341</v>
       </c>
       <c r="C57">
-        <v>-487.7095807970418</v>
+        <v>-629.9866125936223</v>
       </c>
       <c r="D57">
-        <v>3869.475419202959</v>
+        <v>3821.545387406378</v>
       </c>
       <c r="E57">
-        <v>2428.585000000001</v>
+        <v>2522.932000000001</v>
       </c>
       <c r="F57">
-        <v>5189.085000000001</v>
+        <v>5283.432000000001</v>
       </c>
       <c r="G57">
         <v>831.9</v>
@@ -5955,37 +5955,37 @@
         <v>508.5</v>
       </c>
       <c r="M57">
-        <v>1170.62698574563</v>
+        <v>1191.911112759187</v>
       </c>
       <c r="N57">
-        <v>-662.12698574563</v>
+        <v>-683.4111127591868</v>
       </c>
       <c r="O57">
-        <v>-225.1231751535142</v>
+        <v>-232.3597783381235</v>
       </c>
       <c r="P57">
-        <v>-437.0038105921158</v>
+        <v>-451.0513344210633</v>
       </c>
       <c r="Q57">
-        <v>-394.0038105921158</v>
+        <v>-408.0513344210633</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1853358629546102</v>
+        <v>0.188507132567215</v>
       </c>
       <c r="T57">
-        <v>1.818620060575954</v>
+        <v>1.859952334679953</v>
       </c>
       <c r="U57">
         <v>0.2255941048847012</v>
       </c>
       <c r="V57">
-        <v>0.147690085830268</v>
+        <v>0.1450527628690132</v>
       </c>
       <c r="W57">
-        <v>0.1922760921714772</v>
+        <v>0.1928710566842133</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4343826053831411</v>
+        <v>0.4266257731441565</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1909509300727341</v>
+        <v>0.1927488711215811</v>
       </c>
       <c r="C58">
-        <v>-629.9866125936223</v>
+        <v>-771.0907824147171</v>
       </c>
       <c r="D58">
-        <v>3821.545387406378</v>
+        <v>3774.788217585284</v>
       </c>
       <c r="E58">
-        <v>2522.932000000001</v>
+        <v>2617.279000000001</v>
       </c>
       <c r="F58">
-        <v>5283.432000000001</v>
+        <v>5377.779000000001</v>
       </c>
       <c r="G58">
         <v>831.9</v>
@@ -6037,37 +6037,37 @@
         <v>508.5</v>
       </c>
       <c r="M58">
-        <v>1191.911112759187</v>
+        <v>1213.195239772744</v>
       </c>
       <c r="N58">
-        <v>-683.4111127591868</v>
+        <v>-704.6952397727439</v>
       </c>
       <c r="O58">
-        <v>-232.3597783381235</v>
+        <v>-239.5963815227329</v>
       </c>
       <c r="P58">
-        <v>-451.0513344210633</v>
+        <v>-465.0988582500109</v>
       </c>
       <c r="Q58">
-        <v>-408.0513344210633</v>
+        <v>-422.0988582500109</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.188507132567215</v>
+        <v>0.1918259030920339</v>
       </c>
       <c r="T58">
-        <v>1.859952334679953</v>
+        <v>1.903207040137626</v>
       </c>
       <c r="U58">
         <v>0.2255941048847012</v>
       </c>
       <c r="V58">
-        <v>0.1450527628690132</v>
+        <v>0.1425079775555217</v>
       </c>
       <c r="W58">
-        <v>0.1928710566842133</v>
+        <v>0.1934451452491342</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4266257731441565</v>
+        <v>0.4191411104574169</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1927488711215811</v>
+        <v>0.1945468121704281</v>
       </c>
       <c r="C59">
-        <v>-771.0907824147171</v>
+        <v>-911.0646203151136</v>
       </c>
       <c r="D59">
-        <v>3774.788217585284</v>
+        <v>3729.161379684887</v>
       </c>
       <c r="E59">
-        <v>2617.279000000001</v>
+        <v>2711.626000000001</v>
       </c>
       <c r="F59">
-        <v>5377.779000000001</v>
+        <v>5472.126000000001</v>
       </c>
       <c r="G59">
         <v>831.9</v>
@@ -6119,37 +6119,37 @@
         <v>508.5</v>
       </c>
       <c r="M59">
-        <v>1213.195239772744</v>
+        <v>1234.479366786301</v>
       </c>
       <c r="N59">
-        <v>-704.6952397727439</v>
+        <v>-725.9793667863007</v>
       </c>
       <c r="O59">
-        <v>-239.5963815227329</v>
+        <v>-246.8329847073423</v>
       </c>
       <c r="P59">
-        <v>-465.0988582500109</v>
+        <v>-479.1463820789585</v>
       </c>
       <c r="Q59">
-        <v>-422.0988582500109</v>
+        <v>-436.1463820789585</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1918259030920339</v>
+        <v>0.195302710308511</v>
       </c>
       <c r="T59">
-        <v>1.903207040137626</v>
+        <v>1.948521493474236</v>
       </c>
       <c r="U59">
         <v>0.2255941048847012</v>
       </c>
       <c r="V59">
-        <v>0.1425079775555217</v>
+        <v>0.1400509434597369</v>
       </c>
       <c r="W59">
-        <v>0.1934451452491342</v>
+        <v>0.193999437656644</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4191411104574169</v>
+        <v>0.4119145395874615</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1945468121704281</v>
+        <v>0.1963447532192751</v>
       </c>
       <c r="C60">
-        <v>-911.0646203151109</v>
+        <v>-1049.948624620699</v>
       </c>
       <c r="D60">
-        <v>3729.161379684889</v>
+        <v>3684.624375379301</v>
       </c>
       <c r="E60">
-        <v>2711.626</v>
+        <v>2805.973</v>
       </c>
       <c r="F60">
-        <v>5472.126</v>
+        <v>5566.473</v>
       </c>
       <c r="G60">
         <v>831.9</v>
@@ -6201,37 +6201,37 @@
         <v>508.5</v>
       </c>
       <c r="M60">
-        <v>1234.4793667863</v>
+        <v>1255.763493799858</v>
       </c>
       <c r="N60">
-        <v>-725.9793667863005</v>
+        <v>-747.2634937998575</v>
       </c>
       <c r="O60">
-        <v>-246.8329847073422</v>
+        <v>-254.0695878919516</v>
       </c>
       <c r="P60">
-        <v>-479.1463820789583</v>
+        <v>-493.193905907906</v>
       </c>
       <c r="Q60">
-        <v>-436.1463820789583</v>
+        <v>-450.193905907906</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1953027103085109</v>
+        <v>0.1989491178770112</v>
       </c>
       <c r="T60">
-        <v>1.948521493474236</v>
+        <v>1.996046407949217</v>
       </c>
       <c r="U60">
         <v>0.2255941048847012</v>
       </c>
       <c r="V60">
-        <v>0.1400509434597369</v>
+        <v>0.1376771986553346</v>
       </c>
       <c r="W60">
-        <v>0.193999437656644</v>
+        <v>0.1945349404910178</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4119145395874615</v>
+        <v>0.4049329372215723</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1963447532192751</v>
+        <v>0.1981426942681221</v>
       </c>
       <c r="C61">
-        <v>-1049.948624620699</v>
+        <v>-1187.781381820301</v>
       </c>
       <c r="D61">
-        <v>3684.624375379301</v>
+        <v>3641.1386181797</v>
       </c>
       <c r="E61">
-        <v>2805.973</v>
+        <v>2900.320000000001</v>
       </c>
       <c r="F61">
-        <v>5566.473</v>
+        <v>5660.820000000001</v>
       </c>
       <c r="G61">
         <v>831.9</v>
@@ -6283,37 +6283,37 @@
         <v>508.5</v>
       </c>
       <c r="M61">
-        <v>1255.763493799858</v>
+        <v>1277.047620813415</v>
       </c>
       <c r="N61">
-        <v>-747.2634937998575</v>
+        <v>-768.5476208134146</v>
       </c>
       <c r="O61">
-        <v>-254.0695878919516</v>
+        <v>-261.306191076561</v>
       </c>
       <c r="P61">
-        <v>-493.193905907906</v>
+        <v>-507.2414297368536</v>
       </c>
       <c r="Q61">
-        <v>-450.193905907906</v>
+        <v>-464.2414297368536</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1989491178770112</v>
+        <v>0.2027778458239365</v>
       </c>
       <c r="T61">
-        <v>1.996046407949217</v>
+        <v>2.045947568147948</v>
       </c>
       <c r="U61">
         <v>0.2255941048847012</v>
       </c>
       <c r="V61">
-        <v>0.1376771986553346</v>
+        <v>0.1353825786777457</v>
       </c>
       <c r="W61">
-        <v>0.1945349404910178</v>
+        <v>0.1950525932309126</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4049329372215723</v>
+        <v>0.398184054934546</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1981426942681221</v>
+        <v>0.1999406353169692</v>
       </c>
       <c r="C62">
-        <v>-1187.781381820301</v>
+        <v>-1324.59967806678</v>
       </c>
       <c r="D62">
-        <v>3641.1386181797</v>
+        <v>3598.667321933221</v>
       </c>
       <c r="E62">
-        <v>2900.320000000001</v>
+        <v>2994.667</v>
       </c>
       <c r="F62">
-        <v>5660.820000000001</v>
+        <v>5755.167</v>
       </c>
       <c r="G62">
         <v>831.9</v>
@@ -6365,37 +6365,37 @@
         <v>508.5</v>
       </c>
       <c r="M62">
-        <v>1277.047620813415</v>
+        <v>1298.331747826971</v>
       </c>
       <c r="N62">
-        <v>-768.5476208134146</v>
+        <v>-789.8317478269714</v>
       </c>
       <c r="O62">
-        <v>-261.306191076561</v>
+        <v>-268.5427942611703</v>
       </c>
       <c r="P62">
-        <v>-507.2414297368536</v>
+        <v>-521.2889535658012</v>
       </c>
       <c r="Q62">
-        <v>-464.2414297368536</v>
+        <v>-478.2889535658012</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2027778458239365</v>
+        <v>0.206802918793781</v>
       </c>
       <c r="T62">
-        <v>2.045947568147948</v>
+        <v>2.098407762203024</v>
       </c>
       <c r="U62">
         <v>0.2255941048847012</v>
       </c>
       <c r="V62">
-        <v>0.1353825786777457</v>
+        <v>0.1331631921420449</v>
       </c>
       <c r="W62">
-        <v>0.1950525932309126</v>
+        <v>0.1955532737498271</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.398184054934546</v>
+        <v>0.3916564474766027</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1999406353169692</v>
+        <v>0.2017385763658162</v>
       </c>
       <c r="C63">
-        <v>-1324.59967806678</v>
+        <v>-1460.438602964629</v>
       </c>
       <c r="D63">
-        <v>3598.667321933221</v>
+        <v>3557.175397035371</v>
       </c>
       <c r="E63">
-        <v>2994.667</v>
+        <v>3089.014</v>
       </c>
       <c r="F63">
-        <v>5755.167</v>
+        <v>5849.514</v>
       </c>
       <c r="G63">
         <v>831.9</v>
@@ -6447,37 +6447,37 @@
         <v>508.5</v>
       </c>
       <c r="M63">
-        <v>1298.331747826971</v>
+        <v>1319.615874840528</v>
       </c>
       <c r="N63">
-        <v>-789.8317478269714</v>
+        <v>-811.1158748405282</v>
       </c>
       <c r="O63">
-        <v>-268.5427942611703</v>
+        <v>-275.7793974457796</v>
       </c>
       <c r="P63">
-        <v>-521.2889535658012</v>
+        <v>-535.3364773947486</v>
       </c>
       <c r="Q63">
-        <v>-478.2889535658012</v>
+        <v>-492.3364773947486</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.206802918793781</v>
+        <v>0.2110398377094068</v>
       </c>
       <c r="T63">
-        <v>2.098407762203024</v>
+        <v>2.153629019103103</v>
       </c>
       <c r="U63">
         <v>0.2255941048847012</v>
       </c>
       <c r="V63">
-        <v>0.1331631921420449</v>
+        <v>0.131015398720399</v>
       </c>
       <c r="W63">
-        <v>0.1955532737498271</v>
+        <v>0.1960378032842606</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3916564474766027</v>
+        <v>0.3853394080011736</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2017385763658162</v>
+        <v>0.2035365174146632</v>
       </c>
       <c r="C64">
-        <v>-1460.438602964629</v>
+        <v>-1595.33164625951</v>
       </c>
       <c r="D64">
-        <v>3557.175397035371</v>
+        <v>3516.629353740491</v>
       </c>
       <c r="E64">
-        <v>3089.014</v>
+        <v>3183.361000000001</v>
       </c>
       <c r="F64">
-        <v>5849.514</v>
+        <v>5943.861000000001</v>
       </c>
       <c r="G64">
         <v>831.9</v>
@@ -6529,37 +6529,37 @@
         <v>508.5</v>
       </c>
       <c r="M64">
-        <v>1319.615874840528</v>
+        <v>1340.900001854085</v>
       </c>
       <c r="N64">
-        <v>-811.1158748405282</v>
+        <v>-832.4000018540853</v>
       </c>
       <c r="O64">
-        <v>-275.7793974457796</v>
+        <v>-283.016000630389</v>
       </c>
       <c r="P64">
-        <v>-535.3364773947486</v>
+        <v>-549.3840012236963</v>
       </c>
       <c r="Q64">
-        <v>-492.3364773947486</v>
+        <v>-506.3840012236963</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2110398377094068</v>
+        <v>0.2155057792691205</v>
       </c>
       <c r="T64">
-        <v>2.153629019103103</v>
+        <v>2.211835208808592</v>
       </c>
       <c r="U64">
         <v>0.2255941048847012</v>
       </c>
       <c r="V64">
-        <v>0.131015398720399</v>
+        <v>0.1289357892169006</v>
       </c>
       <c r="W64">
-        <v>0.1960378032842606</v>
+        <v>0.196506950928712</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3853394080011736</v>
+        <v>0.3792229094614724</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2035365174146632</v>
+        <v>0.2053344584635102</v>
       </c>
       <c r="C65">
-        <v>-1595.33164625951</v>
+        <v>-1729.310787989672</v>
       </c>
       <c r="D65">
-        <v>3516.629353740491</v>
+        <v>3476.997212010329</v>
       </c>
       <c r="E65">
-        <v>3183.361000000001</v>
+        <v>3277.708000000001</v>
       </c>
       <c r="F65">
-        <v>5943.861000000001</v>
+        <v>6038.208000000001</v>
       </c>
       <c r="G65">
         <v>831.9</v>
@@ -6611,37 +6611,37 @@
         <v>508.5</v>
       </c>
       <c r="M65">
-        <v>1340.900001854085</v>
+        <v>1362.184128867642</v>
       </c>
       <c r="N65">
-        <v>-832.4000018540853</v>
+        <v>-853.6841288676421</v>
       </c>
       <c r="O65">
-        <v>-283.016000630389</v>
+        <v>-290.2526038149983</v>
       </c>
       <c r="P65">
-        <v>-549.3840012236963</v>
+        <v>-563.4315250526438</v>
       </c>
       <c r="Q65">
-        <v>-506.3840012236963</v>
+        <v>-520.4315250526438</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2155057792691205</v>
+        <v>0.2202198286932627</v>
       </c>
       <c r="T65">
-        <v>2.211835208808592</v>
+        <v>2.273275075719942</v>
       </c>
       <c r="U65">
         <v>0.2255941048847012</v>
       </c>
       <c r="V65">
-        <v>0.1289357892169006</v>
+        <v>0.1269211675103866</v>
       </c>
       <c r="W65">
-        <v>0.196506950928712</v>
+        <v>0.1969614377092744</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3792229094614724</v>
+        <v>0.373297551501137</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2053344584635102</v>
+        <v>0.2071323995123572</v>
       </c>
       <c r="C66">
-        <v>-1729.310787989672</v>
+        <v>-1862.406582609322</v>
       </c>
       <c r="D66">
-        <v>3476.997212010329</v>
+        <v>3438.248417390678</v>
       </c>
       <c r="E66">
-        <v>3277.708000000001</v>
+        <v>3372.055</v>
       </c>
       <c r="F66">
-        <v>6038.208000000001</v>
+        <v>6132.555</v>
       </c>
       <c r="G66">
         <v>831.9</v>
@@ -6693,37 +6693,37 @@
         <v>508.5</v>
       </c>
       <c r="M66">
-        <v>1362.184128867642</v>
+        <v>1383.468255881199</v>
       </c>
       <c r="N66">
-        <v>-853.6841288676421</v>
+        <v>-874.968255881199</v>
       </c>
       <c r="O66">
-        <v>-290.2526038149983</v>
+        <v>-297.4892069996077</v>
       </c>
       <c r="P66">
-        <v>-563.4315250526438</v>
+        <v>-577.4790488815913</v>
       </c>
       <c r="Q66">
-        <v>-520.4315250526438</v>
+        <v>-534.4790488815913</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2202198286932627</v>
+        <v>0.2252032523702131</v>
       </c>
       <c r="T66">
-        <v>2.273275075719942</v>
+        <v>2.338225792169083</v>
       </c>
       <c r="U66">
         <v>0.2255941048847012</v>
       </c>
       <c r="V66">
-        <v>0.1269211675103866</v>
+        <v>0.1249685341640729</v>
       </c>
       <c r="W66">
-        <v>0.1969614377092744</v>
+        <v>0.197401940281204</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.373297551501137</v>
+        <v>0.3675545122472733</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2071323995123572</v>
+        <v>0.2089303405612042</v>
       </c>
       <c r="C67">
-        <v>-1862.406582609322</v>
+        <v>-1994.648237549008</v>
       </c>
       <c r="D67">
-        <v>3438.248417390678</v>
+        <v>3400.353762450993</v>
       </c>
       <c r="E67">
-        <v>3372.055</v>
+        <v>3466.402000000001</v>
       </c>
       <c r="F67">
-        <v>6132.555</v>
+        <v>6226.902000000001</v>
       </c>
       <c r="G67">
         <v>831.9</v>
@@ -6775,37 +6775,37 @@
         <v>508.5</v>
       </c>
       <c r="M67">
-        <v>1383.468255881199</v>
+        <v>1404.752382894756</v>
       </c>
       <c r="N67">
-        <v>-874.968255881199</v>
+        <v>-896.252382894756</v>
       </c>
       <c r="O67">
-        <v>-297.4892069996077</v>
+        <v>-304.725810184217</v>
       </c>
       <c r="P67">
-        <v>-577.4790488815913</v>
+        <v>-591.526572710539</v>
       </c>
       <c r="Q67">
-        <v>-534.4790488815913</v>
+        <v>-548.526572710539</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2252032523702131</v>
+        <v>0.2304798186163959</v>
       </c>
       <c r="T67">
-        <v>2.338225792169083</v>
+        <v>2.406997138997586</v>
       </c>
       <c r="U67">
         <v>0.2255941048847012</v>
       </c>
       <c r="V67">
-        <v>0.1249685341640729</v>
+        <v>0.1230750715252233</v>
       </c>
       <c r="W67">
-        <v>0.197401940281204</v>
+        <v>0.1978290942903479</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3675545122472733</v>
+        <v>0.3619855044859509</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2089303405612042</v>
+        <v>0.2107282816100512</v>
       </c>
       <c r="C68">
-        <v>-1994.648237549008</v>
+        <v>-2126.063686637483</v>
       </c>
       <c r="D68">
-        <v>3400.353762450993</v>
+        <v>3363.285313362518</v>
       </c>
       <c r="E68">
-        <v>3466.402000000001</v>
+        <v>3560.749000000001</v>
       </c>
       <c r="F68">
-        <v>6226.902000000001</v>
+        <v>6321.249000000001</v>
       </c>
       <c r="G68">
         <v>831.9</v>
@@ -6857,37 +6857,37 @@
         <v>508.5</v>
       </c>
       <c r="M68">
-        <v>1404.752382894756</v>
+        <v>1426.036509908313</v>
       </c>
       <c r="N68">
-        <v>-896.252382894756</v>
+        <v>-917.5365099083128</v>
       </c>
       <c r="O68">
-        <v>-304.725810184217</v>
+        <v>-311.9624133688264</v>
       </c>
       <c r="P68">
-        <v>-591.526572710539</v>
+        <v>-605.5740965394864</v>
       </c>
       <c r="Q68">
-        <v>-548.526572710539</v>
+        <v>-562.5740965394864</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2304798186163959</v>
+        <v>0.2360761767562866</v>
       </c>
       <c r="T68">
-        <v>2.406997138997586</v>
+        <v>2.479936446239937</v>
       </c>
       <c r="U68">
         <v>0.2255941048847012</v>
       </c>
       <c r="V68">
-        <v>0.1230750715252233</v>
+        <v>0.1212381301591752</v>
       </c>
       <c r="W68">
-        <v>0.1978290942903479</v>
+        <v>0.1982434974335472</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3619855044859509</v>
+        <v>0.3565827357622801</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2107282816100512</v>
+        <v>0.2125262226588982</v>
       </c>
       <c r="C69">
-        <v>-2126.063686637483</v>
+        <v>-2256.67965877302</v>
       </c>
       <c r="D69">
-        <v>3363.285313362518</v>
+        <v>3327.016341226981</v>
       </c>
       <c r="E69">
-        <v>3560.749000000001</v>
+        <v>3655.096000000001</v>
       </c>
       <c r="F69">
-        <v>6321.249000000001</v>
+        <v>6415.596000000001</v>
       </c>
       <c r="G69">
         <v>831.9</v>
@@ -6939,37 +6939,37 @@
         <v>508.5</v>
       </c>
       <c r="M69">
-        <v>1426.036509908313</v>
+        <v>1447.32063692187</v>
       </c>
       <c r="N69">
-        <v>-917.5365099083128</v>
+        <v>-938.8206369218699</v>
       </c>
       <c r="O69">
-        <v>-311.9624133688264</v>
+        <v>-319.1990165534358</v>
       </c>
       <c r="P69">
-        <v>-605.5740965394864</v>
+        <v>-619.6216203684342</v>
       </c>
       <c r="Q69">
-        <v>-562.5740965394864</v>
+        <v>-576.6216203684342</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2360761767562866</v>
+        <v>0.2420223072799206</v>
       </c>
       <c r="T69">
-        <v>2.479936446239937</v>
+        <v>2.557434460184935</v>
       </c>
       <c r="U69">
         <v>0.2255941048847012</v>
       </c>
       <c r="V69">
-        <v>0.1212381301591752</v>
+        <v>0.1194552164803638</v>
       </c>
       <c r="W69">
-        <v>0.1982434974335472</v>
+        <v>0.1986457122490053</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3565827357622801</v>
+        <v>0.3513388720010701</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2125262226588982</v>
+        <v>0.2143241637077452</v>
       </c>
       <c r="C70">
-        <v>-2256.67965877302</v>
+        <v>-2386.521742198863</v>
       </c>
       <c r="D70">
-        <v>3327.016341226981</v>
+        <v>3291.521257801139</v>
       </c>
       <c r="E70">
-        <v>3655.096000000001</v>
+        <v>3749.443000000001</v>
       </c>
       <c r="F70">
-        <v>6415.596000000001</v>
+        <v>6509.943000000001</v>
       </c>
       <c r="G70">
         <v>831.9</v>
@@ -7021,37 +7021,37 @@
         <v>508.5</v>
       </c>
       <c r="M70">
-        <v>1447.32063692187</v>
+        <v>1468.604763935427</v>
       </c>
       <c r="N70">
-        <v>-938.8206369218699</v>
+        <v>-960.1047639354267</v>
       </c>
       <c r="O70">
-        <v>-319.1990165534358</v>
+        <v>-326.4356197380451</v>
       </c>
       <c r="P70">
-        <v>-619.6216203684342</v>
+        <v>-633.6691441973817</v>
       </c>
       <c r="Q70">
-        <v>-576.6216203684342</v>
+        <v>-590.6691441973817</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2420223072799206</v>
+        <v>0.24835205912766</v>
       </c>
       <c r="T70">
-        <v>2.557434460184935</v>
+        <v>2.639932345997352</v>
       </c>
       <c r="U70">
         <v>0.2255941048847012</v>
       </c>
       <c r="V70">
-        <v>0.1194552164803638</v>
+        <v>0.1177239814589093</v>
       </c>
       <c r="W70">
-        <v>0.1986457122490053</v>
+        <v>0.1990362686640154</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3513388720010701</v>
+        <v>0.3462470042909096</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2143241637077452</v>
+        <v>0.2161221047565922</v>
       </c>
       <c r="C71">
-        <v>-2386.521742198863</v>
+        <v>-2515.614444707709</v>
       </c>
       <c r="D71">
-        <v>3291.521257801139</v>
+        <v>3256.775555292291</v>
       </c>
       <c r="E71">
-        <v>3749.443000000001</v>
+        <v>3843.790000000001</v>
       </c>
       <c r="F71">
-        <v>6509.943000000001</v>
+        <v>6604.290000000001</v>
       </c>
       <c r="G71">
         <v>831.9</v>
@@ -7103,37 +7103,37 @@
         <v>508.5</v>
       </c>
       <c r="M71">
-        <v>1468.604763935427</v>
+        <v>1489.888890948984</v>
       </c>
       <c r="N71">
-        <v>-960.1047639354267</v>
+        <v>-981.3888909489835</v>
       </c>
       <c r="O71">
-        <v>-326.4356197380451</v>
+        <v>-333.6722229226544</v>
       </c>
       <c r="P71">
-        <v>-633.6691441973817</v>
+        <v>-647.7166680263291</v>
       </c>
       <c r="Q71">
-        <v>-590.6691441973817</v>
+        <v>-604.7166680263291</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.24835205912766</v>
+        <v>0.2551037944319153</v>
       </c>
       <c r="T71">
-        <v>2.639932345997352</v>
+        <v>2.727930090863931</v>
       </c>
       <c r="U71">
         <v>0.2255941048847012</v>
       </c>
       <c r="V71">
-        <v>0.1177239814589093</v>
+        <v>0.1160422102952106</v>
       </c>
       <c r="W71">
-        <v>0.1990362686640154</v>
+        <v>0.1994156663243109</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3462470042909096</v>
+        <v>0.3413006185153252</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2161221047565922</v>
+        <v>0.2179200458054393</v>
       </c>
       <c r="C72">
-        <v>-2515.614444707709</v>
+        <v>-2643.981250072859</v>
       </c>
       <c r="D72">
-        <v>3256.775555292291</v>
+        <v>3222.755749927142</v>
       </c>
       <c r="E72">
-        <v>3843.790000000001</v>
+        <v>3938.137000000002</v>
       </c>
       <c r="F72">
-        <v>6604.290000000001</v>
+        <v>6698.637000000002</v>
       </c>
       <c r="G72">
         <v>831.9</v>
@@ -7185,37 +7185,37 @@
         <v>508.5</v>
       </c>
       <c r="M72">
-        <v>1489.888890948984</v>
+        <v>1511.173017962541</v>
       </c>
       <c r="N72">
-        <v>-981.3888909489835</v>
+        <v>-1002.673017962541</v>
       </c>
       <c r="O72">
-        <v>-333.6722229226544</v>
+        <v>-340.9088261072638</v>
       </c>
       <c r="P72">
-        <v>-647.7166680263291</v>
+        <v>-661.7641918552767</v>
       </c>
       <c r="Q72">
-        <v>-604.7166680263291</v>
+        <v>-618.7641918552767</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2551037944319153</v>
+        <v>0.2623211666537055</v>
       </c>
       <c r="T72">
-        <v>2.727930090863931</v>
+        <v>2.821996645721308</v>
       </c>
       <c r="U72">
         <v>0.2255941048847012</v>
       </c>
       <c r="V72">
-        <v>0.1160422102952106</v>
+        <v>0.114407812967109</v>
       </c>
       <c r="W72">
-        <v>0.1994156663243109</v>
+        <v>0.19978437672657</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3413006185153252</v>
+        <v>0.3364935675503206</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2179200458054393</v>
+        <v>0.2197179868542862</v>
       </c>
       <c r="C73">
-        <v>-2643.981250072858</v>
+        <v>-2771.644670979088</v>
       </c>
       <c r="D73">
-        <v>3222.755749927142</v>
+        <v>3189.439329020913</v>
       </c>
       <c r="E73">
-        <v>3938.137000000001</v>
+        <v>4032.484</v>
       </c>
       <c r="F73">
-        <v>6698.637000000001</v>
+        <v>6792.984</v>
       </c>
       <c r="G73">
         <v>831.9</v>
@@ -7267,37 +7267,37 @@
         <v>508.5</v>
       </c>
       <c r="M73">
-        <v>1511.17301796254</v>
+        <v>1532.457144976097</v>
       </c>
       <c r="N73">
-        <v>-1002.67301796254</v>
+        <v>-1023.957144976097</v>
       </c>
       <c r="O73">
-        <v>-340.9088261072637</v>
+        <v>-348.1454292918731</v>
       </c>
       <c r="P73">
-        <v>-661.7641918552766</v>
+        <v>-675.8117156842241</v>
       </c>
       <c r="Q73">
-        <v>-618.7641918552766</v>
+        <v>-632.8117156842241</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2623211666537055</v>
+        <v>0.2700540654627663</v>
       </c>
       <c r="T73">
-        <v>2.821996645721307</v>
+        <v>2.922782240211354</v>
       </c>
       <c r="U73">
         <v>0.2255941048847012</v>
       </c>
       <c r="V73">
-        <v>0.114407812967109</v>
+        <v>0.1128188155647881</v>
       </c>
       <c r="W73">
-        <v>0.19978437672657</v>
+        <v>0.2001428451732107</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3364935675503207</v>
+        <v>0.3318200457787884</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2197179868542862</v>
+        <v>0.2215159279031333</v>
       </c>
       <c r="C74">
-        <v>-2771.644670979088</v>
+        <v>-2898.626298703986</v>
       </c>
       <c r="D74">
-        <v>3189.439329020913</v>
+        <v>3156.804701296014</v>
       </c>
       <c r="E74">
-        <v>4032.484</v>
+        <v>4126.831</v>
       </c>
       <c r="F74">
-        <v>6792.984</v>
+        <v>6887.331</v>
       </c>
       <c r="G74">
         <v>831.9</v>
@@ -7349,37 +7349,37 @@
         <v>508.5</v>
       </c>
       <c r="M74">
-        <v>1532.457144976097</v>
+        <v>1553.741271989654</v>
       </c>
       <c r="N74">
-        <v>-1023.957144976097</v>
+        <v>-1045.241271989654</v>
       </c>
       <c r="O74">
-        <v>-348.1454292918731</v>
+        <v>-355.3820324764825</v>
       </c>
       <c r="P74">
-        <v>-675.8117156842241</v>
+        <v>-689.8592395131718</v>
       </c>
       <c r="Q74">
-        <v>-632.8117156842241</v>
+        <v>-646.8592395131718</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2700540654627663</v>
+        <v>0.2783597715910169</v>
       </c>
       <c r="T74">
-        <v>2.922782240211354</v>
+        <v>3.031033434293255</v>
       </c>
       <c r="U74">
         <v>0.2255941048847012</v>
       </c>
       <c r="V74">
-        <v>0.1128188155647881</v>
+        <v>0.1112733523378732</v>
       </c>
       <c r="W74">
-        <v>0.2001428451732107</v>
+        <v>0.2004914925665187</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3318200457787884</v>
+        <v>0.3272745656996269</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2215159279031333</v>
+        <v>0.2233138689519803</v>
       </c>
       <c r="C75">
-        <v>-2898.626298703986</v>
+        <v>-3024.946849780093</v>
       </c>
       <c r="D75">
-        <v>3156.804701296014</v>
+        <v>3124.831150219908</v>
       </c>
       <c r="E75">
-        <v>4126.831</v>
+        <v>4221.178000000001</v>
       </c>
       <c r="F75">
-        <v>6887.331</v>
+        <v>6981.678000000001</v>
       </c>
       <c r="G75">
         <v>831.9</v>
@@ -7431,37 +7431,37 @@
         <v>508.5</v>
       </c>
       <c r="M75">
-        <v>1553.741271989654</v>
+        <v>1575.025399003211</v>
       </c>
       <c r="N75">
-        <v>-1045.241271989654</v>
+        <v>-1066.525399003211</v>
       </c>
       <c r="O75">
-        <v>-355.3820324764825</v>
+        <v>-362.6186356610918</v>
       </c>
       <c r="P75">
-        <v>-689.8592395131718</v>
+        <v>-703.9067633421195</v>
       </c>
       <c r="Q75">
-        <v>-646.8592395131718</v>
+        <v>-660.9067633421195</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2783597715910169</v>
+        <v>0.2873043781906715</v>
       </c>
       <c r="T75">
-        <v>3.031033434293255</v>
+        <v>3.147611643304535</v>
       </c>
       <c r="U75">
         <v>0.2255941048847012</v>
       </c>
       <c r="V75">
-        <v>0.1112733523378732</v>
+        <v>0.1097696583873613</v>
       </c>
       <c r="W75">
-        <v>0.2004914925665187</v>
+        <v>0.200830717057305</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3272745656996269</v>
+        <v>0.3228519364334157</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2233138689519803</v>
+        <v>0.2251118100008273</v>
       </c>
       <c r="C76">
-        <v>-3024.946849780093</v>
+        <v>-3150.626209849796</v>
       </c>
       <c r="D76">
-        <v>3124.831150219908</v>
+        <v>3093.498790150204</v>
       </c>
       <c r="E76">
-        <v>4221.178000000001</v>
+        <v>4315.525000000001</v>
       </c>
       <c r="F76">
-        <v>6981.678000000001</v>
+        <v>7076.025000000001</v>
       </c>
       <c r="G76">
         <v>831.9</v>
@@ -7513,37 +7513,37 @@
         <v>508.5</v>
       </c>
       <c r="M76">
-        <v>1575.025399003211</v>
+        <v>1596.309526016768</v>
       </c>
       <c r="N76">
-        <v>-1066.525399003211</v>
+        <v>-1087.809526016768</v>
       </c>
       <c r="O76">
-        <v>-362.6186356610918</v>
+        <v>-369.8552388457012</v>
       </c>
       <c r="P76">
-        <v>-703.9067633421195</v>
+        <v>-717.9542871710669</v>
       </c>
       <c r="Q76">
-        <v>-660.9067633421195</v>
+        <v>-674.9542871710669</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2873043781906715</v>
+        <v>0.2969645533182984</v>
       </c>
       <c r="T76">
-        <v>3.147611643304535</v>
+        <v>3.273516109036716</v>
       </c>
       <c r="U76">
         <v>0.2255941048847012</v>
       </c>
       <c r="V76">
-        <v>0.1097696583873613</v>
+        <v>0.1083060629421965</v>
       </c>
       <c r="W76">
-        <v>0.200830717057305</v>
+        <v>0.2011608955616703</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3228519364334157</v>
+        <v>0.3185472439476369</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2251118100008273</v>
+        <v>0.2269097510496743</v>
       </c>
       <c r="C77">
-        <v>-3150.626209849796</v>
+        <v>-3275.683474908049</v>
       </c>
       <c r="D77">
-        <v>3093.498790150204</v>
+        <v>3062.788525091952</v>
       </c>
       <c r="E77">
-        <v>4315.525000000001</v>
+        <v>4409.872</v>
       </c>
       <c r="F77">
-        <v>7076.025000000001</v>
+        <v>7170.372</v>
       </c>
       <c r="G77">
         <v>831.9</v>
@@ -7595,37 +7595,37 @@
         <v>508.5</v>
       </c>
       <c r="M77">
-        <v>1596.309526016768</v>
+        <v>1617.593653030325</v>
       </c>
       <c r="N77">
-        <v>-1087.809526016768</v>
+        <v>-1109.093653030325</v>
       </c>
       <c r="O77">
-        <v>-369.8552388457012</v>
+        <v>-377.0918420303105</v>
       </c>
       <c r="P77">
-        <v>-717.9542871710669</v>
+        <v>-732.0018110000144</v>
       </c>
       <c r="Q77">
-        <v>-674.9542871710669</v>
+        <v>-689.0018110000144</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2969645533182984</v>
+        <v>0.3074297430398941</v>
       </c>
       <c r="T77">
-        <v>3.273516109036716</v>
+        <v>3.409912613579913</v>
       </c>
       <c r="U77">
         <v>0.2255941048847012</v>
       </c>
       <c r="V77">
-        <v>0.1083060629421965</v>
+        <v>0.1068809831666413</v>
       </c>
       <c r="W77">
-        <v>0.2011608955616703</v>
+        <v>0.201482385158026</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3185472439476369</v>
+        <v>0.3143558328430627</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2269097510496743</v>
+        <v>0.2287076920985213</v>
       </c>
       <c r="C78">
-        <v>-3275.683474908049</v>
+        <v>-3400.136990112638</v>
       </c>
       <c r="D78">
-        <v>3062.788525091952</v>
+        <v>3032.682009887363</v>
       </c>
       <c r="E78">
-        <v>4409.872</v>
+        <v>4504.219000000001</v>
       </c>
       <c r="F78">
-        <v>7170.372</v>
+        <v>7264.719000000001</v>
       </c>
       <c r="G78">
         <v>831.9</v>
@@ -7677,37 +7677,37 @@
         <v>508.5</v>
       </c>
       <c r="M78">
-        <v>1617.593653030325</v>
+        <v>1638.877780043882</v>
       </c>
       <c r="N78">
-        <v>-1109.093653030325</v>
+        <v>-1130.377780043882</v>
       </c>
       <c r="O78">
-        <v>-377.0918420303105</v>
+        <v>-384.3284452149199</v>
       </c>
       <c r="P78">
-        <v>-732.0018110000144</v>
+        <v>-746.0493348289622</v>
       </c>
       <c r="Q78">
-        <v>-689.0018110000144</v>
+        <v>-703.0493348289622</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3074297430398941</v>
+        <v>0.31880494925902</v>
       </c>
       <c r="T78">
-        <v>3.409912613579913</v>
+        <v>3.558169683735562</v>
       </c>
       <c r="U78">
         <v>0.2255941048847012</v>
       </c>
       <c r="V78">
-        <v>0.1068809831666413</v>
+        <v>0.1054929184501914</v>
       </c>
       <c r="W78">
-        <v>0.201482385158026</v>
+        <v>0.2017955243752555</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3143558328430627</v>
+        <v>0.3102732895593865</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2287076920985213</v>
+        <v>0.2305056331473683</v>
       </c>
       <c r="C79">
-        <v>-3400.136990112638</v>
+        <v>-3524.004386327765</v>
       </c>
       <c r="D79">
-        <v>3032.682009887363</v>
+        <v>3003.161613672235</v>
       </c>
       <c r="E79">
-        <v>4504.219000000001</v>
+        <v>4598.566000000001</v>
       </c>
       <c r="F79">
-        <v>7264.719000000001</v>
+        <v>7359.066000000001</v>
       </c>
       <c r="G79">
         <v>831.9</v>
@@ -7759,37 +7759,37 @@
         <v>508.5</v>
       </c>
       <c r="M79">
-        <v>1638.877780043882</v>
+        <v>1660.161907057439</v>
       </c>
       <c r="N79">
-        <v>-1130.377780043882</v>
+        <v>-1151.661907057439</v>
       </c>
       <c r="O79">
-        <v>-384.3284452149199</v>
+        <v>-391.5650483995292</v>
       </c>
       <c r="P79">
-        <v>-746.0493348289622</v>
+        <v>-760.0968586579096</v>
       </c>
       <c r="Q79">
-        <v>-703.0493348289622</v>
+        <v>-717.0968586579096</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.31880494925902</v>
+        <v>0.33121426513443</v>
       </c>
       <c r="T79">
-        <v>3.558169683735562</v>
+        <v>3.719904669359905</v>
       </c>
       <c r="U79">
         <v>0.2255941048847012</v>
       </c>
       <c r="V79">
-        <v>0.1054929184501914</v>
+        <v>0.1041404451367274</v>
       </c>
       <c r="W79">
-        <v>0.2017955243752555</v>
+        <v>0.2021006343817869</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3102732895593865</v>
+        <v>0.3062954268727277</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2305056331473683</v>
+        <v>0.2323035741962153</v>
       </c>
       <c r="C80">
-        <v>-3524.004386327765</v>
+        <v>-3647.302614553892</v>
       </c>
       <c r="D80">
-        <v>3003.161613672235</v>
+        <v>2974.210385446109</v>
       </c>
       <c r="E80">
-        <v>4598.566000000001</v>
+        <v>4692.913</v>
       </c>
       <c r="F80">
-        <v>7359.066000000001</v>
+        <v>7453.413</v>
       </c>
       <c r="G80">
         <v>831.9</v>
@@ -7841,37 +7841,37 @@
         <v>508.5</v>
       </c>
       <c r="M80">
-        <v>1660.161907057439</v>
+        <v>1681.446034070996</v>
       </c>
       <c r="N80">
-        <v>-1151.661907057439</v>
+        <v>-1172.946034070996</v>
       </c>
       <c r="O80">
-        <v>-391.5650483995292</v>
+        <v>-398.8016515841385</v>
       </c>
       <c r="P80">
-        <v>-760.0968586579096</v>
+        <v>-774.1443824868571</v>
       </c>
       <c r="Q80">
-        <v>-717.0968586579096</v>
+        <v>-731.1443824868571</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.33121426513443</v>
+        <v>0.3448054206170219</v>
       </c>
       <c r="T80">
-        <v>3.719904669359905</v>
+        <v>3.897042986948473</v>
       </c>
       <c r="U80">
         <v>0.2255941048847012</v>
       </c>
       <c r="V80">
-        <v>0.1041404451367274</v>
+        <v>0.1028222116539841</v>
       </c>
       <c r="W80">
-        <v>0.2021006343817869</v>
+        <v>0.2023980200843554</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3062954268727277</v>
+        <v>0.3024182695705413</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2323035741962153</v>
+        <v>0.2341015152450623</v>
       </c>
       <c r="C81">
-        <v>-3647.302614553892</v>
+        <v>-3770.047978385119</v>
       </c>
       <c r="D81">
-        <v>2974.210385446109</v>
+        <v>2945.812021614882</v>
       </c>
       <c r="E81">
-        <v>4692.913</v>
+        <v>4787.260000000001</v>
       </c>
       <c r="F81">
-        <v>7453.413</v>
+        <v>7547.760000000001</v>
       </c>
       <c r="G81">
         <v>831.9</v>
@@ -7923,37 +7923,37 @@
         <v>508.5</v>
       </c>
       <c r="M81">
-        <v>1681.446034070996</v>
+        <v>1702.730161084553</v>
       </c>
       <c r="N81">
-        <v>-1172.946034070996</v>
+        <v>-1194.230161084553</v>
       </c>
       <c r="O81">
-        <v>-398.8016515841385</v>
+        <v>-406.0382547687479</v>
       </c>
       <c r="P81">
-        <v>-774.1443824868571</v>
+        <v>-788.1919063158048</v>
       </c>
       <c r="Q81">
-        <v>-731.1443824868571</v>
+        <v>-745.1919063158048</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3448054206170219</v>
+        <v>0.359755691647873</v>
       </c>
       <c r="T81">
-        <v>3.897042986948473</v>
+        <v>4.091895136295896</v>
       </c>
       <c r="U81">
         <v>0.2255941048847012</v>
       </c>
       <c r="V81">
-        <v>0.1028222116539841</v>
+        <v>0.1015369340083093</v>
       </c>
       <c r="W81">
-        <v>0.2023980200843554</v>
+        <v>0.2026879711443597</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3024182695705413</v>
+        <v>0.2986380412009095</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2341015152450623</v>
+        <v>0.2358994562939094</v>
       </c>
       <c r="C82">
-        <v>-3770.047978385119</v>
+        <v>-3892.256164624705</v>
       </c>
       <c r="D82">
-        <v>2945.812021614882</v>
+        <v>2917.950835375296</v>
       </c>
       <c r="E82">
-        <v>4787.260000000001</v>
+        <v>4881.607000000001</v>
       </c>
       <c r="F82">
-        <v>7547.760000000001</v>
+        <v>7642.107000000001</v>
       </c>
       <c r="G82">
         <v>831.9</v>
@@ -8005,37 +8005,37 @@
         <v>508.5</v>
       </c>
       <c r="M82">
-        <v>1702.730161084553</v>
+        <v>1724.01428809811</v>
       </c>
       <c r="N82">
-        <v>-1194.230161084553</v>
+        <v>-1215.51428809811</v>
       </c>
       <c r="O82">
-        <v>-406.0382547687479</v>
+        <v>-413.2748579533573</v>
       </c>
       <c r="P82">
-        <v>-788.1919063158048</v>
+        <v>-802.2394301447523</v>
       </c>
       <c r="Q82">
-        <v>-745.1919063158048</v>
+        <v>-759.2394301447523</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.359755691647873</v>
+        <v>0.3762796754188137</v>
       </c>
       <c r="T82">
-        <v>4.091895136295896</v>
+        <v>4.307258038206207</v>
       </c>
       <c r="U82">
         <v>0.2255941048847012</v>
       </c>
       <c r="V82">
-        <v>0.1015369340083093</v>
+        <v>0.1002833916131449</v>
       </c>
       <c r="W82">
-        <v>0.2026879711443597</v>
+        <v>0.2029707629189318</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2986380412009095</v>
+        <v>0.2949511518033675</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2358994562939094</v>
+        <v>0.2376973973427564</v>
       </c>
       <c r="C83">
-        <v>-3892.256164624705</v>
+        <v>-4013.942272179499</v>
       </c>
       <c r="D83">
-        <v>2917.950835375296</v>
+        <v>2890.611727820502</v>
       </c>
       <c r="E83">
-        <v>4881.607000000001</v>
+        <v>4975.954000000002</v>
       </c>
       <c r="F83">
-        <v>7642.107000000001</v>
+        <v>7736.454000000002</v>
       </c>
       <c r="G83">
         <v>831.9</v>
@@ -8087,37 +8087,37 @@
         <v>508.5</v>
       </c>
       <c r="M83">
-        <v>1724.01428809811</v>
+        <v>1745.298415111667</v>
       </c>
       <c r="N83">
-        <v>-1215.51428809811</v>
+        <v>-1236.798415111667</v>
       </c>
       <c r="O83">
-        <v>-413.2748579533573</v>
+        <v>-420.5114611379666</v>
       </c>
       <c r="P83">
-        <v>-802.2394301447523</v>
+        <v>-816.2869539737</v>
       </c>
       <c r="Q83">
-        <v>-759.2394301447523</v>
+        <v>-773.2869539737</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3762796754188137</v>
+        <v>0.3946396573865256</v>
       </c>
       <c r="T83">
-        <v>4.307258038206207</v>
+        <v>4.546550151439885</v>
       </c>
       <c r="U83">
         <v>0.2255941048847012</v>
       </c>
       <c r="V83">
-        <v>0.1002833916131449</v>
+        <v>0.09906042342274073</v>
       </c>
       <c r="W83">
-        <v>0.2029707629189318</v>
+        <v>0.2032466573331485</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2949511518033675</v>
+        <v>0.2913541865374727</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2376973973427564</v>
+        <v>0.2394953383916034</v>
       </c>
       <c r="C84">
-        <v>-4013.942272179499</v>
+        <v>-4135.120839345146</v>
       </c>
       <c r="D84">
-        <v>2890.611727820502</v>
+        <v>2863.780160654855</v>
       </c>
       <c r="E84">
-        <v>4975.954000000002</v>
+        <v>5070.301000000001</v>
       </c>
       <c r="F84">
-        <v>7736.454000000002</v>
+        <v>7830.801000000001</v>
       </c>
       <c r="G84">
         <v>831.9</v>
@@ -8169,37 +8169,37 @@
         <v>508.5</v>
       </c>
       <c r="M84">
-        <v>1745.298415111667</v>
+        <v>1766.582542125223</v>
       </c>
       <c r="N84">
-        <v>-1236.798415111667</v>
+        <v>-1258.082542125223</v>
       </c>
       <c r="O84">
-        <v>-420.5114611379666</v>
+        <v>-427.748064322576</v>
       </c>
       <c r="P84">
-        <v>-816.2869539737</v>
+        <v>-830.3344778026474</v>
       </c>
       <c r="Q84">
-        <v>-773.2869539737</v>
+        <v>-787.3344778026474</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3946396573865256</v>
+        <v>0.4151596372327919</v>
       </c>
       <c r="T84">
-        <v>4.546550151439885</v>
+        <v>4.813994277995174</v>
       </c>
       <c r="U84">
         <v>0.2255941048847012</v>
       </c>
       <c r="V84">
-        <v>0.09906042342274073</v>
+        <v>0.09786692434535832</v>
       </c>
       <c r="W84">
-        <v>0.2032466573331485</v>
+        <v>0.2035159036891913</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2913541865374727</v>
+        <v>0.2878438951334068</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2394953383916034</v>
+        <v>0.2412932794404504</v>
       </c>
       <c r="C85">
-        <v>-4135.120839345146</v>
+        <v>-4255.805869585634</v>
       </c>
       <c r="D85">
-        <v>2863.780160654855</v>
+        <v>2837.442130414366</v>
       </c>
       <c r="E85">
-        <v>5070.301000000001</v>
+        <v>5164.648000000001</v>
       </c>
       <c r="F85">
-        <v>7830.801000000001</v>
+        <v>7925.148000000001</v>
       </c>
       <c r="G85">
         <v>831.9</v>
@@ -8251,37 +8251,37 @@
         <v>508.5</v>
       </c>
       <c r="M85">
-        <v>1766.582542125223</v>
+        <v>1787.86666913878</v>
       </c>
       <c r="N85">
-        <v>-1258.082542125223</v>
+        <v>-1279.36666913878</v>
       </c>
       <c r="O85">
-        <v>-427.748064322576</v>
+        <v>-434.9846675071853</v>
       </c>
       <c r="P85">
-        <v>-830.3344778026474</v>
+        <v>-844.3820016315949</v>
       </c>
       <c r="Q85">
-        <v>-787.3344778026474</v>
+        <v>-801.3820016315949</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4151596372327919</v>
+        <v>0.4382446145598414</v>
       </c>
       <c r="T85">
-        <v>4.813994277995174</v>
+        <v>5.114868920369872</v>
       </c>
       <c r="U85">
         <v>0.2255941048847012</v>
       </c>
       <c r="V85">
-        <v>0.09786692434535832</v>
+        <v>0.09670184191267549</v>
       </c>
       <c r="W85">
-        <v>0.2035159036891913</v>
+        <v>0.2037787394177093</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2878438951334068</v>
+        <v>0.2844171820961043</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2412932794404504</v>
+        <v>0.2430912204892974</v>
       </c>
       <c r="C86">
-        <v>-4255.805869585634</v>
+        <v>-4376.01085590326</v>
       </c>
       <c r="D86">
-        <v>2837.442130414366</v>
+        <v>2811.584144096741</v>
       </c>
       <c r="E86">
-        <v>5164.648</v>
+        <v>5258.995000000001</v>
       </c>
       <c r="F86">
-        <v>7925.148</v>
+        <v>8019.495000000001</v>
       </c>
       <c r="G86">
         <v>831.9</v>
@@ -8333,37 +8333,37 @@
         <v>508.5</v>
       </c>
       <c r="M86">
-        <v>1787.86666913878</v>
+        <v>1809.150796152337</v>
       </c>
       <c r="N86">
-        <v>-1279.36666913878</v>
+        <v>-1300.650796152337</v>
       </c>
       <c r="O86">
-        <v>-434.9846675071852</v>
+        <v>-442.2212706917946</v>
       </c>
       <c r="P86">
-        <v>-844.3820016315948</v>
+        <v>-858.4295254605424</v>
       </c>
       <c r="Q86">
-        <v>-801.3820016315948</v>
+        <v>-815.4295254605424</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4382446145598411</v>
+        <v>0.4644075888638305</v>
       </c>
       <c r="T86">
-        <v>5.114868920369869</v>
+        <v>5.45586018172786</v>
       </c>
       <c r="U86">
         <v>0.2255941048847012</v>
       </c>
       <c r="V86">
-        <v>0.0967018419126755</v>
+        <v>0.09556417318429107</v>
       </c>
       <c r="W86">
-        <v>0.2037787394177093</v>
+        <v>0.2040353907761445</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2844171820961043</v>
+        <v>0.281071097600856</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2430912204892974</v>
+        <v>0.2448891615381444</v>
       </c>
       <c r="C87">
-        <v>-4376.01085590326</v>
+        <v>-4495.748803888092</v>
       </c>
       <c r="D87">
-        <v>2811.584144096741</v>
+        <v>2786.193196111908</v>
       </c>
       <c r="E87">
-        <v>5258.995000000001</v>
+        <v>5353.342000000001</v>
       </c>
       <c r="F87">
-        <v>8019.495000000001</v>
+        <v>8113.842000000001</v>
       </c>
       <c r="G87">
         <v>831.9</v>
@@ -8415,37 +8415,37 @@
         <v>508.5</v>
       </c>
       <c r="M87">
-        <v>1809.150796152337</v>
+        <v>1830.434923165894</v>
       </c>
       <c r="N87">
-        <v>-1300.650796152337</v>
+        <v>-1321.934923165894</v>
       </c>
       <c r="O87">
-        <v>-442.2212706917946</v>
+        <v>-449.4578738764041</v>
       </c>
       <c r="P87">
-        <v>-858.4295254605424</v>
+        <v>-872.4770492894901</v>
       </c>
       <c r="Q87">
-        <v>-815.4295254605424</v>
+        <v>-829.4770492894901</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4644075888638305</v>
+        <v>0.4943081309255327</v>
       </c>
       <c r="T87">
-        <v>5.45586018172786</v>
+        <v>5.845564480422707</v>
       </c>
       <c r="U87">
         <v>0.2255941048847012</v>
       </c>
       <c r="V87">
-        <v>0.09556417318429107</v>
+        <v>0.09445296186819466</v>
       </c>
       <c r="W87">
-        <v>0.2040353907761445</v>
+        <v>0.204286073498337</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.281071097600856</v>
+        <v>0.2778028290241019</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2448891615381444</v>
+        <v>0.2466871025869914</v>
       </c>
       <c r="C88">
-        <v>-4495.748803888092</v>
+        <v>-4615.032253529695</v>
       </c>
       <c r="D88">
-        <v>2786.193196111908</v>
+        <v>2761.256746470306</v>
       </c>
       <c r="E88">
-        <v>5353.342000000001</v>
+        <v>5447.689</v>
       </c>
       <c r="F88">
-        <v>8113.842000000001</v>
+        <v>8208.189</v>
       </c>
       <c r="G88">
         <v>831.9</v>
@@ -8497,37 +8497,37 @@
         <v>508.5</v>
       </c>
       <c r="M88">
-        <v>1830.434923165894</v>
+        <v>1851.719050179451</v>
       </c>
       <c r="N88">
-        <v>-1321.934923165894</v>
+        <v>-1343.219050179451</v>
       </c>
       <c r="O88">
-        <v>-449.4578738764041</v>
+        <v>-456.6944770610133</v>
       </c>
       <c r="P88">
-        <v>-872.4770492894901</v>
+        <v>-886.5245731184376</v>
       </c>
       <c r="Q88">
-        <v>-829.4770492894901</v>
+        <v>-843.5245731184376</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4943081309255327</v>
+        <v>0.5288087563813429</v>
       </c>
       <c r="T88">
-        <v>5.845564480422707</v>
+        <v>6.29522328660907</v>
       </c>
       <c r="U88">
         <v>0.2255941048847012</v>
       </c>
       <c r="V88">
-        <v>0.09445296186819466</v>
+        <v>0.0933672956398246</v>
       </c>
       <c r="W88">
-        <v>0.204286073498337</v>
+        <v>0.2045309933993297</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2778028290241019</v>
+        <v>0.2746096930583076</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2466871025869914</v>
+        <v>0.2484850436358385</v>
       </c>
       <c r="C89">
-        <v>-4615.032253529695</v>
+        <v>-4733.873299867935</v>
       </c>
       <c r="D89">
-        <v>2761.256746470306</v>
+        <v>2736.762700132064</v>
       </c>
       <c r="E89">
-        <v>5447.689</v>
+        <v>5542.036</v>
       </c>
       <c r="F89">
-        <v>8208.189</v>
+        <v>8302.536</v>
       </c>
       <c r="G89">
         <v>831.9</v>
@@ -8579,37 +8579,37 @@
         <v>508.5</v>
       </c>
       <c r="M89">
-        <v>1851.719050179451</v>
+        <v>1873.003177193008</v>
       </c>
       <c r="N89">
-        <v>-1343.219050179451</v>
+        <v>-1364.503177193008</v>
       </c>
       <c r="O89">
-        <v>-456.6944770610133</v>
+        <v>-463.9310802456227</v>
       </c>
       <c r="P89">
-        <v>-886.5245731184376</v>
+        <v>-900.572096947385</v>
       </c>
       <c r="Q89">
-        <v>-843.5245731184376</v>
+        <v>-857.572096947385</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5288087563813429</v>
+        <v>0.5690594860797882</v>
       </c>
       <c r="T89">
-        <v>6.29522328660907</v>
+        <v>6.819825227159826</v>
       </c>
       <c r="U89">
         <v>0.2255941048847012</v>
       </c>
       <c r="V89">
-        <v>0.0933672956398246</v>
+        <v>0.09230630364391751</v>
       </c>
       <c r="W89">
-        <v>0.2045309933993297</v>
+        <v>0.2047703469389362</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2746096930583076</v>
+        <v>0.2714891283644633</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2484850436358385</v>
+        <v>0.2502829846846855</v>
       </c>
       <c r="C90">
-        <v>-4733.873299867935</v>
+        <v>-4852.283612554361</v>
       </c>
       <c r="D90">
-        <v>2736.762700132064</v>
+        <v>2712.699387445641</v>
       </c>
       <c r="E90">
-        <v>5542.036</v>
+        <v>5636.383000000002</v>
       </c>
       <c r="F90">
-        <v>8302.536</v>
+        <v>8396.883000000002</v>
       </c>
       <c r="G90">
         <v>831.9</v>
@@ -8661,37 +8661,37 @@
         <v>508.5</v>
       </c>
       <c r="M90">
-        <v>1873.003177193008</v>
+        <v>1894.287304206565</v>
       </c>
       <c r="N90">
-        <v>-1364.503177193008</v>
+        <v>-1385.787304206565</v>
       </c>
       <c r="O90">
-        <v>-463.9310802456227</v>
+        <v>-471.1676834302322</v>
       </c>
       <c r="P90">
-        <v>-900.572096947385</v>
+        <v>-914.6196207763329</v>
       </c>
       <c r="Q90">
-        <v>-857.572096947385</v>
+        <v>-871.6196207763329</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5690594860797882</v>
+        <v>0.6166285302688599</v>
       </c>
       <c r="T90">
-        <v>6.819825227159826</v>
+        <v>7.439809338719811</v>
       </c>
       <c r="U90">
         <v>0.2255941048847012</v>
       </c>
       <c r="V90">
-        <v>0.09230630364391751</v>
+        <v>0.09126915416477235</v>
       </c>
       <c r="W90">
-        <v>0.2047703469389362</v>
+        <v>0.2050043217473156</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2714891283644633</v>
+        <v>0.2684386887199187</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2502829846846855</v>
+        <v>0.2520809257335325</v>
       </c>
       <c r="C91">
-        <v>-4852.283612554361</v>
+        <v>-4970.27445439057</v>
       </c>
       <c r="D91">
-        <v>2712.699387445641</v>
+        <v>2689.055545609431</v>
       </c>
       <c r="E91">
-        <v>5636.383000000002</v>
+        <v>5730.730000000001</v>
       </c>
       <c r="F91">
-        <v>8396.883000000002</v>
+        <v>8491.230000000001</v>
       </c>
       <c r="G91">
         <v>831.9</v>
@@ -8743,37 +8743,37 @@
         <v>508.5</v>
       </c>
       <c r="M91">
-        <v>1894.287304206565</v>
+        <v>1915.571431220122</v>
       </c>
       <c r="N91">
-        <v>-1385.787304206565</v>
+        <v>-1407.071431220122</v>
       </c>
       <c r="O91">
-        <v>-471.1676834302322</v>
+        <v>-478.4042866148415</v>
       </c>
       <c r="P91">
-        <v>-914.6196207763329</v>
+        <v>-928.6671446052804</v>
       </c>
       <c r="Q91">
-        <v>-871.6196207763329</v>
+        <v>-885.6671446052804</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6166285302688599</v>
+        <v>0.6737113832957459</v>
       </c>
       <c r="T91">
-        <v>7.439809338719811</v>
+        <v>8.183790272591793</v>
       </c>
       <c r="U91">
         <v>0.2255941048847012</v>
       </c>
       <c r="V91">
-        <v>0.09126915416477235</v>
+        <v>0.09025505245183044</v>
       </c>
       <c r="W91">
-        <v>0.2050043217473156</v>
+        <v>0.2052330971155088</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2684386887199187</v>
+        <v>0.2654560366230307</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2520809257335325</v>
+        <v>0.2538788667823795</v>
       </c>
       <c r="C92">
-        <v>-4970.27445439057</v>
+        <v>-5087.856698905514</v>
       </c>
       <c r="D92">
-        <v>2689.055545609431</v>
+        <v>2665.820301094487</v>
       </c>
       <c r="E92">
-        <v>5730.730000000001</v>
+        <v>5825.077000000001</v>
       </c>
       <c r="F92">
-        <v>8491.230000000001</v>
+        <v>8585.577000000001</v>
       </c>
       <c r="G92">
         <v>831.9</v>
@@ -8825,37 +8825,37 @@
         <v>508.5</v>
       </c>
       <c r="M92">
-        <v>1915.571431220122</v>
+        <v>1936.855558233679</v>
       </c>
       <c r="N92">
-        <v>-1407.071431220122</v>
+        <v>-1428.355558233679</v>
       </c>
       <c r="O92">
-        <v>-478.4042866148415</v>
+        <v>-485.6408897994508</v>
       </c>
       <c r="P92">
-        <v>-928.6671446052804</v>
+        <v>-942.7146684342279</v>
       </c>
       <c r="Q92">
-        <v>-885.6671446052804</v>
+        <v>-899.7146684342279</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6737113832957459</v>
+        <v>0.7434793147730511</v>
       </c>
       <c r="T92">
-        <v>8.183790272591793</v>
+        <v>9.093100302879771</v>
       </c>
       <c r="U92">
         <v>0.2255941048847012</v>
       </c>
       <c r="V92">
-        <v>0.09025505245183044</v>
+        <v>0.08926323868862351</v>
       </c>
       <c r="W92">
-        <v>0.2052330971155088</v>
+        <v>0.2054568444536318</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2654560366230307</v>
+        <v>0.262538937319481</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2538788667823795</v>
+        <v>0.2556768078312265</v>
       </c>
       <c r="C93">
-        <v>-5087.856698905514</v>
+        <v>-5205.040847029291</v>
       </c>
       <c r="D93">
-        <v>2665.820301094487</v>
+        <v>2642.983152970709</v>
       </c>
       <c r="E93">
-        <v>5825.077000000001</v>
+        <v>5919.424000000001</v>
       </c>
       <c r="F93">
-        <v>8585.577000000001</v>
+        <v>8679.924000000001</v>
       </c>
       <c r="G93">
         <v>831.9</v>
@@ -8907,37 +8907,37 @@
         <v>508.5</v>
       </c>
       <c r="M93">
-        <v>1936.855558233679</v>
+        <v>1958.139685247236</v>
       </c>
       <c r="N93">
-        <v>-1428.355558233679</v>
+        <v>-1449.639685247236</v>
       </c>
       <c r="O93">
-        <v>-485.6408897994508</v>
+        <v>-492.8774929840601</v>
       </c>
       <c r="P93">
-        <v>-942.7146684342279</v>
+        <v>-956.7621922631754</v>
       </c>
       <c r="Q93">
-        <v>-899.7146684342279</v>
+        <v>-913.7621922631754</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7434793147730511</v>
+        <v>0.8306892291196828</v>
       </c>
       <c r="T93">
-        <v>9.093100302879771</v>
+        <v>10.22973784073975</v>
       </c>
       <c r="U93">
         <v>0.2255941048847012</v>
       </c>
       <c r="V93">
-        <v>0.08926323868862351</v>
+        <v>0.08829298609418196</v>
       </c>
       <c r="W93">
-        <v>0.2054568444536318</v>
+        <v>0.2056757277191869</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.262538937319481</v>
+        <v>0.2596852532181823</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2556768078312265</v>
+        <v>0.2574747488800735</v>
       </c>
       <c r="C94">
-        <v>-5205.040847029291</v>
+        <v>-5321.837042917221</v>
       </c>
       <c r="D94">
-        <v>2642.983152970709</v>
+        <v>2620.53395708278</v>
       </c>
       <c r="E94">
-        <v>5919.424000000001</v>
+        <v>6013.771000000001</v>
       </c>
       <c r="F94">
-        <v>8679.924000000001</v>
+        <v>8774.271000000001</v>
       </c>
       <c r="G94">
         <v>831.9</v>
@@ -8989,37 +8989,37 @@
         <v>508.5</v>
       </c>
       <c r="M94">
-        <v>1958.139685247236</v>
+        <v>1979.423812260792</v>
       </c>
       <c r="N94">
-        <v>-1449.639685247236</v>
+        <v>-1470.923812260792</v>
       </c>
       <c r="O94">
-        <v>-492.8774929840601</v>
+        <v>-500.1140961686694</v>
       </c>
       <c r="P94">
-        <v>-956.7621922631754</v>
+        <v>-970.8097160921229</v>
       </c>
       <c r="Q94">
-        <v>-913.7621922631754</v>
+        <v>-927.8097160921229</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8306892291196828</v>
+        <v>0.942816261851066</v>
       </c>
       <c r="T94">
-        <v>10.22973784073975</v>
+        <v>11.69112896084542</v>
       </c>
       <c r="U94">
         <v>0.2255941048847012</v>
       </c>
       <c r="V94">
-        <v>0.08829298609418196</v>
+        <v>0.08734359914693271</v>
       </c>
       <c r="W94">
-        <v>0.2056757277191869</v>
+        <v>0.2058899038177408</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2596852532181823</v>
+        <v>0.2568929386674491</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2574747488800735</v>
+        <v>0.2592726899289206</v>
       </c>
       <c r="C95">
-        <v>-5321.837042917221</v>
+        <v>-5438.255088974239</v>
       </c>
       <c r="D95">
-        <v>2620.53395708278</v>
+        <v>2598.462911025762</v>
       </c>
       <c r="E95">
-        <v>6013.771000000001</v>
+        <v>6108.118</v>
       </c>
       <c r="F95">
-        <v>8774.271000000001</v>
+        <v>8868.618</v>
       </c>
       <c r="G95">
         <v>831.9</v>
@@ -9071,37 +9071,37 @@
         <v>508.5</v>
       </c>
       <c r="M95">
-        <v>1979.423812260792</v>
+        <v>2000.707939274349</v>
       </c>
       <c r="N95">
-        <v>-1470.923812260792</v>
+        <v>-1492.207939274349</v>
       </c>
       <c r="O95">
-        <v>-500.1140961686694</v>
+        <v>-507.3506993532787</v>
       </c>
       <c r="P95">
-        <v>-970.8097160921229</v>
+        <v>-984.8572399210705</v>
       </c>
       <c r="Q95">
-        <v>-927.8097160921229</v>
+        <v>-941.8572399210705</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.942816261851066</v>
+        <v>1.092318972159577</v>
       </c>
       <c r="T95">
-        <v>11.69112896084542</v>
+        <v>13.63965045431966</v>
       </c>
       <c r="U95">
         <v>0.2255941048847012</v>
       </c>
       <c r="V95">
-        <v>0.08734359914693271</v>
+        <v>0.08641441192196532</v>
       </c>
       <c r="W95">
-        <v>0.2058899038177408</v>
+        <v>0.2060995229780276</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2568929386674491</v>
+        <v>0.2541600350646039</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2592726899289206</v>
+        <v>0.2610706309777676</v>
       </c>
       <c r="C96">
-        <v>-5438.255088974239</v>
+        <v>-5554.304460126403</v>
       </c>
       <c r="D96">
-        <v>2598.462911025762</v>
+        <v>2576.760539873599</v>
       </c>
       <c r="E96">
-        <v>6108.118</v>
+        <v>6202.465000000002</v>
       </c>
       <c r="F96">
-        <v>8868.618</v>
+        <v>8962.965000000002</v>
       </c>
       <c r="G96">
         <v>831.9</v>
@@ -9153,37 +9153,37 @@
         <v>508.5</v>
       </c>
       <c r="M96">
-        <v>2000.707939274349</v>
+        <v>2021.992066287906</v>
       </c>
       <c r="N96">
-        <v>-1492.207939274349</v>
+        <v>-1513.492066287906</v>
       </c>
       <c r="O96">
-        <v>-507.3506993532787</v>
+        <v>-514.5873025378883</v>
       </c>
       <c r="P96">
-        <v>-984.8572399210705</v>
+        <v>-998.9047637500182</v>
       </c>
       <c r="Q96">
-        <v>-941.8572399210705</v>
+        <v>-955.9047637500182</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.092318972159577</v>
+        <v>1.301622766591493</v>
       </c>
       <c r="T96">
-        <v>13.63965045431966</v>
+        <v>16.3675805451836</v>
       </c>
       <c r="U96">
         <v>0.2255941048847012</v>
       </c>
       <c r="V96">
-        <v>0.08641441192196532</v>
+        <v>0.08550478653331306</v>
       </c>
       <c r="W96">
-        <v>0.2060995229780276</v>
+        <v>0.206304729103361</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2541600350646039</v>
+        <v>0.2514846662744501</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2610706309777676</v>
+        <v>0.2628685720266146</v>
       </c>
       <c r="C97">
-        <v>-5554.304460126403</v>
+        <v>-5669.994317383142</v>
       </c>
       <c r="D97">
-        <v>2576.760539873599</v>
+        <v>2555.41768261686</v>
       </c>
       <c r="E97">
-        <v>6202.465000000002</v>
+        <v>6296.812000000002</v>
       </c>
       <c r="F97">
-        <v>8962.965000000002</v>
+        <v>9057.312000000002</v>
       </c>
       <c r="G97">
         <v>831.9</v>
@@ -9235,37 +9235,37 @@
         <v>508.5</v>
       </c>
       <c r="M97">
-        <v>2021.992066287906</v>
+        <v>2043.276193301463</v>
       </c>
       <c r="N97">
-        <v>-1513.492066287906</v>
+        <v>-1534.776193301463</v>
       </c>
       <c r="O97">
-        <v>-514.5873025378883</v>
+        <v>-521.8239057224976</v>
       </c>
       <c r="P97">
-        <v>-998.9047637500182</v>
+        <v>-1012.952287578966</v>
       </c>
       <c r="Q97">
-        <v>-955.9047637500182</v>
+        <v>-969.9522875789658</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.301622766591493</v>
+        <v>1.615578458239368</v>
       </c>
       <c r="T97">
-        <v>16.3675805451836</v>
+        <v>20.45947568147952</v>
       </c>
       <c r="U97">
         <v>0.2255941048847012</v>
       </c>
       <c r="V97">
-        <v>0.08550478653331306</v>
+        <v>0.08461411167359105</v>
       </c>
       <c r="W97">
-        <v>0.206304729103361</v>
+        <v>0.2065056601010833</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2514846662744501</v>
+        <v>0.2488650343340912</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2628685720266146</v>
+        <v>0.2646665130754616</v>
       </c>
       <c r="C98">
-        <v>-5669.994317383138</v>
+        <v>-5785.333520731041</v>
       </c>
       <c r="D98">
-        <v>2555.417682616861</v>
+        <v>2534.425479268958</v>
       </c>
       <c r="E98">
-        <v>6296.812</v>
+        <v>6391.159</v>
       </c>
       <c r="F98">
-        <v>9057.312</v>
+        <v>9151.659</v>
       </c>
       <c r="G98">
         <v>831.9</v>
@@ -9317,37 +9317,37 @@
         <v>508.5</v>
       </c>
       <c r="M98">
-        <v>2043.276193301463</v>
+        <v>2064.56032031502</v>
       </c>
       <c r="N98">
-        <v>-1534.776193301463</v>
+        <v>-1556.06032031502</v>
       </c>
       <c r="O98">
-        <v>-521.8239057224974</v>
+        <v>-529.0605089071069</v>
       </c>
       <c r="P98">
-        <v>-1012.952287578965</v>
+        <v>-1026.999811407913</v>
       </c>
       <c r="Q98">
-        <v>-969.9522875789654</v>
+        <v>-983.9998114079131</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.615578458239364</v>
+        <v>2.138837944319151</v>
       </c>
       <c r="T98">
-        <v>20.45947568147946</v>
+        <v>27.27930090863929</v>
       </c>
       <c r="U98">
         <v>0.2255941048847012</v>
       </c>
       <c r="V98">
-        <v>0.08461411167359105</v>
+        <v>0.08374180124396641</v>
       </c>
       <c r="W98">
-        <v>0.2065056601010833</v>
+        <v>0.2067024481916361</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2488650343340914</v>
+        <v>0.2462994154234306</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2646665130754616</v>
+        <v>0.2664644541243086</v>
       </c>
       <c r="C99">
-        <v>-5785.333520731041</v>
+        <v>-5900.330641397302</v>
       </c>
       <c r="D99">
-        <v>2534.425479268958</v>
+        <v>2513.775358602699</v>
       </c>
       <c r="E99">
-        <v>6391.159</v>
+        <v>6485.506000000001</v>
       </c>
       <c r="F99">
-        <v>9151.659</v>
+        <v>9246.006000000001</v>
       </c>
       <c r="G99">
         <v>831.9</v>
@@ -9399,37 +9399,37 @@
         <v>508.5</v>
       </c>
       <c r="M99">
-        <v>2064.56032031502</v>
+        <v>2085.844447328577</v>
       </c>
       <c r="N99">
-        <v>-1556.06032031502</v>
+        <v>-1577.344447328577</v>
       </c>
       <c r="O99">
-        <v>-529.0605089071069</v>
+        <v>-536.2971120917163</v>
       </c>
       <c r="P99">
-        <v>-1026.999811407913</v>
+        <v>-1041.047335236861</v>
       </c>
       <c r="Q99">
-        <v>-983.9998114079131</v>
+        <v>-998.0473352368608</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.138837944319151</v>
+        <v>3.185356916478726</v>
       </c>
       <c r="T99">
-        <v>27.27930090863929</v>
+        <v>40.91895136295892</v>
       </c>
       <c r="U99">
         <v>0.2255941048847012</v>
       </c>
       <c r="V99">
-        <v>0.08374180124396641</v>
+        <v>0.08288729306800756</v>
       </c>
       <c r="W99">
-        <v>0.2067024481916361</v>
+        <v>0.2068952201987082</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2462994154234306</v>
+        <v>0.2437861560823751</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2664644541243086</v>
+        <v>0.2682623951731556</v>
       </c>
       <c r="C100">
-        <v>-5900.330641397302</v>
+        <v>-6014.993973518487</v>
       </c>
       <c r="D100">
-        <v>2513.775358602699</v>
+        <v>2493.459026481514</v>
       </c>
       <c r="E100">
-        <v>6485.506000000001</v>
+        <v>6579.853000000001</v>
       </c>
       <c r="F100">
-        <v>9246.006000000001</v>
+        <v>9340.353000000001</v>
       </c>
       <c r="G100">
         <v>831.9</v>
@@ -9481,37 +9481,37 @@
         <v>508.5</v>
       </c>
       <c r="M100">
-        <v>2085.844447328577</v>
+        <v>2107.128574342134</v>
       </c>
       <c r="N100">
-        <v>-1577.344447328577</v>
+        <v>-1598.628574342134</v>
       </c>
       <c r="O100">
-        <v>-536.2971120917163</v>
+        <v>-543.5337152763256</v>
       </c>
       <c r="P100">
-        <v>-1041.047335236861</v>
+        <v>-1055.094859065809</v>
       </c>
       <c r="Q100">
-        <v>-998.0473352368608</v>
+        <v>-1012.094859065809</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.185356916478726</v>
+        <v>6.324913832957453</v>
       </c>
       <c r="T100">
-        <v>40.91895136295892</v>
+        <v>81.83790272591784</v>
       </c>
       <c r="U100">
         <v>0.2255941048847012</v>
       </c>
       <c r="V100">
-        <v>0.08288729306800756</v>
+        <v>0.08205004768348223</v>
       </c>
       <c r="W100">
-        <v>0.2068952201987082</v>
+        <v>0.207084097821799</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2437861560823751</v>
+        <v>0.2413236696573007</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2682623951731556</v>
-      </c>
-      <c r="C101">
-        <v>-6014.993973518487</v>
-      </c>
-      <c r="D101">
-        <v>2493.459026481514</v>
-      </c>
-      <c r="E101">
-        <v>6579.853000000001</v>
-      </c>
-      <c r="F101">
-        <v>9340.353000000001</v>
-      </c>
-      <c r="G101">
-        <v>831.9</v>
-      </c>
-      <c r="H101">
-        <v>6674.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>551.5</v>
-      </c>
-      <c r="K101">
-        <v>43</v>
-      </c>
-      <c r="L101">
-        <v>508.5</v>
-      </c>
-      <c r="M101">
-        <v>2107.128574342134</v>
-      </c>
-      <c r="N101">
-        <v>-1598.628574342134</v>
-      </c>
-      <c r="O101">
-        <v>-543.5337152763256</v>
-      </c>
-      <c r="P101">
-        <v>-1055.094859065809</v>
-      </c>
-      <c r="Q101">
-        <v>-1012.094859065809</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.324913832957453</v>
-      </c>
-      <c r="T101">
-        <v>81.83790272591784</v>
-      </c>
-      <c r="U101">
-        <v>0.2255941048847012</v>
-      </c>
-      <c r="V101">
-        <v>0.08205004768348223</v>
-      </c>
-      <c r="W101">
-        <v>0.207084097821799</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2413236696573007</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
